--- a/database/event/7128/event_7128_evp_summary.xlsx
+++ b/database/event/7128/event_7128_evp_summary.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,72 +418,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>evp_score</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>weighted_evp_score</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>z_score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>normalized_score</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Norm_Group_Score_Scaled</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Norm_Playoff_Score</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Norm_Group_Score</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Raw_Group_Score</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Raw_Playoff_Score</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>group_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>playoff_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>total_weighted_score</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>total_weighted_rounds_played</t>
         </is>
@@ -508,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.916499999999999</v>
+        <v>5.761</v>
       </c>
       <c r="C2" t="n">
-        <v>8.024849999999999</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>3.41974297547446</v>
+        <v>1.906</v>
       </c>
       <c r="E2" t="n">
-        <v>135.5591</v>
+        <v>5.761</v>
       </c>
       <c r="F2" t="n">
-        <v>28.03591086693743</v>
+        <v>1.7545</v>
       </c>
       <c r="G2" t="n">
-        <v>107.5231526558724</v>
+        <v>4.0065</v>
       </c>
       <c r="H2" t="n">
-        <v>28.03591086693743</v>
+        <v>1.7545</v>
       </c>
       <c r="I2" t="n">
-        <v>19.20127957371307</v>
+        <v>1.7545</v>
       </c>
       <c r="J2" t="n">
-        <v>107.5231526558724</v>
+        <v>4.0065</v>
       </c>
       <c r="K2" t="n">
         <v>47</v>
@@ -541,7 +529,7 @@
         <v>209</v>
       </c>
       <c r="M2" t="n">
-        <v>126.7244</v>
+        <v>5.761</v>
       </c>
       <c r="N2" t="n">
         <v>256</v>
@@ -550,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.618399999999999</v>
+        <v>5.4279</v>
       </c>
       <c r="C3" t="n">
-        <v>7.756559999999999</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>3.205524806018017</v>
+        <v>1.7714</v>
       </c>
       <c r="E3" t="n">
-        <v>126.238</v>
+        <v>5.4279</v>
       </c>
       <c r="F3" t="n">
-        <v>8.466866440918247</v>
+        <v>1.7366</v>
       </c>
       <c r="G3" t="n">
-        <v>117.7711801010648</v>
+        <v>3.6913</v>
       </c>
       <c r="H3" t="n">
-        <v>8.466866440918247</v>
+        <v>1.7366</v>
       </c>
       <c r="I3" t="n">
-        <v>7.032588519232643</v>
+        <v>1.7366</v>
       </c>
       <c r="J3" t="n">
-        <v>117.7711801010648</v>
+        <v>3.6913</v>
       </c>
       <c r="K3" t="n">
         <v>57</v>
@@ -587,7 +575,7 @@
         <v>184</v>
       </c>
       <c r="M3" t="n">
-        <v>124.8038</v>
+        <v>5.4279</v>
       </c>
       <c r="N3" t="n">
         <v>241</v>
@@ -596,139 +584,139 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Maden</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.1606</v>
+        <v>5.2058</v>
       </c>
       <c r="C4" t="n">
-        <v>6.44454</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>2.298382637447688</v>
+        <v>1.6817</v>
       </c>
       <c r="E4" t="n">
-        <v>86.7667</v>
+        <v>5.2058</v>
       </c>
       <c r="F4" t="n">
-        <v>2.900923881238949</v>
+        <v>1.707</v>
       </c>
       <c r="G4" t="n">
-        <v>83.86573898342552</v>
+        <v>3.4988</v>
       </c>
       <c r="H4" t="n">
-        <v>2.900923881238949</v>
+        <v>1.707</v>
       </c>
       <c r="I4" t="n">
-        <v>2.409510546165684</v>
+        <v>1.707</v>
       </c>
       <c r="J4" t="n">
-        <v>83.86573898342552</v>
+        <v>3.4988</v>
       </c>
       <c r="K4" t="n">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="L4" t="n">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="M4" t="n">
-        <v>86.2752</v>
+        <v>5.2058</v>
       </c>
       <c r="N4" t="n">
-        <v>241</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.1145</v>
+        <v>5.097</v>
       </c>
       <c r="C5" t="n">
-        <v>6.403049999999999</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>2.273150019589661</v>
+        <v>1.6377</v>
       </c>
       <c r="E5" t="n">
-        <v>85.6687</v>
+        <v>5.097</v>
       </c>
       <c r="F5" t="n">
-        <v>16.60027195894215</v>
+        <v>0.7759</v>
       </c>
       <c r="G5" t="n">
-        <v>69.06847442122356</v>
+        <v>4.3211</v>
       </c>
       <c r="H5" t="n">
-        <v>16.60027195894215</v>
+        <v>0.7759</v>
       </c>
       <c r="I5" t="n">
-        <v>22.254645103427</v>
+        <v>0.7759</v>
       </c>
       <c r="J5" t="n">
-        <v>69.06847442122356</v>
+        <v>4.3211</v>
       </c>
       <c r="K5" t="n">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="L5" t="n">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="M5" t="n">
-        <v>91.3231</v>
+        <v>5.097</v>
       </c>
       <c r="N5" t="n">
-        <v>260</v>
+        <v>241</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.7194</v>
+        <v>4.5973</v>
       </c>
       <c r="C6" t="n">
-        <v>6.04746</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>2.064571922762696</v>
+        <v>1.4358</v>
       </c>
       <c r="E6" t="n">
-        <v>76.59310000000001</v>
+        <v>4.5973</v>
       </c>
       <c r="F6" t="n">
-        <v>25.55584130350366</v>
+        <v>1.3791</v>
       </c>
       <c r="G6" t="n">
-        <v>51.03729777740354</v>
+        <v>3.2182</v>
       </c>
       <c r="H6" t="n">
-        <v>25.55584130350366</v>
+        <v>1.3791</v>
       </c>
       <c r="I6" t="n">
-        <v>21.22670971657135</v>
+        <v>1.3791</v>
       </c>
       <c r="J6" t="n">
-        <v>51.03729777740354</v>
+        <v>3.2182</v>
       </c>
       <c r="K6" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="L6" t="n">
-        <v>184</v>
+        <v>209</v>
       </c>
       <c r="M6" t="n">
-        <v>72.264</v>
+        <v>4.5973</v>
       </c>
       <c r="N6" t="n">
-        <v>241</v>
+        <v>256</v>
       </c>
     </row>
     <row r="7">
@@ -738,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.4161</v>
+        <v>4.097</v>
       </c>
       <c r="C7" t="n">
-        <v>5.77449</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1.91348994211938</v>
+        <v>1.2337</v>
       </c>
       <c r="E7" t="n">
-        <v>70.0193</v>
+        <v>4.097</v>
       </c>
       <c r="F7" t="n">
-        <v>17.18110631346867</v>
+        <v>1.5364</v>
       </c>
       <c r="G7" t="n">
-        <v>52.83818466367328</v>
+        <v>2.5606</v>
       </c>
       <c r="H7" t="n">
-        <v>17.18110631346867</v>
+        <v>1.5364</v>
       </c>
       <c r="I7" t="n">
-        <v>14.27064568113244</v>
+        <v>1.5364</v>
       </c>
       <c r="J7" t="n">
-        <v>52.83818466367328</v>
+        <v>2.5606</v>
       </c>
       <c r="K7" t="n">
         <v>57</v>
@@ -771,7 +759,7 @@
         <v>184</v>
       </c>
       <c r="M7" t="n">
-        <v>67.1088</v>
+        <v>4.097</v>
       </c>
       <c r="N7" t="n">
         <v>241</v>
@@ -780,47 +768,47 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.3506</v>
+        <v>3.951</v>
       </c>
       <c r="C8" t="n">
-        <v>5.71554</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1.881862050933584</v>
+        <v>1.1748</v>
       </c>
       <c r="E8" t="n">
-        <v>68.6431</v>
+        <v>3.951</v>
       </c>
       <c r="F8" t="n">
-        <v>16.82589928661144</v>
+        <v>0.9883999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>51.81720538682631</v>
+        <v>2.9626</v>
       </c>
       <c r="H8" t="n">
-        <v>16.82589928661144</v>
+        <v>0.9883999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>11.52374887389053</v>
+        <v>0.9883999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>51.81720538682631</v>
+        <v>2.9626</v>
       </c>
       <c r="K8" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="L8" t="n">
-        <v>209</v>
+        <v>130</v>
       </c>
       <c r="M8" t="n">
-        <v>63.341</v>
+        <v>3.951</v>
       </c>
       <c r="N8" t="n">
-        <v>256</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9">
@@ -830,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.3155</v>
+        <v>3.7613</v>
       </c>
       <c r="C9" t="n">
-        <v>4.78395</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1.425187296823699</v>
+        <v>1.0981</v>
       </c>
       <c r="E9" t="n">
-        <v>48.7724</v>
+        <v>3.7613</v>
       </c>
       <c r="F9" t="n">
-        <v>15.51526875866091</v>
+        <v>1.2309</v>
       </c>
       <c r="G9" t="n">
-        <v>33.25709783231615</v>
+        <v>2.5304</v>
       </c>
       <c r="H9" t="n">
-        <v>15.51526875866091</v>
+        <v>1.2309</v>
       </c>
       <c r="I9" t="n">
-        <v>10.62612213707924</v>
+        <v>1.2309</v>
       </c>
       <c r="J9" t="n">
-        <v>33.25709783231615</v>
+        <v>2.5304</v>
       </c>
       <c r="K9" t="n">
         <v>47</v>
@@ -863,7 +851,7 @@
         <v>209</v>
       </c>
       <c r="M9" t="n">
-        <v>43.8832</v>
+        <v>3.7613</v>
       </c>
       <c r="N9" t="n">
         <v>256</v>
@@ -876,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.9329</v>
+        <v>3.4123</v>
       </c>
       <c r="C10" t="n">
-        <v>4.43961</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1.275381889113482</v>
+        <v>0.9571</v>
       </c>
       <c r="E10" t="n">
-        <v>42.2541</v>
+        <v>3.4123</v>
       </c>
       <c r="F10" t="n">
-        <v>10.1110567444699</v>
+        <v>1.7172</v>
       </c>
       <c r="G10" t="n">
-        <v>32.14300772195027</v>
+        <v>1.6951</v>
       </c>
       <c r="H10" t="n">
-        <v>10.1110567444699</v>
+        <v>1.7172</v>
       </c>
       <c r="I10" t="n">
-        <v>13.55507789422558</v>
+        <v>1.7172</v>
       </c>
       <c r="J10" t="n">
-        <v>32.14300772195027</v>
+        <v>1.6951</v>
       </c>
       <c r="K10" t="n">
         <v>92</v>
@@ -909,7 +897,7 @@
         <v>168</v>
       </c>
       <c r="M10" t="n">
-        <v>45.6981</v>
+        <v>3.4123</v>
       </c>
       <c r="N10" t="n">
         <v>260</v>
@@ -918,219 +906,219 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>Maden</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.4442</v>
+        <v>3.1476</v>
       </c>
       <c r="C11" t="n">
-        <v>3.99978</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1.097390220566334</v>
+        <v>0.8502</v>
       </c>
       <c r="E11" t="n">
-        <v>34.5093</v>
+        <v>3.1476</v>
       </c>
       <c r="F11" t="n">
-        <v>14.40619363828937</v>
+        <v>0.0427</v>
       </c>
       <c r="G11" t="n">
-        <v>20.10313391256768</v>
+        <v>3.1049</v>
       </c>
       <c r="H11" t="n">
-        <v>14.40619363828937</v>
+        <v>0.0427</v>
       </c>
       <c r="I11" t="n">
-        <v>9.866536990886706</v>
+        <v>0.0427</v>
       </c>
       <c r="J11" t="n">
-        <v>20.10313391256768</v>
+        <v>3.1049</v>
       </c>
       <c r="K11" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="L11" t="n">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="M11" t="n">
-        <v>29.9697</v>
+        <v>3.1476</v>
       </c>
       <c r="N11" t="n">
-        <v>256</v>
+        <v>241</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.9992</v>
+        <v>2.9742</v>
       </c>
       <c r="C12" t="n">
-        <v>3.59928</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9474786023021551</v>
+        <v>0.7801</v>
       </c>
       <c r="E12" t="n">
-        <v>27.9864</v>
+        <v>2.9742</v>
       </c>
       <c r="F12" t="n">
-        <v>9.904496947874103</v>
+        <v>1.0811</v>
       </c>
       <c r="G12" t="n">
-        <v>18.08190706662178</v>
+        <v>1.8931</v>
       </c>
       <c r="H12" t="n">
-        <v>9.904496947874103</v>
+        <v>1.0811</v>
       </c>
       <c r="I12" t="n">
-        <v>9.525636408884383</v>
+        <v>1.0811</v>
       </c>
       <c r="J12" t="n">
-        <v>18.08190706662178</v>
+        <v>1.8931</v>
       </c>
       <c r="K12" t="n">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="L12" t="n">
-        <v>130</v>
+        <v>209</v>
       </c>
       <c r="M12" t="n">
-        <v>27.6075</v>
+        <v>2.9742</v>
       </c>
       <c r="N12" t="n">
-        <v>196</v>
+        <v>256</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.8835</v>
+        <v>2.969</v>
       </c>
       <c r="C13" t="n">
-        <v>3.49515</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9102649798860828</v>
+        <v>0.778</v>
       </c>
       <c r="E13" t="n">
-        <v>26.3672</v>
+        <v>2.969</v>
       </c>
       <c r="F13" t="n">
-        <v>5.071829470250899</v>
+        <v>1.0488</v>
       </c>
       <c r="G13" t="n">
-        <v>21.29534305077068</v>
+        <v>1.9202</v>
       </c>
       <c r="H13" t="n">
-        <v>5.071829470250899</v>
+        <v>1.0488</v>
       </c>
       <c r="I13" t="n">
-        <v>6.429860312012069</v>
+        <v>1.0488</v>
       </c>
       <c r="J13" t="n">
-        <v>21.29534305077068</v>
+        <v>1.9202</v>
       </c>
       <c r="K13" t="n">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="L13" t="n">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="M13" t="n">
-        <v>27.7252</v>
+        <v>2.969</v>
       </c>
       <c r="N13" t="n">
-        <v>167</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.5195</v>
+        <v>2.2785</v>
       </c>
       <c r="C14" t="n">
-        <v>3.16755</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7978451610612536</v>
+        <v>0.4991</v>
       </c>
       <c r="E14" t="n">
-        <v>21.4756</v>
+        <v>2.2785</v>
       </c>
       <c r="F14" t="n">
-        <v>9.60538984186392</v>
+        <v>1.0943</v>
       </c>
       <c r="G14" t="n">
-        <v>11.87019461775948</v>
+        <v>1.1842</v>
       </c>
       <c r="H14" t="n">
-        <v>9.60538984186392</v>
+        <v>1.0943</v>
       </c>
       <c r="I14" t="n">
-        <v>9.237970558295354</v>
+        <v>1.0943</v>
       </c>
       <c r="J14" t="n">
-        <v>11.87019461775948</v>
+        <v>1.1842</v>
       </c>
       <c r="K14" t="n">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="L14" t="n">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="M14" t="n">
-        <v>21.1082</v>
+        <v>2.2785</v>
       </c>
       <c r="N14" t="n">
-        <v>196</v>
+        <v>260</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.2242</v>
+        <v>1.7001</v>
       </c>
       <c r="C15" t="n">
-        <v>2.90178</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7115025495451375</v>
+        <v>0.2654</v>
       </c>
       <c r="E15" t="n">
-        <v>17.7187</v>
+        <v>1.7001</v>
       </c>
       <c r="F15" t="n">
-        <v>7.203657561066427</v>
+        <v>0.6455</v>
       </c>
       <c r="G15" t="n">
-        <v>10.51500492432503</v>
+        <v>1.0546</v>
       </c>
       <c r="H15" t="n">
-        <v>7.203657561066427</v>
+        <v>0.6455</v>
       </c>
       <c r="I15" t="n">
-        <v>9.132505760477656</v>
+        <v>0.6455</v>
       </c>
       <c r="J15" t="n">
-        <v>10.51500492432503</v>
+        <v>1.0546</v>
       </c>
       <c r="K15" t="n">
         <v>87</v>
@@ -1139,7 +1127,7 @@
         <v>80</v>
       </c>
       <c r="M15" t="n">
-        <v>19.6475</v>
+        <v>1.7001</v>
       </c>
       <c r="N15" t="n">
         <v>167</v>
@@ -1148,308 +1136,308 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>oSee</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.9965</v>
+        <v>1.593</v>
       </c>
       <c r="C16" t="n">
-        <v>2.69685</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6477472886646468</v>
+        <v>0.2222</v>
       </c>
       <c r="E16" t="n">
-        <v>14.9446</v>
+        <v>1.593</v>
       </c>
       <c r="F16" t="n">
-        <v>14.9445566717157</v>
+        <v>1.4701</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.1229</v>
       </c>
       <c r="H16" t="n">
-        <v>14.9445566717157</v>
+        <v>1.4701</v>
       </c>
       <c r="I16" t="n">
-        <v>12.41296510437588</v>
+        <v>1.4701</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.1229</v>
       </c>
       <c r="K16" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="M16" t="n">
-        <v>12.413</v>
+        <v>1.593</v>
       </c>
       <c r="N16" t="n">
-        <v>57</v>
+        <v>196</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>hades</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.7038</v>
+        <v>1.5058</v>
       </c>
       <c r="C17" t="n">
-        <v>2.43342</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5692973487030546</v>
+        <v>0.1869</v>
       </c>
       <c r="E17" t="n">
-        <v>11.5311</v>
+        <v>1.5058</v>
       </c>
       <c r="F17" t="n">
-        <v>11.53105900070918</v>
+        <v>-0.1405</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1.6463</v>
       </c>
       <c r="H17" t="n">
-        <v>11.53105900070918</v>
+        <v>-0.1405</v>
       </c>
       <c r="I17" t="n">
-        <v>15.45876033610557</v>
+        <v>-0.1405</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1.6463</v>
       </c>
       <c r="K17" t="n">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="M17" t="n">
-        <v>15.4588</v>
+        <v>1.5058</v>
       </c>
       <c r="N17" t="n">
-        <v>92</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.6427</v>
+        <v>1.4785</v>
       </c>
       <c r="C18" t="n">
-        <v>2.37843</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5534060005324943</v>
+        <v>0.1759</v>
       </c>
       <c r="E18" t="n">
-        <v>10.8396</v>
+        <v>1.4785</v>
       </c>
       <c r="F18" t="n">
-        <v>10.83959792379926</v>
+        <v>0.9386</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.5399</v>
       </c>
       <c r="H18" t="n">
-        <v>10.83959792379926</v>
+        <v>0.9386</v>
       </c>
       <c r="I18" t="n">
-        <v>12.0045091760837</v>
+        <v>0.9386</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.5399</v>
       </c>
       <c r="K18" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M18" t="n">
-        <v>12.0045</v>
+        <v>1.4785</v>
       </c>
       <c r="N18" t="n">
-        <v>76</v>
+        <v>167</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>isak</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.3615</v>
+        <v>1.3734</v>
       </c>
       <c r="C19" t="n">
-        <v>2.12535</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4822754770604564</v>
+        <v>0.1335</v>
       </c>
       <c r="E19" t="n">
-        <v>7.7446</v>
+        <v>1.3734</v>
       </c>
       <c r="F19" t="n">
-        <v>21.20558250488591</v>
+        <v>1.5713</v>
       </c>
       <c r="G19" t="n">
-        <v>-13.46100130548628</v>
+        <v>-0.1979</v>
       </c>
       <c r="H19" t="n">
-        <v>21.20558250488591</v>
+        <v>1.5713</v>
       </c>
       <c r="I19" t="n">
-        <v>21.93947333838834</v>
+        <v>1.5713</v>
       </c>
       <c r="J19" t="n">
-        <v>-13.46100130548628</v>
+        <v>-0.1979</v>
       </c>
       <c r="K19" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="L19" t="n">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="M19" t="n">
-        <v>8.4785</v>
+        <v>1.3734</v>
       </c>
       <c r="N19" t="n">
-        <v>138</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CacaNito</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.3589</v>
+        <v>1.3455</v>
       </c>
       <c r="C20" t="n">
-        <v>2.12301</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4816403729216848</v>
+        <v>0.1222</v>
       </c>
       <c r="E20" t="n">
-        <v>7.7169</v>
+        <v>1.3455</v>
       </c>
       <c r="F20" t="n">
-        <v>7.716946678587951</v>
+        <v>1.6584</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.3129</v>
       </c>
       <c r="H20" t="n">
-        <v>7.716946678587951</v>
+        <v>1.6584</v>
       </c>
       <c r="I20" t="n">
-        <v>7.984017692965311</v>
+        <v>1.6584</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.3129</v>
       </c>
       <c r="K20" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M20" t="n">
-        <v>7.984</v>
+        <v>1.3455</v>
       </c>
       <c r="N20" t="n">
-        <v>71</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.3476</v>
+        <v>1.1777</v>
       </c>
       <c r="C21" t="n">
-        <v>2.11284</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4788644927063032</v>
+        <v>0.0544</v>
       </c>
       <c r="E21" t="n">
-        <v>7.5962</v>
+        <v>1.1777</v>
       </c>
       <c r="F21" t="n">
-        <v>7.596163148927671</v>
+        <v>1.737</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.5593</v>
       </c>
       <c r="H21" t="n">
-        <v>7.596163148927671</v>
+        <v>1.737</v>
       </c>
       <c r="I21" t="n">
-        <v>9.630108472957485</v>
+        <v>1.737</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.5593</v>
       </c>
       <c r="K21" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M21" t="n">
-        <v>9.630100000000001</v>
+        <v>1.1777</v>
       </c>
       <c r="N21" t="n">
-        <v>87</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>oSee</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.337</v>
+        <v>1.0412</v>
       </c>
       <c r="C22" t="n">
-        <v>2.1033</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4762496240174491</v>
+        <v>-0.0007</v>
       </c>
       <c r="E22" t="n">
-        <v>7.4824</v>
+        <v>1.0412</v>
       </c>
       <c r="F22" t="n">
-        <v>7.482385519731763</v>
+        <v>1.0412</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>7.482385519731763</v>
+        <v>1.0412</v>
       </c>
       <c r="I22" t="n">
-        <v>6.214877590159716</v>
+        <v>1.0412</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1461,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>6.2149</v>
+        <v>1.0412</v>
       </c>
       <c r="N22" t="n">
         <v>57</v>
@@ -1470,584 +1458,584 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.177</v>
+        <v>0.8954</v>
       </c>
       <c r="C23" t="n">
-        <v>1.9593</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4374030097167868</v>
+        <v>-0.0596</v>
       </c>
       <c r="E23" t="n">
-        <v>5.7921</v>
+        <v>0.8954</v>
       </c>
       <c r="F23" t="n">
-        <v>5.792099618853835</v>
+        <v>0.8954</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>5.792099618853835</v>
+        <v>0.8954</v>
       </c>
       <c r="I23" t="n">
-        <v>7.342989680732732</v>
+        <v>0.8954</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>7.343</v>
+        <v>0.8954</v>
       </c>
       <c r="N23" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>isak</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.1261</v>
+        <v>0.8622</v>
       </c>
       <c r="C24" t="n">
-        <v>1.91349</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4252463530865093</v>
+        <v>-0.0731</v>
       </c>
       <c r="E24" t="n">
-        <v>5.2631</v>
+        <v>0.8622</v>
       </c>
       <c r="F24" t="n">
-        <v>23.32815596025804</v>
+        <v>1.6121</v>
       </c>
       <c r="G24" t="n">
-        <v>-18.06501428726107</v>
+        <v>-0.7499</v>
       </c>
       <c r="H24" t="n">
-        <v>23.32815596025804</v>
+        <v>1.6121</v>
       </c>
       <c r="I24" t="n">
-        <v>18.01664504034501</v>
+        <v>1.6121</v>
       </c>
       <c r="J24" t="n">
-        <v>-18.06501428726107</v>
+        <v>-0.7499</v>
       </c>
       <c r="K24" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="L24" t="n">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.0484</v>
+        <v>0.8622000000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>98</v>
+        <v>138</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.0867</v>
+        <v>0.8223</v>
       </c>
       <c r="C25" t="n">
-        <v>1.87803</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4159157828432798</v>
+        <v>-0.0892</v>
       </c>
       <c r="E25" t="n">
-        <v>4.8572</v>
+        <v>0.8223</v>
       </c>
       <c r="F25" t="n">
-        <v>28.01084527522437</v>
+        <v>0.2386</v>
       </c>
       <c r="G25" t="n">
-        <v>-23.15369345779668</v>
+        <v>0.5837</v>
       </c>
       <c r="H25" t="n">
-        <v>28.01084527522437</v>
+        <v>0.2386</v>
       </c>
       <c r="I25" t="n">
-        <v>21.63314826356126</v>
+        <v>0.2386</v>
       </c>
       <c r="J25" t="n">
-        <v>-23.15369345779668</v>
+        <v>0.5837</v>
       </c>
       <c r="K25" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="L25" t="n">
-        <v>45</v>
+        <v>130</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.5205</v>
+        <v>0.8223</v>
       </c>
       <c r="N25" t="n">
-        <v>98</v>
+        <v>196</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.9485</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="C26" t="n">
-        <v>1.75365</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3836947803446822</v>
+        <v>-0.1092</v>
       </c>
       <c r="E26" t="n">
-        <v>3.4552</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>3.455158176128459</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>3.455158176128459</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>3.57473559934602</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5747</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>71</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BOROS</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.9425</v>
+        <v>0.7719</v>
       </c>
       <c r="C27" t="n">
-        <v>1.74825</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3822976142495472</v>
+        <v>-0.1095</v>
       </c>
       <c r="E27" t="n">
-        <v>3.3944</v>
+        <v>0.7719</v>
       </c>
       <c r="F27" t="n">
-        <v>3.394364972028014</v>
+        <v>1.6955</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.9236</v>
       </c>
       <c r="H27" t="n">
-        <v>3.394364972028014</v>
+        <v>1.6955</v>
       </c>
       <c r="I27" t="n">
-        <v>3.264525874737324</v>
+        <v>1.6955</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.9236</v>
       </c>
       <c r="K27" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M27" t="n">
-        <v>3.2645</v>
+        <v>0.7719</v>
       </c>
       <c r="N27" t="n">
-        <v>66</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Goofy</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.9002</v>
+        <v>0.7548</v>
       </c>
       <c r="C28" t="n">
-        <v>1.71018</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3725922565043722</v>
+        <v>-0.1164</v>
       </c>
       <c r="E28" t="n">
-        <v>2.9721</v>
+        <v>0.7548</v>
       </c>
       <c r="F28" t="n">
-        <v>2.972067439669682</v>
+        <v>0.7548</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>2.972067439669682</v>
+        <v>0.7548</v>
       </c>
       <c r="I28" t="n">
-        <v>3.98441099380125</v>
+        <v>0.7548</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.9844</v>
+        <v>0.7548</v>
       </c>
       <c r="N28" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>hades</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.7132</v>
+        <v>0.6974</v>
       </c>
       <c r="C29" t="n">
-        <v>1.54188</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3304647799609249</v>
+        <v>-0.1396</v>
       </c>
       <c r="E29" t="n">
-        <v>1.139</v>
+        <v>0.6974</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2496819971024994</v>
+        <v>0.6974</v>
       </c>
       <c r="G29" t="n">
-        <v>0.8893433377951201</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.2496819971024994</v>
+        <v>0.6974</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3347285061337697</v>
+        <v>0.6974</v>
       </c>
       <c r="J29" t="n">
-        <v>0.8893433377951201</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>92</v>
       </c>
       <c r="L29" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.2241</v>
+        <v>0.6974</v>
       </c>
       <c r="N29" t="n">
-        <v>260</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>neaLaN</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.6846</v>
+        <v>0.6746</v>
       </c>
       <c r="C30" t="n">
-        <v>1.51614</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3241512102134851</v>
+        <v>-0.1488</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8643</v>
+        <v>0.6746</v>
       </c>
       <c r="F30" t="n">
-        <v>0.864310585094445</v>
+        <v>1.6746</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H30" t="n">
-        <v>0.864310585094445</v>
+        <v>1.6746</v>
       </c>
       <c r="I30" t="n">
-        <v>0.9571964221082379</v>
+        <v>1.6746</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K30" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="M30" t="n">
-        <v>0.9572000000000001</v>
+        <v>0.6746000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>76</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>mhL</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.6153</v>
+        <v>0.634</v>
       </c>
       <c r="C31" t="n">
-        <v>1.45377</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3089433025610777</v>
+        <v>-0.1652</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2026</v>
+        <v>0.634</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2025872316057086</v>
+        <v>0.634</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2025872316057086</v>
+        <v>0.634</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1948379932382771</v>
+        <v>0.634</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.1948</v>
+        <v>0.634</v>
       </c>
       <c r="N31" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>mynio</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.4422</v>
+        <v>0.4706</v>
       </c>
       <c r="C32" t="n">
-        <v>1.29798</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2717070786382683</v>
+        <v>-0.2313</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.4176</v>
+        <v>0.4706</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.41762769398653</v>
+        <v>0.4806</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.41762769398653</v>
+        <v>0.4806</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.900499057876296</v>
+        <v>0.4806</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="K32" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M32" t="n">
-        <v>-1.9005</v>
+        <v>0.4706</v>
       </c>
       <c r="N32" t="n">
-        <v>92</v>
+        <v>167</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.4409</v>
+        <v>0.4551</v>
       </c>
       <c r="C33" t="n">
-        <v>1.29681</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2714406185695707</v>
+        <v>-0.2375</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.4292</v>
+        <v>0.4551</v>
       </c>
       <c r="F33" t="n">
-        <v>8.325778648864768</v>
+        <v>0.9208</v>
       </c>
       <c r="G33" t="n">
-        <v>-9.755000498619429</v>
+        <v>-0.4657</v>
       </c>
       <c r="H33" t="n">
-        <v>8.325778648864768</v>
+        <v>0.9208</v>
       </c>
       <c r="I33" t="n">
-        <v>9.220534459944952</v>
+        <v>0.9208</v>
       </c>
       <c r="J33" t="n">
-        <v>-9.755000498619429</v>
+        <v>-0.4657</v>
       </c>
       <c r="K33" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="L33" t="n">
         <v>45</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5345</v>
+        <v>0.4550999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>121</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.3751</v>
+        <v>0.4468</v>
       </c>
       <c r="C34" t="n">
-        <v>1.23759</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2575652098577817</v>
+        <v>-0.2409</v>
       </c>
       <c r="E34" t="n">
-        <v>-2.033</v>
+        <v>0.4468</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8954004712559137</v>
+        <v>0.4468</v>
       </c>
       <c r="G34" t="n">
-        <v>-2.928366254341102</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.8954004712559137</v>
+        <v>0.4468</v>
       </c>
       <c r="I34" t="n">
-        <v>1.135152510007497</v>
+        <v>0.4468</v>
       </c>
       <c r="J34" t="n">
-        <v>-2.928366254341102</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="L34" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.7932</v>
+        <v>0.4468</v>
       </c>
       <c r="N34" t="n">
-        <v>167</v>
+        <v>71</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>nawwk</t>
+          <t>CacaNito</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.2576</v>
+        <v>0.3932</v>
       </c>
       <c r="C35" t="n">
-        <v>1.13184</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0.233190497700552</v>
+        <v>-0.2625</v>
       </c>
       <c r="E35" t="n">
-        <v>-3.0936</v>
+        <v>0.3932</v>
       </c>
       <c r="F35" t="n">
-        <v>-3.093553250977358</v>
+        <v>0.3932</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-3.093553250977358</v>
+        <v>0.3932</v>
       </c>
       <c r="I35" t="n">
-        <v>-3.200616113943788</v>
+        <v>0.3932</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2059,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-3.2006</v>
+        <v>0.3932</v>
       </c>
       <c r="N35" t="n">
         <v>71</v>
@@ -2068,952 +2056,952 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>KEi</t>
+          <t>nawwk</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.0269</v>
+        <v>0.3907</v>
       </c>
       <c r="C36" t="n">
-        <v>0.92421</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1866719131197477</v>
+        <v>-0.2635</v>
       </c>
       <c r="E36" t="n">
-        <v>-5.1177</v>
+        <v>0.3907</v>
       </c>
       <c r="F36" t="n">
-        <v>-5.117660346570247</v>
+        <v>0.3907</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-5.117660346570247</v>
+        <v>0.3907</v>
       </c>
       <c r="I36" t="n">
-        <v>-6.86083427154044</v>
+        <v>0.3907</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-6.8608</v>
+        <v>0.3907</v>
       </c>
       <c r="N36" t="n">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>acoR</t>
+          <t>Goofy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.9903999999999999</v>
+        <v>0.3629</v>
       </c>
       <c r="C37" t="n">
-        <v>0.8913599999999999</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1794778627881228</v>
+        <v>-0.2748</v>
       </c>
       <c r="E37" t="n">
-        <v>-5.4307</v>
+        <v>0.3629</v>
       </c>
       <c r="F37" t="n">
-        <v>-3.288066389423184</v>
+        <v>0.3629</v>
       </c>
       <c r="G37" t="n">
-        <v>-2.14261999724509</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-3.288066389423184</v>
+        <v>0.3629</v>
       </c>
       <c r="I37" t="n">
-        <v>-3.401861036780271</v>
+        <v>0.3629</v>
       </c>
       <c r="J37" t="n">
-        <v>-2.14261999724509</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="L37" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-5.5445</v>
+        <v>0.3629</v>
       </c>
       <c r="N37" t="n">
-        <v>138</v>
+        <v>92</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>neaLaN</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8682</v>
+        <v>0.2899</v>
       </c>
       <c r="C38" t="n">
-        <v>0.78138</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1556889376925187</v>
+        <v>-0.3042</v>
       </c>
       <c r="E38" t="n">
-        <v>-6.4658</v>
+        <v>0.2899</v>
       </c>
       <c r="F38" t="n">
-        <v>22.16138375815863</v>
+        <v>0.5396</v>
       </c>
       <c r="G38" t="n">
-        <v>-28.62716896643656</v>
+        <v>-0.2497</v>
       </c>
       <c r="H38" t="n">
-        <v>22.16138375815863</v>
+        <v>0.5396</v>
       </c>
       <c r="I38" t="n">
-        <v>22.92835332355938</v>
+        <v>0.5396</v>
       </c>
       <c r="J38" t="n">
-        <v>-28.62716896643656</v>
+        <v>-0.2497</v>
       </c>
       <c r="K38" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="L38" t="n">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="M38" t="n">
-        <v>-5.6988</v>
+        <v>0.2898999999999999</v>
       </c>
       <c r="N38" t="n">
-        <v>138</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>roeJ</t>
+          <t>BOROS</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8651</v>
+        <v>0.2498</v>
       </c>
       <c r="C39" t="n">
-        <v>0.77859</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1550931963974064</v>
+        <v>-0.3204</v>
       </c>
       <c r="E39" t="n">
-        <v>-6.4917</v>
+        <v>0.2498</v>
       </c>
       <c r="F39" t="n">
-        <v>-6.491706981122937</v>
+        <v>0.2498</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-6.491706981122937</v>
+        <v>0.2498</v>
       </c>
       <c r="I39" t="n">
-        <v>-5.013631621122268</v>
+        <v>0.2498</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-5.0136</v>
+        <v>0.2498</v>
       </c>
       <c r="N39" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>volt</t>
+          <t>mhL</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8595</v>
+        <v>0.1469</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7735500000000001</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1540160901836343</v>
+        <v>-0.362</v>
       </c>
       <c r="E40" t="n">
-        <v>-6.5386</v>
+        <v>0.1469</v>
       </c>
       <c r="F40" t="n">
-        <v>-11.82478352373321</v>
+        <v>0.1469</v>
       </c>
       <c r="G40" t="n">
-        <v>5.286209718315213</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-11.82478352373321</v>
+        <v>0.1469</v>
       </c>
       <c r="I40" t="n">
-        <v>-12.23402011198627</v>
+        <v>0.1469</v>
       </c>
       <c r="J40" t="n">
-        <v>5.286209718315213</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="L40" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-6.9478</v>
+        <v>0.1469</v>
       </c>
       <c r="N40" t="n">
-        <v>138</v>
+        <v>66</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7615</v>
+        <v>0.1415</v>
       </c>
       <c r="C41" t="n">
-        <v>0.68535</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1353307642526088</v>
+        <v>-0.3642</v>
       </c>
       <c r="E41" t="n">
-        <v>-7.3516</v>
+        <v>0.1415</v>
       </c>
       <c r="F41" t="n">
-        <v>5.370610799537519</v>
+        <v>0.1415</v>
       </c>
       <c r="G41" t="n">
-        <v>-12.72221666818947</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>5.370610799537519</v>
+        <v>0.1415</v>
       </c>
       <c r="I41" t="n">
-        <v>5.165177599555209</v>
+        <v>0.1415</v>
       </c>
       <c r="J41" t="n">
-        <v>-12.72221666818947</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="L41" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-7.557</v>
+        <v>0.1415</v>
       </c>
       <c r="N41" t="n">
-        <v>196</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7165</v>
+        <v>0.1265</v>
       </c>
       <c r="C42" t="n">
-        <v>0.64485</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1268343566941982</v>
+        <v>-0.3703</v>
       </c>
       <c r="E42" t="n">
-        <v>-7.7213</v>
+        <v>0.1265</v>
       </c>
       <c r="F42" t="n">
-        <v>-7.721299808848153</v>
+        <v>0.1265</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-7.721299808848153</v>
+        <v>0.1265</v>
       </c>
       <c r="I42" t="n">
-        <v>-6.413320059808302</v>
+        <v>0.1265</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>-6.4133</v>
+        <v>0.1265</v>
       </c>
       <c r="N42" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6966</v>
+        <v>0.096</v>
       </c>
       <c r="C43" t="n">
-        <v>0.6269400000000001</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1231016595345857</v>
+        <v>-0.3826</v>
       </c>
       <c r="E43" t="n">
-        <v>-7.8837</v>
+        <v>0.096</v>
       </c>
       <c r="F43" t="n">
-        <v>-7.883716160819203</v>
+        <v>0.096</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-7.883716160819203</v>
+        <v>0.096</v>
       </c>
       <c r="I43" t="n">
-        <v>-9.994656553606859</v>
+        <v>0.096</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>-9.9947</v>
+        <v>0.096</v>
       </c>
       <c r="N43" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>mynio</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5790999999999999</v>
+        <v>0.0559</v>
       </c>
       <c r="C44" t="n">
-        <v>0.5211899999999999</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0.101332621607794</v>
+        <v>-0.3988</v>
       </c>
       <c r="E44" t="n">
-        <v>-8.8309</v>
+        <v>0.0559</v>
       </c>
       <c r="F44" t="n">
-        <v>-14.06642406937186</v>
+        <v>0.0559</v>
       </c>
       <c r="G44" t="n">
-        <v>5.235498002470684</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-14.06642406937186</v>
+        <v>0.0559</v>
       </c>
       <c r="I44" t="n">
-        <v>-13.52836413229206</v>
+        <v>0.0559</v>
       </c>
       <c r="J44" t="n">
-        <v>5.235498002470684</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="L44" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>-8.292899999999999</v>
+        <v>0.0559</v>
       </c>
       <c r="N44" t="n">
-        <v>196</v>
+        <v>92</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>roeJ</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4312</v>
+        <v>-0.0843</v>
       </c>
       <c r="C45" t="n">
-        <v>0.38808</v>
+        <v>-0</v>
       </c>
       <c r="D45" t="n">
-        <v>0.07450540059295249</v>
+        <v>-0.4554</v>
       </c>
       <c r="E45" t="n">
-        <v>-9.998200000000001</v>
+        <v>-0.0843</v>
       </c>
       <c r="F45" t="n">
-        <v>11.75983794467387</v>
+        <v>-0.0843</v>
       </c>
       <c r="G45" t="n">
-        <v>-21.75806454104099</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>11.75983794467387</v>
+        <v>-0.0843</v>
       </c>
       <c r="I45" t="n">
-        <v>9.082279214101492</v>
+        <v>-0.0843</v>
       </c>
       <c r="J45" t="n">
-        <v>-21.75806454104099</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
         <v>53</v>
       </c>
       <c r="L45" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>-12.6758</v>
+        <v>-0.0843</v>
       </c>
       <c r="N45" t="n">
-        <v>98</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>afro</t>
+          <t>KEi</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4149</v>
+        <v>-0.0877</v>
       </c>
       <c r="C46" t="n">
-        <v>0.37341</v>
+        <v>-0</v>
       </c>
       <c r="D46" t="n">
-        <v>0.07158975769343405</v>
+        <v>-0.4568</v>
       </c>
       <c r="E46" t="n">
-        <v>-10.1251</v>
+        <v>-0.0877</v>
       </c>
       <c r="F46" t="n">
-        <v>-10.12509145122699</v>
+        <v>-0.0877</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-10.12509145122699</v>
+        <v>-0.0877</v>
       </c>
       <c r="I46" t="n">
-        <v>-7.819742760146164</v>
+        <v>-0.0877</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>-7.8197</v>
+        <v>-0.0877</v>
       </c>
       <c r="N46" t="n">
-        <v>53</v>
+        <v>92</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.2745</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="C47" t="n">
-        <v>0.24705</v>
+        <v>-0</v>
       </c>
       <c r="D47" t="n">
-        <v>0.04680416107102147</v>
+        <v>-0.46</v>
       </c>
       <c r="E47" t="n">
-        <v>-11.2036</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="F47" t="n">
-        <v>-11.2035572395569</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-11.2035572395569</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>-8.652656228728823</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-8.652699999999999</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="N47" t="n">
-        <v>53</v>
+        <v>87</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.1787</v>
+        <v>-0.1378</v>
       </c>
       <c r="C48" t="n">
-        <v>0.16083</v>
+        <v>-0</v>
       </c>
       <c r="D48" t="n">
-        <v>0.03022961653072197</v>
+        <v>-0.477</v>
       </c>
       <c r="E48" t="n">
-        <v>-11.9247</v>
+        <v>-0.1378</v>
       </c>
       <c r="F48" t="n">
-        <v>-11.92474541655238</v>
+        <v>-0.1378</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-11.92474541655238</v>
+        <v>-0.1378</v>
       </c>
       <c r="I48" t="n">
-        <v>-9.209639447392004</v>
+        <v>-0.1378</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>-9.2096</v>
+        <v>-0.1378</v>
       </c>
       <c r="N48" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>afro</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.0155</v>
+        <v>-0.1605</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.01395</v>
+        <v>-0</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.002584428335813578</v>
+        <v>-0.4862</v>
       </c>
       <c r="E49" t="n">
-        <v>-13.3525</v>
+        <v>-0.1605</v>
       </c>
       <c r="F49" t="n">
-        <v>-13.35254339553185</v>
+        <v>-0.1605</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-13.35254339553185</v>
+        <v>-0.1605</v>
       </c>
       <c r="I49" t="n">
-        <v>-16.92781457794202</v>
+        <v>-0.1605</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-16.9278</v>
+        <v>-0.1605</v>
       </c>
       <c r="N49" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.0377</v>
+        <v>-0.1804</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.03393</v>
+        <v>-0</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.006309596568308779</v>
+        <v>-0.4942</v>
       </c>
       <c r="E50" t="n">
-        <v>-13.5146</v>
+        <v>-0.1804</v>
       </c>
       <c r="F50" t="n">
-        <v>-6.43915282102722</v>
+        <v>-0.1804</v>
       </c>
       <c r="G50" t="n">
-        <v>-7.075479329345686</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-6.43915282102722</v>
+        <v>-0.1804</v>
       </c>
       <c r="I50" t="n">
-        <v>-7.131156493960928</v>
+        <v>-0.1804</v>
       </c>
       <c r="J50" t="n">
-        <v>-7.075479329345686</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="L50" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-14.2066</v>
+        <v>-0.1804</v>
       </c>
       <c r="N50" t="n">
-        <v>121</v>
+        <v>47</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>exit</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.1661</v>
+        <v>-0.2484</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.14949</v>
+        <v>-0</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.02806815004175367</v>
+        <v>-0.5217000000000001</v>
       </c>
       <c r="E51" t="n">
-        <v>-14.4614</v>
+        <v>-0.2484</v>
       </c>
       <c r="F51" t="n">
-        <v>-14.46138585907475</v>
+        <v>-0.2484</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-14.46138585907475</v>
+        <v>-0.2484</v>
       </c>
       <c r="I51" t="n">
-        <v>-18.3335602147833</v>
+        <v>-0.2484</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-18.3336</v>
+        <v>-0.2484</v>
       </c>
       <c r="N51" t="n">
-        <v>87</v>
+        <v>47</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.3056</v>
+        <v>-0.2719</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.27504</v>
+        <v>-0</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.0522456945741304</v>
+        <v>-0.5312</v>
       </c>
       <c r="E52" t="n">
-        <v>-15.5134</v>
+        <v>-0.2719</v>
       </c>
       <c r="F52" t="n">
-        <v>-15.51339420978005</v>
+        <v>0.0187</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>-0.2906</v>
       </c>
       <c r="H52" t="n">
-        <v>-15.51339420978005</v>
+        <v>0.0187</v>
       </c>
       <c r="I52" t="n">
-        <v>-17.18058958023</v>
+        <v>0.0187</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>-0.2906</v>
       </c>
       <c r="K52" t="n">
         <v>76</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M52" t="n">
-        <v>-17.1806</v>
+        <v>-0.2719</v>
       </c>
       <c r="N52" t="n">
-        <v>76</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>acoR</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.3586</v>
+        <v>-0.3213</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.32274</v>
+        <v>-0</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.06159120035504551</v>
+        <v>-0.5512</v>
       </c>
       <c r="E53" t="n">
-        <v>-15.92</v>
+        <v>-0.3213</v>
       </c>
       <c r="F53" t="n">
-        <v>-15.92003393739679</v>
+        <v>-0.3691</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>0.0478</v>
       </c>
       <c r="H53" t="n">
-        <v>-15.92003393739679</v>
+        <v>-0.3691</v>
       </c>
       <c r="I53" t="n">
-        <v>-10.9033383614958</v>
+        <v>-0.3691</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>0.0478</v>
       </c>
       <c r="K53" t="n">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="M53" t="n">
-        <v>-10.9033</v>
+        <v>-0.3213</v>
       </c>
       <c r="N53" t="n">
-        <v>47</v>
+        <v>138</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.4013</v>
+        <v>-0.3233</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.36117</v>
+        <v>-0</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.0691662995187278</v>
+        <v>-0.552</v>
       </c>
       <c r="E54" t="n">
-        <v>-16.2496</v>
+        <v>-0.3233</v>
       </c>
       <c r="F54" t="n">
-        <v>-16.24964009599337</v>
+        <v>-0.3233</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-16.24964009599337</v>
+        <v>-0.3233</v>
       </c>
       <c r="I54" t="n">
-        <v>-17.99595843053547</v>
+        <v>-0.3233</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-17.996</v>
+        <v>-0.3233</v>
       </c>
       <c r="N54" t="n">
-        <v>76</v>
+        <v>57</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>lauNX</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.4426</v>
+        <v>-0.3289</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.39834</v>
+        <v>-0</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.07655298086111301</v>
+        <v>-0.5542</v>
       </c>
       <c r="E55" t="n">
-        <v>-16.571</v>
+        <v>-0.3289</v>
       </c>
       <c r="F55" t="n">
-        <v>-16.57104785705787</v>
+        <v>-0.3289</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-16.57104785705787</v>
+        <v>-0.3289</v>
       </c>
       <c r="I55" t="n">
-        <v>-18.35190728067611</v>
+        <v>-0.3289</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-18.3519</v>
+        <v>-0.3289</v>
       </c>
       <c r="N55" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.5149</v>
+        <v>-0.3298</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.46341</v>
+        <v>-0</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.08960204712153119</v>
+        <v>-0.5546</v>
       </c>
       <c r="E56" t="n">
-        <v>-17.1388</v>
+        <v>-0.3298</v>
       </c>
       <c r="F56" t="n">
-        <v>-17.13883614740652</v>
+        <v>-0.3298</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-17.13883614740652</v>
+        <v>-0.3298</v>
       </c>
       <c r="I56" t="n">
-        <v>-16.48325225105764</v>
+        <v>-0.3298</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3025,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-16.4833</v>
+        <v>-0.3298</v>
       </c>
       <c r="N56" t="n">
         <v>66</v>
@@ -3034,691 +3022,691 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.5213</v>
+        <v>-0.3983</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.46917</v>
+        <v>-0</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.09077153322998747</v>
+        <v>-0.5823</v>
       </c>
       <c r="E57" t="n">
-        <v>-17.1897</v>
+        <v>-0.3983</v>
       </c>
       <c r="F57" t="n">
-        <v>-17.18972258670073</v>
+        <v>-0.3983</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-17.18972258670073</v>
+        <v>-0.3983</v>
       </c>
       <c r="I57" t="n">
-        <v>-17.78463101866305</v>
+        <v>-0.3983</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-17.7846</v>
+        <v>-0.3983</v>
       </c>
       <c r="N57" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>dexter</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.555</v>
+        <v>-0.4078</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.4995000000000001</v>
+        <v>-0</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.09691901283592848</v>
+        <v>-0.5861</v>
       </c>
       <c r="E58" t="n">
-        <v>-17.4572</v>
+        <v>-0.4078</v>
       </c>
       <c r="F58" t="n">
-        <v>-17.45721045638825</v>
+        <v>-0.4078</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-17.45721045638825</v>
+        <v>-0.4078</v>
       </c>
       <c r="I58" t="n">
-        <v>-16.78944830778323</v>
+        <v>-0.4078</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-16.7894</v>
+        <v>-0.4078</v>
       </c>
       <c r="N58" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>volt</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.7575</v>
+        <v>-0.4309</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.68175</v>
+        <v>-0</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.1345583148430067</v>
+        <v>-0.5954</v>
       </c>
       <c r="E59" t="n">
-        <v>-19.095</v>
+        <v>-0.4309</v>
       </c>
       <c r="F59" t="n">
-        <v>-19.09496403277562</v>
+        <v>-0.4423</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>0.0114</v>
       </c>
       <c r="H59" t="n">
-        <v>-19.09496403277562</v>
+        <v>-0.4423</v>
       </c>
       <c r="I59" t="n">
-        <v>-13.07778957435999</v>
+        <v>-0.4423</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>0.0114</v>
       </c>
       <c r="K59" t="n">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="M59" t="n">
-        <v>-13.0778</v>
+        <v>-0.4309</v>
       </c>
       <c r="N59" t="n">
-        <v>47</v>
+        <v>138</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.7593</v>
+        <v>-0.4378</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.68337</v>
+        <v>-0</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.1349104712928284</v>
+        <v>-0.5982</v>
       </c>
       <c r="E60" t="n">
-        <v>-19.1103</v>
+        <v>-0.4378</v>
       </c>
       <c r="F60" t="n">
-        <v>-5.338940939527125</v>
+        <v>-0.4378</v>
       </c>
       <c r="G60" t="n">
-        <v>-13.7713460523468</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-5.338940939527125</v>
+        <v>-0.4378</v>
       </c>
       <c r="I60" t="n">
-        <v>-5.912706905705813</v>
+        <v>-0.4378</v>
       </c>
       <c r="J60" t="n">
-        <v>-13.7713460523468</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="L60" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-19.6841</v>
+        <v>-0.4378</v>
       </c>
       <c r="N60" t="n">
-        <v>121</v>
+        <v>87</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-0.5766</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.68904</v>
+        <v>-0</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.1360927271087567</v>
+        <v>-0.6543</v>
       </c>
       <c r="E61" t="n">
-        <v>-19.1617</v>
+        <v>-0.5766</v>
       </c>
       <c r="F61" t="n">
-        <v>7.40364133743423</v>
+        <v>-0.0344</v>
       </c>
       <c r="G61" t="n">
-        <v>-26.5653704014905</v>
+        <v>-0.5422</v>
       </c>
       <c r="H61" t="n">
-        <v>7.40364133743423</v>
+        <v>-0.0344</v>
       </c>
       <c r="I61" t="n">
-        <v>8.199296781712226</v>
+        <v>-0.0344</v>
       </c>
       <c r="J61" t="n">
-        <v>-26.5653704014905</v>
+        <v>-0.5422</v>
       </c>
       <c r="K61" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="L61" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="M61" t="n">
-        <v>-18.3661</v>
+        <v>-0.5766</v>
       </c>
       <c r="N61" t="n">
-        <v>121</v>
+        <v>167</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>lauNX</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.9081</v>
+        <v>-0.6081</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.8172900000000001</v>
+        <v>-0</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.1634107052517131</v>
+        <v>-0.667</v>
       </c>
       <c r="E62" t="n">
-        <v>-20.3504</v>
+        <v>-0.6081</v>
       </c>
       <c r="F62" t="n">
-        <v>-20.35038331686057</v>
+        <v>-0.6081</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-20.35038331686057</v>
+        <v>-0.6081</v>
       </c>
       <c r="I62" t="n">
-        <v>-19.57195335392055</v>
+        <v>-0.6081</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-19.572</v>
+        <v>-0.6081</v>
       </c>
       <c r="N62" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Kylar</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-1.0387</v>
+        <v>-0.6263</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.9348299999999999</v>
+        <v>-0</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.1890129579537508</v>
+        <v>-0.6744</v>
       </c>
       <c r="E63" t="n">
-        <v>-21.4644</v>
+        <v>-0.6263</v>
       </c>
       <c r="F63" t="n">
-        <v>-21.4643832767549</v>
+        <v>-0.6263</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-21.4643832767549</v>
+        <v>-0.6263</v>
       </c>
       <c r="I63" t="n">
-        <v>-28.77556665153298</v>
+        <v>-0.6263</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-28.7756</v>
+        <v>-0.6263</v>
       </c>
       <c r="N63" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-1.0925</v>
+        <v>-0.6573</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.9832500000000001</v>
+        <v>-0</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.1997166267980102</v>
+        <v>-0.6869</v>
       </c>
       <c r="E64" t="n">
-        <v>-21.9301</v>
+        <v>-0.6573</v>
       </c>
       <c r="F64" t="n">
-        <v>-21.93011911656551</v>
+        <v>-0.6573</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-21.93011911656551</v>
+        <v>-0.6573</v>
       </c>
       <c r="I64" t="n">
-        <v>-15.01953513265689</v>
+        <v>-0.6573</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-15.0195</v>
+        <v>-0.6573</v>
       </c>
       <c r="N64" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>dexter</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-1.1107</v>
+        <v>-0.7004</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.99963</v>
+        <v>-0</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.2033512460733814</v>
+        <v>-0.7043</v>
       </c>
       <c r="E65" t="n">
-        <v>-22.0883</v>
+        <v>-0.7004</v>
       </c>
       <c r="F65" t="n">
-        <v>-22.08826792378639</v>
+        <v>-0.7004</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-22.08826792378639</v>
+        <v>-0.7004</v>
       </c>
       <c r="I65" t="n">
-        <v>-17.05906302310643</v>
+        <v>-0.7004</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-17.0591</v>
+        <v>-0.7004</v>
       </c>
       <c r="N65" t="n">
-        <v>53</v>
+        <v>76</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-1.2265</v>
+        <v>-0.7111</v>
       </c>
       <c r="C66" t="n">
-        <v>-1.10385</v>
+        <v>-0</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.2268087153910474</v>
+        <v>-0.7086</v>
       </c>
       <c r="E66" t="n">
-        <v>-23.1089</v>
+        <v>-0.7111</v>
       </c>
       <c r="F66" t="n">
-        <v>-3.39534298227336</v>
+        <v>-0.7111</v>
       </c>
       <c r="G66" t="n">
-        <v>-19.71360152740667</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-3.39534298227336</v>
+        <v>-0.7111</v>
       </c>
       <c r="I66" t="n">
-        <v>-4.304478534903932</v>
+        <v>-0.7111</v>
       </c>
       <c r="J66" t="n">
-        <v>-19.71360152740667</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="L66" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-24.0181</v>
+        <v>-0.7111</v>
       </c>
       <c r="N66" t="n">
-        <v>167</v>
+        <v>76</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>Qikert</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-1.5365</v>
+        <v>-0.7645</v>
       </c>
       <c r="C67" t="n">
-        <v>-1.38285</v>
+        <v>-0</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.2918566594243867</v>
+        <v>-0.7302</v>
       </c>
       <c r="E67" t="n">
-        <v>-25.9393</v>
+        <v>-0.7645</v>
       </c>
       <c r="F67" t="n">
-        <v>-25.93929728713625</v>
+        <v>-0.1015</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>-0.663</v>
       </c>
       <c r="H67" t="n">
-        <v>-25.93929728713625</v>
+        <v>-0.1015</v>
       </c>
       <c r="I67" t="n">
-        <v>-26.8370143152885</v>
+        <v>-0.1015</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>-0.663</v>
       </c>
       <c r="K67" t="n">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M67" t="n">
-        <v>-26.837</v>
+        <v>-0.7645000000000001</v>
       </c>
       <c r="N67" t="n">
-        <v>71</v>
+        <v>167</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Patsi</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.6237</v>
+        <v>-0.8018999999999999</v>
       </c>
       <c r="C68" t="n">
-        <v>-1.46133</v>
+        <v>-0</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.3107781010348004</v>
+        <v>-0.7453</v>
       </c>
       <c r="E68" t="n">
-        <v>-26.7626</v>
+        <v>-0.8018999999999999</v>
       </c>
       <c r="F68" t="n">
-        <v>-26.76260316730459</v>
+        <v>-0.8018999999999999</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-26.76260316730459</v>
+        <v>-0.8018999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>-22.22904743950983</v>
+        <v>-0.8018999999999999</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-22.229</v>
+        <v>-0.8018999999999999</v>
       </c>
       <c r="N68" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>Patsi</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.7566</v>
+        <v>-0.8426</v>
       </c>
       <c r="C69" t="n">
-        <v>-1.58094</v>
+        <v>-0</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.3401267732599947</v>
+        <v>-0.7618</v>
       </c>
       <c r="E69" t="n">
-        <v>-28.0396</v>
+        <v>-0.8426</v>
       </c>
       <c r="F69" t="n">
-        <v>10.54931215468354</v>
+        <v>-0.8426</v>
       </c>
       <c r="G69" t="n">
-        <v>-38.58892871851695</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>10.54931215468354</v>
+        <v>-0.8426</v>
       </c>
       <c r="I69" t="n">
-        <v>10.14578655313827</v>
+        <v>-0.8426</v>
       </c>
       <c r="J69" t="n">
-        <v>-38.58892871851695</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="L69" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-28.4431</v>
+        <v>-0.8426</v>
       </c>
       <c r="N69" t="n">
-        <v>196</v>
+        <v>57</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Qikert</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.9119</v>
+        <v>-0.8484</v>
       </c>
       <c r="C70" t="n">
-        <v>-1.72071</v>
+        <v>-0</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.3752743905769273</v>
+        <v>-0.7641</v>
       </c>
       <c r="E70" t="n">
-        <v>-29.569</v>
+        <v>-0.8484</v>
       </c>
       <c r="F70" t="n">
-        <v>-5.887637718936138</v>
+        <v>0.1516</v>
       </c>
       <c r="G70" t="n">
-        <v>-23.68131474893386</v>
+        <v>-1</v>
       </c>
       <c r="H70" t="n">
-        <v>-5.887637718936138</v>
+        <v>0.1516</v>
       </c>
       <c r="I70" t="n">
-        <v>-7.464109020727782</v>
+        <v>0.1516</v>
       </c>
       <c r="J70" t="n">
-        <v>-23.68131474893386</v>
+        <v>-1</v>
       </c>
       <c r="K70" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="L70" t="n">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="M70" t="n">
-        <v>-31.1454</v>
+        <v>-0.8484</v>
       </c>
       <c r="N70" t="n">
-        <v>167</v>
+        <v>98</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>jL</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-2.2975</v>
+        <v>-0.8608</v>
       </c>
       <c r="C71" t="n">
-        <v>-2.06775</v>
+        <v>-0</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.4665650307074097</v>
+        <v>-0.7691</v>
       </c>
       <c r="E71" t="n">
-        <v>-33.5412</v>
+        <v>-0.8608</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.271720768129149</v>
+        <v>0.1392</v>
       </c>
       <c r="G71" t="n">
-        <v>-33.26945127852777</v>
+        <v>-1</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.271720768129149</v>
+        <v>0.1392</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2098535622709639</v>
+        <v>0.1392</v>
       </c>
       <c r="J71" t="n">
-        <v>-33.26945127852777</v>
+        <v>-1</v>
       </c>
       <c r="K71" t="n">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="L71" t="n">
         <v>45</v>
       </c>
       <c r="M71" t="n">
-        <v>-33.4793</v>
+        <v>-0.8608</v>
       </c>
       <c r="N71" t="n">
-        <v>98</v>
+        <v>121</v>
       </c>
     </row>
     <row r="72">
@@ -3728,28 +3716,28 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-2.3358</v>
+        <v>-0.8979</v>
       </c>
       <c r="C72" t="n">
-        <v>-2.10222</v>
+        <v>-0</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.4759461457636815</v>
+        <v>-0.7841</v>
       </c>
       <c r="E72" t="n">
-        <v>-33.9494</v>
+        <v>-0.8979</v>
       </c>
       <c r="F72" t="n">
-        <v>-33.94936119774748</v>
+        <v>-0.8979</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-33.94936119774748</v>
+        <v>-0.8979</v>
       </c>
       <c r="I72" t="n">
-        <v>-23.25129291503288</v>
+        <v>-0.8979</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -3761,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-23.2513</v>
+        <v>-0.8979</v>
       </c>
       <c r="N72" t="n">
         <v>47</v>
@@ -3770,47 +3758,47 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Ax1Le</t>
+          <t>Kylar</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-2.4573</v>
+        <v>-1</v>
       </c>
       <c r="C73" t="n">
-        <v>-2.21157</v>
+        <v>-0</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.5061298194936314</v>
+        <v>-0.8253</v>
       </c>
       <c r="E73" t="n">
-        <v>-35.2627</v>
+        <v>-1</v>
       </c>
       <c r="F73" t="n">
-        <v>-9.456096126850685</v>
+        <v>-1</v>
       </c>
       <c r="G73" t="n">
-        <v>-25.80661088135946</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-9.456096126850685</v>
+        <v>-1</v>
       </c>
       <c r="I73" t="n">
-        <v>-7.3030687755641</v>
+        <v>-1</v>
       </c>
       <c r="J73" t="n">
-        <v>-25.80661088135946</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="L73" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-33.1097</v>
+        <v>-1</v>
       </c>
       <c r="N73" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="74">
@@ -3820,28 +3808,28 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-2.5727</v>
+        <v>-1</v>
       </c>
       <c r="C74" t="n">
-        <v>-2.31543</v>
+        <v>-0</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.5353815296929263</v>
+        <v>-0.8253</v>
       </c>
       <c r="E74" t="n">
-        <v>-36.5355</v>
+        <v>-1</v>
       </c>
       <c r="F74" t="n">
-        <v>-36.53550141298771</v>
+        <v>-1</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-36.53550141298771</v>
+        <v>-1</v>
       </c>
       <c r="I74" t="n">
-        <v>-30.34642740313733</v>
+        <v>-1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -3853,7 +3841,7 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-30.3464</v>
+        <v>-1</v>
       </c>
       <c r="N74" t="n">
         <v>57</v>
@@ -3866,28 +3854,28 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-2.7108</v>
+        <v>-1</v>
       </c>
       <c r="C75" t="n">
-        <v>-2.43972</v>
+        <v>-0</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.5711360605858958</v>
+        <v>-0.8253</v>
       </c>
       <c r="E75" t="n">
-        <v>-38.0912</v>
+        <v>-1</v>
       </c>
       <c r="F75" t="n">
-        <v>-38.09124521586168</v>
+        <v>-1</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-38.09124521586168</v>
+        <v>-1</v>
       </c>
       <c r="I75" t="n">
-        <v>-26.08799308044443</v>
+        <v>-1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -3899,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-26.088</v>
+        <v>-1</v>
       </c>
       <c r="N75" t="n">
         <v>47</v>
@@ -3908,93 +3896,93 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>jL</t>
+          <t>Ax1Le</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-2.9668</v>
+        <v>-1.631</v>
       </c>
       <c r="C76" t="n">
-        <v>-2.67012</v>
+        <v>-0</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.6396295872094072</v>
+        <v>-1.0803</v>
       </c>
       <c r="E76" t="n">
-        <v>-41.0715</v>
+        <v>-1.631</v>
       </c>
       <c r="F76" t="n">
-        <v>-6.489538045235583</v>
+        <v>-0.9543</v>
       </c>
       <c r="G76" t="n">
-        <v>-34.58198342989212</v>
+        <v>-0.6767</v>
       </c>
       <c r="H76" t="n">
-        <v>-6.489538045235583</v>
+        <v>-0.9543</v>
       </c>
       <c r="I76" t="n">
-        <v>-7.186956523685309</v>
+        <v>-0.9543</v>
       </c>
       <c r="J76" t="n">
-        <v>-34.58198342989212</v>
+        <v>-0.6767</v>
       </c>
       <c r="K76" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="L76" t="n">
         <v>45</v>
       </c>
       <c r="M76" t="n">
-        <v>-41.7689</v>
+        <v>-1.631</v>
       </c>
       <c r="N76" t="n">
-        <v>121</v>
+        <v>98</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-3.6383</v>
+        <v>-1.8003</v>
       </c>
       <c r="C77" t="n">
-        <v>-3.27447</v>
+        <v>-0</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.8337973222801262</v>
+        <v>-1.1486</v>
       </c>
       <c r="E77" t="n">
-        <v>-49.5201</v>
+        <v>-1.8003</v>
       </c>
       <c r="F77" t="n">
-        <v>-15.94661150645521</v>
+        <v>0.4563</v>
       </c>
       <c r="G77" t="n">
-        <v>-33.57349656762974</v>
+        <v>-2.2566</v>
       </c>
       <c r="H77" t="n">
-        <v>-15.94661150645521</v>
+        <v>0.4563</v>
       </c>
       <c r="I77" t="n">
-        <v>-21.37833528005653</v>
+        <v>0.4563</v>
       </c>
       <c r="J77" t="n">
-        <v>-33.57349656762974</v>
+        <v>-2.2566</v>
       </c>
       <c r="K77" t="n">
-        <v>92</v>
+        <v>47</v>
       </c>
       <c r="L77" t="n">
-        <v>168</v>
+        <v>209</v>
       </c>
       <c r="M77" t="n">
-        <v>-54.9518</v>
+        <v>-1.8003</v>
       </c>
       <c r="N77" t="n">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="78">
@@ -4004,31 +3992,31 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-4.0121</v>
+        <v>-1.891</v>
       </c>
       <c r="C78" t="n">
-        <v>-3.61089</v>
+        <v>-0</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.9516629951434683</v>
+        <v>-1.1853</v>
       </c>
       <c r="E78" t="n">
-        <v>-54.6487</v>
+        <v>-1.891</v>
       </c>
       <c r="F78" t="n">
-        <v>-14.09729980545247</v>
+        <v>-0.891</v>
       </c>
       <c r="G78" t="n">
-        <v>-40.55135521216884</v>
+        <v>-1</v>
       </c>
       <c r="H78" t="n">
-        <v>-14.09729980545247</v>
+        <v>-0.891</v>
       </c>
       <c r="I78" t="n">
-        <v>-14.58518449817304</v>
+        <v>-0.891</v>
       </c>
       <c r="J78" t="n">
-        <v>-40.55135521216884</v>
+        <v>-1</v>
       </c>
       <c r="K78" t="n">
         <v>71</v>
@@ -4037,7 +4025,7 @@
         <v>67</v>
       </c>
       <c r="M78" t="n">
-        <v>-55.1365</v>
+        <v>-1.891</v>
       </c>
       <c r="N78" t="n">
         <v>138</v>
@@ -4046,139 +4034,139 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-4.8272</v>
+        <v>-2.6819</v>
       </c>
       <c r="C79" t="n">
-        <v>-4.344480000000001</v>
+        <v>-0</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.235640928297513</v>
+        <v>-1.5048</v>
       </c>
       <c r="E79" t="n">
-        <v>-67.005</v>
+        <v>-2.6819</v>
       </c>
       <c r="F79" t="n">
-        <v>-10.22458506754566</v>
+        <v>-1.6044</v>
       </c>
       <c r="G79" t="n">
-        <v>-56.78045943760306</v>
+        <v>-1.0775</v>
       </c>
       <c r="H79" t="n">
-        <v>-10.22458506754566</v>
+        <v>-1.6044</v>
       </c>
       <c r="I79" t="n">
-        <v>-8.492551531513339</v>
+        <v>-1.6044</v>
       </c>
       <c r="J79" t="n">
-        <v>-56.78045943760306</v>
+        <v>-1.0775</v>
       </c>
       <c r="K79" t="n">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="L79" t="n">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="M79" t="n">
-        <v>-65.273</v>
+        <v>-2.6819</v>
       </c>
       <c r="N79" t="n">
-        <v>241</v>
+        <v>260</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>HooXi</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-5.6462</v>
+        <v>-2.829</v>
       </c>
       <c r="C80" t="n">
-        <v>-5.081580000000001</v>
+        <v>-0</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.562617906617259</v>
+        <v>-1.5642</v>
       </c>
       <c r="E80" t="n">
-        <v>-81.2324</v>
+        <v>-2.829</v>
       </c>
       <c r="F80" t="n">
-        <v>7.897240575697463</v>
+        <v>-0.829</v>
       </c>
       <c r="G80" t="n">
-        <v>-89.1296401879838</v>
+        <v>-2</v>
       </c>
       <c r="H80" t="n">
-        <v>7.897240575697463</v>
+        <v>-0.829</v>
       </c>
       <c r="I80" t="n">
-        <v>5.408674784084237</v>
+        <v>-0.829</v>
       </c>
       <c r="J80" t="n">
-        <v>-89.1296401879838</v>
+        <v>-2</v>
       </c>
       <c r="K80" t="n">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c r="L80" t="n">
-        <v>209</v>
+        <v>168</v>
       </c>
       <c r="M80" t="n">
-        <v>-83.721</v>
+        <v>-2.829</v>
       </c>
       <c r="N80" t="n">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>HooXi</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-6.0858</v>
+        <v>-3.4438</v>
       </c>
       <c r="C81" t="n">
-        <v>-5.47722</v>
+        <v>-0</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.757450500421763</v>
+        <v>-1.8126</v>
       </c>
       <c r="E81" t="n">
-        <v>-89.7099</v>
+        <v>-3.4438</v>
       </c>
       <c r="F81" t="n">
-        <v>-14.65291503357073</v>
+        <v>-1.1491</v>
       </c>
       <c r="G81" t="n">
-        <v>-75.05700037431002</v>
+        <v>-2.2947</v>
       </c>
       <c r="H81" t="n">
-        <v>-14.65291503357073</v>
+        <v>-1.1491</v>
       </c>
       <c r="I81" t="n">
-        <v>-19.64398081003289</v>
+        <v>-1.1491</v>
       </c>
       <c r="J81" t="n">
-        <v>-75.05700037431002</v>
+        <v>-2.2947</v>
       </c>
       <c r="K81" t="n">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="L81" t="n">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="M81" t="n">
-        <v>-94.70099999999999</v>
+        <v>-3.4438</v>
       </c>
       <c r="N81" t="n">
-        <v>260</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -4196,52 +4184,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>opponent</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>opponent_rank</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>match_stage</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>round_differential</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>total_rounds</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>rating</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>perf_score_raw</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>perf_score_weighted</t>
         </is>
@@ -4281,10 +4269,10 @@
         <v>1.62</v>
       </c>
       <c r="I2" t="n">
-        <v>1.914708478128818</v>
+        <v>0.8093</v>
       </c>
       <c r="J2" t="n">
-        <v>44.0382949969628</v>
+        <v>18.6139</v>
       </c>
     </row>
     <row r="3">
@@ -4321,10 +4309,10 @@
         <v>1.43</v>
       </c>
       <c r="I3" t="n">
-        <v>1.527077003072276</v>
+        <v>0.5908</v>
       </c>
       <c r="J3" t="n">
-        <v>35.12277107066235</v>
+        <v>13.5884</v>
       </c>
     </row>
     <row r="4">
@@ -4361,10 +4349,10 @@
         <v>1.34</v>
       </c>
       <c r="I4" t="n">
-        <v>1.280657013067385</v>
+        <v>0.4742</v>
       </c>
       <c r="J4" t="n">
-        <v>29.45511130054986</v>
+        <v>10.9066</v>
       </c>
     </row>
     <row r="5">
@@ -4401,10 +4389,10 @@
         <v>1.14</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6107332669454149</v>
+        <v>0.1739</v>
       </c>
       <c r="J5" t="n">
-        <v>14.04686513974454</v>
+        <v>3.9997</v>
       </c>
     </row>
     <row r="6">
@@ -4441,10 +4429,10 @@
         <v>0.97</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2100786164294307</v>
+        <v>-0.1675</v>
       </c>
       <c r="J6" t="n">
-        <v>4.831808177876907</v>
+        <v>-3.8525</v>
       </c>
     </row>
     <row r="7">
@@ -4481,10 +4469,10 @@
         <v>1.12</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1201183644922993</v>
+        <v>0.3574</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.762722383322884</v>
+        <v>8.2202</v>
       </c>
     </row>
     <row r="8">
@@ -4521,10 +4509,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8222542617193541</v>
+        <v>-0.2527</v>
       </c>
       <c r="J8" t="n">
-        <v>-18.91184801954514</v>
+        <v>-5.8121</v>
       </c>
     </row>
     <row r="9">
@@ -4561,10 +4549,10 @@
         <v>0.67</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.294037847385736</v>
+        <v>-0.4969</v>
       </c>
       <c r="J9" t="n">
-        <v>-29.76287048987194</v>
+        <v>-11.4287</v>
       </c>
     </row>
     <row r="10">
@@ -4601,10 +4589,10 @@
         <v>0.63</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.387220482923885</v>
+        <v>-0.5542</v>
       </c>
       <c r="J10" t="n">
-        <v>-31.90607110724935</v>
+        <v>-12.7466</v>
       </c>
     </row>
     <row r="11">
@@ -4641,10 +4629,10 @@
         <v>0.55</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.550868660892377</v>
+        <v>-0.6617</v>
       </c>
       <c r="J11" t="n">
-        <v>-35.66997920052467</v>
+        <v>-15.2191</v>
       </c>
     </row>
     <row r="12">
@@ -4681,10 +4669,10 @@
         <v>1.17</v>
       </c>
       <c r="I12" t="n">
-        <v>0.394212634053238</v>
+        <v>0.3352</v>
       </c>
       <c r="J12" t="n">
-        <v>11.03795375349066</v>
+        <v>9.3856</v>
       </c>
     </row>
     <row r="13">
@@ -4721,10 +4709,10 @@
         <v>1.13</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2686128180978296</v>
+        <v>0.2731</v>
       </c>
       <c r="J13" t="n">
-        <v>7.521158906739229</v>
+        <v>7.6468</v>
       </c>
     </row>
     <row r="14">
@@ -4761,10 +4749,10 @@
         <v>1.01</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2938494921607969</v>
+        <v>0.0282</v>
       </c>
       <c r="J14" t="n">
-        <v>-8.227785780502314</v>
+        <v>0.7896</v>
       </c>
     </row>
     <row r="15">
@@ -4801,10 +4789,10 @@
         <v>0.9</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7045677186414625</v>
+        <v>-0.2316</v>
       </c>
       <c r="J15" t="n">
-        <v>-19.72789612196095</v>
+        <v>-6.4848</v>
       </c>
     </row>
     <row r="16">
@@ -4841,10 +4829,10 @@
         <v>0.85</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8392909792832408</v>
+        <v>-0.3122</v>
       </c>
       <c r="J16" t="n">
-        <v>-23.50014741993074</v>
+        <v>-8.7416</v>
       </c>
     </row>
     <row r="17">
@@ -4881,10 +4869,10 @@
         <v>1.35</v>
       </c>
       <c r="I17" t="n">
-        <v>1.110769735424904</v>
+        <v>0.9923</v>
       </c>
       <c r="J17" t="n">
-        <v>31.10155259189732</v>
+        <v>27.7844</v>
       </c>
     </row>
     <row r="18">
@@ -4921,10 +4909,10 @@
         <v>1.24</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8852534148089339</v>
+        <v>0.7407</v>
       </c>
       <c r="J18" t="n">
-        <v>24.78709561465015</v>
+        <v>20.7396</v>
       </c>
     </row>
     <row r="19">
@@ -4961,10 +4949,10 @@
         <v>1.05</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3146714010102676</v>
+        <v>0.1972</v>
       </c>
       <c r="J19" t="n">
-        <v>8.810799228287493</v>
+        <v>5.5216</v>
       </c>
     </row>
     <row r="20">
@@ -5001,10 +4989,10 @@
         <v>0.85</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4491550837994263</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>-12.57634234638394</v>
+        <v>-15.5652</v>
       </c>
     </row>
     <row r="21">
@@ -5041,10 +5029,10 @@
         <v>0.72</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7390827817271675</v>
+        <v>-0.8727</v>
       </c>
       <c r="J21" t="n">
-        <v>-20.69431788836069</v>
+        <v>-24.4356</v>
       </c>
     </row>
     <row r="22">
@@ -5081,10 +5069,10 @@
         <v>1.09</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.04705532167870014</v>
+        <v>0.2766</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.176383041967504</v>
+        <v>6.915</v>
       </c>
     </row>
     <row r="23">
@@ -5121,10 +5109,10 @@
         <v>0.98</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.323271864628655</v>
+        <v>0.0225</v>
       </c>
       <c r="J23" t="n">
-        <v>-8.081796615716376</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="24">
@@ -5161,10 +5149,10 @@
         <v>0.74</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.086396067243692</v>
+        <v>-0.4216</v>
       </c>
       <c r="J24" t="n">
-        <v>-27.1599016810923</v>
+        <v>-10.54</v>
       </c>
     </row>
     <row r="25">
@@ -5201,10 +5189,10 @@
         <v>0.73</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.111550469629412</v>
+        <v>-0.4365</v>
       </c>
       <c r="J25" t="n">
-        <v>-27.78876174073531</v>
+        <v>-10.9125</v>
       </c>
     </row>
     <row r="26">
@@ -5241,10 +5229,10 @@
         <v>0.61</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.373466060111495</v>
+        <v>-0.602</v>
       </c>
       <c r="J26" t="n">
-        <v>-34.33665150278738</v>
+        <v>-15.05</v>
       </c>
     </row>
     <row r="27">
@@ -5281,10 +5269,10 @@
         <v>1.56</v>
       </c>
       <c r="I27" t="n">
-        <v>1.563150469349903</v>
+        <v>1.3453</v>
       </c>
       <c r="J27" t="n">
-        <v>39.07876173374758</v>
+        <v>33.6325</v>
       </c>
     </row>
     <row r="28">
@@ -5321,10 +5309,10 @@
         <v>1.3</v>
       </c>
       <c r="I28" t="n">
-        <v>1.084509406143319</v>
+        <v>0.7977</v>
       </c>
       <c r="J28" t="n">
-        <v>27.11273515358299</v>
+        <v>19.9425</v>
       </c>
     </row>
     <row r="29">
@@ -5361,10 +5349,10 @@
         <v>1.21</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8404419908456128</v>
+        <v>0.5704</v>
       </c>
       <c r="J29" t="n">
-        <v>21.01104977114032</v>
+        <v>14.26</v>
       </c>
     </row>
     <row r="30">
@@ -5401,10 +5389,10 @@
         <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2124743716023048</v>
+        <v>-0.1196</v>
       </c>
       <c r="J30" t="n">
-        <v>5.31185929005762</v>
+        <v>-2.99</v>
       </c>
     </row>
     <row r="31">
@@ -5441,10 +5429,10 @@
         <v>0.88</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.08462385974511048</v>
+        <v>-0.5274</v>
       </c>
       <c r="J31" t="n">
-        <v>-2.115596493627762</v>
+        <v>-13.185</v>
       </c>
     </row>
     <row r="32">
@@ -5481,10 +5469,10 @@
         <v>1.38</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9381584533670013</v>
+        <v>1.0061</v>
       </c>
       <c r="J32" t="n">
-        <v>26.26843669427604</v>
+        <v>28.1708</v>
       </c>
     </row>
     <row r="33">
@@ -5521,10 +5509,10 @@
         <v>1.25</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7250849593076431</v>
+        <v>0.7098</v>
       </c>
       <c r="J33" t="n">
-        <v>20.30237886061401</v>
+        <v>19.8744</v>
       </c>
     </row>
     <row r="34">
@@ -5561,10 +5549,10 @@
         <v>1.04</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1942803322745228</v>
+        <v>0.0794</v>
       </c>
       <c r="J34" t="n">
-        <v>5.439849303686639</v>
+        <v>2.2232</v>
       </c>
     </row>
     <row r="35">
@@ -5601,10 +5589,10 @@
         <v>1.01</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1309849328193017</v>
+        <v>-0.0379</v>
       </c>
       <c r="J35" t="n">
-        <v>3.667578118940447</v>
+        <v>-1.0612</v>
       </c>
     </row>
     <row r="36">
@@ -5641,10 +5629,10 @@
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1102851693389572</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="J36" t="n">
-        <v>3.087984741490802</v>
+        <v>-2.7216</v>
       </c>
     </row>
     <row r="37">
@@ -5681,10 +5669,10 @@
         <v>1.03</v>
       </c>
       <c r="I37" t="n">
-        <v>0.004636584379103121</v>
+        <v>0.1607</v>
       </c>
       <c r="J37" t="n">
-        <v>0.1298243626148874</v>
+        <v>4.4996</v>
       </c>
     </row>
     <row r="38">
@@ -5721,10 +5709,10 @@
         <v>0.99</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.06926205138445617</v>
+        <v>0.0442</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.939337438764773</v>
+        <v>1.2376</v>
       </c>
     </row>
     <row r="39">
@@ -5761,10 +5749,10 @@
         <v>0.93</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1815290916784744</v>
+        <v>-0.0839</v>
       </c>
       <c r="J39" t="n">
-        <v>-5.082814566997283</v>
+        <v>-2.3492</v>
       </c>
     </row>
     <row r="40">
@@ -5801,10 +5789,10 @@
         <v>0.64</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.7769066235719029</v>
+        <v>-0.5644</v>
       </c>
       <c r="J40" t="n">
-        <v>-21.75338546001328</v>
+        <v>-15.8032</v>
       </c>
     </row>
     <row r="41">
@@ -5841,10 +5829,10 @@
         <v>0.6</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.831437205388509</v>
+        <v>-0.6168</v>
       </c>
       <c r="J41" t="n">
-        <v>-23.28024175087825</v>
+        <v>-17.2704</v>
       </c>
     </row>
     <row r="42">
@@ -5881,10 +5869,10 @@
         <v>1.12</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.02678687035453673</v>
+        <v>0.3293</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.6964586292179551</v>
+        <v>8.5618</v>
       </c>
     </row>
     <row r="43">
@@ -5921,10 +5909,10 @@
         <v>1.1</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.05729465679859121</v>
+        <v>0.2967</v>
       </c>
       <c r="J43" t="n">
-        <v>-1.489661076763372</v>
+        <v>7.7142</v>
       </c>
     </row>
     <row r="44">
@@ -5961,10 +5949,10 @@
         <v>0.71</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.7938079910539578</v>
+        <v>-0.4629</v>
       </c>
       <c r="J44" t="n">
-        <v>-20.63900776740291</v>
+        <v>-12.0354</v>
       </c>
     </row>
     <row r="45">
@@ -6001,10 +5989,10 @@
         <v>0.64</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.8968868655979674</v>
+        <v>-0.5603</v>
       </c>
       <c r="J45" t="n">
-        <v>-23.31905850554715</v>
+        <v>-14.5678</v>
       </c>
     </row>
     <row r="46">
@@ -6041,10 +6029,10 @@
         <v>0.54</v>
       </c>
       <c r="I46" t="n">
-        <v>-1.023849214130461</v>
+        <v>-0.6894</v>
       </c>
       <c r="J46" t="n">
-        <v>-26.62007956739198</v>
+        <v>-17.9244</v>
       </c>
     </row>
     <row r="47">
@@ -6081,10 +6069,10 @@
         <v>1.64</v>
       </c>
       <c r="I47" t="n">
-        <v>1.316007921724075</v>
+        <v>0.832</v>
       </c>
       <c r="J47" t="n">
-        <v>34.21620596482595</v>
+        <v>21.632</v>
       </c>
     </row>
     <row r="48">
@@ -6121,10 +6109,10 @@
         <v>1.4</v>
       </c>
       <c r="I48" t="n">
-        <v>0.9393502339491884</v>
+        <v>0.5547</v>
       </c>
       <c r="J48" t="n">
-        <v>24.4231060826789</v>
+        <v>14.4222</v>
       </c>
     </row>
     <row r="49">
@@ -6161,10 +6149,10 @@
         <v>1.29</v>
       </c>
       <c r="I49" t="n">
-        <v>0.644250189843466</v>
+        <v>0.3962</v>
       </c>
       <c r="J49" t="n">
-        <v>16.75050493593012</v>
+        <v>10.3012</v>
       </c>
     </row>
     <row r="50">
@@ -6201,10 +6189,10 @@
         <v>1.28</v>
       </c>
       <c r="I50" t="n">
-        <v>0.6108308593956293</v>
+        <v>0.3801</v>
       </c>
       <c r="J50" t="n">
-        <v>15.88160234428636</v>
+        <v>9.8826</v>
       </c>
     </row>
     <row r="51">
@@ -6241,10 +6229,10 @@
         <v>0.87</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.178948847690008</v>
+        <v>-0.3338</v>
       </c>
       <c r="J51" t="n">
-        <v>-4.652670039940207</v>
+        <v>-8.678800000000001</v>
       </c>
     </row>
     <row r="52">
@@ -6281,10 +6269,10 @@
         <v>1.31</v>
       </c>
       <c r="I52" t="n">
-        <v>0.7723974099358353</v>
+        <v>0.88</v>
       </c>
       <c r="J52" t="n">
-        <v>26.2615119378184</v>
+        <v>29.92</v>
       </c>
     </row>
     <row r="53">
@@ -6321,10 +6309,10 @@
         <v>1.25</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6657704573703747</v>
+        <v>0.7403</v>
       </c>
       <c r="J53" t="n">
-        <v>22.63619555059274</v>
+        <v>25.1702</v>
       </c>
     </row>
     <row r="54">
@@ -6361,10 +6349,10 @@
         <v>1.17</v>
       </c>
       <c r="I54" t="n">
-        <v>0.4997760759434383</v>
+        <v>0.5379</v>
       </c>
       <c r="J54" t="n">
-        <v>16.9923865820769</v>
+        <v>18.2886</v>
       </c>
     </row>
     <row r="55">
@@ -6401,10 +6389,10 @@
         <v>0.9</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2737163754941813</v>
+        <v>-0.4361</v>
       </c>
       <c r="J55" t="n">
-        <v>-9.306356766802162</v>
+        <v>-14.8274</v>
       </c>
     </row>
     <row r="56">
@@ -6441,10 +6429,10 @@
         <v>0.79</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4500629151417225</v>
+        <v>-0.7218</v>
       </c>
       <c r="J56" t="n">
-        <v>-15.30213911481856</v>
+        <v>-24.5412</v>
       </c>
     </row>
     <row r="57">
@@ -6481,10 +6469,10 @@
         <v>1.43</v>
       </c>
       <c r="I57" t="n">
-        <v>0.7121135011815518</v>
+        <v>0.672</v>
       </c>
       <c r="J57" t="n">
-        <v>24.21185904017276</v>
+        <v>22.848</v>
       </c>
     </row>
     <row r="58">
@@ -6521,10 +6509,10 @@
         <v>1.35</v>
       </c>
       <c r="I58" t="n">
-        <v>0.585716347370576</v>
+        <v>0.5742</v>
       </c>
       <c r="J58" t="n">
-        <v>19.91435581059958</v>
+        <v>19.5228</v>
       </c>
     </row>
     <row r="59">
@@ -6561,10 +6549,10 @@
         <v>0.82</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.666620739392452</v>
+        <v>-0.3614</v>
       </c>
       <c r="J59" t="n">
-        <v>-22.66510513934337</v>
+        <v>-12.2876</v>
       </c>
     </row>
     <row r="60">
@@ -6601,10 +6589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.6819554833988998</v>
+        <v>-0.3759</v>
       </c>
       <c r="J60" t="n">
-        <v>-23.18648643556259</v>
+        <v>-12.7806</v>
       </c>
     </row>
     <row r="61">
@@ -6641,10 +6629,10 @@
         <v>0.74</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.7824528710309755</v>
+        <v>-0.473</v>
       </c>
       <c r="J61" t="n">
-        <v>-26.60339761505317</v>
+        <v>-16.082</v>
       </c>
     </row>
     <row r="62">
@@ -6681,10 +6669,10 @@
         <v>1.07</v>
       </c>
       <c r="I62" t="n">
-        <v>0.1178308995782353</v>
+        <v>0.1768</v>
       </c>
       <c r="J62" t="n">
-        <v>4.948897782285885</v>
+        <v>7.4256</v>
       </c>
     </row>
     <row r="63">
@@ -6721,10 +6709,10 @@
         <v>1.06</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0879945298467205</v>
+        <v>0.1578</v>
       </c>
       <c r="J63" t="n">
-        <v>3.695770253562261</v>
+        <v>6.6276</v>
       </c>
     </row>
     <row r="64">
@@ -6761,10 +6749,10 @@
         <v>1.01</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.08523527669039198</v>
+        <v>0.0443</v>
       </c>
       <c r="J64" t="n">
-        <v>-3.579881620996463</v>
+        <v>1.8606</v>
       </c>
     </row>
     <row r="65">
@@ -6801,10 +6789,10 @@
         <v>1</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1197604425874962</v>
+        <v>0.0065</v>
       </c>
       <c r="J65" t="n">
-        <v>-5.029938588674838</v>
+        <v>0.273</v>
       </c>
     </row>
     <row r="66">
@@ -6841,10 +6829,10 @@
         <v>0.83</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5236667587075634</v>
+        <v>-0.338</v>
       </c>
       <c r="J66" t="n">
-        <v>-21.99400386571766</v>
+        <v>-14.196</v>
       </c>
     </row>
     <row r="67">
@@ -6881,10 +6869,10 @@
         <v>1.25</v>
       </c>
       <c r="I67" t="n">
-        <v>0.7683420767718967</v>
+        <v>0.7611</v>
       </c>
       <c r="J67" t="n">
-        <v>32.27036722441966</v>
+        <v>31.9662</v>
       </c>
     </row>
     <row r="68">
@@ -6921,10 +6909,10 @@
         <v>1.11</v>
       </c>
       <c r="I68" t="n">
-        <v>0.4287036003250222</v>
+        <v>0.393</v>
       </c>
       <c r="J68" t="n">
-        <v>18.00555121365093</v>
+        <v>16.506</v>
       </c>
     </row>
     <row r="69">
@@ -6961,10 +6949,10 @@
         <v>1.05</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2089084741917987</v>
+        <v>0.1887</v>
       </c>
       <c r="J69" t="n">
-        <v>8.774155916055545</v>
+        <v>7.9254</v>
       </c>
     </row>
     <row r="70">
@@ -7001,10 +6989,10 @@
         <v>0.99</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.05792122540242582</v>
+        <v>-0.1099</v>
       </c>
       <c r="J70" t="n">
-        <v>-2.432691466901884</v>
+        <v>-4.6158</v>
       </c>
     </row>
     <row r="71">
@@ -7041,10 +7029,10 @@
         <v>0.84</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3841391357938242</v>
+        <v>-0.5845</v>
       </c>
       <c r="J71" t="n">
-        <v>-16.13384370334062</v>
+        <v>-24.549</v>
       </c>
     </row>
     <row r="72">
@@ -7081,10 +7069,10 @@
         <v>1.14</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.205423887855585</v>
+        <v>0.3527</v>
       </c>
       <c r="J72" t="n">
-        <v>-4.313901644967286</v>
+        <v>7.4067</v>
       </c>
     </row>
     <row r="73">
@@ -7121,10 +7109,10 @@
         <v>0.84</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.7462234290084825</v>
+        <v>-0.2589</v>
       </c>
       <c r="J73" t="n">
-        <v>-15.67069200917813</v>
+        <v>-5.4369</v>
       </c>
     </row>
     <row r="74">
@@ -7161,10 +7149,10 @@
         <v>0.83</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.7772795272140619</v>
+        <v>-0.2797</v>
       </c>
       <c r="J74" t="n">
-        <v>-16.3228700714953</v>
+        <v>-5.8737</v>
       </c>
     </row>
     <row r="75">
@@ -7201,10 +7189,10 @@
         <v>0.79</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.8653825071204916</v>
+        <v>-0.3489</v>
       </c>
       <c r="J75" t="n">
-        <v>-18.17303264953032</v>
+        <v>-7.3269</v>
       </c>
     </row>
     <row r="76">
@@ -7241,10 +7229,10 @@
         <v>0.61</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.137945596911109</v>
+        <v>-0.6048</v>
       </c>
       <c r="J76" t="n">
-        <v>-23.89685753513328</v>
+        <v>-12.7008</v>
       </c>
     </row>
     <row r="77">
@@ -7281,10 +7269,10 @@
         <v>1.83</v>
       </c>
       <c r="I77" t="n">
-        <v>1.874557307905004</v>
+        <v>1.75</v>
       </c>
       <c r="J77" t="n">
-        <v>39.36570346600507</v>
+        <v>36.75</v>
       </c>
     </row>
     <row r="78">
@@ -7321,10 +7309,10 @@
         <v>1.59</v>
       </c>
       <c r="I78" t="n">
-        <v>1.544950587976138</v>
+        <v>1.339</v>
       </c>
       <c r="J78" t="n">
-        <v>32.44396234749891</v>
+        <v>28.119</v>
       </c>
     </row>
     <row r="79">
@@ -7361,10 +7349,10 @@
         <v>1.16</v>
       </c>
       <c r="I79" t="n">
-        <v>0.5348018630138482</v>
+        <v>0.3443</v>
       </c>
       <c r="J79" t="n">
-        <v>11.23083912329081</v>
+        <v>7.2303</v>
       </c>
     </row>
     <row r="80">
@@ -7401,10 +7389,10 @@
         <v>1.05</v>
       </c>
       <c r="I80" t="n">
-        <v>0.3131630767760465</v>
+        <v>0.039</v>
       </c>
       <c r="J80" t="n">
-        <v>6.576424612296976</v>
+        <v>0.819</v>
       </c>
     </row>
     <row r="81">
@@ -7441,10 +7429,10 @@
         <v>1</v>
       </c>
       <c r="I81" t="n">
-        <v>0.2137657790267844</v>
+        <v>-0.1631</v>
       </c>
       <c r="J81" t="n">
-        <v>4.489081359562473</v>
+        <v>-3.4251</v>
       </c>
     </row>
     <row r="82">
@@ -7481,10 +7469,10 @@
         <v>1.09</v>
       </c>
       <c r="I82" t="n">
-        <v>0.005069539989575184</v>
+        <v>0.2654</v>
       </c>
       <c r="J82" t="n">
-        <v>0.13687757971853</v>
+        <v>7.1658</v>
       </c>
     </row>
     <row r="83">
@@ -7521,10 +7509,10 @@
         <v>0.83</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.5163126961939238</v>
+        <v>-0.2896</v>
       </c>
       <c r="J83" t="n">
-        <v>-13.94044279723594</v>
+        <v>-7.8192</v>
       </c>
     </row>
     <row r="84">
@@ -7561,10 +7549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.5578447462076742</v>
+        <v>-0.3235</v>
       </c>
       <c r="J84" t="n">
-        <v>-15.0618081476072</v>
+        <v>-8.734500000000001</v>
       </c>
     </row>
     <row r="85">
@@ -7601,10 +7589,10 @@
         <v>0.79</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.5954345003649508</v>
+        <v>-0.3558</v>
       </c>
       <c r="J85" t="n">
-        <v>-16.07673150985367</v>
+        <v>-9.6066</v>
       </c>
     </row>
     <row r="86">
@@ -7641,10 +7629,10 @@
         <v>0.77</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.6303627357694519</v>
+        <v>-0.3867</v>
       </c>
       <c r="J86" t="n">
-        <v>-17.0197938657752</v>
+        <v>-10.4409</v>
       </c>
     </row>
     <row r="87">
@@ -7681,10 +7669,10 @@
         <v>1.46</v>
       </c>
       <c r="I87" t="n">
-        <v>0.854811338962054</v>
+        <v>0.6576</v>
       </c>
       <c r="J87" t="n">
-        <v>23.07990615197546</v>
+        <v>17.7552</v>
       </c>
     </row>
     <row r="88">
@@ -7721,10 +7709,10 @@
         <v>1.44</v>
       </c>
       <c r="I88" t="n">
-        <v>0.8311430110742942</v>
+        <v>0.6339</v>
       </c>
       <c r="J88" t="n">
-        <v>22.44086129900595</v>
+        <v>17.1153</v>
       </c>
     </row>
     <row r="89">
@@ -7761,10 +7749,10 @@
         <v>1.27</v>
       </c>
       <c r="I89" t="n">
-        <v>0.5921445409927535</v>
+        <v>0.4158</v>
       </c>
       <c r="J89" t="n">
-        <v>15.98790260680434</v>
+        <v>11.2266</v>
       </c>
     </row>
     <row r="90">
@@ -7801,10 +7789,10 @@
         <v>1.03</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1030431032574464</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="J90" t="n">
-        <v>2.782163787951053</v>
+        <v>0.2673</v>
       </c>
     </row>
     <row r="91">
@@ -7841,10 +7829,10 @@
         <v>0.77</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3116445286511972</v>
+        <v>-0.4589</v>
       </c>
       <c r="J91" t="n">
-        <v>-8.414402273582324</v>
+        <v>-12.3903</v>
       </c>
     </row>
     <row r="92">
@@ -7881,10 +7869,10 @@
         <v>1.41</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5503257820986905</v>
+        <v>1.0451</v>
       </c>
       <c r="J92" t="n">
-        <v>13.75814455246726</v>
+        <v>26.1275</v>
       </c>
     </row>
     <row r="93">
@@ -7921,10 +7909,10 @@
         <v>1.4</v>
       </c>
       <c r="I93" t="n">
-        <v>0.5422646704620433</v>
+        <v>1.0238</v>
       </c>
       <c r="J93" t="n">
-        <v>13.55661676155108</v>
+        <v>25.595</v>
       </c>
     </row>
     <row r="94">
@@ -7961,10 +7949,10 @@
         <v>1.3</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4532024806603395</v>
+        <v>0.8012</v>
       </c>
       <c r="J94" t="n">
-        <v>11.33006201650849</v>
+        <v>20.03</v>
       </c>
     </row>
     <row r="95">
@@ -8001,10 +7989,10 @@
         <v>0.95</v>
       </c>
       <c r="I95" t="n">
-        <v>0.01832067538178248</v>
+        <v>-0.3231</v>
       </c>
       <c r="J95" t="n">
-        <v>0.458016884544562</v>
+        <v>-8.077500000000001</v>
       </c>
     </row>
     <row r="96">
@@ -8041,10 +8029,10 @@
         <v>0.86</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.1684454492900091</v>
+        <v>-0.5779</v>
       </c>
       <c r="J96" t="n">
-        <v>-4.211136232250228</v>
+        <v>-14.4475</v>
       </c>
     </row>
     <row r="97">
@@ -8081,10 +8069,10 @@
         <v>1.12</v>
       </c>
       <c r="I97" t="n">
-        <v>-0.009356333280828856</v>
+        <v>0.3079</v>
       </c>
       <c r="J97" t="n">
-        <v>-0.2339083320207214</v>
+        <v>7.6975</v>
       </c>
     </row>
     <row r="98">
@@ -8121,10 +8109,10 @@
         <v>0.95</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.2560631336051529</v>
+        <v>-0.0621</v>
       </c>
       <c r="J98" t="n">
-        <v>-6.401578340128822</v>
+        <v>-1.5525</v>
       </c>
     </row>
     <row r="99">
@@ -8161,10 +8149,10 @@
         <v>0.91</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.3224361706613091</v>
+        <v>-0.1402</v>
       </c>
       <c r="J99" t="n">
-        <v>-8.060904266532729</v>
+        <v>-3.505</v>
       </c>
     </row>
     <row r="100">
@@ -8201,10 +8189,10 @@
         <v>0.84</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.4785993516458406</v>
+        <v>-0.2815</v>
       </c>
       <c r="J100" t="n">
-        <v>-11.96498379114601</v>
+        <v>-7.0375</v>
       </c>
     </row>
     <row r="101">
@@ -8241,10 +8229,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.8127833591649513</v>
+        <v>-0.6748</v>
       </c>
       <c r="J101" t="n">
-        <v>-20.31958397912378</v>
+        <v>-16.87</v>
       </c>
     </row>
     <row r="102">
@@ -8281,10 +8269,10 @@
         <v>1.45</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5353709474268504</v>
+        <v>1.1764</v>
       </c>
       <c r="J102" t="n">
-        <v>14.99038652795181</v>
+        <v>32.9392</v>
       </c>
     </row>
     <row r="103">
@@ -8321,10 +8309,10 @@
         <v>1.1</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1805442226309896</v>
+        <v>0.3241</v>
       </c>
       <c r="J103" t="n">
-        <v>5.055238233667708</v>
+        <v>9.0748</v>
       </c>
     </row>
     <row r="104">
@@ -8361,10 +8349,10 @@
         <v>1.05</v>
       </c>
       <c r="I104" t="n">
-        <v>0.0834282929027647</v>
+        <v>0.1408</v>
       </c>
       <c r="J104" t="n">
-        <v>2.335992201277412</v>
+        <v>3.9424</v>
       </c>
     </row>
     <row r="105">
@@ -8401,10 +8389,10 @@
         <v>1.01</v>
       </c>
       <c r="I105" t="n">
-        <v>0.02268410922671514</v>
+        <v>-0.0154</v>
       </c>
       <c r="J105" t="n">
-        <v>0.635155058348024</v>
+        <v>-0.4312</v>
       </c>
     </row>
     <row r="106">
@@ -8441,10 +8429,10 @@
         <v>0.85</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3157238863871104</v>
+        <v>-0.5748</v>
       </c>
       <c r="J106" t="n">
-        <v>-8.840268818839089</v>
+        <v>-16.0944</v>
       </c>
     </row>
     <row r="107">
@@ -8481,10 +8469,10 @@
         <v>1.16</v>
       </c>
       <c r="I107" t="n">
-        <v>0.1979053134281093</v>
+        <v>0.3309</v>
       </c>
       <c r="J107" t="n">
-        <v>5.541348775987061</v>
+        <v>9.2652</v>
       </c>
     </row>
     <row r="108">
@@ -8521,10 +8509,10 @@
         <v>1.04</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.07772076200835515</v>
+        <v>0.1227</v>
       </c>
       <c r="J108" t="n">
-        <v>-2.176181336233944</v>
+        <v>3.4356</v>
       </c>
     </row>
     <row r="109">
@@ -8561,10 +8549,10 @@
         <v>1.02</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1179260244359115</v>
+        <v>0.0774</v>
       </c>
       <c r="J109" t="n">
-        <v>-3.30192868420552</v>
+        <v>2.1672</v>
       </c>
     </row>
     <row r="110">
@@ -8601,10 +8589,10 @@
         <v>0.98</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.220118674554343</v>
+        <v>-0.0556</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.163322887521604</v>
+        <v>-1.5568</v>
       </c>
     </row>
     <row r="111">
@@ -8641,10 +8629,10 @@
         <v>0.71</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.6181544031005114</v>
+        <v>-0.5037</v>
       </c>
       <c r="J111" t="n">
-        <v>-17.30832328681432</v>
+        <v>-14.1036</v>
       </c>
     </row>
     <row r="112">
@@ -8681,10 +8669,10 @@
         <v>0.84</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.4193758217972473</v>
+        <v>-0.2097</v>
       </c>
       <c r="J112" t="n">
-        <v>-9.645643901336689</v>
+        <v>-4.8231</v>
       </c>
     </row>
     <row r="113">
@@ -8721,10 +8709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.4647840628647164</v>
+        <v>-0.2606</v>
       </c>
       <c r="J113" t="n">
-        <v>-10.69003344588848</v>
+        <v>-5.9938</v>
       </c>
     </row>
     <row r="114">
@@ -8761,10 +8749,10 @@
         <v>0.74</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.6128039033379977</v>
+        <v>-0.3945</v>
       </c>
       <c r="J114" t="n">
-        <v>-14.09448977677395</v>
+        <v>-9.073499999999999</v>
       </c>
     </row>
     <row r="115">
@@ -8801,10 +8789,10 @@
         <v>0.74</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.6128039033379977</v>
+        <v>-0.3945</v>
       </c>
       <c r="J115" t="n">
-        <v>-14.09448977677395</v>
+        <v>-9.073499999999999</v>
       </c>
     </row>
     <row r="116">
@@ -8841,10 +8829,10 @@
         <v>0.72</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6446344082935975</v>
+        <v>-0.427</v>
       </c>
       <c r="J116" t="n">
-        <v>-14.82659139075274</v>
+        <v>-9.821</v>
       </c>
     </row>
     <row r="117">
@@ -8881,10 +8869,10 @@
         <v>1.65</v>
       </c>
       <c r="I117" t="n">
-        <v>0.9124110533343451</v>
+        <v>1.4546</v>
       </c>
       <c r="J117" t="n">
-        <v>20.98545422668994</v>
+        <v>33.4558</v>
       </c>
     </row>
     <row r="118">
@@ -8921,10 +8909,10 @@
         <v>1.49</v>
       </c>
       <c r="I118" t="n">
-        <v>0.7644455100447223</v>
+        <v>1.1425</v>
       </c>
       <c r="J118" t="n">
-        <v>17.58224673102861</v>
+        <v>26.2775</v>
       </c>
     </row>
     <row r="119">
@@ -8961,10 +8949,10 @@
         <v>1.33</v>
       </c>
       <c r="I119" t="n">
-        <v>0.5506190645140236</v>
+        <v>0.7822</v>
       </c>
       <c r="J119" t="n">
-        <v>12.66423848382254</v>
+        <v>17.9906</v>
       </c>
     </row>
     <row r="120">
@@ -9001,10 +8989,10 @@
         <v>1.14</v>
       </c>
       <c r="I120" t="n">
-        <v>0.2659202889256489</v>
+        <v>0.2943</v>
       </c>
       <c r="J120" t="n">
-        <v>6.116166645289924</v>
+        <v>6.7689</v>
       </c>
     </row>
     <row r="121">
@@ -9041,10 +9029,10 @@
         <v>1</v>
       </c>
       <c r="I121" t="n">
-        <v>0.1118389117988178</v>
+        <v>-0.162</v>
       </c>
       <c r="J121" t="n">
-        <v>2.57229497137281</v>
+        <v>-3.726</v>
       </c>
     </row>
     <row r="122">
@@ -9081,10 +9069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.3352264018805723</v>
+        <v>-0.0523</v>
       </c>
       <c r="J122" t="n">
-        <v>-7.37498084137259</v>
+        <v>-1.1506</v>
       </c>
     </row>
     <row r="123">
@@ -9121,10 +9109,10 @@
         <v>0.93</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.3483443074666836</v>
+        <v>-0.0712</v>
       </c>
       <c r="J123" t="n">
-        <v>-7.66357476426704</v>
+        <v>-1.5664</v>
       </c>
     </row>
     <row r="124">
@@ -9161,10 +9149,10 @@
         <v>0.83</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.4990917950275782</v>
+        <v>-0.2497</v>
       </c>
       <c r="J124" t="n">
-        <v>-10.98001949060672</v>
+        <v>-5.4934</v>
       </c>
     </row>
     <row r="125">
@@ -9201,10 +9189,10 @@
         <v>0.78</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.6140022525663635</v>
+        <v>-0.3496</v>
       </c>
       <c r="J125" t="n">
-        <v>-13.50804955646</v>
+        <v>-7.6912</v>
       </c>
     </row>
     <row r="126">
@@ -9241,10 +9229,10 @@
         <v>0.57</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.8715891591706281</v>
+        <v>-0.649</v>
       </c>
       <c r="J126" t="n">
-        <v>-19.17496150175382</v>
+        <v>-14.278</v>
       </c>
     </row>
     <row r="127">
@@ -9281,10 +9269,10 @@
         <v>1.57</v>
       </c>
       <c r="I127" t="n">
-        <v>0.881224989121663</v>
+        <v>1.3188</v>
       </c>
       <c r="J127" t="n">
-        <v>19.38694976067659</v>
+        <v>29.0136</v>
       </c>
     </row>
     <row r="128">
@@ -9321,10 +9309,10 @@
         <v>1.36</v>
       </c>
       <c r="I128" t="n">
-        <v>0.6572569942482038</v>
+        <v>0.881</v>
       </c>
       <c r="J128" t="n">
-        <v>14.45965387346048</v>
+        <v>19.382</v>
       </c>
     </row>
     <row r="129">
@@ -9361,10 +9349,10 @@
         <v>1.31</v>
       </c>
       <c r="I129" t="n">
-        <v>0.5821383106761944</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="J129" t="n">
-        <v>12.80704283487628</v>
+        <v>16.7332</v>
       </c>
     </row>
     <row r="130">
@@ -9401,10 +9389,10 @@
         <v>1.25</v>
       </c>
       <c r="I130" t="n">
-        <v>0.4540435293273558</v>
+        <v>0.5901</v>
       </c>
       <c r="J130" t="n">
-        <v>9.988957645201827</v>
+        <v>12.9822</v>
       </c>
     </row>
     <row r="131">
@@ -9441,10 +9429,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I131" t="n">
-        <v>0.06930669916698665</v>
+        <v>-0.3851</v>
       </c>
       <c r="J131" t="n">
-        <v>1.524747381673706</v>
+        <v>-8.472200000000001</v>
       </c>
     </row>
     <row r="132">
@@ -9481,10 +9469,10 @@
         <v>0.63</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.575046280170127</v>
+        <v>-0.3662</v>
       </c>
       <c r="J132" t="n">
-        <v>-10.92587932323241</v>
+        <v>-6.9578</v>
       </c>
     </row>
     <row r="133">
@@ -9521,10 +9509,10 @@
         <v>0.59</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.6190898177866455</v>
+        <v>-0.4276</v>
       </c>
       <c r="J133" t="n">
-        <v>-11.76270653794626</v>
+        <v>-8.1244</v>
       </c>
     </row>
     <row r="134">
@@ -9561,10 +9549,10 @@
         <v>0.55</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.6671685846661455</v>
+        <v>-0.4904</v>
       </c>
       <c r="J134" t="n">
-        <v>-12.67620310865676</v>
+        <v>-9.317600000000001</v>
       </c>
     </row>
     <row r="135">
@@ -9601,10 +9589,10 @@
         <v>0.43</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.8772152657269833</v>
+        <v>-0.7163</v>
       </c>
       <c r="J135" t="n">
-        <v>-16.66709004881268</v>
+        <v>-13.6097</v>
       </c>
     </row>
     <row r="136">
@@ -9641,10 +9629,10 @@
         <v>0.16</v>
       </c>
       <c r="I136" t="n">
-        <v>-1.153042753010276</v>
+        <v>-1.0921</v>
       </c>
       <c r="J136" t="n">
-        <v>-21.90781230719524</v>
+        <v>-20.7499</v>
       </c>
     </row>
     <row r="137">
@@ -9681,10 +9669,10 @@
         <v>1.93</v>
       </c>
       <c r="I137" t="n">
-        <v>1.119813691349689</v>
+        <v>1.7962</v>
       </c>
       <c r="J137" t="n">
-        <v>21.27646013564409</v>
+        <v>34.1278</v>
       </c>
     </row>
     <row r="138">
@@ -9721,10 +9709,10 @@
         <v>1.56</v>
       </c>
       <c r="I138" t="n">
-        <v>0.7651033223482862</v>
+        <v>1.1641</v>
       </c>
       <c r="J138" t="n">
-        <v>14.53696312461744</v>
+        <v>22.1179</v>
       </c>
     </row>
     <row r="139">
@@ -9761,10 +9749,10 @@
         <v>1.52</v>
       </c>
       <c r="I139" t="n">
-        <v>0.6823290136366061</v>
+        <v>1.0629</v>
       </c>
       <c r="J139" t="n">
-        <v>12.96425125909552</v>
+        <v>20.1951</v>
       </c>
     </row>
     <row r="140">
@@ -9801,10 +9789,10 @@
         <v>1.46</v>
       </c>
       <c r="I140" t="n">
-        <v>0.6059069578902297</v>
+        <v>0.9345</v>
       </c>
       <c r="J140" t="n">
-        <v>11.51223219991437</v>
+        <v>17.7555</v>
       </c>
     </row>
     <row r="141">
@@ -9841,10 +9829,10 @@
         <v>1.28</v>
       </c>
       <c r="I141" t="n">
-        <v>0.4315901401326414</v>
+        <v>0.5531</v>
       </c>
       <c r="J141" t="n">
-        <v>8.200212662520187</v>
+        <v>10.5089</v>
       </c>
     </row>
     <row r="142">
@@ -9881,10 +9869,10 @@
         <v>1.57</v>
       </c>
       <c r="I142" t="n">
-        <v>1.213885788939911</v>
+        <v>0.8011</v>
       </c>
       <c r="J142" t="n">
-        <v>30.34714472349778</v>
+        <v>20.0275</v>
       </c>
     </row>
     <row r="143">
@@ -9921,10 +9909,10 @@
         <v>1.24</v>
       </c>
       <c r="I143" t="n">
-        <v>0.7220768450705357</v>
+        <v>0.3953</v>
       </c>
       <c r="J143" t="n">
-        <v>18.05192112676339</v>
+        <v>9.8825</v>
       </c>
     </row>
     <row r="144">
@@ -9961,10 +9949,10 @@
         <v>1.16</v>
       </c>
       <c r="I144" t="n">
-        <v>0.5405212235789879</v>
+        <v>0.2735</v>
       </c>
       <c r="J144" t="n">
-        <v>13.5130305894747</v>
+        <v>6.8375</v>
       </c>
     </row>
     <row r="145">
@@ -10001,10 +9989,10 @@
         <v>1.11</v>
       </c>
       <c r="I145" t="n">
-        <v>0.363663648681341</v>
+        <v>0.1771</v>
       </c>
       <c r="J145" t="n">
-        <v>9.091591217033526</v>
+        <v>4.4275</v>
       </c>
     </row>
     <row r="146">
@@ -10041,10 +10029,10 @@
         <v>0.58</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4825681690894887</v>
+        <v>-0.6856</v>
       </c>
       <c r="J146" t="n">
-        <v>-12.06420422723722</v>
+        <v>-17.14</v>
       </c>
     </row>
     <row r="147">
@@ -10081,10 +10069,10 @@
         <v>1.56</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4703550939479831</v>
+        <v>0.8386</v>
       </c>
       <c r="J147" t="n">
-        <v>11.75887734869958</v>
+        <v>20.965</v>
       </c>
     </row>
     <row r="148">
@@ -10121,10 +10109,10 @@
         <v>1</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.265254374138407</v>
+        <v>0.0156</v>
       </c>
       <c r="J148" t="n">
-        <v>-6.631359353460174</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="149">
@@ -10161,10 +10149,10 @@
         <v>0.91</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.4612212019045261</v>
+        <v>-0.2036</v>
       </c>
       <c r="J149" t="n">
-        <v>-11.53053004761315</v>
+        <v>-5.09</v>
       </c>
     </row>
     <row r="150">
@@ -10201,10 +10189,10 @@
         <v>0.83</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.5748341090231553</v>
+        <v>-0.3343</v>
       </c>
       <c r="J150" t="n">
-        <v>-14.37085272557888</v>
+        <v>-8.3575</v>
       </c>
     </row>
     <row r="151">
@@ -10241,10 +10229,10 @@
         <v>0.6</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.8203133583624578</v>
+        <v>-0.6429</v>
       </c>
       <c r="J151" t="n">
-        <v>-20.50783395906144</v>
+        <v>-16.0725</v>
       </c>
     </row>
     <row r="152">
@@ -10281,10 +10269,10 @@
         <v>1.01</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.2056422288472771</v>
+        <v>0.1405</v>
       </c>
       <c r="J152" t="n">
-        <v>-4.729771263487374</v>
+        <v>3.2315</v>
       </c>
     </row>
     <row r="153">
@@ -10321,10 +10309,10 @@
         <v>0.76</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.5781838464015783</v>
+        <v>-0.3621</v>
       </c>
       <c r="J153" t="n">
-        <v>-13.2982284672363</v>
+        <v>-8.3283</v>
       </c>
     </row>
     <row r="154">
@@ -10361,10 +10349,10 @@
         <v>0.72</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.6454709731929128</v>
+        <v>-0.4289</v>
       </c>
       <c r="J154" t="n">
-        <v>-14.84583238343699</v>
+        <v>-9.864699999999999</v>
       </c>
     </row>
     <row r="155">
@@ -10401,10 +10389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.6874325163597762</v>
+        <v>-0.4745</v>
       </c>
       <c r="J155" t="n">
-        <v>-15.81094787627485</v>
+        <v>-10.9135</v>
       </c>
     </row>
     <row r="156">
@@ -10441,10 +10429,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6874325163597762</v>
+        <v>-0.4745</v>
       </c>
       <c r="J156" t="n">
-        <v>-15.81094787627485</v>
+        <v>-10.9135</v>
       </c>
     </row>
     <row r="157">
@@ -10481,10 +10469,10 @@
         <v>1.66</v>
       </c>
       <c r="I157" t="n">
-        <v>0.8921799952260303</v>
+        <v>1.4786</v>
       </c>
       <c r="J157" t="n">
-        <v>20.5201398901987</v>
+        <v>34.0078</v>
       </c>
     </row>
     <row r="158">
@@ -10521,10 +10509,10 @@
         <v>1.36</v>
       </c>
       <c r="I158" t="n">
-        <v>0.5940877772637611</v>
+        <v>0.8663</v>
       </c>
       <c r="J158" t="n">
-        <v>13.6640188770665</v>
+        <v>19.9249</v>
       </c>
     </row>
     <row r="159">
@@ -10561,10 +10549,10 @@
         <v>1.34</v>
       </c>
       <c r="I159" t="n">
-        <v>0.5644228249543274</v>
+        <v>0.8181</v>
       </c>
       <c r="J159" t="n">
-        <v>12.98172497394953</v>
+        <v>18.8163</v>
       </c>
     </row>
     <row r="160">
@@ -10601,10 +10589,10 @@
         <v>1.12</v>
       </c>
       <c r="I160" t="n">
-        <v>0.2410069677682046</v>
+        <v>0.2458</v>
       </c>
       <c r="J160" t="n">
-        <v>5.543160258668706</v>
+        <v>5.6534</v>
       </c>
     </row>
     <row r="161">
@@ -10641,10 +10629,10 @@
         <v>1.07</v>
       </c>
       <c r="I161" t="n">
-        <v>0.1867608524056394</v>
+        <v>0.1052</v>
       </c>
       <c r="J161" t="n">
-        <v>4.295499605329706</v>
+        <v>2.4196</v>
       </c>
     </row>
     <row r="162">
@@ -10681,10 +10669,10 @@
         <v>1.9</v>
       </c>
       <c r="I162" t="n">
-        <v>1.102980110264673</v>
+        <v>1.7788</v>
       </c>
       <c r="J162" t="n">
-        <v>19.85364198476411</v>
+        <v>32.0184</v>
       </c>
     </row>
     <row r="163">
@@ -10721,10 +10709,10 @@
         <v>1.61</v>
       </c>
       <c r="I163" t="n">
-        <v>0.8695799356829829</v>
+        <v>1.2979</v>
       </c>
       <c r="J163" t="n">
-        <v>15.65243884229369</v>
+        <v>23.3622</v>
       </c>
     </row>
     <row r="164">
@@ -10761,10 +10749,10 @@
         <v>1.52</v>
       </c>
       <c r="I164" t="n">
-        <v>0.7596028087813218</v>
+        <v>1.1091</v>
       </c>
       <c r="J164" t="n">
-        <v>13.67285055806379</v>
+        <v>19.9638</v>
       </c>
     </row>
     <row r="165">
@@ -10801,10 +10789,10 @@
         <v>1.49</v>
       </c>
       <c r="I165" t="n">
-        <v>0.6941787799892305</v>
+        <v>1.0288</v>
       </c>
       <c r="J165" t="n">
-        <v>12.49521803980615</v>
+        <v>18.5184</v>
       </c>
     </row>
     <row r="166">
@@ -10841,10 +10829,10 @@
         <v>0.98</v>
       </c>
       <c r="I166" t="n">
-        <v>0.2164034879890168</v>
+        <v>-0.3004</v>
       </c>
       <c r="J166" t="n">
-        <v>3.895262783802302</v>
+        <v>-5.4072</v>
       </c>
     </row>
     <row r="167">
@@ -10881,10 +10869,10 @@
         <v>0.65</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.6132817189753037</v>
+        <v>-0.3724</v>
       </c>
       <c r="J167" t="n">
-        <v>-11.03907094155547</v>
+        <v>-6.7032</v>
       </c>
     </row>
     <row r="168">
@@ -10921,10 +10909,10 @@
         <v>0.59</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.6874671806497249</v>
+        <v>-0.466</v>
       </c>
       <c r="J168" t="n">
-        <v>-12.37440925169505</v>
+        <v>-8.388</v>
       </c>
     </row>
     <row r="169">
@@ -10961,10 +10949,10 @@
         <v>0.59</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.6874671806497249</v>
+        <v>-0.466</v>
       </c>
       <c r="J169" t="n">
-        <v>-12.37440925169505</v>
+        <v>-8.388</v>
       </c>
     </row>
     <row r="170">
@@ -11001,10 +10989,10 @@
         <v>0.41</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.9751389949802728</v>
+        <v>-0.7756999999999999</v>
       </c>
       <c r="J170" t="n">
-        <v>-17.55250190964491</v>
+        <v>-13.9626</v>
       </c>
     </row>
     <row r="171">
@@ -11041,10 +11029,10 @@
         <v>0.39</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.9972081679599089</v>
+        <v>-0.8038999999999999</v>
       </c>
       <c r="J171" t="n">
-        <v>-17.94974702327836</v>
+        <v>-14.4702</v>
       </c>
     </row>
     <row r="172">
@@ -11081,10 +11069,10 @@
         <v>1.44</v>
       </c>
       <c r="I172" t="n">
-        <v>0.6502498577654056</v>
+        <v>1.158</v>
       </c>
       <c r="J172" t="n">
-        <v>17.55674615966595</v>
+        <v>31.266</v>
       </c>
     </row>
     <row r="173">
@@ -11121,10 +11109,10 @@
         <v>1.21</v>
       </c>
       <c r="I173" t="n">
-        <v>0.4141694913660199</v>
+        <v>0.6395</v>
       </c>
       <c r="J173" t="n">
-        <v>11.18257626688254</v>
+        <v>17.2665</v>
       </c>
     </row>
     <row r="174">
@@ -11161,10 +11149,10 @@
         <v>1.2</v>
       </c>
       <c r="I174" t="n">
-        <v>0.4013630656812535</v>
+        <v>0.6141</v>
       </c>
       <c r="J174" t="n">
-        <v>10.83680277339385</v>
+        <v>16.5807</v>
       </c>
     </row>
     <row r="175">
@@ -11201,10 +11189,10 @@
         <v>1.06</v>
       </c>
       <c r="I175" t="n">
-        <v>0.1461684186086805</v>
+        <v>0.1789</v>
       </c>
       <c r="J175" t="n">
-        <v>3.946547302434374</v>
+        <v>4.8303</v>
       </c>
     </row>
     <row r="176">
@@ -11241,10 +11229,10 @@
         <v>0.53</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5784741084272937</v>
+        <v>-1.2854</v>
       </c>
       <c r="J176" t="n">
-        <v>-15.61880092753693</v>
+        <v>-34.7058</v>
       </c>
     </row>
     <row r="177">
@@ -11281,10 +11269,10 @@
         <v>1.29</v>
       </c>
       <c r="I177" t="n">
-        <v>0.4027506553308398</v>
+        <v>0.5133</v>
       </c>
       <c r="J177" t="n">
-        <v>10.87426769393267</v>
+        <v>13.8591</v>
       </c>
     </row>
     <row r="178">
@@ -11321,10 +11309,10 @@
         <v>1.12</v>
       </c>
       <c r="I178" t="n">
-        <v>0.0970151390028007</v>
+        <v>0.2681</v>
       </c>
       <c r="J178" t="n">
-        <v>2.619408753075619</v>
+        <v>7.2387</v>
       </c>
     </row>
     <row r="179">
@@ -11361,10 +11349,10 @@
         <v>1.04</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1011953744737532</v>
+        <v>0.1227</v>
       </c>
       <c r="J179" t="n">
-        <v>-2.732275110791336</v>
+        <v>3.3129</v>
       </c>
     </row>
     <row r="180">
@@ -11401,10 +11389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.3338099441424295</v>
+        <v>-0.1479</v>
       </c>
       <c r="J180" t="n">
-        <v>-9.012868491845596</v>
+        <v>-3.9933</v>
       </c>
     </row>
     <row r="181">
@@ -11441,10 +11429,10 @@
         <v>0.52</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.8225027473406321</v>
+        <v>-0.7385</v>
       </c>
       <c r="J181" t="n">
-        <v>-22.20757417819707</v>
+        <v>-19.9395</v>
       </c>
     </row>
     <row r="182">
@@ -11481,10 +11469,10 @@
         <v>1.39</v>
       </c>
       <c r="I182" t="n">
-        <v>0.4008610693702157</v>
+        <v>0.5888</v>
       </c>
       <c r="J182" t="n">
-        <v>10.82324887299582</v>
+        <v>15.8976</v>
       </c>
     </row>
     <row r="183">
@@ -11521,10 +11509,10 @@
         <v>1.23</v>
       </c>
       <c r="I183" t="n">
-        <v>0.2820602048646765</v>
+        <v>0.3774</v>
       </c>
       <c r="J183" t="n">
-        <v>7.615625531346266</v>
+        <v>10.1898</v>
       </c>
     </row>
     <row r="184">
@@ -11561,10 +11549,10 @@
         <v>1.16</v>
       </c>
       <c r="I184" t="n">
-        <v>0.2104454255377027</v>
+        <v>0.2686</v>
       </c>
       <c r="J184" t="n">
-        <v>5.682026489517974</v>
+        <v>7.2522</v>
       </c>
     </row>
     <row r="185">
@@ -11601,10 +11589,10 @@
         <v>1.08</v>
       </c>
       <c r="I185" t="n">
-        <v>0.1027269685420029</v>
+        <v>0.1193</v>
       </c>
       <c r="J185" t="n">
-        <v>2.773628150634079</v>
+        <v>3.2211</v>
       </c>
     </row>
     <row r="186">
@@ -11641,10 +11629,10 @@
         <v>0.85</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.20805599091497</v>
+        <v>-0.3398</v>
       </c>
       <c r="J186" t="n">
-        <v>-5.617511754704189</v>
+        <v>-9.1746</v>
       </c>
     </row>
     <row r="187">
@@ -11681,10 +11669,10 @@
         <v>1.16</v>
       </c>
       <c r="I187" t="n">
-        <v>0.111937714985958</v>
+        <v>0.3497</v>
       </c>
       <c r="J187" t="n">
-        <v>3.022318304620867</v>
+        <v>9.4419</v>
       </c>
     </row>
     <row r="188">
@@ -11721,10 +11709,10 @@
         <v>1.08</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.01843746692390319</v>
+        <v>0.2201</v>
       </c>
       <c r="J188" t="n">
-        <v>-0.4978116069453861</v>
+        <v>5.9427</v>
       </c>
     </row>
     <row r="189">
@@ -11761,10 +11749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1997155679011784</v>
+        <v>-0.1114</v>
       </c>
       <c r="J189" t="n">
-        <v>-5.392320333331818</v>
+        <v>-3.0078</v>
       </c>
     </row>
     <row r="190">
@@ -11801,10 +11789,10 @@
         <v>0.79</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3972394561939185</v>
+        <v>-0.3801</v>
       </c>
       <c r="J190" t="n">
-        <v>-10.7254653172358</v>
+        <v>-10.2627</v>
       </c>
     </row>
     <row r="191">
@@ -11841,10 +11829,10 @@
         <v>0.68</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.491505224512843</v>
+        <v>-0.5328000000000001</v>
       </c>
       <c r="J191" t="n">
-        <v>-13.27064106184676</v>
+        <v>-14.3856</v>
       </c>
     </row>
     <row r="192">
@@ -11881,10 +11869,10 @@
         <v>1.25</v>
       </c>
       <c r="I192" t="n">
-        <v>0.216913429142991</v>
+        <v>0.4415</v>
       </c>
       <c r="J192" t="n">
-        <v>6.507402874289731</v>
+        <v>13.245</v>
       </c>
     </row>
     <row r="193">
@@ -11921,10 +11909,10 @@
         <v>1.07</v>
       </c>
       <c r="I193" t="n">
-        <v>0.04901555158719013</v>
+        <v>0.1584</v>
       </c>
       <c r="J193" t="n">
-        <v>1.470466547615704</v>
+        <v>4.752</v>
       </c>
     </row>
     <row r="194">
@@ -11961,10 +11949,10 @@
         <v>0.98</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1579211882892509</v>
+        <v>-0.0842</v>
       </c>
       <c r="J194" t="n">
-        <v>-4.737635648677527</v>
+        <v>-2.526</v>
       </c>
     </row>
     <row r="195">
@@ -12001,10 +11989,10 @@
         <v>0.95</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2128554232676769</v>
+        <v>-0.1485</v>
       </c>
       <c r="J195" t="n">
-        <v>-6.385662698030306</v>
+        <v>-4.455</v>
       </c>
     </row>
     <row r="196">
@@ -12041,10 +12029,10 @@
         <v>0.93</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.2451615381365197</v>
+        <v>-0.1862</v>
       </c>
       <c r="J196" t="n">
-        <v>-7.35484614409559</v>
+        <v>-5.586</v>
       </c>
     </row>
     <row r="197">
@@ -12081,10 +12069,10 @@
         <v>1.16</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2970948635485692</v>
+        <v>0.5632</v>
       </c>
       <c r="J197" t="n">
-        <v>8.912845906457076</v>
+        <v>16.896</v>
       </c>
     </row>
     <row r="198">
@@ -12121,10 +12109,10 @@
         <v>1.04</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1089702426979951</v>
+        <v>0.1976</v>
       </c>
       <c r="J198" t="n">
-        <v>3.269107280939854</v>
+        <v>5.928</v>
       </c>
     </row>
     <row r="199">
@@ -12161,10 +12149,10 @@
         <v>0.97</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.05675367813365629</v>
+        <v>-0.1622</v>
       </c>
       <c r="J199" t="n">
-        <v>-1.702610344009689</v>
+        <v>-4.866</v>
       </c>
     </row>
     <row r="200">
@@ -12201,10 +12189,10 @@
         <v>0.93</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.1136379715694227</v>
+        <v>-0.3046</v>
       </c>
       <c r="J200" t="n">
-        <v>-3.40913914708268</v>
+        <v>-9.138</v>
       </c>
     </row>
     <row r="201">
@@ -12241,10 +12229,10 @@
         <v>0.91</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.1386394088867248</v>
+        <v>-0.3675</v>
       </c>
       <c r="J201" t="n">
-        <v>-4.159182266601744</v>
+        <v>-11.025</v>
       </c>
     </row>
     <row r="202">
@@ -12281,10 +12269,10 @@
         <v>1.15</v>
       </c>
       <c r="I202" t="n">
-        <v>0.08258718119412689</v>
+        <v>0.3457</v>
       </c>
       <c r="J202" t="n">
-        <v>2.477615435823807</v>
+        <v>10.371</v>
       </c>
     </row>
     <row r="203">
@@ -12321,10 +12309,10 @@
         <v>0.89</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.2659470937133861</v>
+        <v>-0.2023</v>
       </c>
       <c r="J203" t="n">
-        <v>-7.978412811401583</v>
+        <v>-6.069</v>
       </c>
     </row>
     <row r="204">
@@ -12361,10 +12349,10 @@
         <v>0.85</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.3329220688850941</v>
+        <v>-0.2755</v>
       </c>
       <c r="J204" t="n">
-        <v>-9.987662066552822</v>
+        <v>-8.265000000000001</v>
       </c>
     </row>
     <row r="205">
@@ -12401,10 +12389,10 @@
         <v>0.82</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.374153979564094</v>
+        <v>-0.3246</v>
       </c>
       <c r="J205" t="n">
-        <v>-11.22461938692282</v>
+        <v>-9.738</v>
       </c>
     </row>
     <row r="206">
@@ -12441,10 +12429,10 @@
         <v>0.79</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4115532194826837</v>
+        <v>-0.3709</v>
       </c>
       <c r="J206" t="n">
-        <v>-12.34659658448051</v>
+        <v>-11.127</v>
       </c>
     </row>
     <row r="207">
@@ -12481,10 +12469,10 @@
         <v>1.55</v>
       </c>
       <c r="I207" t="n">
-        <v>0.5938310906312312</v>
+        <v>1.318</v>
       </c>
       <c r="J207" t="n">
-        <v>17.81493271893694</v>
+        <v>39.54</v>
       </c>
     </row>
     <row r="208">
@@ -12521,10 +12509,10 @@
         <v>1.19</v>
       </c>
       <c r="I208" t="n">
-        <v>0.1870660062450799</v>
+        <v>0.4868</v>
       </c>
       <c r="J208" t="n">
-        <v>5.611980187352398</v>
+        <v>14.604</v>
       </c>
     </row>
     <row r="209">
@@ -12561,10 +12549,10 @@
         <v>1.18</v>
       </c>
       <c r="I209" t="n">
-        <v>0.1703384117133631</v>
+        <v>0.458</v>
       </c>
       <c r="J209" t="n">
-        <v>5.110152351400892</v>
+        <v>13.74</v>
       </c>
     </row>
     <row r="210">
@@ -12601,10 +12589,10 @@
         <v>1.06</v>
       </c>
       <c r="I210" t="n">
-        <v>0.01175051128810659</v>
+        <v>0.113</v>
       </c>
       <c r="J210" t="n">
-        <v>0.3525153386431977</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="211">
@@ -12641,10 +12629,10 @@
         <v>1.05</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.0002583661477278329</v>
+        <v>0.081</v>
       </c>
       <c r="J211" t="n">
-        <v>-0.007750984431834987</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="212">
@@ -12681,10 +12669,10 @@
         <v>1.29</v>
       </c>
       <c r="I212" t="n">
-        <v>0.4480455636826353</v>
+        <v>0.475</v>
       </c>
       <c r="J212" t="n">
-        <v>16.12964029257487</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="213">
@@ -12721,10 +12709,10 @@
         <v>1.19</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3195736235082024</v>
+        <v>0.3344</v>
       </c>
       <c r="J213" t="n">
-        <v>11.50465044629529</v>
+        <v>12.0384</v>
       </c>
     </row>
     <row r="214">
@@ -12761,10 +12749,10 @@
         <v>1.16</v>
       </c>
       <c r="I214" t="n">
-        <v>0.2738898307155297</v>
+        <v>0.2881</v>
       </c>
       <c r="J214" t="n">
-        <v>9.860033905759071</v>
+        <v>10.3716</v>
       </c>
     </row>
     <row r="215">
@@ -12801,10 +12789,10 @@
         <v>0.98</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.08710477391807125</v>
+        <v>-0.1043</v>
       </c>
       <c r="J215" t="n">
-        <v>-3.135771861050565</v>
+        <v>-3.7548</v>
       </c>
     </row>
     <row r="216">
@@ -12841,10 +12829,10 @@
         <v>0.87</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.2199554617427208</v>
+        <v>-0.3013</v>
       </c>
       <c r="J216" t="n">
-        <v>-7.91839662273795</v>
+        <v>-10.8468</v>
       </c>
     </row>
     <row r="217">
@@ -12881,10 +12869,10 @@
         <v>1.2</v>
       </c>
       <c r="I217" t="n">
-        <v>0.1577830308101832</v>
+        <v>0.3864</v>
       </c>
       <c r="J217" t="n">
-        <v>5.680189109166597</v>
+        <v>13.9104</v>
       </c>
     </row>
     <row r="218">
@@ -12921,10 +12909,10 @@
         <v>1.07</v>
       </c>
       <c r="I218" t="n">
-        <v>0.01168580928618281</v>
+        <v>0.1776</v>
       </c>
       <c r="J218" t="n">
-        <v>0.4206891343025811</v>
+        <v>6.3936</v>
       </c>
     </row>
     <row r="219">
@@ -12961,10 +12949,10 @@
         <v>0.97</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.2005042580461592</v>
+        <v>-0.0882</v>
       </c>
       <c r="J219" t="n">
-        <v>-7.218153289661731</v>
+        <v>-3.1752</v>
       </c>
     </row>
     <row r="220">
@@ -13001,10 +12989,10 @@
         <v>0.86</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.3702342919345211</v>
+        <v>-0.2912</v>
       </c>
       <c r="J220" t="n">
-        <v>-13.32843450964276</v>
+        <v>-10.4832</v>
       </c>
     </row>
     <row r="221">
@@ -13041,10 +13029,10 @@
         <v>0.86</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3702342919345211</v>
+        <v>-0.2912</v>
       </c>
       <c r="J221" t="n">
-        <v>-13.32843450964276</v>
+        <v>-10.4832</v>
       </c>
     </row>
     <row r="222">
@@ -13081,10 +13069,10 @@
         <v>1.28</v>
       </c>
       <c r="I222" t="n">
-        <v>0.3039056991034886</v>
+        <v>0.5077</v>
       </c>
       <c r="J222" t="n">
-        <v>8.509359574897681</v>
+        <v>14.2156</v>
       </c>
     </row>
     <row r="223">
@@ -13121,10 +13109,10 @@
         <v>1.06</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.03622682620809809</v>
+        <v>0.1718</v>
       </c>
       <c r="J223" t="n">
-        <v>-1.014351133826747</v>
+        <v>4.8104</v>
       </c>
     </row>
     <row r="224">
@@ -13161,10 +13149,10 @@
         <v>0.93</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.2385334755973269</v>
+        <v>-0.1576</v>
       </c>
       <c r="J224" t="n">
-        <v>-6.678937316725153</v>
+        <v>-4.4128</v>
       </c>
     </row>
     <row r="225">
@@ -13201,10 +13189,10 @@
         <v>0.86</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.3230630238373994</v>
+        <v>-0.2814</v>
       </c>
       <c r="J225" t="n">
-        <v>-9.045764667447184</v>
+        <v>-7.8792</v>
       </c>
     </row>
     <row r="226">
@@ -13241,10 +13229,10 @@
         <v>0.67</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4905589840931796</v>
+        <v>-0.5518</v>
       </c>
       <c r="J226" t="n">
-        <v>-13.73565155460903</v>
+        <v>-15.4504</v>
       </c>
     </row>
     <row r="227">
@@ -13281,10 +13269,10 @@
         <v>1.6</v>
       </c>
       <c r="I227" t="n">
-        <v>0.4840009986023552</v>
+        <v>1.4523</v>
       </c>
       <c r="J227" t="n">
-        <v>13.55202796086595</v>
+        <v>40.6644</v>
       </c>
     </row>
     <row r="228">
@@ -13321,10 +13309,10 @@
         <v>1.36</v>
       </c>
       <c r="I228" t="n">
-        <v>0.3511464478456215</v>
+        <v>0.966</v>
       </c>
       <c r="J228" t="n">
-        <v>9.832100539677402</v>
+        <v>27.048</v>
       </c>
     </row>
     <row r="229">
@@ -13361,10 +13349,10 @@
         <v>1.07</v>
       </c>
       <c r="I229" t="n">
-        <v>0.06992797329351853</v>
+        <v>0.1831</v>
       </c>
       <c r="J229" t="n">
-        <v>1.957983252218519</v>
+        <v>5.1268</v>
       </c>
     </row>
     <row r="230">
@@ -13401,10 +13389,10 @@
         <v>1.03</v>
       </c>
       <c r="I230" t="n">
-        <v>0.02867957074807788</v>
+        <v>0.0464</v>
       </c>
       <c r="J230" t="n">
-        <v>0.8030279809461807</v>
+        <v>1.2992</v>
       </c>
     </row>
     <row r="231">
@@ -13441,10 +13429,10 @@
         <v>0.59</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5121584685566671</v>
+        <v>-1.1722</v>
       </c>
       <c r="J231" t="n">
-        <v>-14.34043711958668</v>
+        <v>-32.8216</v>
       </c>
     </row>
     <row r="232">
@@ -13481,10 +13469,10 @@
         <v>1.33</v>
       </c>
       <c r="I232" t="n">
-        <v>0.3575210408613984</v>
+        <v>0.5684</v>
       </c>
       <c r="J232" t="n">
-        <v>10.01058914411915</v>
+        <v>15.9152</v>
       </c>
     </row>
     <row r="233">
@@ -13521,10 +13509,10 @@
         <v>0.97</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.1814855588182219</v>
+        <v>-0.0746</v>
       </c>
       <c r="J233" t="n">
-        <v>-5.081595646910213</v>
+        <v>-2.0888</v>
       </c>
     </row>
     <row r="234">
@@ -13561,10 +13549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.2323531542381175</v>
+        <v>-0.1433</v>
       </c>
       <c r="J234" t="n">
-        <v>-6.50588831866729</v>
+        <v>-4.0124</v>
       </c>
     </row>
     <row r="235">
@@ -13601,10 +13589,10 @@
         <v>0.86</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.3278656975488207</v>
+        <v>-0.2853</v>
       </c>
       <c r="J235" t="n">
-        <v>-9.180239531366981</v>
+        <v>-7.9884</v>
       </c>
     </row>
     <row r="236">
@@ -13641,10 +13629,10 @@
         <v>0.76</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4218359057624231</v>
+        <v>-0.4338</v>
       </c>
       <c r="J236" t="n">
-        <v>-11.81140536134785</v>
+        <v>-12.1464</v>
       </c>
     </row>
     <row r="237">
@@ -13681,10 +13669,10 @@
         <v>1.47</v>
       </c>
       <c r="I237" t="n">
-        <v>0.4180421344127861</v>
+        <v>1.2024</v>
       </c>
       <c r="J237" t="n">
-        <v>11.70517976355801</v>
+        <v>33.6672</v>
       </c>
     </row>
     <row r="238">
@@ -13721,10 +13709,10 @@
         <v>1.23</v>
       </c>
       <c r="I238" t="n">
-        <v>0.257900115107906</v>
+        <v>0.6702</v>
       </c>
       <c r="J238" t="n">
-        <v>7.221203223021368</v>
+        <v>18.7656</v>
       </c>
     </row>
     <row r="239">
@@ -13761,10 +13749,10 @@
         <v>1.21</v>
       </c>
       <c r="I239" t="n">
-        <v>0.2407984090922499</v>
+        <v>0.6197</v>
       </c>
       <c r="J239" t="n">
-        <v>6.742355454582999</v>
+        <v>17.3516</v>
       </c>
     </row>
     <row r="240">
@@ -13801,10 +13789,10 @@
         <v>0.85</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2542347957620109</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.118574281336306</v>
+        <v>-16.3576</v>
       </c>
     </row>
     <row r="241">
@@ -13841,10 +13829,10 @@
         <v>0.84</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2663781176704441</v>
+        <v>-0.6098</v>
       </c>
       <c r="J241" t="n">
-        <v>-7.458587294772434</v>
+        <v>-17.0744</v>
       </c>
     </row>
     <row r="242">
@@ -13881,10 +13869,10 @@
         <v>1.17</v>
       </c>
       <c r="I242" t="n">
-        <v>0.09051472253436127</v>
+        <v>0.3934</v>
       </c>
       <c r="J242" t="n">
-        <v>2.443897508427754</v>
+        <v>10.6218</v>
       </c>
     </row>
     <row r="243">
@@ -13921,10 +13909,10 @@
         <v>1.01</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.08338647120197602</v>
+        <v>0.1068</v>
       </c>
       <c r="J243" t="n">
-        <v>-2.251434722453352</v>
+        <v>2.8836</v>
       </c>
     </row>
     <row r="244">
@@ -13961,10 +13949,10 @@
         <v>0.93</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.1945408372153273</v>
+        <v>-0.0912</v>
       </c>
       <c r="J244" t="n">
-        <v>-5.252602604813837</v>
+        <v>-2.4624</v>
       </c>
     </row>
     <row r="245">
@@ -14001,10 +13989,10 @@
         <v>0.63</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.6398218044247331</v>
+        <v>-0.5815</v>
       </c>
       <c r="J245" t="n">
-        <v>-17.2751887194678</v>
+        <v>-15.7005</v>
       </c>
     </row>
     <row r="246">
@@ -14041,10 +14029,10 @@
         <v>0.53</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.7331375986410321</v>
+        <v>-0.7077</v>
       </c>
       <c r="J246" t="n">
-        <v>-19.79471516330787</v>
+        <v>-19.1079</v>
       </c>
     </row>
     <row r="247">
@@ -14081,10 +14069,10 @@
         <v>1.45</v>
       </c>
       <c r="I247" t="n">
-        <v>0.5216307171195814</v>
+        <v>0.6522</v>
       </c>
       <c r="J247" t="n">
-        <v>14.0840293622287</v>
+        <v>17.6094</v>
       </c>
     </row>
     <row r="248">
@@ -14121,10 +14109,10 @@
         <v>1.13</v>
       </c>
       <c r="I248" t="n">
-        <v>0.1862833357955184</v>
+        <v>0.1948</v>
       </c>
       <c r="J248" t="n">
-        <v>5.029650066478998</v>
+        <v>5.2596</v>
       </c>
     </row>
     <row r="249">
@@ -14161,10 +14149,10 @@
         <v>1.12</v>
       </c>
       <c r="I249" t="n">
-        <v>0.1741786087255912</v>
+        <v>0.178</v>
       </c>
       <c r="J249" t="n">
-        <v>4.702822435590963</v>
+        <v>4.806</v>
       </c>
     </row>
     <row r="250">
@@ -14201,10 +14189,10 @@
         <v>1.1</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1511460616217264</v>
+        <v>0.1442</v>
       </c>
       <c r="J250" t="n">
-        <v>4.080943663786613</v>
+        <v>3.8934</v>
       </c>
     </row>
     <row r="251">
@@ -14241,10 +14229,10 @@
         <v>1.06</v>
       </c>
       <c r="I251" t="n">
-        <v>0.1079893039939983</v>
+        <v>0.0738</v>
       </c>
       <c r="J251" t="n">
-        <v>2.915711207837953</v>
+        <v>1.9926</v>
       </c>
     </row>
     <row r="252">
@@ -14281,10 +14269,10 @@
         <v>1.42</v>
       </c>
       <c r="I252" t="n">
-        <v>0.3703777671019648</v>
+        <v>1.1219</v>
       </c>
       <c r="J252" t="n">
-        <v>10.74095524595698</v>
+        <v>32.5351</v>
       </c>
     </row>
     <row r="253">
@@ -14321,10 +14309,10 @@
         <v>1.25</v>
       </c>
       <c r="I253" t="n">
-        <v>0.2587121109227453</v>
+        <v>0.7437</v>
       </c>
       <c r="J253" t="n">
-        <v>7.502651216759614</v>
+        <v>21.5673</v>
       </c>
     </row>
     <row r="254">
@@ -14361,10 +14349,10 @@
         <v>1.01</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.04595361313773035</v>
+        <v>-0.0072</v>
       </c>
       <c r="J254" t="n">
-        <v>-1.33265478099418</v>
+        <v>-0.2088</v>
       </c>
     </row>
     <row r="255">
@@ -14401,10 +14389,10 @@
         <v>0.93</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.1824973558857018</v>
+        <v>-0.3445</v>
       </c>
       <c r="J255" t="n">
-        <v>-5.292423320685351</v>
+        <v>-9.990500000000001</v>
       </c>
     </row>
     <row r="256">
@@ -14441,10 +14429,10 @@
         <v>0.78</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.3683465406423231</v>
+        <v>-0.7439</v>
       </c>
       <c r="J256" t="n">
-        <v>-10.68204967862737</v>
+        <v>-21.5731</v>
       </c>
     </row>
     <row r="257">
@@ -14481,10 +14469,10 @@
         <v>1.58</v>
       </c>
       <c r="I257" t="n">
-        <v>0.4514656503510367</v>
+        <v>0.8445</v>
       </c>
       <c r="J257" t="n">
-        <v>13.09250386018006</v>
+        <v>24.4905</v>
       </c>
     </row>
     <row r="258">
@@ -14521,10 +14509,10 @@
         <v>1.18</v>
       </c>
       <c r="I258" t="n">
-        <v>0.1419880197116903</v>
+        <v>0.3445</v>
       </c>
       <c r="J258" t="n">
-        <v>4.11765257163902</v>
+        <v>9.990500000000001</v>
       </c>
     </row>
     <row r="259">
@@ -14561,10 +14549,10 @@
         <v>0.86</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.3390754987567634</v>
+        <v>-0.3008</v>
       </c>
       <c r="J259" t="n">
-        <v>-9.833189463946139</v>
+        <v>-8.7232</v>
       </c>
     </row>
     <row r="260">
@@ -14601,10 +14589,10 @@
         <v>0.83</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3686306659654014</v>
+        <v>-0.3463</v>
       </c>
       <c r="J260" t="n">
-        <v>-10.69028931299664</v>
+        <v>-10.0427</v>
       </c>
     </row>
     <row r="261">
@@ -14641,10 +14629,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4881530004954467</v>
+        <v>-0.538</v>
       </c>
       <c r="J261" t="n">
-        <v>-14.15643701436796</v>
+        <v>-15.602</v>
       </c>
     </row>
     <row r="262">
@@ -14681,10 +14669,10 @@
         <v>2.04</v>
       </c>
       <c r="I262" t="n">
-        <v>0.7392277083760121</v>
+        <v>2.0132</v>
       </c>
       <c r="J262" t="n">
-        <v>14.78455416752024</v>
+        <v>40.264</v>
       </c>
     </row>
     <row r="263">
@@ -14721,10 +14709,10 @@
         <v>1.72</v>
       </c>
       <c r="I263" t="n">
-        <v>0.6034530136101275</v>
+        <v>1.5325</v>
       </c>
       <c r="J263" t="n">
-        <v>12.06906027220255</v>
+        <v>30.65</v>
       </c>
     </row>
     <row r="264">
@@ -14761,10 +14749,10 @@
         <v>1.31</v>
       </c>
       <c r="I264" t="n">
-        <v>0.2901163953559897</v>
+        <v>0.6558</v>
       </c>
       <c r="J264" t="n">
-        <v>5.802327907119794</v>
+        <v>13.116</v>
       </c>
     </row>
     <row r="265">
@@ -14801,10 +14789,10 @@
         <v>1.09</v>
       </c>
       <c r="I265" t="n">
-        <v>0.1570526505822537</v>
+        <v>0.1254</v>
       </c>
       <c r="J265" t="n">
-        <v>3.141053011645075</v>
+        <v>2.508</v>
       </c>
     </row>
     <row r="266">
@@ -14841,10 +14829,10 @@
         <v>1.04</v>
       </c>
       <c r="I266" t="n">
-        <v>0.1292790489511436</v>
+        <v>-0.023</v>
       </c>
       <c r="J266" t="n">
-        <v>2.585580979022872</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="267">
@@ -14881,10 +14869,10 @@
         <v>0.87</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.3098586378892009</v>
+        <v>-0.1013</v>
       </c>
       <c r="J267" t="n">
-        <v>-6.197172757784019</v>
+        <v>-2.026</v>
       </c>
     </row>
     <row r="268">
@@ -14921,10 +14909,10 @@
         <v>0.72</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.4449146350949556</v>
+        <v>-0.3404</v>
       </c>
       <c r="J268" t="n">
-        <v>-8.898292701899113</v>
+        <v>-6.808</v>
       </c>
     </row>
     <row r="269">
@@ -14961,10 +14949,10 @@
         <v>0.63</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.575997516685618</v>
+        <v>-0.5058</v>
       </c>
       <c r="J269" t="n">
-        <v>-11.51995033371236</v>
+        <v>-10.116</v>
       </c>
     </row>
     <row r="270">
@@ -15001,10 +14989,10 @@
         <v>0.6</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.612185631518797</v>
+        <v>-0.5545</v>
       </c>
       <c r="J270" t="n">
-        <v>-12.24371263037594</v>
+        <v>-11.09</v>
       </c>
     </row>
     <row r="271">
@@ -15041,10 +15029,10 @@
         <v>0.44</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.752550932295489</v>
+        <v>-0.7768</v>
       </c>
       <c r="J271" t="n">
-        <v>-15.05101864590978</v>
+        <v>-15.536</v>
       </c>
     </row>
     <row r="272">
@@ -15081,10 +15069,10 @@
         <v>1.3</v>
       </c>
       <c r="I272" t="n">
-        <v>0.3496444596661347</v>
+        <v>0.494</v>
       </c>
       <c r="J272" t="n">
-        <v>12.58720054798085</v>
+        <v>17.784</v>
       </c>
     </row>
     <row r="273">
@@ -15121,10 +15109,10 @@
         <v>1.23</v>
       </c>
       <c r="I273" t="n">
-        <v>0.2720717083544352</v>
+        <v>0.3989</v>
       </c>
       <c r="J273" t="n">
-        <v>9.794581500759667</v>
+        <v>14.3604</v>
       </c>
     </row>
     <row r="274">
@@ -15161,10 +15149,10 @@
         <v>1.18</v>
       </c>
       <c r="I274" t="n">
-        <v>0.2091030092103312</v>
+        <v>0.3259</v>
       </c>
       <c r="J274" t="n">
-        <v>7.527708331571923</v>
+        <v>11.7324</v>
       </c>
     </row>
     <row r="275">
@@ -15201,10 +15189,10 @@
         <v>0.91</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.2438007108445157</v>
+        <v>-0.2331</v>
       </c>
       <c r="J275" t="n">
-        <v>-8.776825590402566</v>
+        <v>-8.3916</v>
       </c>
     </row>
     <row r="276">
@@ -15241,10 +15229,10 @@
         <v>0.78</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3722038953312855</v>
+        <v>-0.4279</v>
       </c>
       <c r="J276" t="n">
-        <v>-13.39934023192628</v>
+        <v>-15.4044</v>
       </c>
     </row>
     <row r="277">
@@ -15281,10 +15269,10 @@
         <v>1.1</v>
       </c>
       <c r="I277" t="n">
-        <v>0.1523622202944887</v>
+        <v>0.4059</v>
       </c>
       <c r="J277" t="n">
-        <v>5.485039930601594</v>
+        <v>14.6124</v>
       </c>
     </row>
     <row r="278">
@@ -15321,10 +15309,10 @@
         <v>1.01</v>
       </c>
       <c r="I278" t="n">
-        <v>0.01718645569616715</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="J278" t="n">
-        <v>0.6187124050620176</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="279">
@@ -15361,10 +15349,10 @@
         <v>0.99</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.01979053263553197</v>
+        <v>-0.0456</v>
       </c>
       <c r="J279" t="n">
-        <v>-0.7124591748791511</v>
+        <v>-1.6416</v>
       </c>
     </row>
     <row r="280">
@@ -15401,10 +15389,10 @@
         <v>0.97</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.07093635327809104</v>
+        <v>-0.1477</v>
       </c>
       <c r="J280" t="n">
-        <v>-2.553708718011277</v>
+        <v>-5.3172</v>
       </c>
     </row>
     <row r="281">
@@ -15441,10 +15429,10 @@
         <v>0.86</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.2276301209640212</v>
+        <v>-0.5036</v>
       </c>
       <c r="J281" t="n">
-        <v>-8.194684354704762</v>
+        <v>-18.1296</v>
       </c>
     </row>
     <row r="282">
@@ -15481,10 +15469,10 @@
         <v>1.25</v>
       </c>
       <c r="I282" t="n">
-        <v>-0.008296925885950907</v>
+        <v>0.5472</v>
       </c>
       <c r="J282" t="n">
-        <v>-0.174235443604969</v>
+        <v>11.4912</v>
       </c>
     </row>
     <row r="283">
@@ -15521,10 +15509,10 @@
         <v>1.05</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.1704620909809501</v>
+        <v>0.2351</v>
       </c>
       <c r="J283" t="n">
-        <v>-3.579703910599952</v>
+        <v>4.9371</v>
       </c>
     </row>
     <row r="284">
@@ -15561,10 +15549,10 @@
         <v>0.59</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.6405819928146316</v>
+        <v>-0.6095</v>
       </c>
       <c r="J284" t="n">
-        <v>-13.45222184910726</v>
+        <v>-12.7995</v>
       </c>
     </row>
     <row r="285">
@@ -15601,10 +15589,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.6638584948276298</v>
+        <v>-0.6492</v>
       </c>
       <c r="J285" t="n">
-        <v>-13.94102839138023</v>
+        <v>-13.6332</v>
       </c>
     </row>
     <row r="286">
@@ -15641,10 +15629,10 @@
         <v>0.34</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.8070041510100503</v>
+        <v>-0.9179</v>
       </c>
       <c r="J286" t="n">
-        <v>-16.94708717121106</v>
+        <v>-19.2759</v>
       </c>
     </row>
     <row r="287">
@@ -15681,10 +15669,10 @@
         <v>1.85</v>
       </c>
       <c r="I287" t="n">
-        <v>0.7496033231414168</v>
+        <v>1.7943</v>
       </c>
       <c r="J287" t="n">
-        <v>15.74166978596975</v>
+        <v>37.6803</v>
       </c>
     </row>
     <row r="288">
@@ -15721,10 +15709,10 @@
         <v>1.66</v>
       </c>
       <c r="I288" t="n">
-        <v>0.6500920607652584</v>
+        <v>1.4537</v>
       </c>
       <c r="J288" t="n">
-        <v>13.65193327607043</v>
+        <v>30.5277</v>
       </c>
     </row>
     <row r="289">
@@ -15761,10 +15749,10 @@
         <v>1.4</v>
       </c>
       <c r="I289" t="n">
-        <v>0.4564903446306628</v>
+        <v>0.9236</v>
       </c>
       <c r="J289" t="n">
-        <v>9.586297237243921</v>
+        <v>19.3956</v>
       </c>
     </row>
     <row r="290">
@@ -15801,10 +15789,10 @@
         <v>1.07</v>
       </c>
       <c r="I290" t="n">
-        <v>0.1486652248116588</v>
+        <v>0.0883</v>
       </c>
       <c r="J290" t="n">
-        <v>3.121969721044835</v>
+        <v>1.8543</v>
       </c>
     </row>
     <row r="291">
@@ -15841,10 +15829,10 @@
         <v>0.85</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.01418415127659891</v>
+        <v>-0.6455</v>
       </c>
       <c r="J291" t="n">
-        <v>-0.2978671768085772</v>
+        <v>-13.5555</v>
       </c>
     </row>
     <row r="292">
@@ -15881,10 +15869,10 @@
         <v>1.04</v>
       </c>
       <c r="I292" t="n">
-        <v>-0.1291068568935865</v>
+        <v>0.2093</v>
       </c>
       <c r="J292" t="n">
-        <v>-2.969457708552489</v>
+        <v>4.8139</v>
       </c>
     </row>
     <row r="293">
@@ -15921,10 +15909,10 @@
         <v>0.86</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.2913247987734618</v>
+        <v>-0.177</v>
       </c>
       <c r="J293" t="n">
-        <v>-6.700470371789622</v>
+        <v>-4.071</v>
       </c>
     </row>
     <row r="294">
@@ -15961,10 +15949,10 @@
         <v>0.74</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.4564892045863595</v>
+        <v>-0.3957</v>
       </c>
       <c r="J294" t="n">
-        <v>-10.49925170548627</v>
+        <v>-9.101100000000001</v>
       </c>
     </row>
     <row r="295">
@@ -16001,10 +15989,10 @@
         <v>0.73</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.468524196904409</v>
+        <v>-0.412</v>
       </c>
       <c r="J295" t="n">
-        <v>-10.77605652880141</v>
+        <v>-9.476000000000001</v>
       </c>
     </row>
     <row r="296">
@@ -16041,10 +16029,10 @@
         <v>0.49</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.6715689049121754</v>
+        <v>-0.7413999999999999</v>
       </c>
       <c r="J296" t="n">
-        <v>-15.44608481298003</v>
+        <v>-17.0522</v>
       </c>
     </row>
     <row r="297">
@@ -16081,10 +16069,10 @@
         <v>1.58</v>
       </c>
       <c r="I297" t="n">
-        <v>0.4290396151736387</v>
+        <v>1.3233</v>
       </c>
       <c r="J297" t="n">
-        <v>9.86791114899369</v>
+        <v>30.4359</v>
       </c>
     </row>
     <row r="298">
@@ -16121,10 +16109,10 @@
         <v>1.43</v>
       </c>
       <c r="I298" t="n">
-        <v>0.3519798834254714</v>
+        <v>1.0186</v>
       </c>
       <c r="J298" t="n">
-        <v>8.095537318785842</v>
+        <v>23.4278</v>
       </c>
     </row>
     <row r="299">
@@ -16161,10 +16149,10 @@
         <v>1.28</v>
       </c>
       <c r="I299" t="n">
-        <v>0.2258364796354838</v>
+        <v>0.6455</v>
       </c>
       <c r="J299" t="n">
-        <v>5.194239031616126</v>
+        <v>14.8465</v>
       </c>
     </row>
     <row r="300">
@@ -16201,10 +16189,10 @@
         <v>1.2</v>
       </c>
       <c r="I300" t="n">
-        <v>0.1706976800075387</v>
+        <v>0.448</v>
       </c>
       <c r="J300" t="n">
-        <v>3.926046640173389</v>
+        <v>10.304</v>
       </c>
     </row>
     <row r="301">
@@ -16241,10 +16229,10 @@
         <v>1.1</v>
       </c>
       <c r="I301" t="n">
-        <v>0.111920548047401</v>
+        <v>0.1885</v>
       </c>
       <c r="J301" t="n">
-        <v>2.574172605090222</v>
+        <v>4.3355</v>
       </c>
     </row>
     <row r="302">
@@ -16281,10 +16269,10 @@
         <v>1.06</v>
       </c>
       <c r="I302" t="n">
-        <v>-0.1074390778697383</v>
+        <v>0.2153</v>
       </c>
       <c r="J302" t="n">
-        <v>-2.578537868873719</v>
+        <v>5.1672</v>
       </c>
     </row>
     <row r="303">
@@ -16321,10 +16309,10 @@
         <v>0.99</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.1751194995710907</v>
+        <v>0.0392</v>
       </c>
       <c r="J303" t="n">
-        <v>-4.202867989706178</v>
+        <v>0.9408</v>
       </c>
     </row>
     <row r="304">
@@ -16361,10 +16349,10 @@
         <v>0.78</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.443412844477683</v>
+        <v>-0.3682</v>
       </c>
       <c r="J304" t="n">
-        <v>-10.64190826746439</v>
+        <v>-8.8368</v>
       </c>
     </row>
     <row r="305">
@@ -16401,10 +16389,10 @@
         <v>0.72</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.5020865593376834</v>
+        <v>-0.4577</v>
       </c>
       <c r="J305" t="n">
-        <v>-12.0500774241044</v>
+        <v>-10.9848</v>
       </c>
     </row>
     <row r="306">
@@ -16441,10 +16429,10 @@
         <v>0.7</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.5198015160929781</v>
+        <v>-0.4859</v>
       </c>
       <c r="J306" t="n">
-        <v>-12.47523638623147</v>
+        <v>-11.6616</v>
       </c>
     </row>
     <row r="307">
@@ -16481,10 +16469,10 @@
         <v>1.5</v>
       </c>
       <c r="I307" t="n">
-        <v>0.3888903510299739</v>
+        <v>1.1958</v>
       </c>
       <c r="J307" t="n">
-        <v>9.333368424719374</v>
+        <v>28.6992</v>
       </c>
     </row>
     <row r="308">
@@ -16521,10 +16509,10 @@
         <v>1.31</v>
       </c>
       <c r="I308" t="n">
-        <v>0.279169812371077</v>
+        <v>0.7829</v>
       </c>
       <c r="J308" t="n">
-        <v>6.700075496905847</v>
+        <v>18.7896</v>
       </c>
     </row>
     <row r="309">
@@ -16561,10 +16549,10 @@
         <v>1.29</v>
       </c>
       <c r="I309" t="n">
-        <v>0.2637295767614334</v>
+        <v>0.7336</v>
       </c>
       <c r="J309" t="n">
-        <v>6.329509842274403</v>
+        <v>17.6064</v>
       </c>
     </row>
     <row r="310">
@@ -16601,10 +16589,10 @@
         <v>1.12</v>
       </c>
       <c r="I310" t="n">
-        <v>0.118104257458084</v>
+        <v>0.2678</v>
       </c>
       <c r="J310" t="n">
-        <v>2.834502178994016</v>
+        <v>6.4272</v>
       </c>
     </row>
     <row r="311">
@@ -16641,10 +16629,10 @@
         <v>1.05</v>
       </c>
       <c r="I311" t="n">
-        <v>0.07379165300420264</v>
+        <v>0.0625</v>
       </c>
       <c r="J311" t="n">
-        <v>1.770999672100863</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="312">
@@ -16681,10 +16669,10 @@
         <v>1.2</v>
       </c>
       <c r="I312" t="n">
-        <v>0.1729249401826988</v>
+        <v>0.6287</v>
       </c>
       <c r="J312" t="n">
-        <v>6.916997607307952</v>
+        <v>25.148</v>
       </c>
     </row>
     <row r="313">
@@ -16721,10 +16709,10 @@
         <v>1.18</v>
       </c>
       <c r="I313" t="n">
-        <v>0.1605226498821165</v>
+        <v>0.5772</v>
       </c>
       <c r="J313" t="n">
-        <v>6.420905995284661</v>
+        <v>23.088</v>
       </c>
     </row>
     <row r="314">
@@ -16761,10 +16749,10 @@
         <v>1.1</v>
       </c>
       <c r="I314" t="n">
-        <v>0.1018433059648959</v>
+        <v>0.3503</v>
       </c>
       <c r="J314" t="n">
-        <v>4.073732238595836</v>
+        <v>14.012</v>
       </c>
     </row>
     <row r="315">
@@ -16801,10 +16789,10 @@
         <v>1.04</v>
       </c>
       <c r="I315" t="n">
-        <v>0.03042615154499778</v>
+        <v>0.1258</v>
       </c>
       <c r="J315" t="n">
-        <v>1.217046061799911</v>
+        <v>5.032</v>
       </c>
     </row>
     <row r="316">
@@ -16841,10 +16829,10 @@
         <v>0.8</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.4359641078014744</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="J316" t="n">
-        <v>-17.43856431205898</v>
+        <v>-27.64</v>
       </c>
     </row>
     <row r="317">
@@ -16881,10 +16869,10 @@
         <v>1.2</v>
       </c>
       <c r="I317" t="n">
-        <v>0.2278697258404191</v>
+        <v>0.3718</v>
       </c>
       <c r="J317" t="n">
-        <v>9.114789033616766</v>
+        <v>14.872</v>
       </c>
     </row>
     <row r="318">
@@ -16921,10 +16909,10 @@
         <v>1.17</v>
       </c>
       <c r="I318" t="n">
-        <v>0.1783072481270701</v>
+        <v>0.3274</v>
       </c>
       <c r="J318" t="n">
-        <v>7.132289925082803</v>
+        <v>13.096</v>
       </c>
     </row>
     <row r="319">
@@ -16961,10 +16949,10 @@
         <v>1.04</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.09290693643989373</v>
+        <v>0.0954</v>
       </c>
       <c r="J319" t="n">
-        <v>-3.716277457595749</v>
+        <v>3.816</v>
       </c>
     </row>
     <row r="320">
@@ -17001,10 +16989,10 @@
         <v>0.96</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.2341974818692941</v>
+        <v>-0.1277</v>
       </c>
       <c r="J320" t="n">
-        <v>-9.367899274771762</v>
+        <v>-5.108</v>
       </c>
     </row>
     <row r="321">
@@ -17041,10 +17029,10 @@
         <v>0.8</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.4015266070542382</v>
+        <v>-0.3911</v>
       </c>
       <c r="J321" t="n">
-        <v>-16.06106428216953</v>
+        <v>-15.644</v>
       </c>
     </row>
     <row r="322">
@@ -17081,10 +17069,10 @@
         <v>1.57</v>
       </c>
       <c r="I322" t="n">
-        <v>0.3434130958207062</v>
+        <v>1.3443</v>
       </c>
       <c r="J322" t="n">
-        <v>8.928740491338361</v>
+        <v>34.9518</v>
       </c>
     </row>
     <row r="323">
@@ -17121,10 +17109,10 @@
         <v>1.27</v>
       </c>
       <c r="I323" t="n">
-        <v>0.1986245507576738</v>
+        <v>0.6985</v>
       </c>
       <c r="J323" t="n">
-        <v>5.164238319699518</v>
+        <v>18.161</v>
       </c>
     </row>
     <row r="324">
@@ -17161,10 +17149,10 @@
         <v>1.22</v>
       </c>
       <c r="I324" t="n">
-        <v>0.1503923146064199</v>
+        <v>0.5505</v>
       </c>
       <c r="J324" t="n">
-        <v>3.910200179766918</v>
+        <v>14.313</v>
       </c>
     </row>
     <row r="325">
@@ -17201,10 +17189,10 @@
         <v>1.15</v>
       </c>
       <c r="I325" t="n">
-        <v>0.1003322615990935</v>
+        <v>0.3597</v>
       </c>
       <c r="J325" t="n">
-        <v>2.608638801576431</v>
+        <v>9.3522</v>
       </c>
     </row>
     <row r="326">
@@ -17241,10 +17229,10 @@
         <v>0.95</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.0482972459895943</v>
+        <v>-0.3386</v>
       </c>
       <c r="J326" t="n">
-        <v>-1.255728395729452</v>
+        <v>-8.803599999999999</v>
       </c>
     </row>
     <row r="327">
@@ -17281,10 +17269,10 @@
         <v>1</v>
       </c>
       <c r="I327" t="n">
-        <v>-0.135034195067347</v>
+        <v>0.0622</v>
       </c>
       <c r="J327" t="n">
-        <v>-3.510889071751022</v>
+        <v>1.6172</v>
       </c>
     </row>
     <row r="328">
@@ -17321,10 +17309,10 @@
         <v>0.92</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.2250101214953631</v>
+        <v>-0.122</v>
       </c>
       <c r="J328" t="n">
-        <v>-5.850263158879442</v>
+        <v>-3.172</v>
       </c>
     </row>
     <row r="329">
@@ -17361,10 +17349,10 @@
         <v>0.89</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.2668250743017125</v>
+        <v>-0.1805</v>
       </c>
       <c r="J329" t="n">
-        <v>-6.937451931844526</v>
+        <v>-4.693</v>
       </c>
     </row>
     <row r="330">
@@ -17401,10 +17389,10 @@
         <v>0.88</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.2854441935773642</v>
+        <v>-0.2021</v>
       </c>
       <c r="J330" t="n">
-        <v>-7.421549033011468</v>
+        <v>-5.2546</v>
       </c>
     </row>
     <row r="331">
@@ -17441,10 +17429,10 @@
         <v>0.7</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.4910374920562265</v>
+        <v>-0.4937</v>
       </c>
       <c r="J331" t="n">
-        <v>-12.76697479346189</v>
+        <v>-12.8362</v>
       </c>
     </row>
     <row r="332">
@@ -17481,10 +17469,10 @@
         <v>1.46</v>
       </c>
       <c r="I332" t="n">
-        <v>0.4302209395465859</v>
+        <v>0.7255</v>
       </c>
       <c r="J332" t="n">
-        <v>18.0692794609566</v>
+        <v>30.471</v>
       </c>
     </row>
     <row r="333">
@@ -17521,10 +17509,10 @@
         <v>1.03</v>
       </c>
       <c r="I333" t="n">
-        <v>-0.0160037244702568</v>
+        <v>0.1037</v>
       </c>
       <c r="J333" t="n">
-        <v>-0.6721564277507857</v>
+        <v>4.3554</v>
       </c>
     </row>
     <row r="334">
@@ -17561,10 +17549,10 @@
         <v>1</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.0629543036072705</v>
+        <v>0.0179</v>
       </c>
       <c r="J334" t="n">
-        <v>-2.644080751505361</v>
+        <v>0.7518</v>
       </c>
     </row>
     <row r="335">
@@ -17601,10 +17589,10 @@
         <v>0.7</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.4189332515731087</v>
+        <v>-0.5158</v>
       </c>
       <c r="J335" t="n">
-        <v>-17.59519656607057</v>
+        <v>-21.6636</v>
       </c>
     </row>
     <row r="336">
@@ -17641,10 +17629,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.4267810676172463</v>
+        <v>-0.5288</v>
       </c>
       <c r="J336" t="n">
-        <v>-17.92480483992434</v>
+        <v>-22.2096</v>
       </c>
     </row>
     <row r="337">
@@ -17681,10 +17669,10 @@
         <v>1.34</v>
       </c>
       <c r="I337" t="n">
-        <v>0.3424738946751132</v>
+        <v>0.9525</v>
       </c>
       <c r="J337" t="n">
-        <v>14.38390357635476</v>
+        <v>40.005</v>
       </c>
     </row>
     <row r="338">
@@ -17721,10 +17709,10 @@
         <v>1.26</v>
       </c>
       <c r="I338" t="n">
-        <v>0.2853632328066224</v>
+        <v>0.7699</v>
       </c>
       <c r="J338" t="n">
-        <v>11.98525577787814</v>
+        <v>32.3358</v>
       </c>
     </row>
     <row r="339">
@@ -17761,10 +17749,10 @@
         <v>1.15</v>
       </c>
       <c r="I339" t="n">
-        <v>0.1901041470109377</v>
+        <v>0.49</v>
       </c>
       <c r="J339" t="n">
-        <v>7.984374174459382</v>
+        <v>20.58</v>
       </c>
     </row>
     <row r="340">
@@ -17801,10 +17789,10 @@
         <v>0.91</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.1853810241679198</v>
+        <v>-0.403</v>
       </c>
       <c r="J340" t="n">
-        <v>-7.78600301505263</v>
+        <v>-16.926</v>
       </c>
     </row>
     <row r="341">
@@ -17841,10 +17829,10 @@
         <v>0.71</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.4120282974437595</v>
+        <v>-0.9042</v>
       </c>
       <c r="J341" t="n">
-        <v>-17.3051884926379</v>
+        <v>-37.9764</v>
       </c>
     </row>
     <row r="342">
@@ -17881,10 +17869,10 @@
         <v>1.65</v>
       </c>
       <c r="I342" t="n">
-        <v>0.5077306457234674</v>
+        <v>0.9195</v>
       </c>
       <c r="J342" t="n">
-        <v>14.72418872598055</v>
+        <v>26.6655</v>
       </c>
     </row>
     <row r="343">
@@ -17921,10 +17909,10 @@
         <v>1.18</v>
       </c>
       <c r="I343" t="n">
-        <v>0.1464445526585105</v>
+        <v>0.3431</v>
       </c>
       <c r="J343" t="n">
-        <v>4.246892027096806</v>
+        <v>9.9499</v>
       </c>
     </row>
     <row r="344">
@@ -17961,10 +17949,10 @@
         <v>0.87</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.3186833706626874</v>
+        <v>-0.2861</v>
       </c>
       <c r="J344" t="n">
-        <v>-9.241817749217933</v>
+        <v>-8.296900000000001</v>
       </c>
     </row>
     <row r="345">
@@ -18001,10 +17989,10 @@
         <v>0.84</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.3477676471721136</v>
+        <v>-0.3323</v>
       </c>
       <c r="J345" t="n">
-        <v>-10.08526176799129</v>
+        <v>-9.636699999999999</v>
       </c>
     </row>
     <row r="346">
@@ -18041,10 +18029,10 @@
         <v>0.62</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.5220879402468169</v>
+        <v>-0.626</v>
       </c>
       <c r="J346" t="n">
-        <v>-15.14055026715769</v>
+        <v>-18.154</v>
       </c>
     </row>
     <row r="347">
@@ -18081,10 +18069,10 @@
         <v>1.39</v>
       </c>
       <c r="I347" t="n">
-        <v>0.3773481912303876</v>
+        <v>1.0608</v>
       </c>
       <c r="J347" t="n">
-        <v>10.94309754568124</v>
+        <v>30.7632</v>
       </c>
     </row>
     <row r="348">
@@ -18121,10 +18109,10 @@
         <v>1.23</v>
       </c>
       <c r="I348" t="n">
-        <v>0.2605368883459857</v>
+        <v>0.6976</v>
       </c>
       <c r="J348" t="n">
-        <v>7.555569762033584</v>
+        <v>20.2304</v>
       </c>
     </row>
     <row r="349">
@@ -18161,10 +18149,10 @@
         <v>1.14</v>
       </c>
       <c r="I349" t="n">
-        <v>0.1748678751948838</v>
+        <v>0.4619</v>
       </c>
       <c r="J349" t="n">
-        <v>5.071168380651631</v>
+        <v>13.3951</v>
       </c>
     </row>
     <row r="350">
@@ -18201,10 +18189,10 @@
         <v>0.88</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.2344545339007039</v>
+        <v>-0.488</v>
       </c>
       <c r="J350" t="n">
-        <v>-6.799181483120412</v>
+        <v>-14.152</v>
       </c>
     </row>
     <row r="351">
@@ -18241,10 +18229,10 @@
         <v>0.73</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.3926288003875743</v>
+        <v>-0.8591</v>
       </c>
       <c r="J351" t="n">
-        <v>-11.38623521123965</v>
+        <v>-24.9139</v>
       </c>
     </row>
     <row r="352">
@@ -18281,10 +18269,10 @@
         <v>1.26</v>
       </c>
       <c r="I352" t="n">
-        <v>0.2780981559352056</v>
+        <v>0.7549</v>
       </c>
       <c r="J352" t="n">
-        <v>8.342944678056167</v>
+        <v>22.647</v>
       </c>
     </row>
     <row r="353">
@@ -18321,10 +18309,10 @@
         <v>1.19</v>
       </c>
       <c r="I353" t="n">
-        <v>0.2167384091532623</v>
+        <v>0.5806</v>
       </c>
       <c r="J353" t="n">
-        <v>6.502152274597869</v>
+        <v>17.418</v>
       </c>
     </row>
     <row r="354">
@@ -18361,10 +18349,10 @@
         <v>1.08</v>
       </c>
       <c r="I354" t="n">
-        <v>0.07095427835944534</v>
+        <v>0.2375</v>
       </c>
       <c r="J354" t="n">
-        <v>2.128628350783361</v>
+        <v>7.125</v>
       </c>
     </row>
     <row r="355">
@@ -18401,10 +18389,10 @@
         <v>1.05</v>
       </c>
       <c r="I355" t="n">
-        <v>0.03212608785970589</v>
+        <v>0.1353</v>
       </c>
       <c r="J355" t="n">
-        <v>0.9637826357911766</v>
+        <v>4.059</v>
       </c>
     </row>
     <row r="356">
@@ -18441,10 +18429,10 @@
         <v>0.92</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.1857334087533015</v>
+        <v>-0.3843</v>
       </c>
       <c r="J356" t="n">
-        <v>-5.572002262599044</v>
+        <v>-11.529</v>
       </c>
     </row>
     <row r="357">
@@ -18481,10 +18469,10 @@
         <v>1.38</v>
       </c>
       <c r="I357" t="n">
-        <v>0.3789918708881467</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="J357" t="n">
-        <v>11.3697561266444</v>
+        <v>18.885</v>
       </c>
     </row>
     <row r="358">
@@ -18521,10 +18509,10 @@
         <v>1.21</v>
       </c>
       <c r="I358" t="n">
-        <v>0.2255642260006552</v>
+        <v>0.4063</v>
       </c>
       <c r="J358" t="n">
-        <v>6.766926780019656</v>
+        <v>12.189</v>
       </c>
     </row>
     <row r="359">
@@ -18561,10 +18549,10 @@
         <v>0.83</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.3136630730344597</v>
+        <v>-0.3332</v>
       </c>
       <c r="J359" t="n">
-        <v>-9.409892191033792</v>
+        <v>-9.996</v>
       </c>
     </row>
     <row r="360">
@@ -18601,10 +18589,10 @@
         <v>0.77</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.3690412290527266</v>
+        <v>-0.4207</v>
       </c>
       <c r="J360" t="n">
-        <v>-11.0712368715818</v>
+        <v>-12.621</v>
       </c>
     </row>
     <row r="361">
@@ -18641,10 +18629,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.4344916776646978</v>
+        <v>-0.5288</v>
       </c>
       <c r="J361" t="n">
-        <v>-13.03475032994093</v>
+        <v>-15.864</v>
       </c>
     </row>
     <row r="362">
@@ -18681,10 +18669,10 @@
         <v>1.63</v>
       </c>
       <c r="I362" t="n">
-        <v>0.5778349385002215</v>
+        <v>1.4501</v>
       </c>
       <c r="J362" t="n">
-        <v>13.2902035855051</v>
+        <v>33.3523</v>
       </c>
     </row>
     <row r="363">
@@ -18721,10 +18709,10 @@
         <v>1.5</v>
       </c>
       <c r="I363" t="n">
-        <v>0.5006301202498756</v>
+        <v>1.1977</v>
       </c>
       <c r="J363" t="n">
-        <v>11.51449276574714</v>
+        <v>27.5471</v>
       </c>
     </row>
     <row r="364">
@@ -18761,10 +18749,10 @@
         <v>1.31</v>
       </c>
       <c r="I364" t="n">
-        <v>0.3529781121004485</v>
+        <v>0.7855</v>
       </c>
       <c r="J364" t="n">
-        <v>8.118496578310316</v>
+        <v>18.0665</v>
       </c>
     </row>
     <row r="365">
@@ -18801,10 +18789,10 @@
         <v>1.22</v>
       </c>
       <c r="I365" t="n">
-        <v>0.2331369000142644</v>
+        <v>0.5359</v>
       </c>
       <c r="J365" t="n">
-        <v>5.36214870032808</v>
+        <v>12.3257</v>
       </c>
     </row>
     <row r="366">
@@ -18841,10 +18829,10 @@
         <v>0.59</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.4100737881020635</v>
+        <v>-1.1918</v>
       </c>
       <c r="J366" t="n">
-        <v>-9.43169712634746</v>
+        <v>-27.4114</v>
       </c>
     </row>
     <row r="367">
@@ -18881,10 +18869,10 @@
         <v>1.4</v>
       </c>
       <c r="I367" t="n">
-        <v>0.190525830487483</v>
+        <v>0.6553</v>
       </c>
       <c r="J367" t="n">
-        <v>4.382094101212108</v>
+        <v>15.0719</v>
       </c>
     </row>
     <row r="368">
@@ -18921,10 +18909,10 @@
         <v>1.29</v>
       </c>
       <c r="I368" t="n">
-        <v>0.08093901844303464</v>
+        <v>0.5167</v>
       </c>
       <c r="J368" t="n">
-        <v>1.861597424189797</v>
+        <v>11.8841</v>
       </c>
     </row>
     <row r="369">
@@ -18961,10 +18949,10 @@
         <v>0.97</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.3325726448727231</v>
+        <v>-0.0746</v>
       </c>
       <c r="J369" t="n">
-        <v>-7.649170832072632</v>
+        <v>-1.7158</v>
       </c>
     </row>
     <row r="370">
@@ -19001,10 +18989,10 @@
         <v>0.66</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.6342030234854704</v>
+        <v>-0.5668</v>
       </c>
       <c r="J370" t="n">
-        <v>-14.58666954016582</v>
+        <v>-13.0364</v>
       </c>
     </row>
     <row r="371">
@@ -19041,10 +19029,10 @@
         <v>0.54</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.7123212064246378</v>
+        <v>-0.7138</v>
       </c>
       <c r="J371" t="n">
-        <v>-16.38338774776667</v>
+        <v>-16.4174</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7128/event_7128_evp_summary.xlsx
+++ b/database/event/7128/event_7128_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>5.761</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>3.4385</v>
       </c>
       <c r="D2" t="n">
         <v>1.906</v>
@@ -545,7 +545,7 @@
         <v>5.4279</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>3.2396</v>
       </c>
       <c r="D3" t="n">
         <v>1.7714</v>
@@ -591,7 +591,7 @@
         <v>5.2058</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>3.1071</v>
       </c>
       <c r="D4" t="n">
         <v>1.6817</v>
@@ -637,7 +637,7 @@
         <v>5.097</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>3.0421</v>
       </c>
       <c r="D5" t="n">
         <v>1.6377</v>
@@ -683,7 +683,7 @@
         <v>4.5973</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>2.7439</v>
       </c>
       <c r="D6" t="n">
         <v>1.4358</v>
@@ -729,7 +729,7 @@
         <v>4.097</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2.4453</v>
       </c>
       <c r="D7" t="n">
         <v>1.2337</v>
@@ -775,7 +775,7 @@
         <v>3.951</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2.3582</v>
       </c>
       <c r="D8" t="n">
         <v>1.1748</v>
@@ -821,7 +821,7 @@
         <v>3.7613</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2.2449</v>
       </c>
       <c r="D9" t="n">
         <v>1.0981</v>
@@ -867,7 +867,7 @@
         <v>3.4123</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>2.0366</v>
       </c>
       <c r="D10" t="n">
         <v>0.9571</v>
@@ -913,7 +913,7 @@
         <v>3.1476</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1.8786</v>
       </c>
       <c r="D11" t="n">
         <v>0.8502</v>
@@ -959,7 +959,7 @@
         <v>2.9742</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1.7752</v>
       </c>
       <c r="D12" t="n">
         <v>0.7801</v>
@@ -1005,7 +1005,7 @@
         <v>2.969</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1.772</v>
       </c>
       <c r="D13" t="n">
         <v>0.778</v>
@@ -1051,7 +1051,7 @@
         <v>2.2785</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1.3599</v>
       </c>
       <c r="D14" t="n">
         <v>0.4991</v>
@@ -1097,7 +1097,7 @@
         <v>1.7001</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1.0147</v>
       </c>
       <c r="D15" t="n">
         <v>0.2654</v>
@@ -1143,7 +1143,7 @@
         <v>1.593</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.9508</v>
       </c>
       <c r="D16" t="n">
         <v>0.2222</v>
@@ -1189,7 +1189,7 @@
         <v>1.5058</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.8987000000000001</v>
       </c>
       <c r="D17" t="n">
         <v>0.1869</v>
@@ -1235,7 +1235,7 @@
         <v>1.4785</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.8824</v>
       </c>
       <c r="D18" t="n">
         <v>0.1759</v>
@@ -1281,7 +1281,7 @@
         <v>1.3734</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.8197</v>
       </c>
       <c r="D19" t="n">
         <v>0.1335</v>
@@ -1327,7 +1327,7 @@
         <v>1.3455</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.8031</v>
       </c>
       <c r="D20" t="n">
         <v>0.1222</v>
@@ -1373,7 +1373,7 @@
         <v>1.1777</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.7029</v>
       </c>
       <c r="D21" t="n">
         <v>0.0544</v>
@@ -1419,7 +1419,7 @@
         <v>1.0412</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.6214</v>
       </c>
       <c r="D22" t="n">
         <v>-0.0007</v>
@@ -1465,7 +1465,7 @@
         <v>0.8954</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.5344</v>
       </c>
       <c r="D23" t="n">
         <v>-0.0596</v>
@@ -1511,7 +1511,7 @@
         <v>0.8622</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="D24" t="n">
         <v>-0.0731</v>
@@ -1557,7 +1557,7 @@
         <v>0.8223</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.4908</v>
       </c>
       <c r="D25" t="n">
         <v>-0.0892</v>
@@ -1603,7 +1603,7 @@
         <v>0.7727000000000001</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.4612</v>
       </c>
       <c r="D26" t="n">
         <v>-0.1092</v>
@@ -1649,7 +1649,7 @@
         <v>0.7719</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.4607</v>
       </c>
       <c r="D27" t="n">
         <v>-0.1095</v>
@@ -1695,7 +1695,7 @@
         <v>0.7548</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.4505</v>
       </c>
       <c r="D28" t="n">
         <v>-0.1164</v>
@@ -1741,7 +1741,7 @@
         <v>0.6974</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.4162</v>
       </c>
       <c r="D29" t="n">
         <v>-0.1396</v>
@@ -1787,7 +1787,7 @@
         <v>0.6746</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.4026</v>
       </c>
       <c r="D30" t="n">
         <v>-0.1488</v>
@@ -1833,7 +1833,7 @@
         <v>0.634</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.3784</v>
       </c>
       <c r="D31" t="n">
         <v>-0.1652</v>
@@ -1879,7 +1879,7 @@
         <v>0.4706</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.2809</v>
       </c>
       <c r="D32" t="n">
         <v>-0.2313</v>
@@ -1925,7 +1925,7 @@
         <v>0.4551</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.2716</v>
       </c>
       <c r="D33" t="n">
         <v>-0.2375</v>
@@ -1971,7 +1971,7 @@
         <v>0.4468</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.2667</v>
       </c>
       <c r="D34" t="n">
         <v>-0.2409</v>
@@ -2017,7 +2017,7 @@
         <v>0.3932</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.2347</v>
       </c>
       <c r="D35" t="n">
         <v>-0.2625</v>
@@ -2063,7 +2063,7 @@
         <v>0.3907</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.2332</v>
       </c>
       <c r="D36" t="n">
         <v>-0.2635</v>
@@ -2109,7 +2109,7 @@
         <v>0.3629</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.2166</v>
       </c>
       <c r="D37" t="n">
         <v>-0.2748</v>
@@ -2155,7 +2155,7 @@
         <v>0.2899</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.173</v>
       </c>
       <c r="D38" t="n">
         <v>-0.3042</v>
@@ -2201,7 +2201,7 @@
         <v>0.2498</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.1491</v>
       </c>
       <c r="D39" t="n">
         <v>-0.3204</v>
@@ -2247,7 +2247,7 @@
         <v>0.1469</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.0877</v>
       </c>
       <c r="D40" t="n">
         <v>-0.362</v>
@@ -2293,7 +2293,7 @@
         <v>0.1415</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="D41" t="n">
         <v>-0.3642</v>
@@ -2339,7 +2339,7 @@
         <v>0.1265</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.0755</v>
       </c>
       <c r="D42" t="n">
         <v>-0.3703</v>
@@ -2385,7 +2385,7 @@
         <v>0.096</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.0573</v>
       </c>
       <c r="D43" t="n">
         <v>-0.3826</v>
@@ -2431,7 +2431,7 @@
         <v>0.0559</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.0334</v>
       </c>
       <c r="D44" t="n">
         <v>-0.3988</v>
@@ -2477,7 +2477,7 @@
         <v>-0.0843</v>
       </c>
       <c r="C45" t="n">
-        <v>-0</v>
+        <v>-0.0503</v>
       </c>
       <c r="D45" t="n">
         <v>-0.4554</v>
@@ -2523,7 +2523,7 @@
         <v>-0.0877</v>
       </c>
       <c r="C46" t="n">
-        <v>-0</v>
+        <v>-0.0523</v>
       </c>
       <c r="D46" t="n">
         <v>-0.4568</v>
@@ -2569,7 +2569,7 @@
         <v>-0.09569999999999999</v>
       </c>
       <c r="C47" t="n">
-        <v>-0</v>
+        <v>-0.0571</v>
       </c>
       <c r="D47" t="n">
         <v>-0.46</v>
@@ -2615,7 +2615,7 @@
         <v>-0.1378</v>
       </c>
       <c r="C48" t="n">
-        <v>-0</v>
+        <v>-0.0822</v>
       </c>
       <c r="D48" t="n">
         <v>-0.477</v>
@@ -2661,7 +2661,7 @@
         <v>-0.1605</v>
       </c>
       <c r="C49" t="n">
-        <v>-0</v>
+        <v>-0.0958</v>
       </c>
       <c r="D49" t="n">
         <v>-0.4862</v>
@@ -2707,7 +2707,7 @@
         <v>-0.1804</v>
       </c>
       <c r="C50" t="n">
-        <v>-0</v>
+        <v>-0.1077</v>
       </c>
       <c r="D50" t="n">
         <v>-0.4942</v>
@@ -2753,7 +2753,7 @@
         <v>-0.2484</v>
       </c>
       <c r="C51" t="n">
-        <v>-0</v>
+        <v>-0.1483</v>
       </c>
       <c r="D51" t="n">
         <v>-0.5217000000000001</v>
@@ -2799,7 +2799,7 @@
         <v>-0.2719</v>
       </c>
       <c r="C52" t="n">
-        <v>-0</v>
+        <v>-0.1623</v>
       </c>
       <c r="D52" t="n">
         <v>-0.5312</v>
@@ -2845,7 +2845,7 @@
         <v>-0.3213</v>
       </c>
       <c r="C53" t="n">
-        <v>-0</v>
+        <v>-0.1918</v>
       </c>
       <c r="D53" t="n">
         <v>-0.5512</v>
@@ -2891,7 +2891,7 @@
         <v>-0.3233</v>
       </c>
       <c r="C54" t="n">
-        <v>-0</v>
+        <v>-0.193</v>
       </c>
       <c r="D54" t="n">
         <v>-0.552</v>
@@ -2937,7 +2937,7 @@
         <v>-0.3289</v>
       </c>
       <c r="C55" t="n">
-        <v>-0</v>
+        <v>-0.1963</v>
       </c>
       <c r="D55" t="n">
         <v>-0.5542</v>
@@ -2983,7 +2983,7 @@
         <v>-0.3298</v>
       </c>
       <c r="C56" t="n">
-        <v>-0</v>
+        <v>-0.1968</v>
       </c>
       <c r="D56" t="n">
         <v>-0.5546</v>
@@ -3029,7 +3029,7 @@
         <v>-0.3983</v>
       </c>
       <c r="C57" t="n">
-        <v>-0</v>
+        <v>-0.2377</v>
       </c>
       <c r="D57" t="n">
         <v>-0.5823</v>
@@ -3075,7 +3075,7 @@
         <v>-0.4078</v>
       </c>
       <c r="C58" t="n">
-        <v>-0</v>
+        <v>-0.2434</v>
       </c>
       <c r="D58" t="n">
         <v>-0.5861</v>
@@ -3121,7 +3121,7 @@
         <v>-0.4309</v>
       </c>
       <c r="C59" t="n">
-        <v>-0</v>
+        <v>-0.2572</v>
       </c>
       <c r="D59" t="n">
         <v>-0.5954</v>
@@ -3167,7 +3167,7 @@
         <v>-0.4378</v>
       </c>
       <c r="C60" t="n">
-        <v>-0</v>
+        <v>-0.2613</v>
       </c>
       <c r="D60" t="n">
         <v>-0.5982</v>
@@ -3213,7 +3213,7 @@
         <v>-0.5766</v>
       </c>
       <c r="C61" t="n">
-        <v>-0</v>
+        <v>-0.3441</v>
       </c>
       <c r="D61" t="n">
         <v>-0.6543</v>
@@ -3259,7 +3259,7 @@
         <v>-0.6081</v>
       </c>
       <c r="C62" t="n">
-        <v>-0</v>
+        <v>-0.3629</v>
       </c>
       <c r="D62" t="n">
         <v>-0.667</v>
@@ -3305,7 +3305,7 @@
         <v>-0.6263</v>
       </c>
       <c r="C63" t="n">
-        <v>-0</v>
+        <v>-0.3738</v>
       </c>
       <c r="D63" t="n">
         <v>-0.6744</v>
@@ -3351,7 +3351,7 @@
         <v>-0.6573</v>
       </c>
       <c r="C64" t="n">
-        <v>-0</v>
+        <v>-0.3923</v>
       </c>
       <c r="D64" t="n">
         <v>-0.6869</v>
@@ -3397,7 +3397,7 @@
         <v>-0.7004</v>
       </c>
       <c r="C65" t="n">
-        <v>-0</v>
+        <v>-0.418</v>
       </c>
       <c r="D65" t="n">
         <v>-0.7043</v>
@@ -3443,7 +3443,7 @@
         <v>-0.7111</v>
       </c>
       <c r="C66" t="n">
-        <v>-0</v>
+        <v>-0.4244</v>
       </c>
       <c r="D66" t="n">
         <v>-0.7086</v>
@@ -3489,7 +3489,7 @@
         <v>-0.7645</v>
       </c>
       <c r="C67" t="n">
-        <v>-0</v>
+        <v>-0.4563</v>
       </c>
       <c r="D67" t="n">
         <v>-0.7302</v>
@@ -3535,7 +3535,7 @@
         <v>-0.8018999999999999</v>
       </c>
       <c r="C68" t="n">
-        <v>-0</v>
+        <v>-0.4786</v>
       </c>
       <c r="D68" t="n">
         <v>-0.7453</v>
@@ -3581,7 +3581,7 @@
         <v>-0.8426</v>
       </c>
       <c r="C69" t="n">
-        <v>-0</v>
+        <v>-0.5029</v>
       </c>
       <c r="D69" t="n">
         <v>-0.7618</v>
@@ -3627,7 +3627,7 @@
         <v>-0.8484</v>
       </c>
       <c r="C70" t="n">
-        <v>-0</v>
+        <v>-0.5064</v>
       </c>
       <c r="D70" t="n">
         <v>-0.7641</v>
@@ -3673,7 +3673,7 @@
         <v>-0.8608</v>
       </c>
       <c r="C71" t="n">
-        <v>-0</v>
+        <v>-0.5138</v>
       </c>
       <c r="D71" t="n">
         <v>-0.7691</v>
@@ -3719,7 +3719,7 @@
         <v>-0.8979</v>
       </c>
       <c r="C72" t="n">
-        <v>-0</v>
+        <v>-0.5359</v>
       </c>
       <c r="D72" t="n">
         <v>-0.7841</v>
@@ -3765,7 +3765,7 @@
         <v>-1</v>
       </c>
       <c r="C73" t="n">
-        <v>-0</v>
+        <v>-0.5969</v>
       </c>
       <c r="D73" t="n">
         <v>-0.8253</v>
@@ -3811,7 +3811,7 @@
         <v>-1</v>
       </c>
       <c r="C74" t="n">
-        <v>-0</v>
+        <v>-0.5969</v>
       </c>
       <c r="D74" t="n">
         <v>-0.8253</v>
@@ -3857,7 +3857,7 @@
         <v>-1</v>
       </c>
       <c r="C75" t="n">
-        <v>-0</v>
+        <v>-0.5969</v>
       </c>
       <c r="D75" t="n">
         <v>-0.8253</v>
@@ -3903,7 +3903,7 @@
         <v>-1.631</v>
       </c>
       <c r="C76" t="n">
-        <v>-0</v>
+        <v>-0.9735</v>
       </c>
       <c r="D76" t="n">
         <v>-1.0803</v>
@@ -3949,7 +3949,7 @@
         <v>-1.8003</v>
       </c>
       <c r="C77" t="n">
-        <v>-0</v>
+        <v>-1.0745</v>
       </c>
       <c r="D77" t="n">
         <v>-1.1486</v>
@@ -3995,7 +3995,7 @@
         <v>-1.891</v>
       </c>
       <c r="C78" t="n">
-        <v>-0</v>
+        <v>-1.1286</v>
       </c>
       <c r="D78" t="n">
         <v>-1.1853</v>
@@ -4041,7 +4041,7 @@
         <v>-2.6819</v>
       </c>
       <c r="C79" t="n">
-        <v>-0</v>
+        <v>-1.6007</v>
       </c>
       <c r="D79" t="n">
         <v>-1.5048</v>
@@ -4087,7 +4087,7 @@
         <v>-2.829</v>
       </c>
       <c r="C80" t="n">
-        <v>-0</v>
+        <v>-1.6885</v>
       </c>
       <c r="D80" t="n">
         <v>-1.5642</v>
@@ -4133,7 +4133,7 @@
         <v>-3.4438</v>
       </c>
       <c r="C81" t="n">
-        <v>-0</v>
+        <v>-2.0554</v>
       </c>
       <c r="D81" t="n">
         <v>-1.8126</v>

--- a/database/event/7128/event_7128_evp_summary.xlsx
+++ b/database/event/7128/event_7128_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>3.4385</v>
       </c>
       <c r="D2" t="n">
-        <v>1.906</v>
+        <v>1.8513</v>
       </c>
       <c r="E2" t="n">
         <v>5.761</v>
@@ -548,7 +548,7 @@
         <v>3.2396</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7714</v>
+        <v>1.7186</v>
       </c>
       <c r="E3" t="n">
         <v>5.4279</v>
@@ -594,7 +594,7 @@
         <v>3.1071</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6817</v>
+        <v>1.6301</v>
       </c>
       <c r="E4" t="n">
         <v>5.2058</v>
@@ -640,7 +640,7 @@
         <v>3.0421</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6377</v>
+        <v>1.5867</v>
       </c>
       <c r="E5" t="n">
         <v>5.097</v>
@@ -686,7 +686,7 @@
         <v>2.7439</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4358</v>
+        <v>1.3877</v>
       </c>
       <c r="E6" t="n">
         <v>4.5973</v>
@@ -732,7 +732,7 @@
         <v>2.4453</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2337</v>
+        <v>1.1883</v>
       </c>
       <c r="E7" t="n">
         <v>4.097</v>
@@ -778,7 +778,7 @@
         <v>2.3582</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1748</v>
+        <v>1.1302</v>
       </c>
       <c r="E8" t="n">
         <v>3.951</v>
@@ -824,7 +824,7 @@
         <v>2.2449</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0981</v>
+        <v>1.0546</v>
       </c>
       <c r="E9" t="n">
         <v>3.7613</v>
@@ -870,7 +870,7 @@
         <v>2.0366</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9571</v>
+        <v>0.9156</v>
       </c>
       <c r="E10" t="n">
         <v>3.4123</v>
@@ -916,7 +916,7 @@
         <v>1.8786</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8502</v>
+        <v>0.8101</v>
       </c>
       <c r="E11" t="n">
         <v>3.1476</v>
@@ -962,7 +962,7 @@
         <v>1.7752</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7801</v>
+        <v>0.741</v>
       </c>
       <c r="E12" t="n">
         <v>2.9742</v>
@@ -1008,7 +1008,7 @@
         <v>1.772</v>
       </c>
       <c r="D13" t="n">
-        <v>0.778</v>
+        <v>0.7389</v>
       </c>
       <c r="E13" t="n">
         <v>2.969</v>
@@ -1054,7 +1054,7 @@
         <v>1.3599</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4991</v>
+        <v>0.4638</v>
       </c>
       <c r="E14" t="n">
         <v>2.2785</v>
@@ -1100,7 +1100,7 @@
         <v>1.0147</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2654</v>
+        <v>0.2334</v>
       </c>
       <c r="E15" t="n">
         <v>1.7001</v>
@@ -1146,7 +1146,7 @@
         <v>0.9508</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2222</v>
+        <v>0.1907</v>
       </c>
       <c r="E16" t="n">
         <v>1.593</v>
@@ -1192,7 +1192,7 @@
         <v>0.8987000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1869</v>
+        <v>0.156</v>
       </c>
       <c r="E17" t="n">
         <v>1.5058</v>
@@ -1238,7 +1238,7 @@
         <v>0.8824</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1759</v>
+        <v>0.1451</v>
       </c>
       <c r="E18" t="n">
         <v>1.4785</v>
@@ -1284,7 +1284,7 @@
         <v>0.8197</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1335</v>
+        <v>0.1033</v>
       </c>
       <c r="E19" t="n">
         <v>1.3734</v>
@@ -1330,7 +1330,7 @@
         <v>0.8031</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1222</v>
+        <v>0.0921</v>
       </c>
       <c r="E20" t="n">
         <v>1.3455</v>
@@ -1376,7 +1376,7 @@
         <v>0.7029</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0544</v>
+        <v>0.0253</v>
       </c>
       <c r="E21" t="n">
         <v>1.1777</v>
@@ -1422,7 +1422,7 @@
         <v>0.6214</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0007</v>
+        <v>-0.0291</v>
       </c>
       <c r="E22" t="n">
         <v>1.0412</v>
@@ -1468,7 +1468,7 @@
         <v>0.5344</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0596</v>
+        <v>-0.0872</v>
       </c>
       <c r="E23" t="n">
         <v>0.8954</v>
@@ -1514,7 +1514,7 @@
         <v>0.5145999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0731</v>
+        <v>-0.1004</v>
       </c>
       <c r="E24" t="n">
         <v>0.8622</v>
@@ -1560,7 +1560,7 @@
         <v>0.4908</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0892</v>
+        <v>-0.1163</v>
       </c>
       <c r="E25" t="n">
         <v>0.8223</v>
@@ -1606,7 +1606,7 @@
         <v>0.4612</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.1092</v>
+        <v>-0.1361</v>
       </c>
       <c r="E26" t="n">
         <v>0.7727000000000001</v>
@@ -1652,7 +1652,7 @@
         <v>0.4607</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.1095</v>
+        <v>-0.1364</v>
       </c>
       <c r="E27" t="n">
         <v>0.7719</v>
@@ -1698,7 +1698,7 @@
         <v>0.4505</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.1164</v>
+        <v>-0.1432</v>
       </c>
       <c r="E28" t="n">
         <v>0.7548</v>
@@ -1744,7 +1744,7 @@
         <v>0.4162</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.1396</v>
+        <v>-0.1661</v>
       </c>
       <c r="E29" t="n">
         <v>0.6974</v>
@@ -1790,7 +1790,7 @@
         <v>0.4026</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1488</v>
+        <v>-0.1751</v>
       </c>
       <c r="E30" t="n">
         <v>0.6746</v>
@@ -1836,7 +1836,7 @@
         <v>0.3784</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.1652</v>
+        <v>-0.1913</v>
       </c>
       <c r="E31" t="n">
         <v>0.634</v>
@@ -1882,7 +1882,7 @@
         <v>0.2809</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.2313</v>
+        <v>-0.2564</v>
       </c>
       <c r="E32" t="n">
         <v>0.4706</v>
@@ -1928,7 +1928,7 @@
         <v>0.2716</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.2375</v>
+        <v>-0.2626</v>
       </c>
       <c r="E33" t="n">
         <v>0.4551</v>
@@ -1974,7 +1974,7 @@
         <v>0.2667</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.2409</v>
+        <v>-0.2659</v>
       </c>
       <c r="E34" t="n">
         <v>0.4468</v>
@@ -2020,7 +2020,7 @@
         <v>0.2347</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2625</v>
+        <v>-0.2873</v>
       </c>
       <c r="E35" t="n">
         <v>0.3932</v>
@@ -2066,7 +2066,7 @@
         <v>0.2332</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.2635</v>
+        <v>-0.2883</v>
       </c>
       <c r="E36" t="n">
         <v>0.3907</v>
@@ -2112,7 +2112,7 @@
         <v>0.2166</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2748</v>
+        <v>-0.2993</v>
       </c>
       <c r="E37" t="n">
         <v>0.3629</v>
@@ -2158,7 +2158,7 @@
         <v>0.173</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.3042</v>
+        <v>-0.3284</v>
       </c>
       <c r="E38" t="n">
         <v>0.2899</v>
@@ -2204,7 +2204,7 @@
         <v>0.1491</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.3204</v>
+        <v>-0.3444</v>
       </c>
       <c r="E39" t="n">
         <v>0.2498</v>
@@ -2250,7 +2250,7 @@
         <v>0.0877</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.362</v>
+        <v>-0.3854</v>
       </c>
       <c r="E40" t="n">
         <v>0.1469</v>
@@ -2296,7 +2296,7 @@
         <v>0.08450000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.3642</v>
+        <v>-0.3875</v>
       </c>
       <c r="E41" t="n">
         <v>0.1415</v>
@@ -2342,7 +2342,7 @@
         <v>0.0755</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3703</v>
+        <v>-0.3935</v>
       </c>
       <c r="E42" t="n">
         <v>0.1265</v>
@@ -2388,7 +2388,7 @@
         <v>0.0573</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3826</v>
+        <v>-0.4057</v>
       </c>
       <c r="E43" t="n">
         <v>0.096</v>
@@ -2434,7 +2434,7 @@
         <v>0.0334</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3988</v>
+        <v>-0.4216</v>
       </c>
       <c r="E44" t="n">
         <v>0.0559</v>
@@ -2480,7 +2480,7 @@
         <v>-0.0503</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.4554</v>
+        <v>-0.4775</v>
       </c>
       <c r="E45" t="n">
         <v>-0.0843</v>
@@ -2526,7 +2526,7 @@
         <v>-0.0523</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.4568</v>
+        <v>-0.4789</v>
       </c>
       <c r="E46" t="n">
         <v>-0.0877</v>
@@ -2572,7 +2572,7 @@
         <v>-0.0571</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.46</v>
+        <v>-0.482</v>
       </c>
       <c r="E47" t="n">
         <v>-0.09569999999999999</v>
@@ -2618,7 +2618,7 @@
         <v>-0.0822</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.477</v>
+        <v>-0.4988</v>
       </c>
       <c r="E48" t="n">
         <v>-0.1378</v>
@@ -2664,7 +2664,7 @@
         <v>-0.0958</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4862</v>
+        <v>-0.5079</v>
       </c>
       <c r="E49" t="n">
         <v>-0.1605</v>
@@ -2710,7 +2710,7 @@
         <v>-0.1077</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4942</v>
+        <v>-0.5158</v>
       </c>
       <c r="E50" t="n">
         <v>-0.1804</v>
@@ -2756,7 +2756,7 @@
         <v>-0.1483</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.5217000000000001</v>
+        <v>-0.5429</v>
       </c>
       <c r="E51" t="n">
         <v>-0.2484</v>
@@ -2802,7 +2802,7 @@
         <v>-0.1623</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5312</v>
+        <v>-0.5522</v>
       </c>
       <c r="E52" t="n">
         <v>-0.2719</v>
@@ -2848,7 +2848,7 @@
         <v>-0.1918</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5512</v>
+        <v>-0.5719</v>
       </c>
       <c r="E53" t="n">
         <v>-0.3213</v>
@@ -2894,7 +2894,7 @@
         <v>-0.193</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.552</v>
+        <v>-0.5727</v>
       </c>
       <c r="E54" t="n">
         <v>-0.3233</v>
@@ -2940,7 +2940,7 @@
         <v>-0.1963</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5542</v>
+        <v>-0.5749</v>
       </c>
       <c r="E55" t="n">
         <v>-0.3289</v>
@@ -2986,7 +2986,7 @@
         <v>-0.1968</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5546</v>
+        <v>-0.5753</v>
       </c>
       <c r="E56" t="n">
         <v>-0.3298</v>
@@ -3032,7 +3032,7 @@
         <v>-0.2377</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5823</v>
+        <v>-0.6026</v>
       </c>
       <c r="E57" t="n">
         <v>-0.3983</v>
@@ -3078,7 +3078,7 @@
         <v>-0.2434</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5861</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="E58" t="n">
         <v>-0.4078</v>
@@ -3124,7 +3124,7 @@
         <v>-0.2572</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5954</v>
+        <v>-0.6156</v>
       </c>
       <c r="E59" t="n">
         <v>-0.4309</v>
@@ -3170,7 +3170,7 @@
         <v>-0.2613</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5982</v>
+        <v>-0.6183</v>
       </c>
       <c r="E60" t="n">
         <v>-0.4378</v>
@@ -3216,7 +3216,7 @@
         <v>-0.3441</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6543</v>
+        <v>-0.6736</v>
       </c>
       <c r="E61" t="n">
         <v>-0.5766</v>
@@ -3262,7 +3262,7 @@
         <v>-0.3629</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.667</v>
+        <v>-0.6862</v>
       </c>
       <c r="E62" t="n">
         <v>-0.6081</v>
@@ -3308,7 +3308,7 @@
         <v>-0.3738</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6744</v>
+        <v>-0.6934</v>
       </c>
       <c r="E63" t="n">
         <v>-0.6263</v>
@@ -3354,7 +3354,7 @@
         <v>-0.3923</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6869</v>
+        <v>-0.7058</v>
       </c>
       <c r="E64" t="n">
         <v>-0.6573</v>
@@ -3400,7 +3400,7 @@
         <v>-0.418</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7043</v>
+        <v>-0.7229</v>
       </c>
       <c r="E65" t="n">
         <v>-0.7004</v>
@@ -3446,7 +3446,7 @@
         <v>-0.4244</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7086</v>
+        <v>-0.7272</v>
       </c>
       <c r="E66" t="n">
         <v>-0.7111</v>
@@ -3492,7 +3492,7 @@
         <v>-0.4563</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7302</v>
+        <v>-0.7485000000000001</v>
       </c>
       <c r="E67" t="n">
         <v>-0.7645</v>
@@ -3538,7 +3538,7 @@
         <v>-0.4786</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.7453</v>
+        <v>-0.7634</v>
       </c>
       <c r="E68" t="n">
         <v>-0.8018999999999999</v>
@@ -3584,7 +3584,7 @@
         <v>-0.5029</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.7618</v>
+        <v>-0.7796</v>
       </c>
       <c r="E69" t="n">
         <v>-0.8426</v>
@@ -3630,7 +3630,7 @@
         <v>-0.5064</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.7641</v>
+        <v>-0.7819</v>
       </c>
       <c r="E70" t="n">
         <v>-0.8484</v>
@@ -3676,7 +3676,7 @@
         <v>-0.5138</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.7691</v>
+        <v>-0.7869</v>
       </c>
       <c r="E71" t="n">
         <v>-0.8608</v>
@@ -3722,7 +3722,7 @@
         <v>-0.5359</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.7841</v>
+        <v>-0.8016</v>
       </c>
       <c r="E72" t="n">
         <v>-0.8979</v>
@@ -3768,7 +3768,7 @@
         <v>-0.5969</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.8253</v>
+        <v>-0.8423</v>
       </c>
       <c r="E73" t="n">
         <v>-1</v>
@@ -3814,7 +3814,7 @@
         <v>-0.5969</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.8253</v>
+        <v>-0.8423</v>
       </c>
       <c r="E74" t="n">
         <v>-1</v>
@@ -3860,7 +3860,7 @@
         <v>-0.5969</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.8253</v>
+        <v>-0.8423</v>
       </c>
       <c r="E75" t="n">
         <v>-1</v>
@@ -3906,7 +3906,7 @@
         <v>-0.9735</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0803</v>
+        <v>-1.0937</v>
       </c>
       <c r="E76" t="n">
         <v>-1.631</v>
@@ -3952,7 +3952,7 @@
         <v>-1.0745</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1486</v>
+        <v>-1.1612</v>
       </c>
       <c r="E77" t="n">
         <v>-1.8003</v>
@@ -3998,7 +3998,7 @@
         <v>-1.1286</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.1853</v>
+        <v>-1.1973</v>
       </c>
       <c r="E78" t="n">
         <v>-1.891</v>
@@ -4044,7 +4044,7 @@
         <v>-1.6007</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.5048</v>
+        <v>-1.5124</v>
       </c>
       <c r="E79" t="n">
         <v>-2.6819</v>
@@ -4090,7 +4090,7 @@
         <v>-1.6885</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.5642</v>
+        <v>-1.571</v>
       </c>
       <c r="E80" t="n">
         <v>-2.829</v>
@@ -4136,7 +4136,7 @@
         <v>-2.0554</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.8126</v>
+        <v>-1.8159</v>
       </c>
       <c r="E81" t="n">
         <v>-3.4438</v>

--- a/database/event/7128/event_7128_evp_summary.xlsx
+++ b/database/event/7128/event_7128_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.761</v>
+        <v>5.9144</v>
       </c>
       <c r="C2" t="n">
-        <v>3.4385</v>
+        <v>3.53</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8513</v>
+        <v>2.032</v>
       </c>
       <c r="E2" t="n">
-        <v>5.761</v>
+        <v>5.9144</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7545</v>
+        <v>2.3444</v>
       </c>
       <c r="G2" t="n">
-        <v>4.0065</v>
+        <v>3.57</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7545</v>
+        <v>2.3444</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7545</v>
+        <v>2.3444</v>
       </c>
       <c r="J2" t="n">
-        <v>4.0065</v>
+        <v>3.57</v>
       </c>
       <c r="K2" t="n">
         <v>47</v>
@@ -529,7 +529,7 @@
         <v>209</v>
       </c>
       <c r="M2" t="n">
-        <v>5.761</v>
+        <v>5.9144</v>
       </c>
       <c r="N2" t="n">
         <v>256</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.4279</v>
+        <v>4.7052</v>
       </c>
       <c r="C3" t="n">
-        <v>3.2396</v>
+        <v>2.8083</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7186</v>
+        <v>1.4861</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4279</v>
+        <v>4.7052</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7366</v>
+        <v>1.8789</v>
       </c>
       <c r="G3" t="n">
-        <v>3.6913</v>
+        <v>2.8263</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7366</v>
+        <v>1.8789</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7366</v>
+        <v>1.8789</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6913</v>
+        <v>2.8263</v>
       </c>
       <c r="K3" t="n">
         <v>57</v>
@@ -575,7 +575,7 @@
         <v>184</v>
       </c>
       <c r="M3" t="n">
-        <v>5.4279</v>
+        <v>4.7052</v>
       </c>
       <c r="N3" t="n">
         <v>241</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.2058</v>
+        <v>4.5508</v>
       </c>
       <c r="C4" t="n">
-        <v>3.1071</v>
+        <v>2.7161</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6301</v>
+        <v>1.4164</v>
       </c>
       <c r="E4" t="n">
-        <v>5.2058</v>
+        <v>4.5508</v>
       </c>
       <c r="F4" t="n">
-        <v>1.707</v>
+        <v>1.8921</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4988</v>
+        <v>2.6587</v>
       </c>
       <c r="H4" t="n">
-        <v>1.707</v>
+        <v>1.8921</v>
       </c>
       <c r="I4" t="n">
-        <v>1.707</v>
+        <v>1.8921</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4988</v>
+        <v>2.6587</v>
       </c>
       <c r="K4" t="n">
         <v>92</v>
@@ -621,7 +621,7 @@
         <v>168</v>
       </c>
       <c r="M4" t="n">
-        <v>5.2058</v>
+        <v>4.5508</v>
       </c>
       <c r="N4" t="n">
         <v>260</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.097</v>
+        <v>4.5345</v>
       </c>
       <c r="C5" t="n">
-        <v>3.0421</v>
+        <v>2.7064</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5867</v>
+        <v>1.4091</v>
       </c>
       <c r="E5" t="n">
-        <v>5.097</v>
+        <v>4.5345</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7759</v>
+        <v>0.8431</v>
       </c>
       <c r="G5" t="n">
-        <v>4.3211</v>
+        <v>3.6914</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7759</v>
+        <v>0.8431</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7759</v>
+        <v>0.8431</v>
       </c>
       <c r="J5" t="n">
-        <v>4.3211</v>
+        <v>3.6914</v>
       </c>
       <c r="K5" t="n">
         <v>57</v>
@@ -667,7 +667,7 @@
         <v>184</v>
       </c>
       <c r="M5" t="n">
-        <v>5.097</v>
+        <v>4.5345</v>
       </c>
       <c r="N5" t="n">
         <v>241</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.5973</v>
+        <v>4.0215</v>
       </c>
       <c r="C6" t="n">
-        <v>2.7439</v>
+        <v>2.4002</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3877</v>
+        <v>1.1775</v>
       </c>
       <c r="E6" t="n">
-        <v>4.5973</v>
+        <v>4.0215</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3791</v>
+        <v>1.4841</v>
       </c>
       <c r="G6" t="n">
-        <v>3.2182</v>
+        <v>2.5374</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3791</v>
+        <v>1.4841</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3791</v>
+        <v>1.4841</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2182</v>
+        <v>2.5374</v>
       </c>
       <c r="K6" t="n">
         <v>47</v>
@@ -713,7 +713,7 @@
         <v>209</v>
       </c>
       <c r="M6" t="n">
-        <v>4.5973</v>
+        <v>4.0215</v>
       </c>
       <c r="N6" t="n">
         <v>256</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.097</v>
+        <v>3.6714</v>
       </c>
       <c r="C7" t="n">
-        <v>2.4453</v>
+        <v>2.1913</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1883</v>
+        <v>1.0194</v>
       </c>
       <c r="E7" t="n">
-        <v>4.097</v>
+        <v>3.6714</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5364</v>
+        <v>1.3583</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5606</v>
+        <v>2.3131</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5364</v>
+        <v>1.3583</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5364</v>
+        <v>1.3583</v>
       </c>
       <c r="J7" t="n">
-        <v>2.5606</v>
+        <v>2.3131</v>
       </c>
       <c r="K7" t="n">
         <v>57</v>
@@ -759,7 +759,7 @@
         <v>184</v>
       </c>
       <c r="M7" t="n">
-        <v>4.097</v>
+        <v>3.6714</v>
       </c>
       <c r="N7" t="n">
         <v>241</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.951</v>
+        <v>3.6071</v>
       </c>
       <c r="C8" t="n">
-        <v>2.3582</v>
+        <v>2.1529</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1302</v>
+        <v>0.9903999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>3.951</v>
+        <v>3.6071</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9883999999999999</v>
+        <v>1.3405</v>
       </c>
       <c r="G8" t="n">
-        <v>2.9626</v>
+        <v>2.2666</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9883999999999999</v>
+        <v>1.3405</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9883999999999999</v>
+        <v>1.3405</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9626</v>
+        <v>2.2666</v>
       </c>
       <c r="K8" t="n">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="L8" t="n">
-        <v>130</v>
+        <v>209</v>
       </c>
       <c r="M8" t="n">
-        <v>3.951</v>
+        <v>3.6071</v>
       </c>
       <c r="N8" t="n">
-        <v>196</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.7613</v>
+        <v>3.4956</v>
       </c>
       <c r="C9" t="n">
-        <v>2.2449</v>
+        <v>2.0864</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0546</v>
+        <v>0.9401</v>
       </c>
       <c r="E9" t="n">
-        <v>3.7613</v>
+        <v>3.4956</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2309</v>
+        <v>1.0254</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5304</v>
+        <v>2.4702</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2309</v>
+        <v>1.0254</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2309</v>
+        <v>1.0254</v>
       </c>
       <c r="J9" t="n">
-        <v>2.5304</v>
+        <v>2.4702</v>
       </c>
       <c r="K9" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="L9" t="n">
-        <v>209</v>
+        <v>130</v>
       </c>
       <c r="M9" t="n">
-        <v>3.7613</v>
+        <v>3.4956</v>
       </c>
       <c r="N9" t="n">
-        <v>256</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.4123</v>
+        <v>3.4896</v>
       </c>
       <c r="C10" t="n">
-        <v>2.0366</v>
+        <v>2.0828</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9156</v>
+        <v>0.9374</v>
       </c>
       <c r="E10" t="n">
-        <v>3.4123</v>
+        <v>3.4896</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7172</v>
+        <v>1.8914</v>
       </c>
       <c r="G10" t="n">
-        <v>1.6951</v>
+        <v>1.5982</v>
       </c>
       <c r="H10" t="n">
-        <v>1.7172</v>
+        <v>1.8914</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7172</v>
+        <v>1.8914</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6951</v>
+        <v>1.5982</v>
       </c>
       <c r="K10" t="n">
         <v>92</v>
@@ -897,7 +897,7 @@
         <v>168</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4123</v>
+        <v>3.4896</v>
       </c>
       <c r="N10" t="n">
         <v>260</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Maden</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.1476</v>
+        <v>2.9196</v>
       </c>
       <c r="C11" t="n">
-        <v>1.8786</v>
+        <v>1.7426</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8101</v>
+        <v>0.68</v>
       </c>
       <c r="E11" t="n">
-        <v>3.1476</v>
+        <v>2.9196</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0427</v>
+        <v>1.1657</v>
       </c>
       <c r="G11" t="n">
-        <v>3.1049</v>
+        <v>1.7539</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0427</v>
+        <v>1.1657</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0427</v>
+        <v>1.1657</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1049</v>
+        <v>1.7539</v>
       </c>
       <c r="K11" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="L11" t="n">
-        <v>184</v>
+        <v>209</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1476</v>
+        <v>2.9196</v>
       </c>
       <c r="N11" t="n">
-        <v>241</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>Maden</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.9742</v>
+        <v>2.7551</v>
       </c>
       <c r="C12" t="n">
-        <v>1.7752</v>
+        <v>1.6444</v>
       </c>
       <c r="D12" t="n">
-        <v>0.741</v>
+        <v>0.6058</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9742</v>
+        <v>2.7551</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0811</v>
+        <v>0.1247</v>
       </c>
       <c r="G12" t="n">
-        <v>1.8931</v>
+        <v>2.6304</v>
       </c>
       <c r="H12" t="n">
-        <v>1.0811</v>
+        <v>0.1247</v>
       </c>
       <c r="I12" t="n">
-        <v>1.0811</v>
+        <v>0.1247</v>
       </c>
       <c r="J12" t="n">
-        <v>1.8931</v>
+        <v>2.6304</v>
       </c>
       <c r="K12" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="L12" t="n">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9742</v>
+        <v>2.7551</v>
       </c>
       <c r="N12" t="n">
-        <v>256</v>
+        <v>241</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.969</v>
+        <v>2.6777</v>
       </c>
       <c r="C13" t="n">
-        <v>1.772</v>
+        <v>1.5982</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7389</v>
+        <v>0.5708</v>
       </c>
       <c r="E13" t="n">
-        <v>2.969</v>
+        <v>2.6777</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0488</v>
+        <v>1.0467</v>
       </c>
       <c r="G13" t="n">
-        <v>1.9202</v>
+        <v>1.631</v>
       </c>
       <c r="H13" t="n">
-        <v>1.0488</v>
+        <v>1.0467</v>
       </c>
       <c r="I13" t="n">
-        <v>1.0488</v>
+        <v>1.0467</v>
       </c>
       <c r="J13" t="n">
-        <v>1.9202</v>
+        <v>1.631</v>
       </c>
       <c r="K13" t="n">
         <v>66</v>
@@ -1035,7 +1035,7 @@
         <v>130</v>
       </c>
       <c r="M13" t="n">
-        <v>2.969</v>
+        <v>2.6777</v>
       </c>
       <c r="N13" t="n">
         <v>196</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.2785</v>
+        <v>2.1917</v>
       </c>
       <c r="C14" t="n">
-        <v>1.3599</v>
+        <v>1.3081</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4638</v>
+        <v>0.3514</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2785</v>
+        <v>2.1917</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0943</v>
+        <v>1.1789</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1842</v>
+        <v>1.0128</v>
       </c>
       <c r="H14" t="n">
-        <v>1.0943</v>
+        <v>1.1789</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0943</v>
+        <v>1.1789</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1842</v>
+        <v>1.0128</v>
       </c>
       <c r="K14" t="n">
         <v>92</v>
@@ -1081,7 +1081,7 @@
         <v>168</v>
       </c>
       <c r="M14" t="n">
-        <v>2.2785</v>
+        <v>2.1917</v>
       </c>
       <c r="N14" t="n">
         <v>260</v>
@@ -1090,323 +1090,323 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.7001</v>
+        <v>1.718</v>
       </c>
       <c r="C15" t="n">
-        <v>1.0147</v>
+        <v>1.0254</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2334</v>
+        <v>0.1376</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7001</v>
+        <v>1.718</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6455</v>
+        <v>1.3741</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0546</v>
+        <v>0.3439</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6455</v>
+        <v>1.3741</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6455</v>
+        <v>1.3741</v>
       </c>
       <c r="J15" t="n">
-        <v>1.0546</v>
+        <v>0.3439</v>
       </c>
       <c r="K15" t="n">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="L15" t="n">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="M15" t="n">
-        <v>1.7001</v>
+        <v>1.718</v>
       </c>
       <c r="N15" t="n">
-        <v>167</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.593</v>
+        <v>1.7109</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9508</v>
+        <v>1.0212</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1907</v>
+        <v>0.1344</v>
       </c>
       <c r="E16" t="n">
-        <v>1.593</v>
+        <v>1.7109</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4701</v>
+        <v>0.6775</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1229</v>
+        <v>1.0334</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4701</v>
+        <v>0.6775</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4701</v>
+        <v>0.6775</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1229</v>
+        <v>1.0334</v>
       </c>
       <c r="K16" t="n">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="L16" t="n">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="M16" t="n">
-        <v>1.593</v>
+        <v>1.7109</v>
       </c>
       <c r="N16" t="n">
-        <v>196</v>
+        <v>167</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.5058</v>
+        <v>1.616</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8987000000000001</v>
+        <v>0.9645</v>
       </c>
       <c r="D17" t="n">
-        <v>0.156</v>
+        <v>0.0915</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5058</v>
+        <v>1.616</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1405</v>
+        <v>2.0231</v>
       </c>
       <c r="G17" t="n">
-        <v>1.6463</v>
+        <v>-0.4071</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1405</v>
+        <v>2.0231</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1405</v>
+        <v>2.0231</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6463</v>
+        <v>-0.4071</v>
       </c>
       <c r="K17" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="L17" t="n">
-        <v>130</v>
+        <v>45</v>
       </c>
       <c r="M17" t="n">
-        <v>1.5058</v>
+        <v>1.616</v>
       </c>
       <c r="N17" t="n">
-        <v>196</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.4785</v>
+        <v>1.4203</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8824</v>
+        <v>0.8477</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1451</v>
+        <v>0.0032</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4785</v>
+        <v>1.4203</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9386</v>
+        <v>1.6879</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5399</v>
+        <v>-0.2676</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9386</v>
+        <v>1.6879</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9386</v>
+        <v>1.6879</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5399</v>
+        <v>-0.2676</v>
       </c>
       <c r="K18" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="L18" t="n">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="M18" t="n">
-        <v>1.4785</v>
+        <v>1.4203</v>
       </c>
       <c r="N18" t="n">
-        <v>167</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.3734</v>
+        <v>1.3492</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8197</v>
+        <v>0.8053</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1033</v>
+        <v>-0.0289</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3734</v>
+        <v>1.3492</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5713</v>
+        <v>0.9681</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1979</v>
+        <v>0.3811</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5713</v>
+        <v>0.9681</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5713</v>
+        <v>0.9681</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1979</v>
+        <v>0.3811</v>
       </c>
       <c r="K19" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="L19" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="M19" t="n">
-        <v>1.3734</v>
+        <v>1.3492</v>
       </c>
       <c r="N19" t="n">
-        <v>121</v>
+        <v>167</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.3455</v>
+        <v>1.3492</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8031</v>
+        <v>0.8053</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0921</v>
+        <v>-0.0289</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3455</v>
+        <v>1.3492</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6584</v>
+        <v>-0.037</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3129</v>
+        <v>1.3862</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6584</v>
+        <v>-0.037</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6584</v>
+        <v>-0.037</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3129</v>
+        <v>1.3862</v>
       </c>
       <c r="K20" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="L20" t="n">
-        <v>45</v>
+        <v>130</v>
       </c>
       <c r="M20" t="n">
-        <v>1.3455</v>
+        <v>1.3492</v>
       </c>
       <c r="N20" t="n">
-        <v>98</v>
+        <v>196</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.1777</v>
+        <v>1.3363</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7029</v>
+        <v>0.7976</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0253</v>
+        <v>-0.0347</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1777</v>
+        <v>1.3363</v>
       </c>
       <c r="F21" t="n">
-        <v>1.737</v>
+        <v>1.4133</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5593</v>
+        <v>-0.077</v>
       </c>
       <c r="H21" t="n">
-        <v>1.737</v>
+        <v>1.4133</v>
       </c>
       <c r="I21" t="n">
-        <v>1.737</v>
+        <v>1.4133</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5593</v>
+        <v>-0.077</v>
       </c>
       <c r="K21" t="n">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="L21" t="n">
         <v>45</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1777</v>
+        <v>1.3363</v>
       </c>
       <c r="N21" t="n">
-        <v>98</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.0412</v>
+        <v>1.248</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6214</v>
+        <v>0.7449</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0291</v>
+        <v>-0.0746</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0412</v>
+        <v>1.248</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0412</v>
+        <v>1.248</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0412</v>
+        <v>1.248</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0412</v>
+        <v>1.248</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.0412</v>
+        <v>1.248</v>
       </c>
       <c r="N22" t="n">
         <v>57</v>
@@ -1458,93 +1458,93 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>isak</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8954</v>
+        <v>1.1407</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5344</v>
+        <v>0.6808</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0872</v>
+        <v>-0.123</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8954</v>
+        <v>1.1407</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8954</v>
+        <v>1.5987</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.458</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8954</v>
+        <v>1.5987</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8954</v>
+        <v>1.5987</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.458</v>
       </c>
       <c r="K23" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8954</v>
+        <v>1.1407</v>
       </c>
       <c r="N23" t="n">
-        <v>76</v>
+        <v>138</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>isak</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8622</v>
+        <v>1.0527</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.6283</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1004</v>
+        <v>-0.1628</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8622</v>
+        <v>1.0527</v>
       </c>
       <c r="F24" t="n">
-        <v>1.6121</v>
+        <v>1.6744</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.7499</v>
+        <v>-0.6217</v>
       </c>
       <c r="H24" t="n">
-        <v>1.6121</v>
+        <v>1.6744</v>
       </c>
       <c r="I24" t="n">
-        <v>1.6121</v>
+        <v>1.6744</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7499</v>
+        <v>-0.6217</v>
       </c>
       <c r="K24" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="L24" t="n">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8622000000000001</v>
+        <v>1.0527</v>
       </c>
       <c r="N24" t="n">
-        <v>138</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25">
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8223</v>
+        <v>1.0321</v>
       </c>
       <c r="C25" t="n">
-        <v>0.4908</v>
+        <v>0.616</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1163</v>
+        <v>-0.1721</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8223</v>
+        <v>1.0321</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2386</v>
+        <v>0.2855</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5837</v>
+        <v>0.7466</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2386</v>
+        <v>0.2855</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2386</v>
+        <v>0.2855</v>
       </c>
       <c r="J25" t="n">
-        <v>0.5837</v>
+        <v>0.7466</v>
       </c>
       <c r="K25" t="n">
         <v>66</v>
@@ -1587,7 +1587,7 @@
         <v>130</v>
       </c>
       <c r="M25" t="n">
-        <v>0.8223</v>
+        <v>1.0321</v>
       </c>
       <c r="N25" t="n">
         <v>196</v>
@@ -1596,139 +1596,139 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7727000000000001</v>
+        <v>0.8591</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4612</v>
+        <v>0.5128</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.1361</v>
+        <v>-0.2502</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7727000000000001</v>
+        <v>0.8591</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7727000000000001</v>
+        <v>0.8591</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7727000000000001</v>
+        <v>0.8591</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7727000000000001</v>
+        <v>0.8591</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7727000000000001</v>
+        <v>0.8591</v>
       </c>
       <c r="N26" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7719</v>
+        <v>0.8536</v>
       </c>
       <c r="C27" t="n">
-        <v>0.4607</v>
+        <v>0.5095</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.1364</v>
+        <v>-0.2527</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7719</v>
+        <v>0.8536</v>
       </c>
       <c r="F27" t="n">
-        <v>1.6955</v>
+        <v>0.8536</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.9236</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.6955</v>
+        <v>0.8536</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6955</v>
+        <v>0.8536</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.9236</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="L27" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.7719</v>
+        <v>0.8536</v>
       </c>
       <c r="N27" t="n">
-        <v>121</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>neaLaN</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7548</v>
+        <v>0.848</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4505</v>
+        <v>0.5061</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.1432</v>
+        <v>-0.2552</v>
       </c>
       <c r="E28" t="n">
-        <v>0.7548</v>
+        <v>0.848</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7548</v>
+        <v>1.7679</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-0.9199000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>0.7548</v>
+        <v>1.7679</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7548</v>
+        <v>1.7679</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>-0.9199000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="M28" t="n">
-        <v>0.7548</v>
+        <v>0.848</v>
       </c>
       <c r="N28" t="n">
-        <v>87</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6974</v>
+        <v>0.8280999999999999</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4162</v>
+        <v>0.4943</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.1661</v>
+        <v>-0.2642</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6974</v>
+        <v>0.8280999999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6974</v>
+        <v>0.8280999999999999</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.6974</v>
+        <v>0.8280999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6974</v>
+        <v>0.8280999999999999</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.6974</v>
+        <v>0.8280999999999999</v>
       </c>
       <c r="N29" t="n">
         <v>92</v>
@@ -1780,630 +1780,630 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>neaLaN</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6746</v>
+        <v>0.7934</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4026</v>
+        <v>0.4735</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1751</v>
+        <v>-0.2798</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6746</v>
+        <v>0.7934</v>
       </c>
       <c r="F30" t="n">
-        <v>1.6746</v>
+        <v>0.7934</v>
       </c>
       <c r="G30" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.6746</v>
+        <v>0.7934</v>
       </c>
       <c r="I30" t="n">
-        <v>1.6746</v>
+        <v>0.7934</v>
       </c>
       <c r="J30" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="L30" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.6746000000000001</v>
+        <v>0.7934</v>
       </c>
       <c r="N30" t="n">
-        <v>138</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>nawwk</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.634</v>
+        <v>0.7611</v>
       </c>
       <c r="C31" t="n">
-        <v>0.3784</v>
+        <v>0.4543</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.1913</v>
+        <v>-0.2944</v>
       </c>
       <c r="E31" t="n">
-        <v>0.634</v>
+        <v>0.7611</v>
       </c>
       <c r="F31" t="n">
-        <v>0.634</v>
+        <v>0.7611</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.634</v>
+        <v>0.7611</v>
       </c>
       <c r="I31" t="n">
-        <v>0.634</v>
+        <v>0.7611</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.634</v>
+        <v>0.7611</v>
       </c>
       <c r="N31" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.4706</v>
+        <v>0.6982</v>
       </c>
       <c r="C32" t="n">
-        <v>0.2809</v>
+        <v>0.4167</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.2564</v>
+        <v>-0.3228</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4706</v>
+        <v>0.6982</v>
       </c>
       <c r="F32" t="n">
-        <v>0.4806</v>
+        <v>0.6982</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.4806</v>
+        <v>0.6982</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4806</v>
+        <v>0.6982</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="L32" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.4706</v>
+        <v>0.6982</v>
       </c>
       <c r="N32" t="n">
-        <v>167</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>CacaNito</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.4551</v>
+        <v>0.6973</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2716</v>
+        <v>0.4162</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.2626</v>
+        <v>-0.3232</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4551</v>
+        <v>0.6973</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9208</v>
+        <v>0.6973</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.4657</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9208</v>
+        <v>0.6973</v>
       </c>
       <c r="I33" t="n">
-        <v>0.9208</v>
+        <v>0.6973</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.4657</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="L33" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.4550999999999999</v>
+        <v>0.6973</v>
       </c>
       <c r="N33" t="n">
-        <v>98</v>
+        <v>71</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.4468</v>
+        <v>0.6342</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2667</v>
+        <v>0.3785</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.2659</v>
+        <v>-0.3517</v>
       </c>
       <c r="E34" t="n">
-        <v>0.4468</v>
+        <v>0.6342</v>
       </c>
       <c r="F34" t="n">
-        <v>0.4468</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-0.3461</v>
       </c>
       <c r="H34" t="n">
-        <v>0.4468</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4468</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-0.3461</v>
       </c>
       <c r="K34" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M34" t="n">
-        <v>0.4468</v>
+        <v>0.6341999999999999</v>
       </c>
       <c r="N34" t="n">
-        <v>71</v>
+        <v>98</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CacaNito</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.3932</v>
+        <v>0.6266</v>
       </c>
       <c r="C35" t="n">
-        <v>0.2347</v>
+        <v>0.374</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2873</v>
+        <v>-0.3551</v>
       </c>
       <c r="E35" t="n">
-        <v>0.3932</v>
+        <v>0.6266</v>
       </c>
       <c r="F35" t="n">
-        <v>0.3932</v>
+        <v>0.5962</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>0.0304</v>
       </c>
       <c r="H35" t="n">
-        <v>0.3932</v>
+        <v>0.5962</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3932</v>
+        <v>0.5962</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>0.0304</v>
       </c>
       <c r="K35" t="n">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M35" t="n">
-        <v>0.3932</v>
+        <v>0.6265999999999999</v>
       </c>
       <c r="N35" t="n">
-        <v>71</v>
+        <v>167</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>nawwk</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.3907</v>
+        <v>0.6244</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2332</v>
+        <v>0.3727</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.2883</v>
+        <v>-0.3561</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3907</v>
+        <v>0.6244</v>
       </c>
       <c r="F36" t="n">
-        <v>0.3907</v>
+        <v>0.8121</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-0.1877</v>
       </c>
       <c r="H36" t="n">
-        <v>0.3907</v>
+        <v>0.8121</v>
       </c>
       <c r="I36" t="n">
-        <v>0.3907</v>
+        <v>0.8121</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>-0.1877</v>
       </c>
       <c r="K36" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M36" t="n">
-        <v>0.3907</v>
+        <v>0.6244000000000001</v>
       </c>
       <c r="N36" t="n">
-        <v>71</v>
+        <v>121</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Goofy</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.3629</v>
+        <v>0.6038</v>
       </c>
       <c r="C37" t="n">
-        <v>0.2166</v>
+        <v>0.3604</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2993</v>
+        <v>-0.3654</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3629</v>
+        <v>0.6038</v>
       </c>
       <c r="F37" t="n">
-        <v>0.3629</v>
+        <v>0.6038</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.3629</v>
+        <v>0.6038</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3629</v>
+        <v>0.6038</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.3629</v>
+        <v>0.6038</v>
       </c>
       <c r="N37" t="n">
-        <v>92</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.2899</v>
+        <v>0.4889</v>
       </c>
       <c r="C38" t="n">
-        <v>0.173</v>
+        <v>0.2918</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.3284</v>
+        <v>-0.4173</v>
       </c>
       <c r="E38" t="n">
-        <v>0.2899</v>
+        <v>0.4889</v>
       </c>
       <c r="F38" t="n">
-        <v>0.5396</v>
+        <v>0.4889</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.2497</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.5396</v>
+        <v>0.4889</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5396</v>
+        <v>0.4889</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.2497</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="L38" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.2898999999999999</v>
+        <v>0.4889</v>
       </c>
       <c r="N38" t="n">
-        <v>121</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BOROS</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.2498</v>
+        <v>0.4577</v>
       </c>
       <c r="C39" t="n">
-        <v>0.1491</v>
+        <v>0.2732</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.3444</v>
+        <v>-0.4314</v>
       </c>
       <c r="E39" t="n">
-        <v>0.2498</v>
+        <v>0.4577</v>
       </c>
       <c r="F39" t="n">
-        <v>0.2498</v>
+        <v>0.4577</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.2498</v>
+        <v>0.4577</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2498</v>
+        <v>0.4577</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.2498</v>
+        <v>0.4577</v>
       </c>
       <c r="N39" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>mhL</t>
+          <t>Goofy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.1469</v>
+        <v>0.3668</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0877</v>
+        <v>0.2189</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.3854</v>
+        <v>-0.4724</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1469</v>
+        <v>0.3668</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1469</v>
+        <v>0.3668</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1469</v>
+        <v>0.3668</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1469</v>
+        <v>0.3668</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.1469</v>
+        <v>0.3668</v>
       </c>
       <c r="N40" t="n">
-        <v>66</v>
+        <v>92</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.1415</v>
+        <v>0.3448</v>
       </c>
       <c r="C41" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.2058</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.3875</v>
+        <v>-0.4824</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1415</v>
+        <v>0.3448</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1415</v>
+        <v>0.3448</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.1415</v>
+        <v>0.3448</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1415</v>
+        <v>0.3448</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.1415</v>
+        <v>0.3448</v>
       </c>
       <c r="N41" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>BOROS</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.1265</v>
+        <v>0.3282</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0755</v>
+        <v>0.1959</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3935</v>
+        <v>-0.4898</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1265</v>
+        <v>0.3282</v>
       </c>
       <c r="F42" t="n">
-        <v>0.1265</v>
+        <v>0.3282</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.1265</v>
+        <v>0.3282</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1265</v>
+        <v>0.3282</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.1265</v>
+        <v>0.3282</v>
       </c>
       <c r="N42" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>roeJ</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.096</v>
+        <v>0.284</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0573</v>
+        <v>0.1695</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.4057</v>
+        <v>-0.5098</v>
       </c>
       <c r="E43" t="n">
-        <v>0.096</v>
+        <v>0.284</v>
       </c>
       <c r="F43" t="n">
-        <v>0.096</v>
+        <v>0.284</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.096</v>
+        <v>0.284</v>
       </c>
       <c r="I43" t="n">
-        <v>0.096</v>
+        <v>0.284</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.096</v>
+        <v>0.284</v>
       </c>
       <c r="N43" t="n">
         <v>53</v>
@@ -2424,32 +2424,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>mynio</t>
+          <t>KEi</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.0559</v>
+        <v>0.2752</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0334</v>
+        <v>0.1643</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.4216</v>
+        <v>-0.5138</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0559</v>
+        <v>0.2752</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0559</v>
+        <v>0.2752</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0559</v>
+        <v>0.2752</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0559</v>
+        <v>0.2752</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.0559</v>
+        <v>0.2752</v>
       </c>
       <c r="N44" t="n">
         <v>92</v>
@@ -2470,78 +2470,78 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>roeJ</t>
+          <t>mhL</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.0843</v>
+        <v>0.24</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.0503</v>
+        <v>0.1432</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.4775</v>
+        <v>-0.5296999999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.0843</v>
+        <v>0.24</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.0843</v>
+        <v>0.24</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.0843</v>
+        <v>0.24</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0843</v>
+        <v>0.24</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.0843</v>
+        <v>0.24</v>
       </c>
       <c r="N45" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>KEi</t>
+          <t>mynio</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.0877</v>
+        <v>0.0985</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.0523</v>
+        <v>0.0588</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.4789</v>
+        <v>-0.5935</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.0877</v>
+        <v>0.0985</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.0877</v>
+        <v>0.0985</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.0877</v>
+        <v>0.0985</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.0877</v>
+        <v>0.0985</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.0877</v>
+        <v>0.0985</v>
       </c>
       <c r="N46" t="n">
         <v>92</v>
@@ -2562,216 +2562,216 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>afro</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.09569999999999999</v>
+        <v>0.0945</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.0571</v>
+        <v>0.0564</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.482</v>
+        <v>-0.5954</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.09569999999999999</v>
+        <v>0.0945</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.09569999999999999</v>
+        <v>0.0945</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.09569999999999999</v>
+        <v>0.0945</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.09569999999999999</v>
+        <v>0.0945</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.09569999999999999</v>
+        <v>0.0945</v>
       </c>
       <c r="N47" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.1378</v>
+        <v>0.0727</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.0822</v>
+        <v>0.0434</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4988</v>
+        <v>-0.6052</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.1378</v>
+        <v>0.0727</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.1378</v>
+        <v>0.1328</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>-0.0601</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.1378</v>
+        <v>0.1328</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1378</v>
+        <v>0.1328</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>-0.0601</v>
       </c>
       <c r="K48" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.1378</v>
+        <v>0.0727</v>
       </c>
       <c r="N48" t="n">
-        <v>47</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>afro</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.1605</v>
+        <v>0.0378</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.0958</v>
+        <v>0.0226</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.5079</v>
+        <v>-0.6209</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.1605</v>
+        <v>0.0378</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.1605</v>
+        <v>0.0378</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.1605</v>
+        <v>0.0378</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1605</v>
+        <v>0.0378</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.1605</v>
+        <v>0.0378</v>
       </c>
       <c r="N49" t="n">
-        <v>53</v>
+        <v>87</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.1804</v>
+        <v>-0.0554</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.1077</v>
+        <v>-0.0331</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.5158</v>
+        <v>-0.663</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.1804</v>
+        <v>-0.0554</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.1804</v>
+        <v>-0.0554</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.1804</v>
+        <v>-0.0554</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1804</v>
+        <v>-0.0554</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.1804</v>
+        <v>-0.0554</v>
       </c>
       <c r="N50" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.2484</v>
+        <v>-0.0607</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.1483</v>
+        <v>-0.0362</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.5429</v>
+        <v>-0.6654</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.2484</v>
+        <v>-0.0607</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.2484</v>
+        <v>-0.0607</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.2484</v>
+        <v>-0.0607</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2484</v>
+        <v>-0.0607</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.2484</v>
+        <v>-0.0607</v>
       </c>
       <c r="N51" t="n">
         <v>47</v>
@@ -2792,170 +2792,170 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>exit</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.2719</v>
+        <v>-0.1028</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.1623</v>
+        <v>-0.0614</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5522</v>
+        <v>-0.6844</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.2719</v>
+        <v>-0.1028</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0187</v>
+        <v>-0.1028</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.2906</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0187</v>
+        <v>-0.1028</v>
       </c>
       <c r="I52" t="n">
-        <v>0.0187</v>
+        <v>-0.1028</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.2906</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="L52" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.2719</v>
+        <v>-0.1028</v>
       </c>
       <c r="N52" t="n">
-        <v>121</v>
+        <v>47</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>acoR</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.3213</v>
+        <v>-0.1522</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.1918</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5719</v>
+        <v>-0.7067</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.3213</v>
+        <v>-0.1522</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.3691</v>
+        <v>-0.1522</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0478</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.3691</v>
+        <v>-0.1522</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.3691</v>
+        <v>-0.1522</v>
       </c>
       <c r="J53" t="n">
-        <v>0.0478</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="L53" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.3213</v>
+        <v>-0.1522</v>
       </c>
       <c r="N53" t="n">
-        <v>138</v>
+        <v>47</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.3233</v>
+        <v>-0.2102</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.193</v>
+        <v>-0.1255</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5727</v>
+        <v>-0.7329</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.3233</v>
+        <v>-0.2102</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.3233</v>
+        <v>-0.2102</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.3233</v>
+        <v>-0.2102</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.3233</v>
+        <v>-0.2102</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.3233</v>
+        <v>-0.2102</v>
       </c>
       <c r="N54" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>lauNX</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.3289</v>
+        <v>-0.2105</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.1963</v>
+        <v>-0.1256</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5749</v>
+        <v>-0.733</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.3289</v>
+        <v>-0.2105</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.3289</v>
+        <v>-0.2105</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.3289</v>
+        <v>-0.2105</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3289</v>
+        <v>-0.2105</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.3289</v>
+        <v>-0.2105</v>
       </c>
       <c r="N55" t="n">
         <v>66</v>
@@ -2976,78 +2976,78 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.3298</v>
+        <v>-0.2107</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.1968</v>
+        <v>-0.1258</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5753</v>
+        <v>-0.7331</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.3298</v>
+        <v>-0.2107</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.3298</v>
+        <v>-0.2107</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.3298</v>
+        <v>-0.2107</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3298</v>
+        <v>-0.2107</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.3298</v>
+        <v>-0.2107</v>
       </c>
       <c r="N56" t="n">
-        <v>66</v>
+        <v>87</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>lauNX</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.3983</v>
+        <v>-0.2155</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.2377</v>
+        <v>-0.1286</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6026</v>
+        <v>-0.7353</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.3983</v>
+        <v>-0.2155</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.3983</v>
+        <v>-0.2155</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.3983</v>
+        <v>-0.2155</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.3983</v>
+        <v>-0.2155</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -3059,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.3983</v>
+        <v>-0.2155</v>
       </c>
       <c r="N57" t="n">
         <v>66</v>
@@ -3072,28 +3072,28 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.4078</v>
+        <v>-0.2537</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.2434</v>
+        <v>-0.1514</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.7524999999999999</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.4078</v>
+        <v>-0.2537</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.4078</v>
+        <v>-0.2537</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.4078</v>
+        <v>-0.2537</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.4078</v>
+        <v>-0.2537</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.4078</v>
+        <v>-0.2537</v>
       </c>
       <c r="N58" t="n">
         <v>53</v>
@@ -3114,127 +3114,127 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>volt</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.4309</v>
+        <v>-0.2551</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.2572</v>
+        <v>-0.1523</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6156</v>
+        <v>-0.7532</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.4309</v>
+        <v>-0.2551</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.4423</v>
+        <v>0.0339</v>
       </c>
       <c r="G59" t="n">
-        <v>0.0114</v>
+        <v>-0.289</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.4423</v>
+        <v>0.0339</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.4423</v>
+        <v>0.0339</v>
       </c>
       <c r="J59" t="n">
-        <v>0.0114</v>
+        <v>-0.289</v>
       </c>
       <c r="K59" t="n">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="L59" t="n">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.4309</v>
+        <v>-0.2551</v>
       </c>
       <c r="N59" t="n">
-        <v>138</v>
+        <v>167</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>acoR</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.4378</v>
+        <v>-0.317</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.2613</v>
+        <v>-0.1892</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6183</v>
+        <v>-0.7811</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.4378</v>
+        <v>-0.317</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.4378</v>
+        <v>-0.3577</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>0.0407</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.4378</v>
+        <v>-0.3577</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4378</v>
+        <v>-0.3577</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>0.0407</v>
       </c>
       <c r="K60" t="n">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.4378</v>
+        <v>-0.317</v>
       </c>
       <c r="N60" t="n">
-        <v>87</v>
+        <v>138</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>Qikert</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.5766</v>
+        <v>-0.3294</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.3441</v>
+        <v>-0.1966</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6736</v>
+        <v>-0.7867</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.5766</v>
+        <v>-0.3294</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.0344</v>
+        <v>0.074</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.5422</v>
+        <v>-0.4034</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.0344</v>
+        <v>0.074</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.0344</v>
+        <v>0.074</v>
       </c>
       <c r="J61" t="n">
-        <v>-0.5422</v>
+        <v>-0.4034</v>
       </c>
       <c r="K61" t="n">
         <v>87</v>
@@ -3243,7 +3243,7 @@
         <v>80</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.5766</v>
+        <v>-0.3294</v>
       </c>
       <c r="N61" t="n">
         <v>167</v>
@@ -3252,47 +3252,47 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.6081</v>
+        <v>-0.3693</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.3629</v>
+        <v>-0.2204</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6862</v>
+        <v>-0.8047</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.6081</v>
+        <v>-0.3693</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.6081</v>
+        <v>-0.3693</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.6081</v>
+        <v>-0.3693</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.6081</v>
+        <v>-0.3693</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.6081</v>
+        <v>-0.3693</v>
       </c>
       <c r="N62" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="63">
@@ -3302,28 +3302,28 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.6263</v>
+        <v>-0.3774</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.3738</v>
+        <v>-0.2253</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6934</v>
+        <v>-0.8084</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.6263</v>
+        <v>-0.3774</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.6263</v>
+        <v>-0.3774</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.6263</v>
+        <v>-0.3774</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.6263</v>
+        <v>-0.3774</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -3335,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.6263</v>
+        <v>-0.3774</v>
       </c>
       <c r="N63" t="n">
         <v>87</v>
@@ -3344,32 +3344,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.6573</v>
+        <v>-0.4066</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.3923</v>
+        <v>-0.2427</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7058</v>
+        <v>-0.8216</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.6573</v>
+        <v>-0.4066</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.6573</v>
+        <v>-0.4066</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.6573</v>
+        <v>-0.4066</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.6573</v>
+        <v>-0.4066</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -3381,7 +3381,7 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.6573</v>
+        <v>-0.4066</v>
       </c>
       <c r="N64" t="n">
         <v>76</v>
@@ -3390,323 +3390,323 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.7004</v>
+        <v>-0.411</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.418</v>
+        <v>-0.2453</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7229</v>
+        <v>-0.8236</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.7004</v>
+        <v>-0.411</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.7004</v>
+        <v>-0.411</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.7004</v>
+        <v>-0.411</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.7004</v>
+        <v>-0.411</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.7004</v>
+        <v>-0.411</v>
       </c>
       <c r="N65" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.7111</v>
+        <v>-0.421</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.4244</v>
+        <v>-0.2513</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7272</v>
+        <v>-0.8280999999999999</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.7111</v>
+        <v>-0.421</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.7111</v>
+        <v>0.2817</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>-0.7027</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.7111</v>
+        <v>0.2817</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.7111</v>
+        <v>0.2817</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>-0.7027</v>
       </c>
       <c r="K66" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.7111</v>
+        <v>-0.421</v>
       </c>
       <c r="N66" t="n">
-        <v>76</v>
+        <v>98</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Qikert</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.7645</v>
+        <v>-0.4368</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.4563</v>
+        <v>-0.2607</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7485000000000001</v>
+        <v>-0.8352000000000001</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.7645</v>
+        <v>-0.4368</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.1015</v>
+        <v>-0.4368</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.663</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.1015</v>
+        <v>-0.4368</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.1015</v>
+        <v>-0.4368</v>
       </c>
       <c r="J67" t="n">
-        <v>-0.663</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="L67" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.7645000000000001</v>
+        <v>-0.4368</v>
       </c>
       <c r="N67" t="n">
-        <v>167</v>
+        <v>76</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>jL</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.8018999999999999</v>
+        <v>-0.4733</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.4786</v>
+        <v>-0.2825</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.7634</v>
+        <v>-0.8517</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.8018999999999999</v>
+        <v>-0.4733</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.8018999999999999</v>
+        <v>0.395</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>-0.8683</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.8018999999999999</v>
+        <v>0.395</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.8018999999999999</v>
+        <v>0.395</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>-0.8683</v>
       </c>
       <c r="K68" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.8018999999999999</v>
+        <v>-0.4732999999999999</v>
       </c>
       <c r="N68" t="n">
-        <v>71</v>
+        <v>121</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Patsi</t>
+          <t>volt</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.8426</v>
+        <v>-0.4747</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.5029</v>
+        <v>-0.2833</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.7796</v>
+        <v>-0.8522999999999999</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.8426</v>
+        <v>-0.4747</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.8426</v>
+        <v>-0.4336</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>-0.0411</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.8426</v>
+        <v>-0.4336</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.8426</v>
+        <v>-0.4336</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>-0.0411</v>
       </c>
       <c r="K69" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.8426</v>
+        <v>-0.4747</v>
       </c>
       <c r="N69" t="n">
-        <v>57</v>
+        <v>138</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.8484</v>
+        <v>-0.504</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.5064</v>
+        <v>-0.3008</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.7819</v>
+        <v>-0.8655</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.8484</v>
+        <v>-0.504</v>
       </c>
       <c r="F70" t="n">
-        <v>0.1516</v>
+        <v>-0.504</v>
       </c>
       <c r="G70" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>0.1516</v>
+        <v>-0.504</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1516</v>
+        <v>-0.504</v>
       </c>
       <c r="J70" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="L70" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.8484</v>
+        <v>-0.504</v>
       </c>
       <c r="N70" t="n">
-        <v>98</v>
+        <v>71</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>jL</t>
+          <t>Patsi</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.8608</v>
+        <v>-0.5396</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.5138</v>
+        <v>-0.3221</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.7869</v>
+        <v>-0.8816000000000001</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.8608</v>
+        <v>-0.5396</v>
       </c>
       <c r="F71" t="n">
-        <v>0.1392</v>
+        <v>-0.5396</v>
       </c>
       <c r="G71" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>0.1392</v>
+        <v>-0.5396</v>
       </c>
       <c r="I71" t="n">
-        <v>0.1392</v>
+        <v>-0.5396</v>
       </c>
       <c r="J71" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="L71" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.8608</v>
+        <v>-0.5396</v>
       </c>
       <c r="N71" t="n">
-        <v>121</v>
+        <v>57</v>
       </c>
     </row>
     <row r="72">
@@ -3716,28 +3716,28 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.8979</v>
+        <v>-0.5957</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.5359</v>
+        <v>-0.3555</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.8016</v>
+        <v>-0.9069</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.8979</v>
+        <v>-0.5957</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.8979</v>
+        <v>-0.5957</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.8979</v>
+        <v>-0.5957</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.8979</v>
+        <v>-0.5957</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.8979</v>
+        <v>-0.5957</v>
       </c>
       <c r="N72" t="n">
         <v>47</v>
@@ -3762,28 +3762,28 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1</v>
+        <v>-0.6258</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.5969</v>
+        <v>-0.3735</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.8423</v>
+        <v>-0.9205</v>
       </c>
       <c r="E73" t="n">
-        <v>-1</v>
+        <v>-0.6258</v>
       </c>
       <c r="F73" t="n">
-        <v>-1</v>
+        <v>-0.6258</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1</v>
+        <v>-0.6258</v>
       </c>
       <c r="I73" t="n">
-        <v>-1</v>
+        <v>-0.6258</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -3795,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-1</v>
+        <v>-0.6258</v>
       </c>
       <c r="N73" t="n">
         <v>92</v>
@@ -3804,93 +3804,93 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Rainwaker</t>
+          <t>brnz4n</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1</v>
+        <v>-0.7431</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.5969</v>
+        <v>-0.4435</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.8423</v>
+        <v>-0.9735</v>
       </c>
       <c r="E74" t="n">
-        <v>-1</v>
+        <v>-0.7431</v>
       </c>
       <c r="F74" t="n">
-        <v>-1</v>
+        <v>-0.7431</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1</v>
+        <v>-0.7431</v>
       </c>
       <c r="I74" t="n">
-        <v>-1</v>
+        <v>-0.7431</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1</v>
+        <v>-0.7431</v>
       </c>
       <c r="N74" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>brnz4n</t>
+          <t>Rainwaker</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1</v>
+        <v>-0.9067</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.5969</v>
+        <v>-0.5412</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.8423</v>
+        <v>-1.0473</v>
       </c>
       <c r="E75" t="n">
-        <v>-1</v>
+        <v>-0.9067</v>
       </c>
       <c r="F75" t="n">
-        <v>-1</v>
+        <v>-0.9067</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1</v>
+        <v>-0.9067</v>
       </c>
       <c r="I75" t="n">
-        <v>-1</v>
+        <v>-0.9067</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-1</v>
+        <v>-0.9067</v>
       </c>
       <c r="N75" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="76">
@@ -3900,31 +3900,31 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.631</v>
+        <v>-1.4016</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.9735</v>
+        <v>-0.8365</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0937</v>
+        <v>-1.2708</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.631</v>
+        <v>-1.4016</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.9543</v>
+        <v>-0.9265</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.6767</v>
+        <v>-0.4751</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.9543</v>
+        <v>-0.9265</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.9543</v>
+        <v>-0.9265</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.6767</v>
+        <v>-0.4751</v>
       </c>
       <c r="K76" t="n">
         <v>53</v>
@@ -3933,7 +3933,7 @@
         <v>45</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.631</v>
+        <v>-1.4016</v>
       </c>
       <c r="N76" t="n">
         <v>98</v>
@@ -3942,93 +3942,93 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>Keoz</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.8003</v>
+        <v>-1.7678</v>
       </c>
       <c r="C77" t="n">
-        <v>-1.0745</v>
+        <v>-1.0551</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1612</v>
+        <v>-1.4361</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.8003</v>
+        <v>-1.7678</v>
       </c>
       <c r="F77" t="n">
-        <v>0.4563</v>
+        <v>-0.7678</v>
       </c>
       <c r="G77" t="n">
-        <v>-2.2566</v>
+        <v>-1</v>
       </c>
       <c r="H77" t="n">
-        <v>0.4563</v>
+        <v>-0.7678</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4563</v>
+        <v>-0.7678</v>
       </c>
       <c r="J77" t="n">
-        <v>-2.2566</v>
+        <v>-1</v>
       </c>
       <c r="K77" t="n">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="L77" t="n">
-        <v>209</v>
+        <v>67</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.8003</v>
+        <v>-1.7678</v>
       </c>
       <c r="N77" t="n">
-        <v>256</v>
+        <v>138</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Keoz</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.891</v>
+        <v>-1.871</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.1286</v>
+        <v>-1.1167</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.1973</v>
+        <v>-1.4827</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.891</v>
+        <v>-1.871</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.891</v>
+        <v>0.6203</v>
       </c>
       <c r="G78" t="n">
-        <v>-1</v>
+        <v>-2.4913</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.891</v>
+        <v>0.6203</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.891</v>
+        <v>0.6203</v>
       </c>
       <c r="J78" t="n">
-        <v>-1</v>
+        <v>-2.4913</v>
       </c>
       <c r="K78" t="n">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="L78" t="n">
-        <v>67</v>
+        <v>209</v>
       </c>
       <c r="M78" t="n">
-        <v>-1.891</v>
+        <v>-1.871</v>
       </c>
       <c r="N78" t="n">
-        <v>138</v>
+        <v>256</v>
       </c>
     </row>
     <row r="79">
@@ -4038,31 +4038,31 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.6819</v>
+        <v>-2.2919</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.6007</v>
+        <v>-1.3679</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.5124</v>
+        <v>-1.6727</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.6819</v>
+        <v>-2.2919</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.6044</v>
+        <v>-1.578</v>
       </c>
       <c r="G79" t="n">
-        <v>-1.0775</v>
+        <v>-0.7139</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.6044</v>
+        <v>-1.578</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.6044</v>
+        <v>-1.578</v>
       </c>
       <c r="J79" t="n">
-        <v>-1.0775</v>
+        <v>-0.7139</v>
       </c>
       <c r="K79" t="n">
         <v>92</v>
@@ -4071,7 +4071,7 @@
         <v>168</v>
       </c>
       <c r="M79" t="n">
-        <v>-2.6819</v>
+        <v>-2.2919</v>
       </c>
       <c r="N79" t="n">
         <v>260</v>
@@ -4084,31 +4084,31 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.829</v>
+        <v>-2.4189</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.6885</v>
+        <v>-1.4437</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.571</v>
+        <v>-1.73</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.829</v>
+        <v>-2.4189</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.829</v>
+        <v>-0.5971</v>
       </c>
       <c r="G80" t="n">
-        <v>-2</v>
+        <v>-1.8218</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.829</v>
+        <v>-0.5971</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.829</v>
+        <v>-0.5971</v>
       </c>
       <c r="J80" t="n">
-        <v>-2</v>
+        <v>-1.8218</v>
       </c>
       <c r="K80" t="n">
         <v>92</v>
@@ -4117,7 +4117,7 @@
         <v>168</v>
       </c>
       <c r="M80" t="n">
-        <v>-2.829</v>
+        <v>-2.4189</v>
       </c>
       <c r="N80" t="n">
         <v>260</v>
@@ -4130,31 +4130,31 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-3.4438</v>
+        <v>-2.6412</v>
       </c>
       <c r="C81" t="n">
-        <v>-2.0554</v>
+        <v>-1.5764</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.8159</v>
+        <v>-1.8304</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.4438</v>
+        <v>-2.6412</v>
       </c>
       <c r="F81" t="n">
-        <v>-1.1491</v>
+        <v>-1.037</v>
       </c>
       <c r="G81" t="n">
-        <v>-2.2947</v>
+        <v>-1.6042</v>
       </c>
       <c r="H81" t="n">
-        <v>-1.1491</v>
+        <v>-1.037</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.1491</v>
+        <v>-1.037</v>
       </c>
       <c r="J81" t="n">
-        <v>-2.2947</v>
+        <v>-1.6042</v>
       </c>
       <c r="K81" t="n">
         <v>57</v>
@@ -4163,7 +4163,7 @@
         <v>184</v>
       </c>
       <c r="M81" t="n">
-        <v>-3.4438</v>
+        <v>-2.6412</v>
       </c>
       <c r="N81" t="n">
         <v>241</v>
@@ -4269,10 +4269,10 @@
         <v>1.62</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8093</v>
+        <v>0.7315</v>
       </c>
       <c r="J2" t="n">
-        <v>18.6139</v>
+        <v>16.8245</v>
       </c>
     </row>
     <row r="3">
@@ -4309,10 +4309,10 @@
         <v>1.43</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5908</v>
+        <v>0.5303</v>
       </c>
       <c r="J3" t="n">
-        <v>13.5884</v>
+        <v>12.1969</v>
       </c>
     </row>
     <row r="4">
@@ -4349,10 +4349,10 @@
         <v>1.34</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4742</v>
+        <v>0.4323</v>
       </c>
       <c r="J4" t="n">
-        <v>10.9066</v>
+        <v>9.9429</v>
       </c>
     </row>
     <row r="5">
@@ -4389,10 +4389,10 @@
         <v>1.14</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1739</v>
+        <v>0.1955</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9997</v>
+        <v>4.4965</v>
       </c>
     </row>
     <row r="6">
@@ -4429,10 +4429,10 @@
         <v>0.97</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1675</v>
+        <v>-0.0793</v>
       </c>
       <c r="J6" t="n">
-        <v>-3.8525</v>
+        <v>-1.8239</v>
       </c>
     </row>
     <row r="7">
@@ -4469,10 +4469,10 @@
         <v>1.12</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3574</v>
+        <v>0.2998</v>
       </c>
       <c r="J7" t="n">
-        <v>8.2202</v>
+        <v>6.8954</v>
       </c>
     </row>
     <row r="8">
@@ -4509,10 +4509,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2527</v>
+        <v>-0.2004</v>
       </c>
       <c r="J8" t="n">
-        <v>-5.8121</v>
+        <v>-4.6092</v>
       </c>
     </row>
     <row r="9">
@@ -4549,10 +4549,10 @@
         <v>0.67</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4969</v>
+        <v>-0.3325</v>
       </c>
       <c r="J9" t="n">
-        <v>-11.4287</v>
+        <v>-7.6475</v>
       </c>
     </row>
     <row r="10">
@@ -4589,10 +4589,10 @@
         <v>0.63</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5542</v>
+        <v>-0.37</v>
       </c>
       <c r="J10" t="n">
-        <v>-12.7466</v>
+        <v>-8.51</v>
       </c>
     </row>
     <row r="11">
@@ -4629,10 +4629,10 @@
         <v>0.55</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6617</v>
+        <v>-0.4449</v>
       </c>
       <c r="J11" t="n">
-        <v>-15.2191</v>
+        <v>-10.2327</v>
       </c>
     </row>
     <row r="12">
@@ -4669,10 +4669,10 @@
         <v>1.17</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3352</v>
+        <v>0.3794</v>
       </c>
       <c r="J12" t="n">
-        <v>9.3856</v>
+        <v>10.6232</v>
       </c>
     </row>
     <row r="13">
@@ -4709,10 +4709,10 @@
         <v>1.13</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2731</v>
+        <v>0.3031</v>
       </c>
       <c r="J13" t="n">
-        <v>7.6468</v>
+        <v>8.486800000000001</v>
       </c>
     </row>
     <row r="14">
@@ -4749,10 +4749,10 @@
         <v>1.01</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0282</v>
+        <v>0.0365</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7896</v>
+        <v>1.022</v>
       </c>
     </row>
     <row r="15">
@@ -4789,10 +4789,10 @@
         <v>0.9</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2316</v>
+        <v>-0.1356</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.4848</v>
+        <v>-3.7968</v>
       </c>
     </row>
     <row r="16">
@@ -4829,10 +4829,10 @@
         <v>0.85</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3122</v>
+        <v>-0.1893</v>
       </c>
       <c r="J16" t="n">
-        <v>-8.7416</v>
+        <v>-5.3004</v>
       </c>
     </row>
     <row r="17">
@@ -4869,10 +4869,10 @@
         <v>1.35</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9923</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>27.7844</v>
+        <v>27.0816</v>
       </c>
     </row>
     <row r="18">
@@ -4909,10 +4909,10 @@
         <v>1.24</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7407</v>
+        <v>0.7047</v>
       </c>
       <c r="J18" t="n">
-        <v>20.7396</v>
+        <v>19.7316</v>
       </c>
     </row>
     <row r="19">
@@ -4949,10 +4949,10 @@
         <v>1.05</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1972</v>
+        <v>0.1874</v>
       </c>
       <c r="J19" t="n">
-        <v>5.5216</v>
+        <v>5.2472</v>
       </c>
     </row>
     <row r="20">
@@ -4989,10 +4989,10 @@
         <v>0.85</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-0.5008</v>
       </c>
       <c r="J20" t="n">
-        <v>-15.5652</v>
+        <v>-14.0224</v>
       </c>
     </row>
     <row r="21">
@@ -5029,10 +5029,10 @@
         <v>0.72</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8727</v>
+        <v>-0.8364</v>
       </c>
       <c r="J21" t="n">
-        <v>-24.4356</v>
+        <v>-23.4192</v>
       </c>
     </row>
     <row r="22">
@@ -5069,10 +5069,10 @@
         <v>1.09</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2766</v>
+        <v>0.285</v>
       </c>
       <c r="J22" t="n">
-        <v>6.915</v>
+        <v>7.125</v>
       </c>
     </row>
     <row r="23">
@@ -5109,10 +5109,10 @@
         <v>0.98</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0225</v>
+        <v>-0.014</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5625</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="24">
@@ -5149,10 +5149,10 @@
         <v>0.74</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4216</v>
+        <v>-0.2765</v>
       </c>
       <c r="J24" t="n">
-        <v>-10.54</v>
+        <v>-6.9125</v>
       </c>
     </row>
     <row r="25">
@@ -5189,10 +5189,10 @@
         <v>0.73</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4365</v>
+        <v>-0.2861</v>
       </c>
       <c r="J25" t="n">
-        <v>-10.9125</v>
+        <v>-7.1525</v>
       </c>
     </row>
     <row r="26">
@@ -5229,10 +5229,10 @@
         <v>0.61</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.602</v>
+        <v>-0.3996</v>
       </c>
       <c r="J26" t="n">
-        <v>-15.05</v>
+        <v>-9.99</v>
       </c>
     </row>
     <row r="27">
@@ -5269,10 +5269,10 @@
         <v>1.56</v>
       </c>
       <c r="I27" t="n">
-        <v>1.3453</v>
+        <v>1.2204</v>
       </c>
       <c r="J27" t="n">
-        <v>33.6325</v>
+        <v>30.51</v>
       </c>
     </row>
     <row r="28">
@@ -5309,10 +5309,10 @@
         <v>1.3</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7977</v>
+        <v>0.7963</v>
       </c>
       <c r="J28" t="n">
-        <v>19.9425</v>
+        <v>19.9075</v>
       </c>
     </row>
     <row r="29">
@@ -5349,10 +5349,10 @@
         <v>1.21</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5704</v>
+        <v>0.5851</v>
       </c>
       <c r="J29" t="n">
-        <v>14.26</v>
+        <v>14.6275</v>
       </c>
     </row>
     <row r="30">
@@ -5389,10 +5389,10 @@
         <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1196</v>
+        <v>-0.0461</v>
       </c>
       <c r="J30" t="n">
-        <v>-2.99</v>
+        <v>-1.1525</v>
       </c>
     </row>
     <row r="31">
@@ -5429,10 +5429,10 @@
         <v>0.88</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5274</v>
+        <v>-0.458</v>
       </c>
       <c r="J31" t="n">
-        <v>-13.185</v>
+        <v>-11.45</v>
       </c>
     </row>
     <row r="32">
@@ -5469,10 +5469,10 @@
         <v>1.38</v>
       </c>
       <c r="I32" t="n">
-        <v>1.0061</v>
+        <v>0.7258</v>
       </c>
       <c r="J32" t="n">
-        <v>28.1708</v>
+        <v>20.3224</v>
       </c>
     </row>
     <row r="33">
@@ -5509,10 +5509,10 @@
         <v>1.25</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7098</v>
+        <v>0.5465</v>
       </c>
       <c r="J33" t="n">
-        <v>19.8744</v>
+        <v>15.302</v>
       </c>
     </row>
     <row r="34">
@@ -5549,10 +5549,10 @@
         <v>1.04</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0794</v>
+        <v>0.1351</v>
       </c>
       <c r="J34" t="n">
-        <v>2.2232</v>
+        <v>3.7828</v>
       </c>
     </row>
     <row r="35">
@@ -5589,10 +5589,10 @@
         <v>1.01</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.0379</v>
+        <v>0.0226</v>
       </c>
       <c r="J35" t="n">
-        <v>-1.0612</v>
+        <v>0.6328</v>
       </c>
     </row>
     <row r="36">
@@ -5629,10 +5629,10 @@
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.09719999999999999</v>
+        <v>-0.0322</v>
       </c>
       <c r="J36" t="n">
-        <v>-2.7216</v>
+        <v>-0.9016</v>
       </c>
     </row>
     <row r="37">
@@ -5669,10 +5669,10 @@
         <v>1.03</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1607</v>
+        <v>0.1387</v>
       </c>
       <c r="J37" t="n">
-        <v>4.4996</v>
+        <v>3.8836</v>
       </c>
     </row>
     <row r="38">
@@ -5709,10 +5709,10 @@
         <v>0.99</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0442</v>
+        <v>0.0015</v>
       </c>
       <c r="J38" t="n">
-        <v>1.2376</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="39">
@@ -5749,10 +5749,10 @@
         <v>0.93</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.0839</v>
+        <v>-0.0825</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.3492</v>
+        <v>-2.31</v>
       </c>
     </row>
     <row r="40">
@@ -5789,10 +5789,10 @@
         <v>0.64</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5644</v>
+        <v>-0.3726</v>
       </c>
       <c r="J40" t="n">
-        <v>-15.8032</v>
+        <v>-10.4328</v>
       </c>
     </row>
     <row r="41">
@@ -5829,10 +5829,10 @@
         <v>0.6</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6168</v>
+        <v>-0.41</v>
       </c>
       <c r="J41" t="n">
-        <v>-17.2704</v>
+        <v>-11.48</v>
       </c>
     </row>
     <row r="42">
@@ -5869,10 +5869,10 @@
         <v>1.12</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3293</v>
+        <v>0.2707</v>
       </c>
       <c r="J42" t="n">
-        <v>8.5618</v>
+        <v>7.0382</v>
       </c>
     </row>
     <row r="43">
@@ -5909,10 +5909,10 @@
         <v>1.1</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2967</v>
+        <v>0.2378</v>
       </c>
       <c r="J43" t="n">
-        <v>7.7142</v>
+        <v>6.1828</v>
       </c>
     </row>
     <row r="44">
@@ -5949,10 +5949,10 @@
         <v>0.71</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.4629</v>
+        <v>-0.3041</v>
       </c>
       <c r="J44" t="n">
-        <v>-12.0354</v>
+        <v>-7.9066</v>
       </c>
     </row>
     <row r="45">
@@ -5989,10 +5989,10 @@
         <v>0.64</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5603</v>
+        <v>-0.3704</v>
       </c>
       <c r="J45" t="n">
-        <v>-14.5678</v>
+        <v>-9.6304</v>
       </c>
     </row>
     <row r="46">
@@ -6029,10 +6029,10 @@
         <v>0.54</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6894</v>
+        <v>-0.4635</v>
       </c>
       <c r="J46" t="n">
-        <v>-17.9244</v>
+        <v>-12.051</v>
       </c>
     </row>
     <row r="47">
@@ -6069,10 +6069,10 @@
         <v>1.64</v>
       </c>
       <c r="I47" t="n">
-        <v>0.832</v>
+        <v>0.5809</v>
       </c>
       <c r="J47" t="n">
-        <v>21.632</v>
+        <v>15.1034</v>
       </c>
     </row>
     <row r="48">
@@ -6109,10 +6109,10 @@
         <v>1.4</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5547</v>
+        <v>0.4309</v>
       </c>
       <c r="J48" t="n">
-        <v>14.4222</v>
+        <v>11.2034</v>
       </c>
     </row>
     <row r="49">
@@ -6149,10 +6149,10 @@
         <v>1.29</v>
       </c>
       <c r="I49" t="n">
-        <v>0.3962</v>
+        <v>0.36</v>
       </c>
       <c r="J49" t="n">
-        <v>10.3012</v>
+        <v>9.359999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -6189,10 +6189,10 @@
         <v>1.28</v>
       </c>
       <c r="I50" t="n">
-        <v>0.3801</v>
+        <v>0.3534</v>
       </c>
       <c r="J50" t="n">
-        <v>9.8826</v>
+        <v>9.1884</v>
       </c>
     </row>
     <row r="51">
@@ -6229,10 +6229,10 @@
         <v>0.87</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3338</v>
+        <v>-0.1966</v>
       </c>
       <c r="J51" t="n">
-        <v>-8.678800000000001</v>
+        <v>-5.1116</v>
       </c>
     </row>
     <row r="52">
@@ -6269,10 +6269,10 @@
         <v>1.31</v>
       </c>
       <c r="I52" t="n">
-        <v>0.88</v>
+        <v>0.6424</v>
       </c>
       <c r="J52" t="n">
-        <v>29.92</v>
+        <v>21.8416</v>
       </c>
     </row>
     <row r="53">
@@ -6309,10 +6309,10 @@
         <v>1.25</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7403</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="J53" t="n">
-        <v>25.1702</v>
+        <v>18.938</v>
       </c>
     </row>
     <row r="54">
@@ -6349,10 +6349,10 @@
         <v>1.17</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5379</v>
+        <v>0.4387</v>
       </c>
       <c r="J54" t="n">
-        <v>18.2886</v>
+        <v>14.9158</v>
       </c>
     </row>
     <row r="55">
@@ -6389,10 +6389,10 @@
         <v>0.9</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4361</v>
+        <v>-0.3728</v>
       </c>
       <c r="J55" t="n">
-        <v>-14.8274</v>
+        <v>-12.6752</v>
       </c>
     </row>
     <row r="56">
@@ -6429,10 +6429,10 @@
         <v>0.79</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.7218</v>
+        <v>-0.6713</v>
       </c>
       <c r="J56" t="n">
-        <v>-24.5412</v>
+        <v>-22.8242</v>
       </c>
     </row>
     <row r="57">
@@ -6469,10 +6469,10 @@
         <v>1.43</v>
       </c>
       <c r="I57" t="n">
-        <v>0.672</v>
+        <v>0.6231</v>
       </c>
       <c r="J57" t="n">
-        <v>22.848</v>
+        <v>21.1854</v>
       </c>
     </row>
     <row r="58">
@@ -6509,10 +6509,10 @@
         <v>1.35</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5742</v>
+        <v>0.5446</v>
       </c>
       <c r="J58" t="n">
-        <v>19.5228</v>
+        <v>18.5164</v>
       </c>
     </row>
     <row r="59">
@@ -6549,10 +6549,10 @@
         <v>0.82</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3614</v>
+        <v>-0.2223</v>
       </c>
       <c r="J59" t="n">
-        <v>-12.2876</v>
+        <v>-7.5582</v>
       </c>
     </row>
     <row r="60">
@@ -6589,10 +6589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3759</v>
+        <v>-0.2324</v>
       </c>
       <c r="J60" t="n">
-        <v>-12.7806</v>
+        <v>-7.9016</v>
       </c>
     </row>
     <row r="61">
@@ -6629,10 +6629,10 @@
         <v>0.74</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.473</v>
+        <v>-0.3014</v>
       </c>
       <c r="J61" t="n">
-        <v>-16.082</v>
+        <v>-10.2476</v>
       </c>
     </row>
     <row r="62">
@@ -6669,10 +6669,10 @@
         <v>1.07</v>
       </c>
       <c r="I62" t="n">
-        <v>0.1768</v>
+        <v>0.185</v>
       </c>
       <c r="J62" t="n">
-        <v>7.4256</v>
+        <v>7.77</v>
       </c>
     </row>
     <row r="63">
@@ -6709,10 +6709,10 @@
         <v>1.06</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1578</v>
+        <v>0.1631</v>
       </c>
       <c r="J63" t="n">
-        <v>6.6276</v>
+        <v>6.8502</v>
       </c>
     </row>
     <row r="64">
@@ -6749,10 +6749,10 @@
         <v>1.01</v>
       </c>
       <c r="I64" t="n">
-        <v>0.0443</v>
+        <v>0.0385</v>
       </c>
       <c r="J64" t="n">
-        <v>1.8606</v>
+        <v>1.617</v>
       </c>
     </row>
     <row r="65">
@@ -6789,10 +6789,10 @@
         <v>1</v>
       </c>
       <c r="I65" t="n">
-        <v>0.0065</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="J65" t="n">
-        <v>0.273</v>
+        <v>0.0252</v>
       </c>
     </row>
     <row r="66">
@@ -6829,10 +6829,10 @@
         <v>0.83</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.338</v>
+        <v>-0.2079</v>
       </c>
       <c r="J66" t="n">
-        <v>-14.196</v>
+        <v>-8.7318</v>
       </c>
     </row>
     <row r="67">
@@ -6869,10 +6869,10 @@
         <v>1.25</v>
       </c>
       <c r="I67" t="n">
-        <v>0.7611</v>
+        <v>0.5655</v>
       </c>
       <c r="J67" t="n">
-        <v>31.9662</v>
+        <v>23.751</v>
       </c>
     </row>
     <row r="68">
@@ -6909,10 +6909,10 @@
         <v>1.11</v>
       </c>
       <c r="I68" t="n">
-        <v>0.393</v>
+        <v>0.3503</v>
       </c>
       <c r="J68" t="n">
-        <v>16.506</v>
+        <v>14.7126</v>
       </c>
     </row>
     <row r="69">
@@ -6949,10 +6949,10 @@
         <v>1.05</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1887</v>
+        <v>0.1865</v>
       </c>
       <c r="J69" t="n">
-        <v>7.9254</v>
+        <v>7.833</v>
       </c>
     </row>
     <row r="70">
@@ -6989,10 +6989,10 @@
         <v>0.99</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1099</v>
+        <v>-0.0643</v>
       </c>
       <c r="J70" t="n">
-        <v>-4.6158</v>
+        <v>-2.7006</v>
       </c>
     </row>
     <row r="71">
@@ -7029,10 +7029,10 @@
         <v>0.84</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5845</v>
+        <v>-0.5296</v>
       </c>
       <c r="J71" t="n">
-        <v>-24.549</v>
+        <v>-22.2432</v>
       </c>
     </row>
     <row r="72">
@@ -7069,10 +7069,10 @@
         <v>1.14</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3527</v>
+        <v>0.3644</v>
       </c>
       <c r="J72" t="n">
-        <v>7.4067</v>
+        <v>7.6524</v>
       </c>
     </row>
     <row r="73">
@@ -7109,10 +7109,10 @@
         <v>0.84</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.2589</v>
+        <v>-0.1807</v>
       </c>
       <c r="J73" t="n">
-        <v>-5.4369</v>
+        <v>-3.7947</v>
       </c>
     </row>
     <row r="74">
@@ -7149,10 +7149,10 @@
         <v>0.83</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.2797</v>
+        <v>-0.1903</v>
       </c>
       <c r="J74" t="n">
-        <v>-5.8737</v>
+        <v>-3.9963</v>
       </c>
     </row>
     <row r="75">
@@ -7189,10 +7189,10 @@
         <v>0.79</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3489</v>
+        <v>-0.2295</v>
       </c>
       <c r="J75" t="n">
-        <v>-7.3269</v>
+        <v>-4.8195</v>
       </c>
     </row>
     <row r="76">
@@ -7229,10 +7229,10 @@
         <v>0.61</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.6048</v>
+        <v>-0.4012</v>
       </c>
       <c r="J76" t="n">
-        <v>-12.7008</v>
+        <v>-8.4252</v>
       </c>
     </row>
     <row r="77">
@@ -7269,10 +7269,10 @@
         <v>1.83</v>
       </c>
       <c r="I77" t="n">
-        <v>1.75</v>
+        <v>1.2384</v>
       </c>
       <c r="J77" t="n">
-        <v>36.75</v>
+        <v>26.0064</v>
       </c>
     </row>
     <row r="78">
@@ -7309,10 +7309,10 @@
         <v>1.59</v>
       </c>
       <c r="I78" t="n">
-        <v>1.339</v>
+        <v>0.952</v>
       </c>
       <c r="J78" t="n">
-        <v>28.119</v>
+        <v>19.992</v>
       </c>
     </row>
     <row r="79">
@@ -7349,10 +7349,10 @@
         <v>1.16</v>
       </c>
       <c r="I79" t="n">
-        <v>0.3443</v>
+        <v>0.3936</v>
       </c>
       <c r="J79" t="n">
-        <v>7.2303</v>
+        <v>8.265599999999999</v>
       </c>
     </row>
     <row r="80">
@@ -7389,10 +7389,10 @@
         <v>1.05</v>
       </c>
       <c r="I80" t="n">
-        <v>0.039</v>
+        <v>0.1223</v>
       </c>
       <c r="J80" t="n">
-        <v>0.819</v>
+        <v>2.5683</v>
       </c>
     </row>
     <row r="81">
@@ -7429,10 +7429,10 @@
         <v>1</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.1631</v>
+        <v>-0.0788</v>
       </c>
       <c r="J81" t="n">
-        <v>-3.4251</v>
+        <v>-1.6548</v>
       </c>
     </row>
     <row r="82">
@@ -7469,10 +7469,10 @@
         <v>1.09</v>
       </c>
       <c r="I82" t="n">
-        <v>0.2654</v>
+        <v>0.2085</v>
       </c>
       <c r="J82" t="n">
-        <v>7.1658</v>
+        <v>5.6295</v>
       </c>
     </row>
     <row r="83">
@@ -7509,10 +7509,10 @@
         <v>0.83</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.2896</v>
+        <v>-0.1919</v>
       </c>
       <c r="J83" t="n">
-        <v>-7.8192</v>
+        <v>-5.1813</v>
       </c>
     </row>
     <row r="84">
@@ -7549,10 +7549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.3235</v>
+        <v>-0.2118</v>
       </c>
       <c r="J84" t="n">
-        <v>-8.734500000000001</v>
+        <v>-5.7186</v>
       </c>
     </row>
     <row r="85">
@@ -7589,10 +7589,10 @@
         <v>0.79</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3558</v>
+        <v>-0.2315</v>
       </c>
       <c r="J85" t="n">
-        <v>-9.6066</v>
+        <v>-6.2505</v>
       </c>
     </row>
     <row r="86">
@@ -7629,10 +7629,10 @@
         <v>0.77</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3867</v>
+        <v>-0.2511</v>
       </c>
       <c r="J86" t="n">
-        <v>-10.4409</v>
+        <v>-6.7797</v>
       </c>
     </row>
     <row r="87">
@@ -7669,10 +7669,10 @@
         <v>1.46</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6576</v>
+        <v>0.4795</v>
       </c>
       <c r="J87" t="n">
-        <v>17.7552</v>
+        <v>12.9465</v>
       </c>
     </row>
     <row r="88">
@@ -7709,10 +7709,10 @@
         <v>1.44</v>
       </c>
       <c r="I88" t="n">
-        <v>0.6339</v>
+        <v>0.4664</v>
       </c>
       <c r="J88" t="n">
-        <v>17.1153</v>
+        <v>12.5928</v>
       </c>
     </row>
     <row r="89">
@@ -7749,10 +7749,10 @@
         <v>1.27</v>
       </c>
       <c r="I89" t="n">
-        <v>0.4158</v>
+        <v>0.3522</v>
       </c>
       <c r="J89" t="n">
-        <v>11.2266</v>
+        <v>9.509399999999999</v>
       </c>
     </row>
     <row r="90">
@@ -7789,10 +7789,10 @@
         <v>1.03</v>
       </c>
       <c r="I90" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0432</v>
       </c>
       <c r="J90" t="n">
-        <v>0.2673</v>
+        <v>1.1664</v>
       </c>
     </row>
     <row r="91">
@@ -7829,10 +7829,10 @@
         <v>0.77</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4589</v>
+        <v>-0.2887</v>
       </c>
       <c r="J91" t="n">
-        <v>-12.3903</v>
+        <v>-7.7949</v>
       </c>
     </row>
     <row r="92">
@@ -7869,10 +7869,10 @@
         <v>1.41</v>
       </c>
       <c r="I92" t="n">
-        <v>1.0451</v>
+        <v>0.7546</v>
       </c>
       <c r="J92" t="n">
-        <v>26.1275</v>
+        <v>18.865</v>
       </c>
     </row>
     <row r="93">
@@ -7909,10 +7909,10 @@
         <v>1.4</v>
       </c>
       <c r="I93" t="n">
-        <v>1.0238</v>
+        <v>0.7415</v>
       </c>
       <c r="J93" t="n">
-        <v>25.595</v>
+        <v>18.5375</v>
       </c>
     </row>
     <row r="94">
@@ -7949,10 +7949,10 @@
         <v>1.3</v>
       </c>
       <c r="I94" t="n">
-        <v>0.8012</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="J94" t="n">
-        <v>20.03</v>
+        <v>15.185</v>
       </c>
     </row>
     <row r="95">
@@ -7989,10 +7989,10 @@
         <v>0.95</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3231</v>
+        <v>-0.2464</v>
       </c>
       <c r="J95" t="n">
-        <v>-8.077500000000001</v>
+        <v>-6.16</v>
       </c>
     </row>
     <row r="96">
@@ -8029,10 +8029,10 @@
         <v>0.86</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5779</v>
+        <v>-0.512</v>
       </c>
       <c r="J96" t="n">
-        <v>-14.4475</v>
+        <v>-12.8</v>
       </c>
     </row>
     <row r="97">
@@ -8069,10 +8069,10 @@
         <v>1.12</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3079</v>
+        <v>0.3263</v>
       </c>
       <c r="J97" t="n">
-        <v>7.6975</v>
+        <v>8.157500000000001</v>
       </c>
     </row>
     <row r="98">
@@ -8109,10 +8109,10 @@
         <v>0.95</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.0621</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="J98" t="n">
-        <v>-1.5525</v>
+        <v>-1.5925</v>
       </c>
     </row>
     <row r="99">
@@ -8149,10 +8149,10 @@
         <v>0.91</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1402</v>
+        <v>-0.1113</v>
       </c>
       <c r="J99" t="n">
-        <v>-3.505</v>
+        <v>-2.7825</v>
       </c>
     </row>
     <row r="100">
@@ -8189,10 +8189,10 @@
         <v>0.84</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2815</v>
+        <v>-0.1839</v>
       </c>
       <c r="J100" t="n">
-        <v>-7.0375</v>
+        <v>-4.5975</v>
       </c>
     </row>
     <row r="101">
@@ -8229,10 +8229,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.6748</v>
+        <v>-0.4519</v>
       </c>
       <c r="J101" t="n">
-        <v>-16.87</v>
+        <v>-11.2975</v>
       </c>
     </row>
     <row r="102">
@@ -8269,10 +8269,10 @@
         <v>1.45</v>
       </c>
       <c r="I102" t="n">
-        <v>1.1764</v>
+        <v>0.8318</v>
       </c>
       <c r="J102" t="n">
-        <v>32.9392</v>
+        <v>23.2904</v>
       </c>
     </row>
     <row r="103">
@@ -8309,10 +8309,10 @@
         <v>1.1</v>
       </c>
       <c r="I103" t="n">
-        <v>0.3241</v>
+        <v>0.3224</v>
       </c>
       <c r="J103" t="n">
-        <v>9.0748</v>
+        <v>9.027200000000001</v>
       </c>
     </row>
     <row r="104">
@@ -8349,10 +8349,10 @@
         <v>1.05</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1408</v>
+        <v>0.1784</v>
       </c>
       <c r="J104" t="n">
-        <v>3.9424</v>
+        <v>4.9952</v>
       </c>
     </row>
     <row r="105">
@@ -8389,10 +8389,10 @@
         <v>1.01</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.0154</v>
+        <v>0.0338</v>
       </c>
       <c r="J105" t="n">
-        <v>-0.4312</v>
+        <v>0.9464</v>
       </c>
     </row>
     <row r="106">
@@ -8429,10 +8429,10 @@
         <v>0.85</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5748</v>
+        <v>-0.515</v>
       </c>
       <c r="J106" t="n">
-        <v>-16.0944</v>
+        <v>-14.42</v>
       </c>
     </row>
     <row r="107">
@@ -8469,10 +8469,10 @@
         <v>1.16</v>
       </c>
       <c r="I107" t="n">
-        <v>0.3309</v>
+        <v>0.3549</v>
       </c>
       <c r="J107" t="n">
-        <v>9.2652</v>
+        <v>9.937200000000001</v>
       </c>
     </row>
     <row r="108">
@@ -8509,10 +8509,10 @@
         <v>1.04</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1227</v>
+        <v>0.1197</v>
       </c>
       <c r="J108" t="n">
-        <v>3.4356</v>
+        <v>3.3516</v>
       </c>
     </row>
     <row r="109">
@@ -8549,10 +8549,10 @@
         <v>1.02</v>
       </c>
       <c r="I109" t="n">
-        <v>0.0774</v>
+        <v>0.0692</v>
       </c>
       <c r="J109" t="n">
-        <v>2.1672</v>
+        <v>1.9376</v>
       </c>
     </row>
     <row r="110">
@@ -8589,10 +8589,10 @@
         <v>0.98</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.0556</v>
+        <v>-0.0347</v>
       </c>
       <c r="J110" t="n">
-        <v>-1.5568</v>
+        <v>-0.9716</v>
       </c>
     </row>
     <row r="111">
@@ -8629,10 +8629,10 @@
         <v>0.71</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5037</v>
+        <v>-0.3247</v>
       </c>
       <c r="J111" t="n">
-        <v>-14.1036</v>
+        <v>-9.0916</v>
       </c>
     </row>
     <row r="112">
@@ -8669,10 +8669,10 @@
         <v>0.84</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.2097</v>
+        <v>-0.1717</v>
       </c>
       <c r="J112" t="n">
-        <v>-4.8231</v>
+        <v>-3.9491</v>
       </c>
     </row>
     <row r="113">
@@ -8709,10 +8709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.2606</v>
+        <v>-0.2026</v>
       </c>
       <c r="J113" t="n">
-        <v>-5.9938</v>
+        <v>-4.6598</v>
       </c>
     </row>
     <row r="114">
@@ -8749,10 +8749,10 @@
         <v>0.74</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.3945</v>
+        <v>-0.2686</v>
       </c>
       <c r="J114" t="n">
-        <v>-9.073499999999999</v>
+        <v>-6.1778</v>
       </c>
     </row>
     <row r="115">
@@ -8789,10 +8789,10 @@
         <v>0.74</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3945</v>
+        <v>-0.2686</v>
       </c>
       <c r="J115" t="n">
-        <v>-9.073499999999999</v>
+        <v>-6.1778</v>
       </c>
     </row>
     <row r="116">
@@ -8829,10 +8829,10 @@
         <v>0.72</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.427</v>
+        <v>-0.2874</v>
       </c>
       <c r="J116" t="n">
-        <v>-9.821</v>
+        <v>-6.6102</v>
       </c>
     </row>
     <row r="117">
@@ -8869,10 +8869,10 @@
         <v>1.65</v>
       </c>
       <c r="I117" t="n">
-        <v>1.4546</v>
+        <v>1.0255</v>
       </c>
       <c r="J117" t="n">
-        <v>33.4558</v>
+        <v>23.5865</v>
       </c>
     </row>
     <row r="118">
@@ -8909,10 +8909,10 @@
         <v>1.49</v>
       </c>
       <c r="I118" t="n">
-        <v>1.1425</v>
+        <v>0.8299</v>
       </c>
       <c r="J118" t="n">
-        <v>26.2775</v>
+        <v>19.0877</v>
       </c>
     </row>
     <row r="119">
@@ -8949,10 +8949,10 @@
         <v>1.33</v>
       </c>
       <c r="I119" t="n">
-        <v>0.7822</v>
+        <v>0.6289</v>
       </c>
       <c r="J119" t="n">
-        <v>17.9906</v>
+        <v>14.4647</v>
       </c>
     </row>
     <row r="120">
@@ -8989,10 +8989,10 @@
         <v>1.14</v>
       </c>
       <c r="I120" t="n">
-        <v>0.2943</v>
+        <v>0.3633</v>
       </c>
       <c r="J120" t="n">
-        <v>6.7689</v>
+        <v>8.3559</v>
       </c>
     </row>
     <row r="121">
@@ -9029,10 +9029,10 @@
         <v>1</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.162</v>
+        <v>-0.0779</v>
       </c>
       <c r="J121" t="n">
-        <v>-3.726</v>
+        <v>-1.7917</v>
       </c>
     </row>
     <row r="122">
@@ -9069,10 +9069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.0523</v>
+        <v>-0.065</v>
       </c>
       <c r="J122" t="n">
-        <v>-1.1506</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="123">
@@ -9109,10 +9109,10 @@
         <v>0.93</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.0712</v>
+        <v>-0.0775</v>
       </c>
       <c r="J123" t="n">
-        <v>-1.5664</v>
+        <v>-1.705</v>
       </c>
     </row>
     <row r="124">
@@ -9149,10 +9149,10 @@
         <v>0.83</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2497</v>
+        <v>-0.1877</v>
       </c>
       <c r="J124" t="n">
-        <v>-5.4934</v>
+        <v>-4.1294</v>
       </c>
     </row>
     <row r="125">
@@ -9189,10 +9189,10 @@
         <v>0.78</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3496</v>
+        <v>-0.2354</v>
       </c>
       <c r="J125" t="n">
-        <v>-7.6912</v>
+        <v>-5.1788</v>
       </c>
     </row>
     <row r="126">
@@ -9229,10 +9229,10 @@
         <v>0.57</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.649</v>
+        <v>-0.4341</v>
       </c>
       <c r="J126" t="n">
-        <v>-14.278</v>
+        <v>-9.5502</v>
       </c>
     </row>
     <row r="127">
@@ -9269,10 +9269,10 @@
         <v>1.57</v>
       </c>
       <c r="I127" t="n">
-        <v>1.3188</v>
+        <v>0.9358</v>
       </c>
       <c r="J127" t="n">
-        <v>29.0136</v>
+        <v>20.5876</v>
       </c>
     </row>
     <row r="128">
@@ -9309,10 +9309,10 @@
         <v>1.36</v>
       </c>
       <c r="I128" t="n">
-        <v>0.881</v>
+        <v>0.6712</v>
       </c>
       <c r="J128" t="n">
-        <v>19.382</v>
+        <v>14.7664</v>
       </c>
     </row>
     <row r="129">
@@ -9349,10 +9349,10 @@
         <v>1.31</v>
       </c>
       <c r="I129" t="n">
-        <v>0.7606000000000001</v>
+        <v>0.6065</v>
       </c>
       <c r="J129" t="n">
-        <v>16.7332</v>
+        <v>13.343</v>
       </c>
     </row>
     <row r="130">
@@ -9389,10 +9389,10 @@
         <v>1.25</v>
       </c>
       <c r="I130" t="n">
-        <v>0.5901</v>
+        <v>0.5281</v>
       </c>
       <c r="J130" t="n">
-        <v>12.9822</v>
+        <v>11.6182</v>
       </c>
     </row>
     <row r="131">
@@ -9429,10 +9429,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3851</v>
+        <v>-0.3034</v>
       </c>
       <c r="J131" t="n">
-        <v>-8.472200000000001</v>
+        <v>-6.6748</v>
       </c>
     </row>
     <row r="132">
@@ -9469,10 +9469,10 @@
         <v>0.63</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.3662</v>
+        <v>-0.3069</v>
       </c>
       <c r="J132" t="n">
-        <v>-6.9578</v>
+        <v>-5.8311</v>
       </c>
     </row>
     <row r="133">
@@ -9509,10 +9509,10 @@
         <v>0.59</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.4276</v>
+        <v>-0.3502</v>
       </c>
       <c r="J133" t="n">
-        <v>-8.1244</v>
+        <v>-6.6538</v>
       </c>
     </row>
     <row r="134">
@@ -9549,10 +9549,10 @@
         <v>0.55</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.4904</v>
+        <v>-0.3919</v>
       </c>
       <c r="J134" t="n">
-        <v>-9.317600000000001</v>
+        <v>-7.4461</v>
       </c>
     </row>
     <row r="135">
@@ -9589,10 +9589,10 @@
         <v>0.43</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.7163</v>
+        <v>-0.5037</v>
       </c>
       <c r="J135" t="n">
-        <v>-13.6097</v>
+        <v>-9.5703</v>
       </c>
     </row>
     <row r="136">
@@ -9629,10 +9629,10 @@
         <v>0.16</v>
       </c>
       <c r="I136" t="n">
-        <v>-1.0921</v>
+        <v>-0.7771</v>
       </c>
       <c r="J136" t="n">
-        <v>-20.7499</v>
+        <v>-14.7649</v>
       </c>
     </row>
     <row r="137">
@@ -9669,10 +9669,10 @@
         <v>1.93</v>
       </c>
       <c r="I137" t="n">
-        <v>1.7962</v>
+        <v>1.3015</v>
       </c>
       <c r="J137" t="n">
-        <v>34.1278</v>
+        <v>24.7285</v>
       </c>
     </row>
     <row r="138">
@@ -9709,10 +9709,10 @@
         <v>1.56</v>
       </c>
       <c r="I138" t="n">
-        <v>1.1641</v>
+        <v>0.8852</v>
       </c>
       <c r="J138" t="n">
-        <v>22.1179</v>
+        <v>16.8188</v>
       </c>
     </row>
     <row r="139">
@@ -9749,10 +9749,10 @@
         <v>1.52</v>
       </c>
       <c r="I139" t="n">
-        <v>1.0629</v>
+        <v>0.84</v>
       </c>
       <c r="J139" t="n">
-        <v>20.1951</v>
+        <v>15.96</v>
       </c>
     </row>
     <row r="140">
@@ -9789,10 +9789,10 @@
         <v>1.46</v>
       </c>
       <c r="I140" t="n">
-        <v>0.9345</v>
+        <v>0.7689</v>
       </c>
       <c r="J140" t="n">
-        <v>17.7555</v>
+        <v>14.6091</v>
       </c>
     </row>
     <row r="141">
@@ -9829,10 +9829,10 @@
         <v>1.28</v>
       </c>
       <c r="I141" t="n">
-        <v>0.5531</v>
+        <v>0.5381</v>
       </c>
       <c r="J141" t="n">
-        <v>10.5089</v>
+        <v>10.2239</v>
       </c>
     </row>
     <row r="142">
@@ -9869,10 +9869,10 @@
         <v>1.57</v>
       </c>
       <c r="I142" t="n">
-        <v>0.8011</v>
+        <v>0.5594</v>
       </c>
       <c r="J142" t="n">
-        <v>20.0275</v>
+        <v>13.985</v>
       </c>
     </row>
     <row r="143">
@@ -9909,10 +9909,10 @@
         <v>1.24</v>
       </c>
       <c r="I143" t="n">
-        <v>0.3953</v>
+        <v>0.3336</v>
       </c>
       <c r="J143" t="n">
-        <v>9.8825</v>
+        <v>8.34</v>
       </c>
     </row>
     <row r="144">
@@ -9949,10 +9949,10 @@
         <v>1.16</v>
       </c>
       <c r="I144" t="n">
-        <v>0.2735</v>
+        <v>0.2383</v>
       </c>
       <c r="J144" t="n">
-        <v>6.8375</v>
+        <v>5.9575</v>
       </c>
     </row>
     <row r="145">
@@ -9989,10 +9989,10 @@
         <v>1.11</v>
       </c>
       <c r="I145" t="n">
-        <v>0.1771</v>
+        <v>0.1735</v>
       </c>
       <c r="J145" t="n">
-        <v>4.4275</v>
+        <v>4.3375</v>
       </c>
     </row>
     <row r="146">
@@ -10029,10 +10029,10 @@
         <v>0.58</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.6856</v>
+        <v>-0.4595</v>
       </c>
       <c r="J146" t="n">
-        <v>-17.14</v>
+        <v>-11.4875</v>
       </c>
     </row>
     <row r="147">
@@ -10069,10 +10069,10 @@
         <v>1.56</v>
       </c>
       <c r="I147" t="n">
-        <v>0.8386</v>
+        <v>0.6158</v>
       </c>
       <c r="J147" t="n">
-        <v>20.965</v>
+        <v>15.395</v>
       </c>
     </row>
     <row r="148">
@@ -10109,10 +10109,10 @@
         <v>1</v>
       </c>
       <c r="I148" t="n">
-        <v>0.0156</v>
+        <v>0.0019</v>
       </c>
       <c r="J148" t="n">
-        <v>0.39</v>
+        <v>0.0475</v>
       </c>
     </row>
     <row r="149">
@@ -10149,10 +10149,10 @@
         <v>0.91</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2036</v>
+        <v>-0.1209</v>
       </c>
       <c r="J149" t="n">
-        <v>-5.09</v>
+        <v>-3.0225</v>
       </c>
     </row>
     <row r="150">
@@ -10189,10 +10189,10 @@
         <v>0.83</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3343</v>
+        <v>-0.2063</v>
       </c>
       <c r="J150" t="n">
-        <v>-8.3575</v>
+        <v>-5.1575</v>
       </c>
     </row>
     <row r="151">
@@ -10229,10 +10229,10 @@
         <v>0.6</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6429</v>
+        <v>-0.4271</v>
       </c>
       <c r="J151" t="n">
-        <v>-16.0725</v>
+        <v>-10.6775</v>
       </c>
     </row>
     <row r="152">
@@ -10269,10 +10269,10 @@
         <v>1.01</v>
       </c>
       <c r="I152" t="n">
-        <v>0.1405</v>
+        <v>0.1093</v>
       </c>
       <c r="J152" t="n">
-        <v>3.2315</v>
+        <v>2.5139</v>
       </c>
     </row>
     <row r="153">
@@ -10309,10 +10309,10 @@
         <v>0.76</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.3621</v>
+        <v>-0.2503</v>
       </c>
       <c r="J153" t="n">
-        <v>-8.3283</v>
+        <v>-5.7569</v>
       </c>
     </row>
     <row r="154">
@@ -10349,10 +10349,10 @@
         <v>0.72</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.4289</v>
+        <v>-0.2879</v>
       </c>
       <c r="J154" t="n">
-        <v>-9.864699999999999</v>
+        <v>-6.6217</v>
       </c>
     </row>
     <row r="155">
@@ -10389,10 +10389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4745</v>
+        <v>-0.3163</v>
       </c>
       <c r="J155" t="n">
-        <v>-10.9135</v>
+        <v>-7.2749</v>
       </c>
     </row>
     <row r="156">
@@ -10429,10 +10429,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4745</v>
+        <v>-0.3163</v>
       </c>
       <c r="J156" t="n">
-        <v>-10.9135</v>
+        <v>-7.2749</v>
       </c>
     </row>
     <row r="157">
@@ -10469,10 +10469,10 @@
         <v>1.66</v>
       </c>
       <c r="I157" t="n">
-        <v>1.4786</v>
+        <v>1.0402</v>
       </c>
       <c r="J157" t="n">
-        <v>34.0078</v>
+        <v>23.9246</v>
       </c>
     </row>
     <row r="158">
@@ -10509,10 +10509,10 @@
         <v>1.36</v>
       </c>
       <c r="I158" t="n">
-        <v>0.8663</v>
+        <v>0.6681</v>
       </c>
       <c r="J158" t="n">
-        <v>19.9249</v>
+        <v>15.3663</v>
       </c>
     </row>
     <row r="159">
@@ -10549,10 +10549,10 @@
         <v>1.34</v>
       </c>
       <c r="I159" t="n">
-        <v>0.8181</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="J159" t="n">
-        <v>18.8163</v>
+        <v>14.7798</v>
       </c>
     </row>
     <row r="160">
@@ -10589,10 +10589,10 @@
         <v>1.12</v>
       </c>
       <c r="I160" t="n">
-        <v>0.2458</v>
+        <v>0.3294</v>
       </c>
       <c r="J160" t="n">
-        <v>5.6534</v>
+        <v>7.5762</v>
       </c>
     </row>
     <row r="161">
@@ -10629,10 +10629,10 @@
         <v>1.07</v>
       </c>
       <c r="I161" t="n">
-        <v>0.1052</v>
+        <v>0.1887</v>
       </c>
       <c r="J161" t="n">
-        <v>2.4196</v>
+        <v>4.3401</v>
       </c>
     </row>
     <row r="162">
@@ -10669,10 +10669,10 @@
         <v>1.9</v>
       </c>
       <c r="I162" t="n">
-        <v>1.7788</v>
+        <v>1.2779</v>
       </c>
       <c r="J162" t="n">
-        <v>32.0184</v>
+        <v>23.0022</v>
       </c>
     </row>
     <row r="163">
@@ -10709,10 +10709,10 @@
         <v>1.61</v>
       </c>
       <c r="I163" t="n">
-        <v>1.2979</v>
+        <v>0.9475</v>
       </c>
       <c r="J163" t="n">
-        <v>23.3622</v>
+        <v>17.055</v>
       </c>
     </row>
     <row r="164">
@@ -10749,10 +10749,10 @@
         <v>1.52</v>
       </c>
       <c r="I164" t="n">
-        <v>1.1091</v>
+        <v>0.8431999999999999</v>
       </c>
       <c r="J164" t="n">
-        <v>19.9638</v>
+        <v>15.1776</v>
       </c>
     </row>
     <row r="165">
@@ -10789,10 +10789,10 @@
         <v>1.49</v>
       </c>
       <c r="I165" t="n">
-        <v>1.0288</v>
+        <v>0.8089</v>
       </c>
       <c r="J165" t="n">
-        <v>18.5184</v>
+        <v>14.5602</v>
       </c>
     </row>
     <row r="166">
@@ -10829,10 +10829,10 @@
         <v>0.98</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3004</v>
+        <v>-0.2107</v>
       </c>
       <c r="J166" t="n">
-        <v>-5.4072</v>
+        <v>-3.7926</v>
       </c>
     </row>
     <row r="167">
@@ -10869,10 +10869,10 @@
         <v>0.65</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.3724</v>
+        <v>-0.3074</v>
       </c>
       <c r="J167" t="n">
-        <v>-6.7032</v>
+        <v>-5.5332</v>
       </c>
     </row>
     <row r="168">
@@ -10909,10 +10909,10 @@
         <v>0.59</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.466</v>
+        <v>-0.3685</v>
       </c>
       <c r="J168" t="n">
-        <v>-8.388</v>
+        <v>-6.633</v>
       </c>
     </row>
     <row r="169">
@@ -10949,10 +10949,10 @@
         <v>0.59</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.466</v>
+        <v>-0.3685</v>
       </c>
       <c r="J169" t="n">
-        <v>-8.388</v>
+        <v>-6.633</v>
       </c>
     </row>
     <row r="170">
@@ -10989,10 +10989,10 @@
         <v>0.41</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.7756999999999999</v>
+        <v>-0.5354</v>
       </c>
       <c r="J170" t="n">
-        <v>-13.9626</v>
+        <v>-9.6372</v>
       </c>
     </row>
     <row r="171">
@@ -11029,10 +11029,10 @@
         <v>0.39</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.5548</v>
       </c>
       <c r="J171" t="n">
-        <v>-14.4702</v>
+        <v>-9.9864</v>
       </c>
     </row>
     <row r="172">
@@ -11069,10 +11069,10 @@
         <v>1.44</v>
       </c>
       <c r="I172" t="n">
-        <v>1.158</v>
+        <v>0.8196</v>
       </c>
       <c r="J172" t="n">
-        <v>31.266</v>
+        <v>22.1292</v>
       </c>
     </row>
     <row r="173">
@@ -11109,10 +11109,10 @@
         <v>1.21</v>
       </c>
       <c r="I173" t="n">
-        <v>0.6395</v>
+        <v>0.4978</v>
       </c>
       <c r="J173" t="n">
-        <v>17.2665</v>
+        <v>13.4406</v>
       </c>
     </row>
     <row r="174">
@@ -11149,10 +11149,10 @@
         <v>1.2</v>
       </c>
       <c r="I174" t="n">
-        <v>0.6141</v>
+        <v>0.483</v>
       </c>
       <c r="J174" t="n">
-        <v>16.5807</v>
+        <v>13.041</v>
       </c>
     </row>
     <row r="175">
@@ -11189,10 +11189,10 @@
         <v>1.06</v>
       </c>
       <c r="I175" t="n">
-        <v>0.1789</v>
+        <v>0.2106</v>
       </c>
       <c r="J175" t="n">
-        <v>4.8303</v>
+        <v>5.6862</v>
       </c>
     </row>
     <row r="176">
@@ -11229,10 +11229,10 @@
         <v>0.53</v>
       </c>
       <c r="I176" t="n">
-        <v>-1.2854</v>
+        <v>-1.3002</v>
       </c>
       <c r="J176" t="n">
-        <v>-34.7058</v>
+        <v>-35.1054</v>
       </c>
     </row>
     <row r="177">
@@ -11269,10 +11269,10 @@
         <v>1.29</v>
       </c>
       <c r="I177" t="n">
-        <v>0.5133</v>
+        <v>0.4947</v>
       </c>
       <c r="J177" t="n">
-        <v>13.8591</v>
+        <v>13.3569</v>
       </c>
     </row>
     <row r="178">
@@ -11309,10 +11309,10 @@
         <v>1.12</v>
       </c>
       <c r="I178" t="n">
-        <v>0.2681</v>
+        <v>0.2915</v>
       </c>
       <c r="J178" t="n">
-        <v>7.2387</v>
+        <v>7.8705</v>
       </c>
     </row>
     <row r="179">
@@ -11349,10 +11349,10 @@
         <v>1.04</v>
       </c>
       <c r="I179" t="n">
-        <v>0.1227</v>
+        <v>0.1197</v>
       </c>
       <c r="J179" t="n">
-        <v>3.3129</v>
+        <v>3.2319</v>
       </c>
     </row>
     <row r="180">
@@ -11389,10 +11389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1479</v>
+        <v>-0.0863</v>
       </c>
       <c r="J180" t="n">
-        <v>-3.9933</v>
+        <v>-2.3301</v>
       </c>
     </row>
     <row r="181">
@@ -11429,10 +11429,10 @@
         <v>0.52</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.7385</v>
+        <v>-0.4998</v>
       </c>
       <c r="J181" t="n">
-        <v>-19.9395</v>
+        <v>-13.4946</v>
       </c>
     </row>
     <row r="182">
@@ -11469,10 +11469,10 @@
         <v>1.39</v>
       </c>
       <c r="I182" t="n">
-        <v>0.5888</v>
+        <v>0.5127</v>
       </c>
       <c r="J182" t="n">
-        <v>15.8976</v>
+        <v>13.8429</v>
       </c>
     </row>
     <row r="183">
@@ -11509,10 +11509,10 @@
         <v>1.23</v>
       </c>
       <c r="I183" t="n">
-        <v>0.3774</v>
+        <v>0.3242</v>
       </c>
       <c r="J183" t="n">
-        <v>10.1898</v>
+        <v>8.753399999999999</v>
       </c>
     </row>
     <row r="184">
@@ -11549,10 +11549,10 @@
         <v>1.16</v>
       </c>
       <c r="I184" t="n">
-        <v>0.2686</v>
+        <v>0.2373</v>
       </c>
       <c r="J184" t="n">
-        <v>7.2522</v>
+        <v>6.4071</v>
       </c>
     </row>
     <row r="185">
@@ -11589,10 +11589,10 @@
         <v>1.08</v>
       </c>
       <c r="I185" t="n">
-        <v>0.1193</v>
+        <v>0.13</v>
       </c>
       <c r="J185" t="n">
-        <v>3.2211</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="186">
@@ -11629,10 +11629,10 @@
         <v>0.85</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3398</v>
+        <v>-0.2034</v>
       </c>
       <c r="J186" t="n">
-        <v>-9.1746</v>
+        <v>-5.4918</v>
       </c>
     </row>
     <row r="187">
@@ -11669,10 +11669,10 @@
         <v>1.16</v>
       </c>
       <c r="I187" t="n">
-        <v>0.3497</v>
+        <v>0.2965</v>
       </c>
       <c r="J187" t="n">
-        <v>9.4419</v>
+        <v>8.0055</v>
       </c>
     </row>
     <row r="188">
@@ -11709,10 +11709,10 @@
         <v>1.08</v>
       </c>
       <c r="I188" t="n">
-        <v>0.2201</v>
+        <v>0.1715</v>
       </c>
       <c r="J188" t="n">
-        <v>5.9427</v>
+        <v>4.6305</v>
       </c>
     </row>
     <row r="189">
@@ -11749,10 +11749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1114</v>
+        <v>-0.0822</v>
       </c>
       <c r="J189" t="n">
-        <v>-3.0078</v>
+        <v>-2.2194</v>
       </c>
     </row>
     <row r="190">
@@ -11789,10 +11789,10 @@
         <v>0.79</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3801</v>
+        <v>-0.2406</v>
       </c>
       <c r="J190" t="n">
-        <v>-10.2627</v>
+        <v>-6.4962</v>
       </c>
     </row>
     <row r="191">
@@ -11829,10 +11829,10 @@
         <v>0.68</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.3469</v>
       </c>
       <c r="J191" t="n">
-        <v>-14.3856</v>
+        <v>-9.366300000000001</v>
       </c>
     </row>
     <row r="192">
@@ -11869,10 +11869,10 @@
         <v>1.25</v>
       </c>
       <c r="I192" t="n">
-        <v>0.4415</v>
+        <v>0.5172</v>
       </c>
       <c r="J192" t="n">
-        <v>13.245</v>
+        <v>15.516</v>
       </c>
     </row>
     <row r="193">
@@ -11909,10 +11909,10 @@
         <v>1.07</v>
       </c>
       <c r="I193" t="n">
-        <v>0.1584</v>
+        <v>0.1765</v>
       </c>
       <c r="J193" t="n">
-        <v>4.752</v>
+        <v>5.295</v>
       </c>
     </row>
     <row r="194">
@@ -11949,10 +11949,10 @@
         <v>0.98</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.0842</v>
+        <v>-0.0393</v>
       </c>
       <c r="J194" t="n">
-        <v>-2.526</v>
+        <v>-1.179</v>
       </c>
     </row>
     <row r="195">
@@ -11989,10 +11989,10 @@
         <v>0.95</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1485</v>
+        <v>-0.0796</v>
       </c>
       <c r="J195" t="n">
-        <v>-4.455</v>
+        <v>-2.388</v>
       </c>
     </row>
     <row r="196">
@@ -12029,10 +12029,10 @@
         <v>0.93</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.1862</v>
+        <v>-0.1039</v>
       </c>
       <c r="J196" t="n">
-        <v>-5.586</v>
+        <v>-3.117</v>
       </c>
     </row>
     <row r="197">
@@ -12069,10 +12069,10 @@
         <v>1.16</v>
       </c>
       <c r="I197" t="n">
-        <v>0.5632</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="J197" t="n">
-        <v>16.896</v>
+        <v>15.438</v>
       </c>
     </row>
     <row r="198">
@@ -12109,10 +12109,10 @@
         <v>1.04</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1976</v>
+        <v>0.1638</v>
       </c>
       <c r="J198" t="n">
-        <v>5.928</v>
+        <v>4.914</v>
       </c>
     </row>
     <row r="199">
@@ -12149,10 +12149,10 @@
         <v>0.97</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1622</v>
+        <v>-0.1304</v>
       </c>
       <c r="J199" t="n">
-        <v>-4.866</v>
+        <v>-3.912</v>
       </c>
     </row>
     <row r="200">
@@ -12189,10 +12189,10 @@
         <v>0.93</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.3046</v>
+        <v>-0.2605</v>
       </c>
       <c r="J200" t="n">
-        <v>-9.138</v>
+        <v>-7.815</v>
       </c>
     </row>
     <row r="201">
@@ -12229,10 +12229,10 @@
         <v>0.91</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3675</v>
+        <v>-0.3203</v>
       </c>
       <c r="J201" t="n">
-        <v>-11.025</v>
+        <v>-9.609</v>
       </c>
     </row>
     <row r="202">
@@ -12269,10 +12269,10 @@
         <v>1.15</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3457</v>
+        <v>0.3796</v>
       </c>
       <c r="J202" t="n">
-        <v>10.371</v>
+        <v>11.388</v>
       </c>
     </row>
     <row r="203">
@@ -12309,10 +12309,10 @@
         <v>0.89</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.2023</v>
+        <v>-0.1347</v>
       </c>
       <c r="J203" t="n">
-        <v>-6.069</v>
+        <v>-4.041</v>
       </c>
     </row>
     <row r="204">
@@ -12349,10 +12349,10 @@
         <v>0.85</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2755</v>
+        <v>-0.1763</v>
       </c>
       <c r="J204" t="n">
-        <v>-8.265000000000001</v>
+        <v>-5.289</v>
       </c>
     </row>
     <row r="205">
@@ -12389,10 +12389,10 @@
         <v>0.82</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3246</v>
+        <v>-0.2068</v>
       </c>
       <c r="J205" t="n">
-        <v>-9.738</v>
+        <v>-6.204</v>
       </c>
     </row>
     <row r="206">
@@ -12429,10 +12429,10 @@
         <v>0.79</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3709</v>
+        <v>-0.2368</v>
       </c>
       <c r="J206" t="n">
-        <v>-11.127</v>
+        <v>-7.104</v>
       </c>
     </row>
     <row r="207">
@@ -12469,10 +12469,10 @@
         <v>1.55</v>
       </c>
       <c r="I207" t="n">
-        <v>1.318</v>
+        <v>1.2036</v>
       </c>
       <c r="J207" t="n">
-        <v>39.54</v>
+        <v>36.108</v>
       </c>
     </row>
     <row r="208">
@@ -12509,10 +12509,10 @@
         <v>1.19</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4868</v>
+        <v>0.5357</v>
       </c>
       <c r="J208" t="n">
-        <v>14.604</v>
+        <v>16.071</v>
       </c>
     </row>
     <row r="209">
@@ -12549,10 +12549,10 @@
         <v>1.18</v>
       </c>
       <c r="I209" t="n">
-        <v>0.458</v>
+        <v>0.5114</v>
       </c>
       <c r="J209" t="n">
-        <v>13.74</v>
+        <v>15.342</v>
       </c>
     </row>
     <row r="210">
@@ -12589,10 +12589,10 @@
         <v>1.06</v>
       </c>
       <c r="I210" t="n">
-        <v>0.113</v>
+        <v>0.1827</v>
       </c>
       <c r="J210" t="n">
-        <v>3.39</v>
+        <v>5.481</v>
       </c>
     </row>
     <row r="211">
@@ -12629,10 +12629,10 @@
         <v>1.05</v>
       </c>
       <c r="I211" t="n">
-        <v>0.081</v>
+        <v>0.1508</v>
       </c>
       <c r="J211" t="n">
-        <v>2.43</v>
+        <v>4.524</v>
       </c>
     </row>
     <row r="212">
@@ -12669,10 +12669,10 @@
         <v>1.29</v>
       </c>
       <c r="I212" t="n">
-        <v>0.475</v>
+        <v>0.4043</v>
       </c>
       <c r="J212" t="n">
-        <v>17.1</v>
+        <v>14.5548</v>
       </c>
     </row>
     <row r="213">
@@ -12709,10 +12709,10 @@
         <v>1.19</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3344</v>
+        <v>0.2809</v>
       </c>
       <c r="J213" t="n">
-        <v>12.0384</v>
+        <v>10.1124</v>
       </c>
     </row>
     <row r="214">
@@ -12749,10 +12749,10 @@
         <v>1.16</v>
       </c>
       <c r="I214" t="n">
-        <v>0.2881</v>
+        <v>0.2424</v>
       </c>
       <c r="J214" t="n">
-        <v>10.3716</v>
+        <v>8.7264</v>
       </c>
     </row>
     <row r="215">
@@ -12789,10 +12789,10 @@
         <v>0.98</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.1043</v>
+        <v>-0.0455</v>
       </c>
       <c r="J215" t="n">
-        <v>-3.7548</v>
+        <v>-1.638</v>
       </c>
     </row>
     <row r="216">
@@ -12829,10 +12829,10 @@
         <v>0.87</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3013</v>
+        <v>-0.1777</v>
       </c>
       <c r="J216" t="n">
-        <v>-10.8468</v>
+        <v>-6.3972</v>
       </c>
     </row>
     <row r="217">
@@ -12869,10 +12869,10 @@
         <v>1.2</v>
       </c>
       <c r="I217" t="n">
-        <v>0.3864</v>
+        <v>0.3377</v>
       </c>
       <c r="J217" t="n">
-        <v>13.9104</v>
+        <v>12.1572</v>
       </c>
     </row>
     <row r="218">
@@ -12909,10 +12909,10 @@
         <v>1.07</v>
       </c>
       <c r="I218" t="n">
-        <v>0.1776</v>
+        <v>0.1419</v>
       </c>
       <c r="J218" t="n">
-        <v>6.3936</v>
+        <v>5.1084</v>
       </c>
     </row>
     <row r="219">
@@ -12949,10 +12949,10 @@
         <v>0.97</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.0882</v>
+        <v>-0.0493</v>
       </c>
       <c r="J219" t="n">
-        <v>-3.1752</v>
+        <v>-1.7748</v>
       </c>
     </row>
     <row r="220">
@@ -12989,10 +12989,10 @@
         <v>0.86</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2912</v>
+        <v>-0.1765</v>
       </c>
       <c r="J220" t="n">
-        <v>-10.4832</v>
+        <v>-6.354</v>
       </c>
     </row>
     <row r="221">
@@ -13029,10 +13029,10 @@
         <v>0.86</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.2912</v>
+        <v>-0.1765</v>
       </c>
       <c r="J221" t="n">
-        <v>-10.4832</v>
+        <v>-6.354</v>
       </c>
     </row>
     <row r="222">
@@ -13069,10 +13069,10 @@
         <v>1.28</v>
       </c>
       <c r="I222" t="n">
-        <v>0.5077</v>
+        <v>0.598</v>
       </c>
       <c r="J222" t="n">
-        <v>14.2156</v>
+        <v>16.744</v>
       </c>
     </row>
     <row r="223">
@@ -13109,10 +13109,10 @@
         <v>1.06</v>
       </c>
       <c r="I223" t="n">
-        <v>0.1718</v>
+        <v>0.1713</v>
       </c>
       <c r="J223" t="n">
-        <v>4.8104</v>
+        <v>4.7964</v>
       </c>
     </row>
     <row r="224">
@@ -13149,10 +13149,10 @@
         <v>0.93</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1576</v>
+        <v>-0.096</v>
       </c>
       <c r="J224" t="n">
-        <v>-4.4128</v>
+        <v>-2.688</v>
       </c>
     </row>
     <row r="225">
@@ -13189,10 +13189,10 @@
         <v>0.86</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2814</v>
+        <v>-0.1728</v>
       </c>
       <c r="J225" t="n">
-        <v>-7.8792</v>
+        <v>-4.8384</v>
       </c>
     </row>
     <row r="226">
@@ -13229,10 +13229,10 @@
         <v>0.67</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.5518</v>
+        <v>-0.36</v>
       </c>
       <c r="J226" t="n">
-        <v>-15.4504</v>
+        <v>-10.08</v>
       </c>
     </row>
     <row r="227">
@@ -13269,10 +13269,10 @@
         <v>1.6</v>
       </c>
       <c r="I227" t="n">
-        <v>1.4523</v>
+        <v>1.2896</v>
       </c>
       <c r="J227" t="n">
-        <v>40.6644</v>
+        <v>36.1088</v>
       </c>
     </row>
     <row r="228">
@@ -13309,10 +13309,10 @@
         <v>1.36</v>
       </c>
       <c r="I228" t="n">
-        <v>0.966</v>
+        <v>0.9524</v>
       </c>
       <c r="J228" t="n">
-        <v>27.048</v>
+        <v>26.6672</v>
       </c>
     </row>
     <row r="229">
@@ -13349,10 +13349,10 @@
         <v>1.07</v>
       </c>
       <c r="I229" t="n">
-        <v>0.1831</v>
+        <v>0.2316</v>
       </c>
       <c r="J229" t="n">
-        <v>5.1268</v>
+        <v>6.4848</v>
       </c>
     </row>
     <row r="230">
@@ -13389,10 +13389,10 @@
         <v>1.03</v>
       </c>
       <c r="I230" t="n">
-        <v>0.0464</v>
+        <v>0.102</v>
       </c>
       <c r="J230" t="n">
-        <v>1.2992</v>
+        <v>2.856</v>
       </c>
     </row>
     <row r="231">
@@ -13429,10 +13429,10 @@
         <v>0.59</v>
       </c>
       <c r="I231" t="n">
-        <v>-1.1722</v>
+        <v>-1.1703</v>
       </c>
       <c r="J231" t="n">
-        <v>-32.8216</v>
+        <v>-32.7684</v>
       </c>
     </row>
     <row r="232">
@@ -13469,10 +13469,10 @@
         <v>1.33</v>
       </c>
       <c r="I232" t="n">
-        <v>0.5684</v>
+        <v>0.6807</v>
       </c>
       <c r="J232" t="n">
-        <v>15.9152</v>
+        <v>19.0596</v>
       </c>
     </row>
     <row r="233">
@@ -13509,10 +13509,10 @@
         <v>0.97</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.0746</v>
+        <v>-0.0479</v>
       </c>
       <c r="J233" t="n">
-        <v>-2.0888</v>
+        <v>-1.3412</v>
       </c>
     </row>
     <row r="234">
@@ -13549,10 +13549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.1433</v>
+        <v>-0.0854</v>
       </c>
       <c r="J234" t="n">
-        <v>-4.0124</v>
+        <v>-2.3912</v>
       </c>
     </row>
     <row r="235">
@@ -13589,10 +13589,10 @@
         <v>0.86</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.2853</v>
+        <v>-0.1742</v>
       </c>
       <c r="J235" t="n">
-        <v>-7.9884</v>
+        <v>-4.8776</v>
       </c>
     </row>
     <row r="236">
@@ -13629,10 +13629,10 @@
         <v>0.76</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4338</v>
+        <v>-0.2753</v>
       </c>
       <c r="J236" t="n">
-        <v>-12.1464</v>
+        <v>-7.7084</v>
       </c>
     </row>
     <row r="237">
@@ -13669,10 +13669,10 @@
         <v>1.47</v>
       </c>
       <c r="I237" t="n">
-        <v>1.2024</v>
+        <v>1.1238</v>
       </c>
       <c r="J237" t="n">
-        <v>33.6672</v>
+        <v>31.4664</v>
       </c>
     </row>
     <row r="238">
@@ -13709,10 +13709,10 @@
         <v>1.23</v>
       </c>
       <c r="I238" t="n">
-        <v>0.6702</v>
+        <v>0.6511</v>
       </c>
       <c r="J238" t="n">
-        <v>18.7656</v>
+        <v>18.2308</v>
       </c>
     </row>
     <row r="239">
@@ -13749,10 +13749,10 @@
         <v>1.21</v>
       </c>
       <c r="I239" t="n">
-        <v>0.6197</v>
+        <v>0.602</v>
       </c>
       <c r="J239" t="n">
-        <v>17.3516</v>
+        <v>16.856</v>
       </c>
     </row>
     <row r="240">
@@ -13789,10 +13789,10 @@
         <v>0.85</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.5842000000000001</v>
+        <v>-0.5226</v>
       </c>
       <c r="J240" t="n">
-        <v>-16.3576</v>
+        <v>-14.6328</v>
       </c>
     </row>
     <row r="241">
@@ -13829,10 +13829,10 @@
         <v>0.84</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.6098</v>
+        <v>-0.5496</v>
       </c>
       <c r="J241" t="n">
-        <v>-17.0744</v>
+        <v>-15.3888</v>
       </c>
     </row>
     <row r="242">
@@ -13869,10 +13869,10 @@
         <v>1.17</v>
       </c>
       <c r="I242" t="n">
-        <v>0.3934</v>
+        <v>0.3368</v>
       </c>
       <c r="J242" t="n">
-        <v>10.6218</v>
+        <v>9.0936</v>
       </c>
     </row>
     <row r="243">
@@ -13909,10 +13909,10 @@
         <v>1.01</v>
       </c>
       <c r="I243" t="n">
-        <v>0.1068</v>
+        <v>0.0575</v>
       </c>
       <c r="J243" t="n">
-        <v>2.8836</v>
+        <v>1.5525</v>
       </c>
     </row>
     <row r="244">
@@ -13949,10 +13949,10 @@
         <v>0.93</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.0912</v>
+        <v>-0.0851</v>
       </c>
       <c r="J244" t="n">
-        <v>-2.4624</v>
+        <v>-2.2977</v>
       </c>
     </row>
     <row r="245">
@@ -13989,10 +13989,10 @@
         <v>0.63</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.5815</v>
+        <v>-0.3842</v>
       </c>
       <c r="J245" t="n">
-        <v>-15.7005</v>
+        <v>-10.3734</v>
       </c>
     </row>
     <row r="246">
@@ -14029,10 +14029,10 @@
         <v>0.53</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.7077</v>
+        <v>-0.4768</v>
       </c>
       <c r="J246" t="n">
-        <v>-19.1079</v>
+        <v>-12.8736</v>
       </c>
     </row>
     <row r="247">
@@ -14069,10 +14069,10 @@
         <v>1.45</v>
       </c>
       <c r="I247" t="n">
-        <v>0.6522</v>
+        <v>0.5743</v>
       </c>
       <c r="J247" t="n">
-        <v>17.6094</v>
+        <v>15.5061</v>
       </c>
     </row>
     <row r="248">
@@ -14109,10 +14109,10 @@
         <v>1.13</v>
       </c>
       <c r="I248" t="n">
-        <v>0.1948</v>
+        <v>0.1965</v>
       </c>
       <c r="J248" t="n">
-        <v>5.2596</v>
+        <v>5.3055</v>
       </c>
     </row>
     <row r="249">
@@ -14149,10 +14149,10 @@
         <v>1.12</v>
       </c>
       <c r="I249" t="n">
-        <v>0.178</v>
+        <v>0.1831</v>
       </c>
       <c r="J249" t="n">
-        <v>4.806</v>
+        <v>4.9437</v>
       </c>
     </row>
     <row r="250">
@@ -14189,10 +14189,10 @@
         <v>1.1</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1442</v>
+        <v>0.1554</v>
       </c>
       <c r="J250" t="n">
-        <v>3.8934</v>
+        <v>4.1958</v>
       </c>
     </row>
     <row r="251">
@@ -14229,10 +14229,10 @@
         <v>1.06</v>
       </c>
       <c r="I251" t="n">
-        <v>0.0738</v>
+        <v>0.096</v>
       </c>
       <c r="J251" t="n">
-        <v>1.9926</v>
+        <v>2.592</v>
       </c>
     </row>
     <row r="252">
@@ -14269,10 +14269,10 @@
         <v>1.42</v>
       </c>
       <c r="I252" t="n">
-        <v>1.1219</v>
+        <v>1.0694</v>
       </c>
       <c r="J252" t="n">
-        <v>32.5351</v>
+        <v>31.0126</v>
       </c>
     </row>
     <row r="253">
@@ -14309,10 +14309,10 @@
         <v>1.25</v>
       </c>
       <c r="I253" t="n">
-        <v>0.7437</v>
+        <v>0.7148</v>
       </c>
       <c r="J253" t="n">
-        <v>21.5673</v>
+        <v>20.7292</v>
       </c>
     </row>
     <row r="254">
@@ -14349,10 +14349,10 @@
         <v>1.01</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.0072</v>
+        <v>0.0374</v>
       </c>
       <c r="J254" t="n">
-        <v>-0.2088</v>
+        <v>1.0846</v>
       </c>
     </row>
     <row r="255">
@@ -14389,10 +14389,10 @@
         <v>0.93</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.3445</v>
+        <v>-0.2816</v>
       </c>
       <c r="J255" t="n">
-        <v>-9.990500000000001</v>
+        <v>-8.166399999999999</v>
       </c>
     </row>
     <row r="256">
@@ -14429,10 +14429,10 @@
         <v>0.78</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.7439</v>
+        <v>-0.6953</v>
       </c>
       <c r="J256" t="n">
-        <v>-21.5731</v>
+        <v>-20.1637</v>
       </c>
     </row>
     <row r="257">
@@ -14469,10 +14469,10 @@
         <v>1.58</v>
       </c>
       <c r="I257" t="n">
-        <v>0.8445</v>
+        <v>1.0389</v>
       </c>
       <c r="J257" t="n">
-        <v>24.4905</v>
+        <v>30.1281</v>
       </c>
     </row>
     <row r="258">
@@ -14509,10 +14509,10 @@
         <v>1.18</v>
       </c>
       <c r="I258" t="n">
-        <v>0.3445</v>
+        <v>0.3935</v>
       </c>
       <c r="J258" t="n">
-        <v>9.990500000000001</v>
+        <v>11.4115</v>
       </c>
     </row>
     <row r="259">
@@ -14549,10 +14549,10 @@
         <v>0.86</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.3008</v>
+        <v>-0.1807</v>
       </c>
       <c r="J259" t="n">
-        <v>-8.7232</v>
+        <v>-5.2403</v>
       </c>
     </row>
     <row r="260">
@@ -14589,10 +14589,10 @@
         <v>0.83</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3463</v>
+        <v>-0.2119</v>
       </c>
       <c r="J260" t="n">
-        <v>-10.0427</v>
+        <v>-6.1451</v>
       </c>
     </row>
     <row r="261">
@@ -14629,10 +14629,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.538</v>
+        <v>-0.3488</v>
       </c>
       <c r="J261" t="n">
-        <v>-15.602</v>
+        <v>-10.1152</v>
       </c>
     </row>
     <row r="262">
@@ -14669,10 +14669,10 @@
         <v>2.04</v>
       </c>
       <c r="I262" t="n">
-        <v>2.0132</v>
+        <v>1.7221</v>
       </c>
       <c r="J262" t="n">
-        <v>40.264</v>
+        <v>34.442</v>
       </c>
     </row>
     <row r="263">
@@ -14709,10 +14709,10 @@
         <v>1.72</v>
       </c>
       <c r="I263" t="n">
-        <v>1.5325</v>
+        <v>1.3581</v>
       </c>
       <c r="J263" t="n">
-        <v>30.65</v>
+        <v>27.162</v>
       </c>
     </row>
     <row r="264">
@@ -14749,10 +14749,10 @@
         <v>1.31</v>
       </c>
       <c r="I264" t="n">
-        <v>0.6558</v>
+        <v>0.7706</v>
       </c>
       <c r="J264" t="n">
-        <v>13.116</v>
+        <v>15.412</v>
       </c>
     </row>
     <row r="265">
@@ -14789,10 +14789,10 @@
         <v>1.09</v>
       </c>
       <c r="I265" t="n">
-        <v>0.1254</v>
+        <v>0.2195</v>
       </c>
       <c r="J265" t="n">
-        <v>2.508</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="266">
@@ -14829,10 +14829,10 @@
         <v>1.04</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.023</v>
+        <v>0.0644</v>
       </c>
       <c r="J266" t="n">
-        <v>-0.46</v>
+        <v>1.288</v>
       </c>
     </row>
     <row r="267">
@@ -14869,10 +14869,10 @@
         <v>0.87</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.1013</v>
+        <v>-0.1087</v>
       </c>
       <c r="J267" t="n">
-        <v>-2.026</v>
+        <v>-2.174</v>
       </c>
     </row>
     <row r="268">
@@ -14909,10 +14909,10 @@
         <v>0.72</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.3404</v>
+        <v>-0.2711</v>
       </c>
       <c r="J268" t="n">
-        <v>-6.808</v>
+        <v>-5.422</v>
       </c>
     </row>
     <row r="269">
@@ -14949,10 +14949,10 @@
         <v>0.63</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.5058</v>
+        <v>-0.3539</v>
       </c>
       <c r="J269" t="n">
-        <v>-10.116</v>
+        <v>-7.078</v>
       </c>
     </row>
     <row r="270">
@@ -14989,10 +14989,10 @@
         <v>0.6</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.5545</v>
+        <v>-0.3813</v>
       </c>
       <c r="J270" t="n">
-        <v>-11.09</v>
+        <v>-7.626</v>
       </c>
     </row>
     <row r="271">
@@ -15029,10 +15029,10 @@
         <v>0.44</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.7768</v>
+        <v>-0.5311</v>
       </c>
       <c r="J271" t="n">
-        <v>-15.536</v>
+        <v>-10.622</v>
       </c>
     </row>
     <row r="272">
@@ -15069,10 +15069,10 @@
         <v>1.3</v>
       </c>
       <c r="I272" t="n">
-        <v>0.494</v>
+        <v>0.59</v>
       </c>
       <c r="J272" t="n">
-        <v>17.784</v>
+        <v>21.24</v>
       </c>
     </row>
     <row r="273">
@@ -15109,10 +15109,10 @@
         <v>1.23</v>
       </c>
       <c r="I273" t="n">
-        <v>0.3989</v>
+        <v>0.4695</v>
       </c>
       <c r="J273" t="n">
-        <v>14.3604</v>
+        <v>16.902</v>
       </c>
     </row>
     <row r="274">
@@ -15149,10 +15149,10 @@
         <v>1.18</v>
       </c>
       <c r="I274" t="n">
-        <v>0.3259</v>
+        <v>0.3804</v>
       </c>
       <c r="J274" t="n">
-        <v>11.7324</v>
+        <v>13.6944</v>
       </c>
     </row>
     <row r="275">
@@ -15189,10 +15189,10 @@
         <v>0.91</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.2331</v>
+        <v>-0.1318</v>
       </c>
       <c r="J275" t="n">
-        <v>-8.3916</v>
+        <v>-4.7448</v>
       </c>
     </row>
     <row r="276">
@@ -15229,10 +15229,10 @@
         <v>0.78</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.4279</v>
+        <v>-0.2678</v>
       </c>
       <c r="J276" t="n">
-        <v>-15.4044</v>
+        <v>-9.6408</v>
       </c>
     </row>
     <row r="277">
@@ -15269,10 +15269,10 @@
         <v>1.1</v>
       </c>
       <c r="I277" t="n">
-        <v>0.4059</v>
+        <v>0.3539</v>
       </c>
       <c r="J277" t="n">
-        <v>14.6124</v>
+        <v>12.7404</v>
       </c>
     </row>
     <row r="278">
@@ -15309,10 +15309,10 @@
         <v>1.01</v>
       </c>
       <c r="I278" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.0564</v>
       </c>
       <c r="J278" t="n">
-        <v>3.06</v>
+        <v>2.0304</v>
       </c>
     </row>
     <row r="279">
@@ -15349,10 +15349,10 @@
         <v>0.99</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.0456</v>
+        <v>-0.0514</v>
       </c>
       <c r="J279" t="n">
-        <v>-1.6416</v>
+        <v>-1.8504</v>
       </c>
     </row>
     <row r="280">
@@ -15389,10 +15389,10 @@
         <v>0.97</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.1477</v>
+        <v>-0.1269</v>
       </c>
       <c r="J280" t="n">
-        <v>-5.3172</v>
+        <v>-4.5684</v>
       </c>
     </row>
     <row r="281">
@@ -15429,10 +15429,10 @@
         <v>0.86</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5036</v>
+        <v>-0.457</v>
       </c>
       <c r="J281" t="n">
-        <v>-18.1296</v>
+        <v>-16.452</v>
       </c>
     </row>
     <row r="282">
@@ -15469,10 +15469,10 @@
         <v>1.25</v>
       </c>
       <c r="I282" t="n">
-        <v>0.5472</v>
+        <v>0.658</v>
       </c>
       <c r="J282" t="n">
-        <v>11.4912</v>
+        <v>13.818</v>
       </c>
     </row>
     <row r="283">
@@ -15509,10 +15509,10 @@
         <v>1.05</v>
       </c>
       <c r="I283" t="n">
-        <v>0.2351</v>
+        <v>0.2287</v>
       </c>
       <c r="J283" t="n">
-        <v>4.9371</v>
+        <v>4.8027</v>
       </c>
     </row>
     <row r="284">
@@ -15549,10 +15549,10 @@
         <v>0.59</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.6095</v>
+        <v>-0.4078</v>
       </c>
       <c r="J284" t="n">
-        <v>-12.7995</v>
+        <v>-8.563800000000001</v>
       </c>
     </row>
     <row r="285">
@@ -15589,10 +15589,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.6492</v>
+        <v>-0.4358</v>
       </c>
       <c r="J285" t="n">
-        <v>-13.6332</v>
+        <v>-9.1518</v>
       </c>
     </row>
     <row r="286">
@@ -15629,10 +15629,10 @@
         <v>0.34</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.9179</v>
+        <v>-0.6389</v>
       </c>
       <c r="J286" t="n">
-        <v>-19.2759</v>
+        <v>-13.4169</v>
       </c>
     </row>
     <row r="287">
@@ -15669,10 +15669,10 @@
         <v>1.85</v>
       </c>
       <c r="I287" t="n">
-        <v>1.7943</v>
+        <v>1.525</v>
       </c>
       <c r="J287" t="n">
-        <v>37.6803</v>
+        <v>32.025</v>
       </c>
     </row>
     <row r="288">
@@ -15709,10 +15709,10 @@
         <v>1.66</v>
       </c>
       <c r="I288" t="n">
-        <v>1.4537</v>
+        <v>1.3019</v>
       </c>
       <c r="J288" t="n">
-        <v>30.5277</v>
+        <v>27.3399</v>
       </c>
     </row>
     <row r="289">
@@ -15749,10 +15749,10 @@
         <v>1.4</v>
       </c>
       <c r="I289" t="n">
-        <v>0.9236</v>
+        <v>0.97</v>
       </c>
       <c r="J289" t="n">
-        <v>19.3956</v>
+        <v>20.37</v>
       </c>
     </row>
     <row r="290">
@@ -15789,10 +15789,10 @@
         <v>1.07</v>
       </c>
       <c r="I290" t="n">
-        <v>0.0883</v>
+        <v>0.1761</v>
       </c>
       <c r="J290" t="n">
-        <v>1.8543</v>
+        <v>3.6981</v>
       </c>
     </row>
     <row r="291">
@@ -15829,10 +15829,10 @@
         <v>0.85</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.6455</v>
+        <v>-0.58</v>
       </c>
       <c r="J291" t="n">
-        <v>-13.5555</v>
+        <v>-12.18</v>
       </c>
     </row>
     <row r="292">
@@ -15869,10 +15869,10 @@
         <v>1.04</v>
       </c>
       <c r="I292" t="n">
-        <v>0.2093</v>
+        <v>0.1956</v>
       </c>
       <c r="J292" t="n">
-        <v>4.8139</v>
+        <v>4.4988</v>
       </c>
     </row>
     <row r="293">
@@ -15909,10 +15909,10 @@
         <v>0.86</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.177</v>
+        <v>-0.1507</v>
       </c>
       <c r="J293" t="n">
-        <v>-4.071</v>
+        <v>-3.4661</v>
       </c>
     </row>
     <row r="294">
@@ -15949,10 +15949,10 @@
         <v>0.74</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.3957</v>
+        <v>-0.2688</v>
       </c>
       <c r="J294" t="n">
-        <v>-9.101100000000001</v>
+        <v>-6.1824</v>
       </c>
     </row>
     <row r="295">
@@ -15989,10 +15989,10 @@
         <v>0.73</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.412</v>
+        <v>-0.2782</v>
       </c>
       <c r="J295" t="n">
-        <v>-9.476000000000001</v>
+        <v>-6.3986</v>
       </c>
     </row>
     <row r="296">
@@ -16029,10 +16029,10 @@
         <v>0.49</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.5028</v>
       </c>
       <c r="J296" t="n">
-        <v>-17.0522</v>
+        <v>-11.5644</v>
       </c>
     </row>
     <row r="297">
@@ -16069,10 +16069,10 @@
         <v>1.58</v>
       </c>
       <c r="I297" t="n">
-        <v>1.3233</v>
+        <v>1.2152</v>
       </c>
       <c r="J297" t="n">
-        <v>30.4359</v>
+        <v>27.9496</v>
       </c>
     </row>
     <row r="298">
@@ -16109,10 +16109,10 @@
         <v>1.43</v>
       </c>
       <c r="I298" t="n">
-        <v>1.0186</v>
+        <v>1.0266</v>
       </c>
       <c r="J298" t="n">
-        <v>23.4278</v>
+        <v>23.6118</v>
       </c>
     </row>
     <row r="299">
@@ -16149,10 +16149,10 @@
         <v>1.28</v>
       </c>
       <c r="I299" t="n">
-        <v>0.6455</v>
+        <v>0.7262</v>
       </c>
       <c r="J299" t="n">
-        <v>14.8465</v>
+        <v>16.7026</v>
       </c>
     </row>
     <row r="300">
@@ -16189,10 +16189,10 @@
         <v>1.2</v>
       </c>
       <c r="I300" t="n">
-        <v>0.448</v>
+        <v>0.5377</v>
       </c>
       <c r="J300" t="n">
-        <v>10.304</v>
+        <v>12.3671</v>
       </c>
     </row>
     <row r="301">
@@ -16229,10 +16229,10 @@
         <v>1.1</v>
       </c>
       <c r="I301" t="n">
-        <v>0.1885</v>
+        <v>0.2749</v>
       </c>
       <c r="J301" t="n">
-        <v>4.3355</v>
+        <v>6.3227</v>
       </c>
     </row>
     <row r="302">
@@ -16269,10 +16269,10 @@
         <v>1.06</v>
       </c>
       <c r="I302" t="n">
-        <v>0.2153</v>
+        <v>0.2081</v>
       </c>
       <c r="J302" t="n">
-        <v>5.1672</v>
+        <v>4.9944</v>
       </c>
     </row>
     <row r="303">
@@ -16309,10 +16309,10 @@
         <v>0.99</v>
       </c>
       <c r="I303" t="n">
-        <v>0.0392</v>
+        <v>-0.0015</v>
       </c>
       <c r="J303" t="n">
-        <v>0.9408</v>
+        <v>-0.036</v>
       </c>
     </row>
     <row r="304">
@@ -16349,10 +16349,10 @@
         <v>0.78</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.3682</v>
+        <v>-0.2403</v>
       </c>
       <c r="J304" t="n">
-        <v>-8.8368</v>
+        <v>-5.7672</v>
       </c>
     </row>
     <row r="305">
@@ -16389,10 +16389,10 @@
         <v>0.72</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.4577</v>
+        <v>-0.2984</v>
       </c>
       <c r="J305" t="n">
-        <v>-10.9848</v>
+        <v>-7.1616</v>
       </c>
     </row>
     <row r="306">
@@ -16429,10 +16429,10 @@
         <v>0.7</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.4859</v>
+        <v>-0.3175</v>
       </c>
       <c r="J306" t="n">
-        <v>-11.6616</v>
+        <v>-7.62</v>
       </c>
     </row>
     <row r="307">
@@ -16469,10 +16469,10 @@
         <v>1.5</v>
       </c>
       <c r="I307" t="n">
-        <v>1.1958</v>
+        <v>1.1292</v>
       </c>
       <c r="J307" t="n">
-        <v>28.6992</v>
+        <v>27.1008</v>
       </c>
     </row>
     <row r="308">
@@ -16509,10 +16509,10 @@
         <v>1.31</v>
       </c>
       <c r="I308" t="n">
-        <v>0.7829</v>
+        <v>0.8028</v>
       </c>
       <c r="J308" t="n">
-        <v>18.7896</v>
+        <v>19.2672</v>
       </c>
     </row>
     <row r="309">
@@ -16549,10 +16549,10 @@
         <v>1.29</v>
       </c>
       <c r="I309" t="n">
-        <v>0.7336</v>
+        <v>0.7579</v>
       </c>
       <c r="J309" t="n">
-        <v>17.6064</v>
+        <v>18.1896</v>
       </c>
     </row>
     <row r="310">
@@ -16589,10 +16589,10 @@
         <v>1.12</v>
       </c>
       <c r="I310" t="n">
-        <v>0.2678</v>
+        <v>0.3454</v>
       </c>
       <c r="J310" t="n">
-        <v>6.4272</v>
+        <v>8.2896</v>
       </c>
     </row>
     <row r="311">
@@ -16629,10 +16629,10 @@
         <v>1.05</v>
       </c>
       <c r="I311" t="n">
-        <v>0.0625</v>
+        <v>0.1391</v>
       </c>
       <c r="J311" t="n">
-        <v>1.5</v>
+        <v>3.3384</v>
       </c>
     </row>
     <row r="312">
@@ -16669,10 +16669,10 @@
         <v>1.2</v>
       </c>
       <c r="I312" t="n">
-        <v>0.6287</v>
+        <v>0.5952</v>
       </c>
       <c r="J312" t="n">
-        <v>25.148</v>
+        <v>23.808</v>
       </c>
     </row>
     <row r="313">
@@ -16709,10 +16709,10 @@
         <v>1.18</v>
       </c>
       <c r="I313" t="n">
-        <v>0.5772</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="J313" t="n">
-        <v>23.088</v>
+        <v>21.756</v>
       </c>
     </row>
     <row r="314">
@@ -16749,10 +16749,10 @@
         <v>1.1</v>
       </c>
       <c r="I314" t="n">
-        <v>0.3503</v>
+        <v>0.3298</v>
       </c>
       <c r="J314" t="n">
-        <v>14.012</v>
+        <v>13.192</v>
       </c>
     </row>
     <row r="315">
@@ -16789,10 +16789,10 @@
         <v>1.04</v>
       </c>
       <c r="I315" t="n">
-        <v>0.1258</v>
+        <v>0.152</v>
       </c>
       <c r="J315" t="n">
-        <v>5.032</v>
+        <v>6.08</v>
       </c>
     </row>
     <row r="316">
@@ -16829,10 +16829,10 @@
         <v>0.8</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.6398</v>
       </c>
       <c r="J316" t="n">
-        <v>-27.64</v>
+        <v>-25.592</v>
       </c>
     </row>
     <row r="317">
@@ -16869,10 +16869,10 @@
         <v>1.2</v>
       </c>
       <c r="I317" t="n">
-        <v>0.3718</v>
+        <v>0.4284</v>
       </c>
       <c r="J317" t="n">
-        <v>14.872</v>
+        <v>17.136</v>
       </c>
     </row>
     <row r="318">
@@ -16909,10 +16909,10 @@
         <v>1.17</v>
       </c>
       <c r="I318" t="n">
-        <v>0.3274</v>
+        <v>0.3733</v>
       </c>
       <c r="J318" t="n">
-        <v>13.096</v>
+        <v>14.932</v>
       </c>
     </row>
     <row r="319">
@@ -16949,10 +16949,10 @@
         <v>1.04</v>
       </c>
       <c r="I319" t="n">
-        <v>0.0954</v>
+        <v>0.1108</v>
       </c>
       <c r="J319" t="n">
-        <v>3.816</v>
+        <v>4.432</v>
       </c>
     </row>
     <row r="320">
@@ -16989,10 +16989,10 @@
         <v>0.96</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.1277</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="J320" t="n">
-        <v>-5.108</v>
+        <v>-2.664</v>
       </c>
     </row>
     <row r="321">
@@ -17029,10 +17029,10 @@
         <v>0.8</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.3911</v>
+        <v>-0.2429</v>
       </c>
       <c r="J321" t="n">
-        <v>-15.644</v>
+        <v>-9.715999999999999</v>
       </c>
     </row>
     <row r="322">
@@ -17069,10 +17069,10 @@
         <v>1.57</v>
       </c>
       <c r="I322" t="n">
-        <v>1.3443</v>
+        <v>1.2221</v>
       </c>
       <c r="J322" t="n">
-        <v>34.9518</v>
+        <v>31.7746</v>
       </c>
     </row>
     <row r="323">
@@ -17109,10 +17109,10 @@
         <v>1.27</v>
       </c>
       <c r="I323" t="n">
-        <v>0.6985</v>
+        <v>0.7169</v>
       </c>
       <c r="J323" t="n">
-        <v>18.161</v>
+        <v>18.6394</v>
       </c>
     </row>
     <row r="324">
@@ -17149,10 +17149,10 @@
         <v>1.22</v>
       </c>
       <c r="I324" t="n">
-        <v>0.5505</v>
+        <v>0.6028</v>
       </c>
       <c r="J324" t="n">
-        <v>14.313</v>
+        <v>15.6728</v>
       </c>
     </row>
     <row r="325">
@@ -17189,10 +17189,10 @@
         <v>1.15</v>
       </c>
       <c r="I325" t="n">
-        <v>0.3597</v>
+        <v>0.4302</v>
       </c>
       <c r="J325" t="n">
-        <v>9.3522</v>
+        <v>11.1852</v>
       </c>
     </row>
     <row r="326">
@@ -17229,10 +17229,10 @@
         <v>0.95</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.3386</v>
+        <v>-0.2584</v>
       </c>
       <c r="J326" t="n">
-        <v>-8.803599999999999</v>
+        <v>-6.7184</v>
       </c>
     </row>
     <row r="327">
@@ -17269,10 +17269,10 @@
         <v>1</v>
       </c>
       <c r="I327" t="n">
-        <v>0.0622</v>
+        <v>0.0274</v>
       </c>
       <c r="J327" t="n">
-        <v>1.6172</v>
+        <v>0.7124</v>
       </c>
     </row>
     <row r="328">
@@ -17309,10 +17309,10 @@
         <v>0.92</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.122</v>
+        <v>-0.1002</v>
       </c>
       <c r="J328" t="n">
-        <v>-3.172</v>
+        <v>-2.6052</v>
       </c>
     </row>
     <row r="329">
@@ -17349,10 +17349,10 @@
         <v>0.89</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.1805</v>
+        <v>-0.1333</v>
       </c>
       <c r="J329" t="n">
-        <v>-4.693</v>
+        <v>-3.4658</v>
       </c>
     </row>
     <row r="330">
@@ -17389,10 +17389,10 @@
         <v>0.88</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.2021</v>
+        <v>-0.1436</v>
       </c>
       <c r="J330" t="n">
-        <v>-5.2546</v>
+        <v>-3.7336</v>
       </c>
     </row>
     <row r="331">
@@ -17429,10 +17429,10 @@
         <v>0.7</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.4937</v>
+        <v>-0.3213</v>
       </c>
       <c r="J331" t="n">
-        <v>-12.8362</v>
+        <v>-8.3538</v>
       </c>
     </row>
     <row r="332">
@@ -17469,10 +17469,10 @@
         <v>1.46</v>
       </c>
       <c r="I332" t="n">
-        <v>0.7255</v>
+        <v>0.8993</v>
       </c>
       <c r="J332" t="n">
-        <v>30.471</v>
+        <v>37.7706</v>
       </c>
     </row>
     <row r="333">
@@ -17509,10 +17509,10 @@
         <v>1.03</v>
       </c>
       <c r="I333" t="n">
-        <v>0.1037</v>
+        <v>0.0965</v>
       </c>
       <c r="J333" t="n">
-        <v>4.3554</v>
+        <v>4.053</v>
       </c>
     </row>
     <row r="334">
@@ -17549,10 +17549,10 @@
         <v>1</v>
       </c>
       <c r="I334" t="n">
-        <v>0.0179</v>
+        <v>0.0032</v>
       </c>
       <c r="J334" t="n">
-        <v>0.7518</v>
+        <v>0.1344</v>
       </c>
     </row>
     <row r="335">
@@ -17589,10 +17589,10 @@
         <v>0.7</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.5158</v>
+        <v>-0.3335</v>
       </c>
       <c r="J335" t="n">
-        <v>-21.6636</v>
+        <v>-14.007</v>
       </c>
     </row>
     <row r="336">
@@ -17629,10 +17629,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.5288</v>
+        <v>-0.343</v>
       </c>
       <c r="J336" t="n">
-        <v>-22.2096</v>
+        <v>-14.406</v>
       </c>
     </row>
     <row r="337">
@@ -17669,10 +17669,10 @@
         <v>1.34</v>
       </c>
       <c r="I337" t="n">
-        <v>0.9525</v>
+        <v>0.9318</v>
       </c>
       <c r="J337" t="n">
-        <v>40.005</v>
+        <v>39.1356</v>
       </c>
     </row>
     <row r="338">
@@ -17709,10 +17709,10 @@
         <v>1.26</v>
       </c>
       <c r="I338" t="n">
-        <v>0.7699</v>
+        <v>0.7409</v>
       </c>
       <c r="J338" t="n">
-        <v>32.3358</v>
+        <v>31.1178</v>
       </c>
     </row>
     <row r="339">
@@ -17749,10 +17749,10 @@
         <v>1.15</v>
       </c>
       <c r="I339" t="n">
-        <v>0.49</v>
+        <v>0.4626</v>
       </c>
       <c r="J339" t="n">
-        <v>20.58</v>
+        <v>19.4292</v>
       </c>
     </row>
     <row r="340">
@@ -17789,10 +17789,10 @@
         <v>0.91</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.403</v>
+        <v>-0.3407</v>
       </c>
       <c r="J340" t="n">
-        <v>-16.926</v>
+        <v>-14.3094</v>
       </c>
     </row>
     <row r="341">
@@ -17829,10 +17829,10 @@
         <v>0.71</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.9042</v>
+        <v>-0.8697</v>
       </c>
       <c r="J341" t="n">
-        <v>-37.9764</v>
+        <v>-36.5274</v>
       </c>
     </row>
     <row r="342">
@@ -17869,10 +17869,10 @@
         <v>1.65</v>
       </c>
       <c r="I342" t="n">
-        <v>0.9195</v>
+        <v>1.1041</v>
       </c>
       <c r="J342" t="n">
-        <v>26.6655</v>
+        <v>32.0189</v>
       </c>
     </row>
     <row r="343">
@@ -17909,10 +17909,10 @@
         <v>1.18</v>
       </c>
       <c r="I343" t="n">
-        <v>0.3431</v>
+        <v>0.3924</v>
       </c>
       <c r="J343" t="n">
-        <v>9.9499</v>
+        <v>11.3796</v>
       </c>
     </row>
     <row r="344">
@@ -17949,10 +17949,10 @@
         <v>0.87</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.2861</v>
+        <v>-0.1705</v>
       </c>
       <c r="J344" t="n">
-        <v>-8.296900000000001</v>
+        <v>-4.9445</v>
       </c>
     </row>
     <row r="345">
@@ -17989,10 +17989,10 @@
         <v>0.84</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.3323</v>
+        <v>-0.202</v>
       </c>
       <c r="J345" t="n">
-        <v>-9.636699999999999</v>
+        <v>-5.858</v>
       </c>
     </row>
     <row r="346">
@@ -18029,10 +18029,10 @@
         <v>0.62</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.626</v>
+        <v>-0.4142</v>
       </c>
       <c r="J346" t="n">
-        <v>-18.154</v>
+        <v>-12.0118</v>
       </c>
     </row>
     <row r="347">
@@ -18069,10 +18069,10 @@
         <v>1.39</v>
       </c>
       <c r="I347" t="n">
-        <v>1.0608</v>
+        <v>1.027</v>
       </c>
       <c r="J347" t="n">
-        <v>30.7632</v>
+        <v>29.783</v>
       </c>
     </row>
     <row r="348">
@@ -18109,10 +18109,10 @@
         <v>1.23</v>
       </c>
       <c r="I348" t="n">
-        <v>0.6976</v>
+        <v>0.6669</v>
       </c>
       <c r="J348" t="n">
-        <v>20.2304</v>
+        <v>19.3401</v>
       </c>
     </row>
     <row r="349">
@@ -18149,10 +18149,10 @@
         <v>1.14</v>
       </c>
       <c r="I349" t="n">
-        <v>0.4619</v>
+        <v>0.4361</v>
       </c>
       <c r="J349" t="n">
-        <v>13.3951</v>
+        <v>12.6469</v>
       </c>
     </row>
     <row r="350">
@@ -18189,10 +18189,10 @@
         <v>0.88</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.488</v>
+        <v>-0.4271</v>
       </c>
       <c r="J350" t="n">
-        <v>-14.152</v>
+        <v>-12.3859</v>
       </c>
     </row>
     <row r="351">
@@ -18229,10 +18229,10 @@
         <v>0.73</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.8591</v>
+        <v>-0.8203</v>
       </c>
       <c r="J351" t="n">
-        <v>-24.9139</v>
+        <v>-23.7887</v>
       </c>
     </row>
     <row r="352">
@@ -18269,10 +18269,10 @@
         <v>1.26</v>
       </c>
       <c r="I352" t="n">
-        <v>0.7549</v>
+        <v>0.731</v>
       </c>
       <c r="J352" t="n">
-        <v>22.647</v>
+        <v>21.93</v>
       </c>
     </row>
     <row r="353">
@@ -18309,10 +18309,10 @@
         <v>1.19</v>
       </c>
       <c r="I353" t="n">
-        <v>0.5806</v>
+        <v>0.5579</v>
       </c>
       <c r="J353" t="n">
-        <v>17.418</v>
+        <v>16.737</v>
       </c>
     </row>
     <row r="354">
@@ -18349,10 +18349,10 @@
         <v>1.08</v>
       </c>
       <c r="I354" t="n">
-        <v>0.2375</v>
+        <v>0.2675</v>
       </c>
       <c r="J354" t="n">
-        <v>7.125</v>
+        <v>8.025</v>
       </c>
     </row>
     <row r="355">
@@ -18389,10 +18389,10 @@
         <v>1.05</v>
       </c>
       <c r="I355" t="n">
-        <v>0.1353</v>
+        <v>0.1766</v>
       </c>
       <c r="J355" t="n">
-        <v>4.059</v>
+        <v>5.298</v>
       </c>
     </row>
     <row r="356">
@@ -18429,10 +18429,10 @@
         <v>0.92</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.3843</v>
+        <v>-0.3181</v>
       </c>
       <c r="J356" t="n">
-        <v>-11.529</v>
+        <v>-9.542999999999999</v>
       </c>
     </row>
     <row r="357">
@@ -18469,10 +18469,10 @@
         <v>1.38</v>
       </c>
       <c r="I357" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.7648</v>
       </c>
       <c r="J357" t="n">
-        <v>18.885</v>
+        <v>22.944</v>
       </c>
     </row>
     <row r="358">
@@ -18509,10 +18509,10 @@
         <v>1.21</v>
       </c>
       <c r="I358" t="n">
-        <v>0.4063</v>
+        <v>0.4652</v>
       </c>
       <c r="J358" t="n">
-        <v>12.189</v>
+        <v>13.956</v>
       </c>
     </row>
     <row r="359">
@@ -18549,10 +18549,10 @@
         <v>0.83</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.3332</v>
+        <v>-0.2058</v>
       </c>
       <c r="J359" t="n">
-        <v>-9.996</v>
+        <v>-6.174</v>
       </c>
     </row>
     <row r="360">
@@ -18589,10 +18589,10 @@
         <v>0.77</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.4207</v>
+        <v>-0.2659</v>
       </c>
       <c r="J360" t="n">
-        <v>-12.621</v>
+        <v>-7.977</v>
       </c>
     </row>
     <row r="361">
@@ -18629,10 +18629,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.5288</v>
+        <v>-0.343</v>
       </c>
       <c r="J361" t="n">
-        <v>-15.864</v>
+        <v>-10.29</v>
       </c>
     </row>
     <row r="362">
@@ -18669,10 +18669,10 @@
         <v>1.63</v>
       </c>
       <c r="I362" t="n">
-        <v>1.4501</v>
+        <v>1.2921</v>
       </c>
       <c r="J362" t="n">
-        <v>33.3523</v>
+        <v>29.7183</v>
       </c>
     </row>
     <row r="363">
@@ -18709,10 +18709,10 @@
         <v>1.5</v>
       </c>
       <c r="I363" t="n">
-        <v>1.1977</v>
+        <v>1.13</v>
       </c>
       <c r="J363" t="n">
-        <v>27.5471</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="364">
@@ -18749,10 +18749,10 @@
         <v>1.31</v>
       </c>
       <c r="I364" t="n">
-        <v>0.7855</v>
+        <v>0.8037</v>
       </c>
       <c r="J364" t="n">
-        <v>18.0665</v>
+        <v>18.4851</v>
       </c>
     </row>
     <row r="365">
@@ -18789,10 +18789,10 @@
         <v>1.22</v>
       </c>
       <c r="I365" t="n">
-        <v>0.5359</v>
+        <v>0.5998</v>
       </c>
       <c r="J365" t="n">
-        <v>12.3257</v>
+        <v>13.7954</v>
       </c>
     </row>
     <row r="366">
@@ -18829,10 +18829,10 @@
         <v>0.59</v>
       </c>
       <c r="I366" t="n">
-        <v>-1.1918</v>
+        <v>-1.194</v>
       </c>
       <c r="J366" t="n">
-        <v>-27.4114</v>
+        <v>-27.462</v>
       </c>
     </row>
     <row r="367">
@@ -18869,10 +18869,10 @@
         <v>1.4</v>
       </c>
       <c r="I367" t="n">
-        <v>0.6553</v>
+        <v>0.8007</v>
       </c>
       <c r="J367" t="n">
-        <v>15.0719</v>
+        <v>18.4161</v>
       </c>
     </row>
     <row r="368">
@@ -18909,10 +18909,10 @@
         <v>1.29</v>
       </c>
       <c r="I368" t="n">
-        <v>0.5167</v>
+        <v>0.6107</v>
       </c>
       <c r="J368" t="n">
-        <v>11.8841</v>
+        <v>14.0461</v>
       </c>
     </row>
     <row r="369">
@@ -18949,10 +18949,10 @@
         <v>0.97</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.0746</v>
+        <v>-0.0479</v>
       </c>
       <c r="J369" t="n">
-        <v>-1.7158</v>
+        <v>-1.1017</v>
       </c>
     </row>
     <row r="370">
@@ -18989,10 +18989,10 @@
         <v>0.66</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.5668</v>
+        <v>-0.3707</v>
       </c>
       <c r="J370" t="n">
-        <v>-13.0364</v>
+        <v>-8.5261</v>
       </c>
     </row>
     <row r="371">
@@ -19029,10 +19029,10 @@
         <v>0.54</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.7138</v>
+        <v>-0.4808</v>
       </c>
       <c r="J371" t="n">
-        <v>-16.4174</v>
+        <v>-11.0584</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7128/event_7128_evp_summary.xlsx
+++ b/database/event/7128/event_7128_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.9144</v>
+        <v>5.9454</v>
       </c>
       <c r="C2" t="n">
-        <v>3.53</v>
+        <v>3.5485</v>
       </c>
       <c r="D2" t="n">
-        <v>2.032</v>
+        <v>2.0823</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9144</v>
+        <v>5.9454</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3444</v>
+        <v>2.2816</v>
       </c>
       <c r="G2" t="n">
-        <v>3.57</v>
+        <v>3.6638</v>
       </c>
       <c r="H2" t="n">
-        <v>2.3444</v>
+        <v>2.2816</v>
       </c>
       <c r="I2" t="n">
-        <v>2.3444</v>
+        <v>2.2816</v>
       </c>
       <c r="J2" t="n">
-        <v>3.57</v>
+        <v>3.6638</v>
       </c>
       <c r="K2" t="n">
         <v>47</v>
@@ -529,7 +529,7 @@
         <v>209</v>
       </c>
       <c r="M2" t="n">
-        <v>5.9144</v>
+        <v>5.9454</v>
       </c>
       <c r="N2" t="n">
         <v>256</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.7052</v>
+        <v>4.9969</v>
       </c>
       <c r="C3" t="n">
-        <v>2.8083</v>
+        <v>2.9824</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4861</v>
+        <v>1.6505</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7052</v>
+        <v>4.9969</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8789</v>
+        <v>1.8639</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8263</v>
+        <v>3.133</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8789</v>
+        <v>1.8639</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8789</v>
+        <v>1.8639</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8263</v>
+        <v>3.133</v>
       </c>
       <c r="K3" t="n">
         <v>57</v>
@@ -575,7 +575,7 @@
         <v>184</v>
       </c>
       <c r="M3" t="n">
-        <v>4.7052</v>
+        <v>4.9969</v>
       </c>
       <c r="N3" t="n">
         <v>241</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.5508</v>
+        <v>4.7571</v>
       </c>
       <c r="C4" t="n">
-        <v>2.7161</v>
+        <v>2.8393</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4164</v>
+        <v>1.5413</v>
       </c>
       <c r="E4" t="n">
-        <v>4.5508</v>
+        <v>4.7571</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8921</v>
+        <v>1.8104</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6587</v>
+        <v>2.9467</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8921</v>
+        <v>1.8104</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8921</v>
+        <v>1.8104</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6587</v>
+        <v>2.9467</v>
       </c>
       <c r="K4" t="n">
         <v>92</v>
@@ -621,7 +621,7 @@
         <v>168</v>
       </c>
       <c r="M4" t="n">
-        <v>4.5508</v>
+        <v>4.757099999999999</v>
       </c>
       <c r="N4" t="n">
         <v>260</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.5345</v>
+        <v>4.7052</v>
       </c>
       <c r="C5" t="n">
-        <v>2.7064</v>
+        <v>2.8083</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4091</v>
+        <v>1.5177</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5345</v>
+        <v>4.7052</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8431</v>
+        <v>0.7862</v>
       </c>
       <c r="G5" t="n">
-        <v>3.6914</v>
+        <v>3.919</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8431</v>
+        <v>0.7862</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8431</v>
+        <v>0.7862</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6914</v>
+        <v>3.919</v>
       </c>
       <c r="K5" t="n">
         <v>57</v>
@@ -667,7 +667,7 @@
         <v>184</v>
       </c>
       <c r="M5" t="n">
-        <v>4.5345</v>
+        <v>4.7052</v>
       </c>
       <c r="N5" t="n">
         <v>241</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.0215</v>
+        <v>4.1952</v>
       </c>
       <c r="C6" t="n">
-        <v>2.4002</v>
+        <v>2.5039</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1775</v>
+        <v>1.2855</v>
       </c>
       <c r="E6" t="n">
-        <v>4.0215</v>
+        <v>4.1952</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4841</v>
+        <v>1.4219</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5374</v>
+        <v>2.7733</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4841</v>
+        <v>1.4219</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4841</v>
+        <v>1.4219</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5374</v>
+        <v>2.7733</v>
       </c>
       <c r="K6" t="n">
         <v>47</v>
@@ -713,7 +713,7 @@
         <v>209</v>
       </c>
       <c r="M6" t="n">
-        <v>4.0215</v>
+        <v>4.1952</v>
       </c>
       <c r="N6" t="n">
         <v>256</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.6714</v>
+        <v>3.8586</v>
       </c>
       <c r="C7" t="n">
-        <v>2.1913</v>
+        <v>2.303</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0194</v>
+        <v>1.1323</v>
       </c>
       <c r="E7" t="n">
-        <v>3.6714</v>
+        <v>3.8586</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3583</v>
+        <v>1.3433</v>
       </c>
       <c r="G7" t="n">
-        <v>2.3131</v>
+        <v>2.5153</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3583</v>
+        <v>1.3433</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3583</v>
+        <v>1.3433</v>
       </c>
       <c r="J7" t="n">
-        <v>2.3131</v>
+        <v>2.5153</v>
       </c>
       <c r="K7" t="n">
         <v>57</v>
@@ -759,7 +759,7 @@
         <v>184</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6714</v>
+        <v>3.8586</v>
       </c>
       <c r="N7" t="n">
         <v>241</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.6071</v>
+        <v>3.7979</v>
       </c>
       <c r="C8" t="n">
-        <v>2.1529</v>
+        <v>2.2668</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9903999999999999</v>
+        <v>1.1047</v>
       </c>
       <c r="E8" t="n">
-        <v>3.6071</v>
+        <v>3.7979</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3405</v>
+        <v>1.2936</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2666</v>
+        <v>2.5043</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3405</v>
+        <v>1.2936</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3405</v>
+        <v>1.2936</v>
       </c>
       <c r="J8" t="n">
-        <v>2.2666</v>
+        <v>2.5043</v>
       </c>
       <c r="K8" t="n">
         <v>47</v>
@@ -805,7 +805,7 @@
         <v>209</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6071</v>
+        <v>3.7979</v>
       </c>
       <c r="N8" t="n">
         <v>256</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.4956</v>
+        <v>3.6852</v>
       </c>
       <c r="C9" t="n">
-        <v>2.0864</v>
+        <v>2.1995</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9401</v>
+        <v>1.0534</v>
       </c>
       <c r="E9" t="n">
-        <v>3.4956</v>
+        <v>3.6852</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0254</v>
+        <v>0.9982</v>
       </c>
       <c r="G9" t="n">
-        <v>2.4702</v>
+        <v>2.687</v>
       </c>
       <c r="H9" t="n">
-        <v>1.0254</v>
+        <v>0.9982</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0254</v>
+        <v>0.9982</v>
       </c>
       <c r="J9" t="n">
-        <v>2.4702</v>
+        <v>2.687</v>
       </c>
       <c r="K9" t="n">
         <v>66</v>
@@ -851,7 +851,7 @@
         <v>130</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4956</v>
+        <v>3.6852</v>
       </c>
       <c r="N9" t="n">
         <v>196</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.4896</v>
+        <v>3.5869</v>
       </c>
       <c r="C10" t="n">
-        <v>2.0828</v>
+        <v>2.1408</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9374</v>
+        <v>1.0086</v>
       </c>
       <c r="E10" t="n">
-        <v>3.4896</v>
+        <v>3.5869</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8914</v>
+        <v>1.8236</v>
       </c>
       <c r="G10" t="n">
-        <v>1.5982</v>
+        <v>1.7633</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8914</v>
+        <v>1.8236</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8914</v>
+        <v>1.8236</v>
       </c>
       <c r="J10" t="n">
-        <v>1.5982</v>
+        <v>1.7633</v>
       </c>
       <c r="K10" t="n">
         <v>92</v>
@@ -897,7 +897,7 @@
         <v>168</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4896</v>
+        <v>3.5869</v>
       </c>
       <c r="N10" t="n">
         <v>260</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.9196</v>
+        <v>3.0171</v>
       </c>
       <c r="C11" t="n">
-        <v>1.7426</v>
+        <v>1.8008</v>
       </c>
       <c r="D11" t="n">
-        <v>0.68</v>
+        <v>0.7492</v>
       </c>
       <c r="E11" t="n">
-        <v>2.9196</v>
+        <v>3.0171</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1657</v>
+        <v>1.1387</v>
       </c>
       <c r="G11" t="n">
-        <v>1.7539</v>
+        <v>1.8784</v>
       </c>
       <c r="H11" t="n">
-        <v>1.1657</v>
+        <v>1.1387</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1657</v>
+        <v>1.1387</v>
       </c>
       <c r="J11" t="n">
-        <v>1.7539</v>
+        <v>1.8784</v>
       </c>
       <c r="K11" t="n">
         <v>47</v>
@@ -943,7 +943,7 @@
         <v>209</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9196</v>
+        <v>3.0171</v>
       </c>
       <c r="N11" t="n">
         <v>256</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.7551</v>
+        <v>2.9761</v>
       </c>
       <c r="C12" t="n">
-        <v>1.6444</v>
+        <v>1.7763</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6058</v>
+        <v>0.7306</v>
       </c>
       <c r="E12" t="n">
-        <v>2.7551</v>
+        <v>2.9761</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1247</v>
+        <v>0.1441</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6304</v>
+        <v>2.832</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1247</v>
+        <v>0.1441</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1247</v>
+        <v>0.1441</v>
       </c>
       <c r="J12" t="n">
-        <v>2.6304</v>
+        <v>2.832</v>
       </c>
       <c r="K12" t="n">
         <v>57</v>
@@ -989,7 +989,7 @@
         <v>184</v>
       </c>
       <c r="M12" t="n">
-        <v>2.7551</v>
+        <v>2.9761</v>
       </c>
       <c r="N12" t="n">
         <v>241</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.6777</v>
+        <v>2.8517</v>
       </c>
       <c r="C13" t="n">
-        <v>1.5982</v>
+        <v>1.702</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5708</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6777</v>
+        <v>2.8517</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0467</v>
+        <v>1.0156</v>
       </c>
       <c r="G13" t="n">
-        <v>1.631</v>
+        <v>1.8361</v>
       </c>
       <c r="H13" t="n">
-        <v>1.0467</v>
+        <v>1.0156</v>
       </c>
       <c r="I13" t="n">
-        <v>1.0467</v>
+        <v>1.0156</v>
       </c>
       <c r="J13" t="n">
-        <v>1.631</v>
+        <v>1.8361</v>
       </c>
       <c r="K13" t="n">
         <v>66</v>
@@ -1035,7 +1035,7 @@
         <v>130</v>
       </c>
       <c r="M13" t="n">
-        <v>2.6777</v>
+        <v>2.8517</v>
       </c>
       <c r="N13" t="n">
         <v>196</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.1917</v>
+        <v>2.2459</v>
       </c>
       <c r="C14" t="n">
-        <v>1.3081</v>
+        <v>1.3405</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3514</v>
+        <v>0.3982</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1917</v>
+        <v>2.2459</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1789</v>
+        <v>1.1312</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0128</v>
+        <v>1.1147</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1789</v>
+        <v>1.1312</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1789</v>
+        <v>1.1312</v>
       </c>
       <c r="J14" t="n">
-        <v>1.0128</v>
+        <v>1.1147</v>
       </c>
       <c r="K14" t="n">
         <v>92</v>
@@ -1081,7 +1081,7 @@
         <v>168</v>
       </c>
       <c r="M14" t="n">
-        <v>2.1917</v>
+        <v>2.2459</v>
       </c>
       <c r="N14" t="n">
         <v>260</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.718</v>
+        <v>1.781</v>
       </c>
       <c r="C15" t="n">
-        <v>1.0254</v>
+        <v>1.063</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1376</v>
+        <v>0.1865</v>
       </c>
       <c r="E15" t="n">
-        <v>1.718</v>
+        <v>1.781</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3741</v>
+        <v>1.3525</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3439</v>
+        <v>0.4285</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3741</v>
+        <v>1.3525</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3741</v>
+        <v>1.3525</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3439</v>
+        <v>0.4285</v>
       </c>
       <c r="K15" t="n">
         <v>66</v>
@@ -1127,7 +1127,7 @@
         <v>130</v>
       </c>
       <c r="M15" t="n">
-        <v>1.718</v>
+        <v>1.781</v>
       </c>
       <c r="N15" t="n">
         <v>196</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.7109</v>
+        <v>1.7341</v>
       </c>
       <c r="C16" t="n">
-        <v>1.0212</v>
+        <v>1.035</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1344</v>
+        <v>0.1652</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7109</v>
+        <v>1.7341</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6775</v>
+        <v>0.6642</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0334</v>
+        <v>1.0699</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6775</v>
+        <v>0.6642</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6775</v>
+        <v>0.6642</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0334</v>
+        <v>1.0699</v>
       </c>
       <c r="K16" t="n">
         <v>87</v>
@@ -1173,7 +1173,7 @@
         <v>80</v>
       </c>
       <c r="M16" t="n">
-        <v>1.7109</v>
+        <v>1.7341</v>
       </c>
       <c r="N16" t="n">
         <v>167</v>
@@ -1182,81 +1182,81 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.616</v>
+        <v>1.5256</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9645</v>
+        <v>0.9106</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0915</v>
+        <v>0.0703</v>
       </c>
       <c r="E17" t="n">
-        <v>1.616</v>
+        <v>1.5256</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0231</v>
+        <v>-0.0158</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4071</v>
+        <v>1.5414</v>
       </c>
       <c r="H17" t="n">
-        <v>2.0231</v>
+        <v>-0.0158</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0231</v>
+        <v>-0.0158</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4071</v>
+        <v>1.5414</v>
       </c>
       <c r="K17" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="L17" t="n">
-        <v>45</v>
+        <v>130</v>
       </c>
       <c r="M17" t="n">
-        <v>1.616</v>
+        <v>1.5256</v>
       </c>
       <c r="N17" t="n">
-        <v>98</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.4203</v>
+        <v>1.514</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8477</v>
+        <v>0.9036</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0032</v>
+        <v>0.065</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4203</v>
+        <v>1.514</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6879</v>
+        <v>1.9593</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2676</v>
+        <v>-0.4453</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6879</v>
+        <v>1.9593</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6879</v>
+        <v>1.9593</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2676</v>
+        <v>-0.4453</v>
       </c>
       <c r="K18" t="n">
         <v>53</v>
@@ -1265,7 +1265,7 @@
         <v>45</v>
       </c>
       <c r="M18" t="n">
-        <v>1.4203</v>
+        <v>1.514</v>
       </c>
       <c r="N18" t="n">
         <v>98</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.3492</v>
+        <v>1.3496</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8053</v>
+        <v>0.8055</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0289</v>
+        <v>-0.0098</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3492</v>
+        <v>1.3496</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9681</v>
+        <v>0.9213</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3811</v>
+        <v>0.4283</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9681</v>
+        <v>0.9213</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9681</v>
+        <v>0.9213</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3811</v>
+        <v>0.4283</v>
       </c>
       <c r="K19" t="n">
         <v>87</v>
@@ -1311,7 +1311,7 @@
         <v>80</v>
       </c>
       <c r="M19" t="n">
-        <v>1.3492</v>
+        <v>1.3496</v>
       </c>
       <c r="N19" t="n">
         <v>167</v>
@@ -1320,47 +1320,47 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.3492</v>
+        <v>1.3291</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8053</v>
+        <v>0.7933</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0289</v>
+        <v>-0.0192</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3492</v>
+        <v>1.3291</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.037</v>
+        <v>1.6325</v>
       </c>
       <c r="G20" t="n">
-        <v>1.3862</v>
+        <v>-0.3034</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.037</v>
+        <v>1.6325</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.037</v>
+        <v>1.6325</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3862</v>
+        <v>-0.3034</v>
       </c>
       <c r="K20" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="L20" t="n">
-        <v>130</v>
+        <v>45</v>
       </c>
       <c r="M20" t="n">
-        <v>1.3492</v>
+        <v>1.3291</v>
       </c>
       <c r="N20" t="n">
-        <v>196</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21">
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.3363</v>
+        <v>1.3054</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7976</v>
+        <v>0.7791</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0347</v>
+        <v>-0.03</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3363</v>
+        <v>1.3054</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4133</v>
+        <v>1.4025</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.077</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>1.4133</v>
+        <v>1.4025</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4133</v>
+        <v>1.4025</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.077</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="K21" t="n">
         <v>76</v>
@@ -1403,7 +1403,7 @@
         <v>45</v>
       </c>
       <c r="M21" t="n">
-        <v>1.3363</v>
+        <v>1.3054</v>
       </c>
       <c r="N21" t="n">
         <v>121</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.248</v>
+        <v>1.1898</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7449</v>
+        <v>0.7101</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0746</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>1.248</v>
+        <v>1.1898</v>
       </c>
       <c r="F22" t="n">
-        <v>1.248</v>
+        <v>1.1898</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.248</v>
+        <v>1.1898</v>
       </c>
       <c r="I22" t="n">
-        <v>1.248</v>
+        <v>1.1898</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.248</v>
+        <v>1.1898</v>
       </c>
       <c r="N22" t="n">
         <v>57</v>
@@ -1458,47 +1458,47 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>isak</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.1407</v>
+        <v>1.1208</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6808</v>
+        <v>0.669</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.123</v>
+        <v>-0.114</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1407</v>
+        <v>1.1208</v>
       </c>
       <c r="F23" t="n">
-        <v>1.5987</v>
+        <v>0.2806</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.458</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>1.5987</v>
+        <v>0.2806</v>
       </c>
       <c r="I23" t="n">
-        <v>1.5987</v>
+        <v>0.2806</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.458</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="L23" t="n">
-        <v>67</v>
+        <v>130</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1407</v>
+        <v>1.1208</v>
       </c>
       <c r="N23" t="n">
-        <v>138</v>
+        <v>196</v>
       </c>
     </row>
     <row r="24">
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.0527</v>
+        <v>1.03</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6283</v>
+        <v>0.6148</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1628</v>
+        <v>-0.1553</v>
       </c>
       <c r="E24" t="n">
-        <v>1.0527</v>
+        <v>1.03</v>
       </c>
       <c r="F24" t="n">
-        <v>1.6744</v>
+        <v>1.6753</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.6217</v>
+        <v>-0.6453</v>
       </c>
       <c r="H24" t="n">
-        <v>1.6744</v>
+        <v>1.6753</v>
       </c>
       <c r="I24" t="n">
-        <v>1.6744</v>
+        <v>1.6753</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6217</v>
+        <v>-0.6453</v>
       </c>
       <c r="K24" t="n">
         <v>76</v>
@@ -1541,7 +1541,7 @@
         <v>45</v>
       </c>
       <c r="M24" t="n">
-        <v>1.0527</v>
+        <v>1.03</v>
       </c>
       <c r="N24" t="n">
         <v>121</v>
@@ -1550,47 +1550,47 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>isak</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.0321</v>
+        <v>1.026</v>
       </c>
       <c r="C25" t="n">
-        <v>0.616</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1721</v>
+        <v>-0.1571</v>
       </c>
       <c r="E25" t="n">
-        <v>1.0321</v>
+        <v>1.026</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2855</v>
+        <v>1.5005</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7466</v>
+        <v>-0.4745</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2855</v>
+        <v>1.5005</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2855</v>
+        <v>1.5005</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7466</v>
+        <v>-0.4745</v>
       </c>
       <c r="K25" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="L25" t="n">
-        <v>130</v>
+        <v>67</v>
       </c>
       <c r="M25" t="n">
-        <v>1.0321</v>
+        <v>1.026</v>
       </c>
       <c r="N25" t="n">
-        <v>196</v>
+        <v>138</v>
       </c>
     </row>
     <row r="26">
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8591</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="C26" t="n">
-        <v>0.5128</v>
+        <v>0.4991</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2502</v>
+        <v>-0.2435</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8591</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8591</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8591</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8591</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.8591</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="N26" t="n">
         <v>76</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8536</v>
+        <v>0.8349</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5095</v>
+        <v>0.4983</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2527</v>
+        <v>-0.2441</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8536</v>
+        <v>0.8349</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8536</v>
+        <v>0.8349</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8536</v>
+        <v>0.8349</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8536</v>
+        <v>0.8349</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.8536</v>
+        <v>0.8349</v>
       </c>
       <c r="N27" t="n">
         <v>87</v>
@@ -1688,47 +1688,47 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>neaLaN</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.848</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="C28" t="n">
-        <v>0.5061</v>
+        <v>0.4846</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.2552</v>
+        <v>-0.2546</v>
       </c>
       <c r="E28" t="n">
-        <v>0.848</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>1.7679</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.9199000000000001</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.7679</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>1.7679</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.9199000000000001</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="L28" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.848</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="N28" t="n">
-        <v>138</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8280999999999999</v>
+        <v>0.8036</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4943</v>
+        <v>0.4796</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.2642</v>
+        <v>-0.2584</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8280999999999999</v>
+        <v>0.8036</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8280999999999999</v>
+        <v>0.8036</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8280999999999999</v>
+        <v>0.8036</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8280999999999999</v>
+        <v>0.8036</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.8280999999999999</v>
+        <v>0.8036</v>
       </c>
       <c r="N29" t="n">
         <v>92</v>
@@ -1780,47 +1780,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>neaLaN</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7934</v>
+        <v>0.7521</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4735</v>
+        <v>0.4489</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.2798</v>
+        <v>-0.2818</v>
       </c>
       <c r="E30" t="n">
-        <v>0.7934</v>
+        <v>0.7521</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7934</v>
+        <v>1.6644</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-0.9123</v>
       </c>
       <c r="H30" t="n">
-        <v>0.7934</v>
+        <v>1.6644</v>
       </c>
       <c r="I30" t="n">
-        <v>0.7934</v>
+        <v>1.6644</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-0.9123</v>
       </c>
       <c r="K30" t="n">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="M30" t="n">
-        <v>0.7934</v>
+        <v>0.7521000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>87</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7611</v>
+        <v>0.7183</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4543</v>
+        <v>0.4287</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.2944</v>
+        <v>-0.2972</v>
       </c>
       <c r="E31" t="n">
-        <v>0.7611</v>
+        <v>0.7183</v>
       </c>
       <c r="F31" t="n">
-        <v>0.7611</v>
+        <v>0.7183</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.7611</v>
+        <v>0.7183</v>
       </c>
       <c r="I31" t="n">
-        <v>0.7611</v>
+        <v>0.7183</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.7611</v>
+        <v>0.7183</v>
       </c>
       <c r="N31" t="n">
         <v>71</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6982</v>
+        <v>0.68</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4167</v>
+        <v>0.4059</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.3228</v>
+        <v>-0.3147</v>
       </c>
       <c r="E32" t="n">
-        <v>0.6982</v>
+        <v>0.68</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6982</v>
+        <v>0.68</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.6982</v>
+        <v>0.68</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6982</v>
+        <v>0.68</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.6982</v>
+        <v>0.68</v>
       </c>
       <c r="N32" t="n">
         <v>57</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6973</v>
+        <v>0.6342</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4162</v>
+        <v>0.3785</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.3232</v>
+        <v>-0.3355</v>
       </c>
       <c r="E33" t="n">
-        <v>0.6973</v>
+        <v>0.6342</v>
       </c>
       <c r="F33" t="n">
-        <v>0.6973</v>
+        <v>0.6342</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.6973</v>
+        <v>0.6342</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6973</v>
+        <v>0.6342</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.6973</v>
+        <v>0.6342</v>
       </c>
       <c r="N33" t="n">
         <v>71</v>
@@ -1964,139 +1964,139 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6342</v>
+        <v>0.6198</v>
       </c>
       <c r="C34" t="n">
-        <v>0.3785</v>
+        <v>0.3699</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.3517</v>
+        <v>-0.3421</v>
       </c>
       <c r="E34" t="n">
-        <v>0.6342</v>
+        <v>0.6198</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9802999999999999</v>
+        <v>0.5516</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.3461</v>
+        <v>0.0682</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9802999999999999</v>
+        <v>0.5516</v>
       </c>
       <c r="I34" t="n">
-        <v>0.9802999999999999</v>
+        <v>0.5516</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.3461</v>
+        <v>0.0682</v>
       </c>
       <c r="K34" t="n">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="L34" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="M34" t="n">
-        <v>0.6341999999999999</v>
+        <v>0.6198</v>
       </c>
       <c r="N34" t="n">
-        <v>98</v>
+        <v>167</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6266</v>
+        <v>0.5704</v>
       </c>
       <c r="C35" t="n">
-        <v>0.374</v>
+        <v>0.3404</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.3551</v>
+        <v>-0.3645</v>
       </c>
       <c r="E35" t="n">
-        <v>0.6266</v>
+        <v>0.5704</v>
       </c>
       <c r="F35" t="n">
-        <v>0.5962</v>
+        <v>0.7773</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0304</v>
+        <v>-0.2069</v>
       </c>
       <c r="H35" t="n">
-        <v>0.5962</v>
+        <v>0.7773</v>
       </c>
       <c r="I35" t="n">
-        <v>0.5962</v>
+        <v>0.7773</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0304</v>
+        <v>-0.2069</v>
       </c>
       <c r="K35" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="L35" t="n">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="M35" t="n">
-        <v>0.6265999999999999</v>
+        <v>0.5704</v>
       </c>
       <c r="N35" t="n">
-        <v>167</v>
+        <v>121</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6244</v>
+        <v>0.5689</v>
       </c>
       <c r="C36" t="n">
-        <v>0.3727</v>
+        <v>0.3395</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.3561</v>
+        <v>-0.3652</v>
       </c>
       <c r="E36" t="n">
-        <v>0.6244</v>
+        <v>0.5689</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8121</v>
+        <v>0.9506</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.1877</v>
+        <v>-0.3817</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8121</v>
+        <v>0.9506</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8121</v>
+        <v>0.9506</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.1877</v>
+        <v>-0.3817</v>
       </c>
       <c r="K36" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="L36" t="n">
         <v>45</v>
       </c>
       <c r="M36" t="n">
-        <v>0.6244000000000001</v>
+        <v>0.5689</v>
       </c>
       <c r="N36" t="n">
-        <v>121</v>
+        <v>98</v>
       </c>
     </row>
     <row r="37">
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6038</v>
+        <v>0.5677</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3604</v>
+        <v>0.3388</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.3654</v>
+        <v>-0.3658</v>
       </c>
       <c r="E37" t="n">
-        <v>0.6038</v>
+        <v>0.5677</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6038</v>
+        <v>0.5677</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6038</v>
+        <v>0.5677</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6038</v>
+        <v>0.5677</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.6038</v>
+        <v>0.5677</v>
       </c>
       <c r="N37" t="n">
         <v>76</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4889</v>
+        <v>0.4958</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2918</v>
+        <v>0.2959</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.4173</v>
+        <v>-0.3985</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4889</v>
+        <v>0.4958</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4889</v>
+        <v>0.4958</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.4889</v>
+        <v>0.4958</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4889</v>
+        <v>0.4958</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.4889</v>
+        <v>0.4958</v>
       </c>
       <c r="N38" t="n">
         <v>71</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.4577</v>
+        <v>0.4061</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2732</v>
+        <v>0.2424</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.4314</v>
+        <v>-0.4393</v>
       </c>
       <c r="E39" t="n">
-        <v>0.4577</v>
+        <v>0.4061</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4577</v>
+        <v>0.4061</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.4577</v>
+        <v>0.4061</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4577</v>
+        <v>0.4061</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.4577</v>
+        <v>0.4061</v>
       </c>
       <c r="N39" t="n">
         <v>53</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.3668</v>
+        <v>0.3757</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2189</v>
+        <v>0.2242</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.4724</v>
+        <v>-0.4532</v>
       </c>
       <c r="E40" t="n">
-        <v>0.3668</v>
+        <v>0.3757</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3668</v>
+        <v>0.3757</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.3668</v>
+        <v>0.3757</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3668</v>
+        <v>0.3757</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.3668</v>
+        <v>0.3757</v>
       </c>
       <c r="N40" t="n">
         <v>92</v>
@@ -2286,93 +2286,93 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>BOROS</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.3448</v>
+        <v>0.3113</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2058</v>
+        <v>0.1858</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.4824</v>
+        <v>-0.4825</v>
       </c>
       <c r="E41" t="n">
-        <v>0.3448</v>
+        <v>0.3113</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3448</v>
+        <v>0.3113</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.3448</v>
+        <v>0.3113</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3448</v>
+        <v>0.3113</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.3448</v>
+        <v>0.3113</v>
       </c>
       <c r="N41" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BOROS</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.3282</v>
+        <v>0.3101</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1959</v>
+        <v>0.1851</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4898</v>
+        <v>-0.483</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3282</v>
+        <v>0.3101</v>
       </c>
       <c r="F42" t="n">
-        <v>0.3282</v>
+        <v>0.3101</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.3282</v>
+        <v>0.3101</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3282</v>
+        <v>0.3101</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.3282</v>
+        <v>0.3101</v>
       </c>
       <c r="N42" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43">
@@ -2382,28 +2382,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.284</v>
+        <v>0.2422</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1695</v>
+        <v>0.1446</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.5098</v>
+        <v>-0.5139</v>
       </c>
       <c r="E43" t="n">
-        <v>0.284</v>
+        <v>0.2422</v>
       </c>
       <c r="F43" t="n">
-        <v>0.284</v>
+        <v>0.2422</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.284</v>
+        <v>0.2422</v>
       </c>
       <c r="I43" t="n">
-        <v>0.284</v>
+        <v>0.2422</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.284</v>
+        <v>0.2422</v>
       </c>
       <c r="N43" t="n">
         <v>53</v>
@@ -2428,28 +2428,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2752</v>
+        <v>0.2315</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1643</v>
+        <v>0.1382</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.5138</v>
+        <v>-0.5188</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2752</v>
+        <v>0.2315</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2752</v>
+        <v>0.2315</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2752</v>
+        <v>0.2315</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2752</v>
+        <v>0.2315</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.2752</v>
+        <v>0.2315</v>
       </c>
       <c r="N44" t="n">
         <v>92</v>
@@ -2474,28 +2474,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.24</v>
+        <v>0.2258</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1432</v>
+        <v>0.1348</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.5296999999999999</v>
+        <v>-0.5214</v>
       </c>
       <c r="E45" t="n">
-        <v>0.24</v>
+        <v>0.2258</v>
       </c>
       <c r="F45" t="n">
-        <v>0.24</v>
+        <v>0.2258</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.24</v>
+        <v>0.2258</v>
       </c>
       <c r="I45" t="n">
-        <v>0.24</v>
+        <v>0.2258</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.24</v>
+        <v>0.2258</v>
       </c>
       <c r="N45" t="n">
         <v>66</v>
@@ -2516,139 +2516,139 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>mynio</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.0985</v>
+        <v>0.1305</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0588</v>
+        <v>0.0779</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.5935</v>
+        <v>-0.5648</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0985</v>
+        <v>0.1305</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0985</v>
+        <v>0.1479</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>-0.0174</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0985</v>
+        <v>0.1479</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0985</v>
+        <v>0.1479</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>-0.0174</v>
       </c>
       <c r="K46" t="n">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M46" t="n">
-        <v>0.0985</v>
+        <v>0.1305</v>
       </c>
       <c r="N46" t="n">
-        <v>92</v>
+        <v>121</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>afro</t>
+          <t>mynio</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.0945</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0564</v>
+        <v>0.0554</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.5954</v>
+        <v>-0.582</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0945</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0945</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0945</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>0.0945</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.0945</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="N47" t="n">
-        <v>53</v>
+        <v>92</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>afro</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.0727</v>
+        <v>0.0751</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0434</v>
+        <v>0.0448</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.6052</v>
+        <v>-0.59</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0727</v>
+        <v>0.0751</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1328</v>
+        <v>0.0751</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.0601</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1328</v>
+        <v>0.0751</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1328</v>
+        <v>0.0751</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.0601</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="L48" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.0727</v>
+        <v>0.0751</v>
       </c>
       <c r="N48" t="n">
-        <v>121</v>
+        <v>53</v>
       </c>
     </row>
     <row r="49">
@@ -2658,28 +2658,28 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.0378</v>
+        <v>0.0272</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0226</v>
+        <v>0.0162</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.6209</v>
+        <v>-0.6118</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0378</v>
+        <v>0.0272</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0378</v>
+        <v>0.0272</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0378</v>
+        <v>0.0272</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0378</v>
+        <v>0.0272</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2691,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.0378</v>
+        <v>0.0272</v>
       </c>
       <c r="N49" t="n">
         <v>87</v>
@@ -2704,28 +2704,28 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.0554</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.0331</v>
+        <v>-0.0386</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.663</v>
+        <v>-0.6536999999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.0554</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.0554</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.0554</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.0554</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.0554</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="N50" t="n">
         <v>57</v>
@@ -2750,28 +2750,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.0607</v>
+        <v>-0.0838</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.0362</v>
+        <v>-0.05</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.6654</v>
+        <v>-0.6624</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.0607</v>
+        <v>-0.0838</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.0607</v>
+        <v>-0.0838</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.0607</v>
+        <v>-0.0838</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.0607</v>
+        <v>-0.0838</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.0607</v>
+        <v>-0.0838</v>
       </c>
       <c r="N51" t="n">
         <v>47</v>
@@ -2796,28 +2796,28 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.1028</v>
+        <v>-0.1318</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.0614</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.6844</v>
+        <v>-0.6842</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.1028</v>
+        <v>-0.1318</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.1028</v>
+        <v>-0.1318</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.1028</v>
+        <v>-0.1318</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.1028</v>
+        <v>-0.1318</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.1028</v>
+        <v>-0.1318</v>
       </c>
       <c r="N52" t="n">
         <v>47</v>
@@ -2842,28 +2842,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.1522</v>
+        <v>-0.181</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.09080000000000001</v>
+        <v>-0.108</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.7067</v>
+        <v>-0.7066</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.1522</v>
+        <v>-0.181</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.1522</v>
+        <v>-0.181</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.1522</v>
+        <v>-0.181</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1522</v>
+        <v>-0.181</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.1522</v>
+        <v>-0.181</v>
       </c>
       <c r="N53" t="n">
         <v>47</v>
@@ -2884,32 +2884,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.2102</v>
+        <v>-0.2152</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.1255</v>
+        <v>-0.1284</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.7329</v>
+        <v>-0.7222</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.2102</v>
+        <v>-0.2152</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.2102</v>
+        <v>-0.2152</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.2102</v>
+        <v>-0.2152</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2102</v>
+        <v>-0.2152</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.2102</v>
+        <v>-0.2152</v>
       </c>
       <c r="N54" t="n">
         <v>66</v>
@@ -2930,47 +2930,47 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.2105</v>
+        <v>-0.2157</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.1256</v>
+        <v>-0.1287</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.733</v>
+        <v>-0.7224</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.2105</v>
+        <v>-0.2157</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.2105</v>
+        <v>0.0605</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>-0.2762</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.2105</v>
+        <v>0.0605</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2105</v>
+        <v>0.0605</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>-0.2762</v>
       </c>
       <c r="K55" t="n">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.2105</v>
+        <v>-0.2157</v>
       </c>
       <c r="N55" t="n">
-        <v>66</v>
+        <v>167</v>
       </c>
     </row>
     <row r="56">
@@ -2980,28 +2980,28 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.2107</v>
+        <v>-0.2213</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.1258</v>
+        <v>-0.1321</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.7331</v>
+        <v>-0.7249</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.2107</v>
+        <v>-0.2213</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.2107</v>
+        <v>-0.2213</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.2107</v>
+        <v>-0.2213</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2107</v>
+        <v>-0.2213</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.2107</v>
+        <v>-0.2213</v>
       </c>
       <c r="N56" t="n">
         <v>87</v>
@@ -3022,32 +3022,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>lauNX</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.2155</v>
+        <v>-0.2348</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.1286</v>
+        <v>-0.1401</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.7353</v>
+        <v>-0.7311</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.2155</v>
+        <v>-0.2348</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.2155</v>
+        <v>-0.2348</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.2155</v>
+        <v>-0.2348</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.2155</v>
+        <v>-0.2348</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -3059,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.2155</v>
+        <v>-0.2348</v>
       </c>
       <c r="N57" t="n">
         <v>66</v>
@@ -3068,93 +3068,93 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>dexter</t>
+          <t>lauNX</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.2537</v>
+        <v>-0.2358</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.1514</v>
+        <v>-0.1407</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.7524999999999999</v>
+        <v>-0.7315</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.2537</v>
+        <v>-0.2358</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.2537</v>
+        <v>-0.2358</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.2537</v>
+        <v>-0.2358</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.2537</v>
+        <v>-0.2358</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.2537</v>
+        <v>-0.2358</v>
       </c>
       <c r="N58" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>dexter</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.2551</v>
+        <v>-0.2766</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.1523</v>
+        <v>-0.1651</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.7532</v>
+        <v>-0.7501</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.2551</v>
+        <v>-0.2766</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0339</v>
+        <v>-0.2766</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.289</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>0.0339</v>
+        <v>-0.2766</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0339</v>
+        <v>-0.2766</v>
       </c>
       <c r="J59" t="n">
-        <v>-0.289</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="L59" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.2551</v>
+        <v>-0.2766</v>
       </c>
       <c r="N59" t="n">
-        <v>167</v>
+        <v>53</v>
       </c>
     </row>
     <row r="60">
@@ -3164,31 +3164,31 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.317</v>
+        <v>-0.2949</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.1892</v>
+        <v>-0.176</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.7811</v>
+        <v>-0.7584</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.317</v>
+        <v>-0.2949</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.3577</v>
+        <v>-0.3081</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0407</v>
+        <v>0.0132</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.3577</v>
+        <v>-0.3081</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3577</v>
+        <v>-0.3081</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0407</v>
+        <v>0.0132</v>
       </c>
       <c r="K60" t="n">
         <v>71</v>
@@ -3197,7 +3197,7 @@
         <v>67</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.317</v>
+        <v>-0.2949</v>
       </c>
       <c r="N60" t="n">
         <v>138</v>
@@ -3210,31 +3210,31 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.3294</v>
+        <v>-0.3413</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.1966</v>
+        <v>-0.2037</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7867</v>
+        <v>-0.7796</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.3294</v>
+        <v>-0.3413</v>
       </c>
       <c r="F61" t="n">
-        <v>0.074</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.4034</v>
+        <v>-0.4225</v>
       </c>
       <c r="H61" t="n">
-        <v>0.074</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>0.074</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="J61" t="n">
-        <v>-0.4034</v>
+        <v>-0.4225</v>
       </c>
       <c r="K61" t="n">
         <v>87</v>
@@ -3243,7 +3243,7 @@
         <v>80</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.3294</v>
+        <v>-0.3413</v>
       </c>
       <c r="N61" t="n">
         <v>167</v>
@@ -3252,139 +3252,139 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>volt</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.3693</v>
+        <v>-0.3837</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.2204</v>
+        <v>-0.229</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.8047</v>
+        <v>-0.7989000000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.3693</v>
+        <v>-0.3837</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.3693</v>
+        <v>-0.3753</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.3693</v>
+        <v>-0.3753</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.3693</v>
+        <v>-0.3753</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="K62" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.3693</v>
+        <v>-0.3837</v>
       </c>
       <c r="N62" t="n">
-        <v>76</v>
+        <v>138</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.3774</v>
+        <v>-0.3843</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.2253</v>
+        <v>-0.2294</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.8084</v>
+        <v>-0.7991</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.3774</v>
+        <v>-0.3843</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.3774</v>
+        <v>-0.3843</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.3774</v>
+        <v>-0.3843</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.3774</v>
+        <v>-0.3843</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.3774</v>
+        <v>-0.3843</v>
       </c>
       <c r="N63" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.4066</v>
+        <v>-0.4088</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.2427</v>
+        <v>-0.244</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.8216</v>
+        <v>-0.8103</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.4066</v>
+        <v>-0.4088</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.4066</v>
+        <v>-0.4088</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.4066</v>
+        <v>-0.4088</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.4066</v>
+        <v>-0.4088</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.4066</v>
+        <v>-0.4088</v>
       </c>
       <c r="N64" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
     </row>
     <row r="65">
@@ -3394,28 +3394,28 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.411</v>
+        <v>-0.42</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.2453</v>
+        <v>-0.2507</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8236</v>
+        <v>-0.8154</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.411</v>
+        <v>-0.42</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.411</v>
+        <v>-0.42</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.411</v>
+        <v>-0.42</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.411</v>
+        <v>-0.42</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -3427,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.411</v>
+        <v>-0.42</v>
       </c>
       <c r="N65" t="n">
         <v>71</v>
@@ -3436,47 +3436,47 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.421</v>
+        <v>-0.4204</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.2513</v>
+        <v>-0.2509</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8280999999999999</v>
+        <v>-0.8156</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.421</v>
+        <v>-0.4204</v>
       </c>
       <c r="F66" t="n">
-        <v>0.2817</v>
+        <v>-0.4204</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.7027</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>0.2817</v>
+        <v>-0.4204</v>
       </c>
       <c r="I66" t="n">
-        <v>0.2817</v>
+        <v>-0.4204</v>
       </c>
       <c r="J66" t="n">
-        <v>-0.7027</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="L66" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.421</v>
+        <v>-0.4204</v>
       </c>
       <c r="N66" t="n">
-        <v>98</v>
+        <v>76</v>
       </c>
     </row>
     <row r="67">
@@ -3486,28 +3486,28 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.4368</v>
+        <v>-0.4523</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.2607</v>
+        <v>-0.27</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8352000000000001</v>
+        <v>-0.8300999999999999</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.4368</v>
+        <v>-0.4523</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.4368</v>
+        <v>-0.4523</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.4368</v>
+        <v>-0.4523</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.4368</v>
+        <v>-0.4523</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -3519,7 +3519,7 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.4368</v>
+        <v>-0.4523</v>
       </c>
       <c r="N67" t="n">
         <v>76</v>
@@ -3528,93 +3528,93 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>jL</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.4733</v>
+        <v>-0.4575</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.2825</v>
+        <v>-0.2731</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8517</v>
+        <v>-0.8325</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.4733</v>
+        <v>-0.4575</v>
       </c>
       <c r="F68" t="n">
-        <v>0.395</v>
+        <v>0.2756</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.8683</v>
+        <v>-0.7331</v>
       </c>
       <c r="H68" t="n">
-        <v>0.395</v>
+        <v>0.2756</v>
       </c>
       <c r="I68" t="n">
-        <v>0.395</v>
+        <v>0.2756</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.8683</v>
+        <v>-0.7331</v>
       </c>
       <c r="K68" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="L68" t="n">
         <v>45</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.4732999999999999</v>
+        <v>-0.4575</v>
       </c>
       <c r="N68" t="n">
-        <v>121</v>
+        <v>98</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>volt</t>
+          <t>jL</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.4747</v>
+        <v>-0.5175999999999999</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.2833</v>
+        <v>-0.3089</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8522999999999999</v>
+        <v>-0.8598</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.4747</v>
+        <v>-0.5175999999999999</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.4336</v>
+        <v>0.3787</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.0411</v>
+        <v>-0.8963</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.4336</v>
+        <v>0.3787</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.4336</v>
+        <v>0.3787</v>
       </c>
       <c r="J69" t="n">
-        <v>-0.0411</v>
+        <v>-0.8963</v>
       </c>
       <c r="K69" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="L69" t="n">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.4747</v>
+        <v>-0.5176000000000001</v>
       </c>
       <c r="N69" t="n">
-        <v>138</v>
+        <v>121</v>
       </c>
     </row>
     <row r="70">
@@ -3624,28 +3624,28 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.504</v>
+        <v>-0.5285</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.3008</v>
+        <v>-0.3154</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8655</v>
+        <v>-0.8648</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.504</v>
+        <v>-0.5285</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.504</v>
+        <v>-0.5285</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.504</v>
+        <v>-0.5285</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.504</v>
+        <v>-0.5285</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -3657,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.504</v>
+        <v>-0.5285</v>
       </c>
       <c r="N70" t="n">
         <v>71</v>
@@ -3670,28 +3670,28 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.5396</v>
+        <v>-0.5641</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.3221</v>
+        <v>-0.3367</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8816000000000001</v>
+        <v>-0.881</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.5396</v>
+        <v>-0.5641</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.5396</v>
+        <v>-0.5641</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.5396</v>
+        <v>-0.5641</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5396</v>
+        <v>-0.5641</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.5396</v>
+        <v>-0.5641</v>
       </c>
       <c r="N71" t="n">
         <v>57</v>
@@ -3716,28 +3716,28 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.5957</v>
+        <v>-0.6299</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.3555</v>
+        <v>-0.376</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9069</v>
+        <v>-0.9109</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.5957</v>
+        <v>-0.6299</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.5957</v>
+        <v>-0.6299</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.5957</v>
+        <v>-0.6299</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.5957</v>
+        <v>-0.6299</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.5957</v>
+        <v>-0.6299</v>
       </c>
       <c r="N72" t="n">
         <v>47</v>
@@ -3762,28 +3762,28 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.6258</v>
+        <v>-0.6647</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.3735</v>
+        <v>-0.3967</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9205</v>
+        <v>-0.9268</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.6258</v>
+        <v>-0.6647</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.6258</v>
+        <v>-0.6647</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.6258</v>
+        <v>-0.6647</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.6258</v>
+        <v>-0.6647</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -3795,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.6258</v>
+        <v>-0.6647</v>
       </c>
       <c r="N73" t="n">
         <v>92</v>
@@ -3808,28 +3808,28 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.7431</v>
+        <v>-0.7688</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.4435</v>
+        <v>-0.4589</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9735</v>
+        <v>-0.9742</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.7431</v>
+        <v>-0.7688</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.7431</v>
+        <v>-0.7688</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.7431</v>
+        <v>-0.7688</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.7431</v>
+        <v>-0.7688</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -3841,7 +3841,7 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-0.7431</v>
+        <v>-0.7688</v>
       </c>
       <c r="N74" t="n">
         <v>47</v>
@@ -3854,28 +3854,28 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.9067</v>
+        <v>-0.9172</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.5412</v>
+        <v>-0.5474</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0473</v>
+        <v>-1.0417</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.9067</v>
+        <v>-0.9172</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.9067</v>
+        <v>-0.9172</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.9067</v>
+        <v>-0.9172</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.9067</v>
+        <v>-0.9172</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-0.9067</v>
+        <v>-0.9172</v>
       </c>
       <c r="N75" t="n">
         <v>57</v>
@@ -3900,31 +3900,31 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.4016</v>
+        <v>-1.3163</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.8365</v>
+        <v>-0.7856</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.2708</v>
+        <v>-1.2234</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.4016</v>
+        <v>-1.3163</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.9265</v>
+        <v>-0.8043</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.4751</v>
+        <v>-0.512</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.9265</v>
+        <v>-0.8043</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.9265</v>
+        <v>-0.8043</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.4751</v>
+        <v>-0.512</v>
       </c>
       <c r="K76" t="n">
         <v>53</v>
@@ -3933,7 +3933,7 @@
         <v>45</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.4016</v>
+        <v>-1.3163</v>
       </c>
       <c r="N76" t="n">
         <v>98</v>
@@ -3942,93 +3942,93 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Keoz</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.7678</v>
+        <v>-1.5998</v>
       </c>
       <c r="C77" t="n">
-        <v>-1.0551</v>
+        <v>-0.9548</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.4361</v>
+        <v>-1.3525</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.7678</v>
+        <v>-1.5998</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.7678</v>
+        <v>0.6435999999999999</v>
       </c>
       <c r="G77" t="n">
-        <v>-1</v>
+        <v>-2.2434</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.7678</v>
+        <v>0.6435999999999999</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.7678</v>
+        <v>0.6435999999999999</v>
       </c>
       <c r="J77" t="n">
-        <v>-1</v>
+        <v>-2.2434</v>
       </c>
       <c r="K77" t="n">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="L77" t="n">
-        <v>67</v>
+        <v>209</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.7678</v>
+        <v>-1.5998</v>
       </c>
       <c r="N77" t="n">
-        <v>138</v>
+        <v>256</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>Keoz</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.871</v>
+        <v>-1.7386</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.1167</v>
+        <v>-1.0377</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.4827</v>
+        <v>-1.4156</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.871</v>
+        <v>-1.7386</v>
       </c>
       <c r="F78" t="n">
-        <v>0.6203</v>
+        <v>-0.7386</v>
       </c>
       <c r="G78" t="n">
-        <v>-2.4913</v>
+        <v>-1</v>
       </c>
       <c r="H78" t="n">
-        <v>0.6203</v>
+        <v>-0.7386</v>
       </c>
       <c r="I78" t="n">
-        <v>0.6203</v>
+        <v>-0.7386</v>
       </c>
       <c r="J78" t="n">
-        <v>-2.4913</v>
+        <v>-1</v>
       </c>
       <c r="K78" t="n">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="L78" t="n">
-        <v>209</v>
+        <v>67</v>
       </c>
       <c r="M78" t="n">
-        <v>-1.871</v>
+        <v>-1.7386</v>
       </c>
       <c r="N78" t="n">
-        <v>256</v>
+        <v>138</v>
       </c>
     </row>
     <row r="79">
@@ -4038,31 +4038,31 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.2919</v>
+        <v>-2.1056</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.3679</v>
+        <v>-1.2567</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.6727</v>
+        <v>-1.5827</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.2919</v>
+        <v>-2.1056</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.578</v>
+        <v>-1.4258</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.7139</v>
+        <v>-0.6798</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.578</v>
+        <v>-1.4258</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.578</v>
+        <v>-1.4258</v>
       </c>
       <c r="J79" t="n">
-        <v>-0.7139</v>
+        <v>-0.6798</v>
       </c>
       <c r="K79" t="n">
         <v>92</v>
@@ -4071,7 +4071,7 @@
         <v>168</v>
       </c>
       <c r="M79" t="n">
-        <v>-2.2919</v>
+        <v>-2.1056</v>
       </c>
       <c r="N79" t="n">
         <v>260</v>
@@ -4084,31 +4084,31 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.4189</v>
+        <v>-2.3979</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.4437</v>
+        <v>-1.4312</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.73</v>
+        <v>-1.7158</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.4189</v>
+        <v>-2.3979</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.5971</v>
+        <v>-0.5666</v>
       </c>
       <c r="G80" t="n">
-        <v>-1.8218</v>
+        <v>-1.8313</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.5971</v>
+        <v>-0.5666</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.5971</v>
+        <v>-0.5666</v>
       </c>
       <c r="J80" t="n">
-        <v>-1.8218</v>
+        <v>-1.8313</v>
       </c>
       <c r="K80" t="n">
         <v>92</v>
@@ -4117,7 +4117,7 @@
         <v>168</v>
       </c>
       <c r="M80" t="n">
-        <v>-2.4189</v>
+        <v>-2.3979</v>
       </c>
       <c r="N80" t="n">
         <v>260</v>
@@ -4130,31 +4130,31 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.6412</v>
+        <v>-2.5099</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.5764</v>
+        <v>-1.498</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.8304</v>
+        <v>-1.7668</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.6412</v>
+        <v>-2.5099</v>
       </c>
       <c r="F81" t="n">
-        <v>-1.037</v>
+        <v>-0.9746</v>
       </c>
       <c r="G81" t="n">
-        <v>-1.6042</v>
+        <v>-1.5353</v>
       </c>
       <c r="H81" t="n">
-        <v>-1.037</v>
+        <v>-0.9746</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.037</v>
+        <v>-0.9746</v>
       </c>
       <c r="J81" t="n">
-        <v>-1.6042</v>
+        <v>-1.5353</v>
       </c>
       <c r="K81" t="n">
         <v>57</v>
@@ -4163,7 +4163,7 @@
         <v>184</v>
       </c>
       <c r="M81" t="n">
-        <v>-2.6412</v>
+        <v>-2.5099</v>
       </c>
       <c r="N81" t="n">
         <v>241</v>
@@ -4269,10 +4269,10 @@
         <v>1.62</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7315</v>
+        <v>0.7286</v>
       </c>
       <c r="J2" t="n">
-        <v>16.8245</v>
+        <v>16.7578</v>
       </c>
     </row>
     <row r="3">
@@ -4309,10 +4309,10 @@
         <v>1.43</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5303</v>
+        <v>0.5406</v>
       </c>
       <c r="J3" t="n">
-        <v>12.1969</v>
+        <v>12.4338</v>
       </c>
     </row>
     <row r="4">
@@ -4349,10 +4349,10 @@
         <v>1.34</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4323</v>
+        <v>0.4475</v>
       </c>
       <c r="J4" t="n">
-        <v>9.9429</v>
+        <v>10.2925</v>
       </c>
     </row>
     <row r="5">
@@ -4389,10 +4389,10 @@
         <v>1.14</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1955</v>
+        <v>0.2164</v>
       </c>
       <c r="J5" t="n">
-        <v>4.4965</v>
+        <v>4.9772</v>
       </c>
     </row>
     <row r="6">
@@ -4429,10 +4429,10 @@
         <v>0.97</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0793</v>
+        <v>-0.081</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.8239</v>
+        <v>-1.863</v>
       </c>
     </row>
     <row r="7">
@@ -4469,10 +4469,10 @@
         <v>1.12</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2998</v>
+        <v>0.2885</v>
       </c>
       <c r="J7" t="n">
-        <v>6.8954</v>
+        <v>6.6355</v>
       </c>
     </row>
     <row r="8">
@@ -4509,10 +4509,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2004</v>
+        <v>-0.2205</v>
       </c>
       <c r="J8" t="n">
-        <v>-4.6092</v>
+        <v>-5.0715</v>
       </c>
     </row>
     <row r="9">
@@ -4549,10 +4549,10 @@
         <v>0.67</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3325</v>
+        <v>-0.35</v>
       </c>
       <c r="J9" t="n">
-        <v>-7.6475</v>
+        <v>-8.050000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -4589,10 +4589,10 @@
         <v>0.63</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.37</v>
+        <v>-0.386</v>
       </c>
       <c r="J10" t="n">
-        <v>-8.51</v>
+        <v>-8.878</v>
       </c>
     </row>
     <row r="11">
@@ -4629,10 +4629,10 @@
         <v>0.55</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4449</v>
+        <v>-0.457</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.2327</v>
+        <v>-10.511</v>
       </c>
     </row>
     <row r="12">
@@ -4669,10 +4669,10 @@
         <v>1.17</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3794</v>
+        <v>0.3792</v>
       </c>
       <c r="J12" t="n">
-        <v>10.6232</v>
+        <v>10.6176</v>
       </c>
     </row>
     <row r="13">
@@ -4709,10 +4709,10 @@
         <v>1.13</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3031</v>
+        <v>0.3073</v>
       </c>
       <c r="J13" t="n">
-        <v>8.486800000000001</v>
+        <v>8.6044</v>
       </c>
     </row>
     <row r="14">
@@ -4749,10 +4749,10 @@
         <v>1.01</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0365</v>
+        <v>0.0425</v>
       </c>
       <c r="J14" t="n">
-        <v>1.022</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="15">
@@ -4789,10 +4789,10 @@
         <v>0.9</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1356</v>
+        <v>-0.148</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.7968</v>
+        <v>-4.144</v>
       </c>
     </row>
     <row r="16">
@@ -4829,10 +4829,10 @@
         <v>0.85</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1893</v>
+        <v>-0.2026</v>
       </c>
       <c r="J16" t="n">
-        <v>-5.3004</v>
+        <v>-5.6728</v>
       </c>
     </row>
     <row r="17">
@@ -4869,10 +4869,10 @@
         <v>1.35</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.8983</v>
       </c>
       <c r="J17" t="n">
-        <v>27.0816</v>
+        <v>25.1524</v>
       </c>
     </row>
     <row r="18">
@@ -4909,10 +4909,10 @@
         <v>1.24</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7047</v>
+        <v>0.6647</v>
       </c>
       <c r="J18" t="n">
-        <v>19.7316</v>
+        <v>18.6116</v>
       </c>
     </row>
     <row r="19">
@@ -4949,10 +4949,10 @@
         <v>1.05</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1874</v>
+        <v>0.1936</v>
       </c>
       <c r="J19" t="n">
-        <v>5.2472</v>
+        <v>5.4208</v>
       </c>
     </row>
     <row r="20">
@@ -4989,10 +4989,10 @@
         <v>0.85</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5008</v>
+        <v>-0.4775</v>
       </c>
       <c r="J20" t="n">
-        <v>-14.0224</v>
+        <v>-13.37</v>
       </c>
     </row>
     <row r="21">
@@ -5029,10 +5029,10 @@
         <v>0.72</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8364</v>
+        <v>-0.7745</v>
       </c>
       <c r="J21" t="n">
-        <v>-23.4192</v>
+        <v>-21.686</v>
       </c>
     </row>
     <row r="22">
@@ -5069,10 +5069,10 @@
         <v>1.09</v>
       </c>
       <c r="I22" t="n">
-        <v>0.285</v>
+        <v>0.276</v>
       </c>
       <c r="J22" t="n">
-        <v>7.125</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="23">
@@ -5109,10 +5109,10 @@
         <v>0.98</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.014</v>
+        <v>-0.0257</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.35</v>
+        <v>-0.6425</v>
       </c>
     </row>
     <row r="24">
@@ -5149,10 +5149,10 @@
         <v>0.74</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2765</v>
+        <v>-0.2936</v>
       </c>
       <c r="J24" t="n">
-        <v>-6.9125</v>
+        <v>-7.34</v>
       </c>
     </row>
     <row r="25">
@@ -5189,10 +5189,10 @@
         <v>0.73</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2861</v>
+        <v>-0.303</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.1525</v>
+        <v>-7.575</v>
       </c>
     </row>
     <row r="26">
@@ -5229,10 +5229,10 @@
         <v>0.61</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3996</v>
+        <v>-0.4123</v>
       </c>
       <c r="J26" t="n">
-        <v>-9.99</v>
+        <v>-10.3075</v>
       </c>
     </row>
     <row r="27">
@@ -5269,10 +5269,10 @@
         <v>1.56</v>
       </c>
       <c r="I27" t="n">
-        <v>1.2204</v>
+        <v>1.2532</v>
       </c>
       <c r="J27" t="n">
-        <v>30.51</v>
+        <v>31.33</v>
       </c>
     </row>
     <row r="28">
@@ -5309,10 +5309,10 @@
         <v>1.3</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7963</v>
+        <v>0.7549</v>
       </c>
       <c r="J28" t="n">
-        <v>19.9075</v>
+        <v>18.8725</v>
       </c>
     </row>
     <row r="29">
@@ -5349,10 +5349,10 @@
         <v>1.21</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5851</v>
+        <v>0.5674</v>
       </c>
       <c r="J29" t="n">
-        <v>14.6275</v>
+        <v>14.185</v>
       </c>
     </row>
     <row r="30">
@@ -5389,10 +5389,10 @@
         <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0461</v>
+        <v>-0.0318</v>
       </c>
       <c r="J30" t="n">
-        <v>-1.1525</v>
+        <v>-0.795</v>
       </c>
     </row>
     <row r="31">
@@ -5429,10 +5429,10 @@
         <v>0.88</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.458</v>
+        <v>-0.4306</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.45</v>
+        <v>-10.765</v>
       </c>
     </row>
     <row r="32">
@@ -5469,10 +5469,10 @@
         <v>1.38</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7258</v>
+        <v>0.8007</v>
       </c>
       <c r="J32" t="n">
-        <v>20.3224</v>
+        <v>22.4196</v>
       </c>
     </row>
     <row r="33">
@@ -5509,10 +5509,10 @@
         <v>1.25</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5465</v>
+        <v>0.604</v>
       </c>
       <c r="J33" t="n">
-        <v>15.302</v>
+        <v>16.912</v>
       </c>
     </row>
     <row r="34">
@@ -5549,10 +5549,10 @@
         <v>1.04</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1351</v>
+        <v>0.1489</v>
       </c>
       <c r="J34" t="n">
-        <v>3.7828</v>
+        <v>4.1692</v>
       </c>
     </row>
     <row r="35">
@@ -5589,10 +5589,10 @@
         <v>1.01</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0226</v>
+        <v>0.0376</v>
       </c>
       <c r="J35" t="n">
-        <v>0.6328</v>
+        <v>1.0528</v>
       </c>
     </row>
     <row r="36">
@@ -5629,10 +5629,10 @@
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.0322</v>
+        <v>-0.0222</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.9016</v>
+        <v>-0.6216</v>
       </c>
     </row>
     <row r="37">
@@ -5669,10 +5669,10 @@
         <v>1.03</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1387</v>
+        <v>0.1341</v>
       </c>
       <c r="J37" t="n">
-        <v>3.8836</v>
+        <v>3.7548</v>
       </c>
     </row>
     <row r="38">
@@ -5709,10 +5709,10 @@
         <v>0.99</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0015</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>0.042</v>
+        <v>-0.2464</v>
       </c>
     </row>
     <row r="39">
@@ -5749,10 +5749,10 @@
         <v>0.93</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.0825</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.31</v>
+        <v>-2.7468</v>
       </c>
     </row>
     <row r="40">
@@ -5789,10 +5789,10 @@
         <v>0.64</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3726</v>
+        <v>-0.3864</v>
       </c>
       <c r="J40" t="n">
-        <v>-10.4328</v>
+        <v>-10.8192</v>
       </c>
     </row>
     <row r="41">
@@ -5829,10 +5829,10 @@
         <v>0.6</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.41</v>
+        <v>-0.4221</v>
       </c>
       <c r="J41" t="n">
-        <v>-11.48</v>
+        <v>-11.8188</v>
       </c>
     </row>
     <row r="42">
@@ -5869,10 +5869,10 @@
         <v>1.12</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2707</v>
+        <v>0.2665</v>
       </c>
       <c r="J42" t="n">
-        <v>7.0382</v>
+        <v>6.929</v>
       </c>
     </row>
     <row r="43">
@@ -5909,10 +5909,10 @@
         <v>1.1</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2378</v>
+        <v>0.2347</v>
       </c>
       <c r="J43" t="n">
-        <v>6.1828</v>
+        <v>6.1022</v>
       </c>
     </row>
     <row r="44">
@@ -5949,10 +5949,10 @@
         <v>0.71</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.3041</v>
+        <v>-0.3207</v>
       </c>
       <c r="J44" t="n">
-        <v>-7.9066</v>
+        <v>-8.338200000000001</v>
       </c>
     </row>
     <row r="45">
@@ -5989,10 +5989,10 @@
         <v>0.64</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3704</v>
+        <v>-0.3846</v>
       </c>
       <c r="J45" t="n">
-        <v>-9.6304</v>
+        <v>-9.999599999999999</v>
       </c>
     </row>
     <row r="46">
@@ -6029,10 +6029,10 @@
         <v>0.54</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4635</v>
+        <v>-0.4731</v>
       </c>
       <c r="J46" t="n">
-        <v>-12.051</v>
+        <v>-12.3006</v>
       </c>
     </row>
     <row r="47">
@@ -6069,10 +6069,10 @@
         <v>1.64</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5809</v>
+        <v>0.6677</v>
       </c>
       <c r="J47" t="n">
-        <v>15.1034</v>
+        <v>17.3602</v>
       </c>
     </row>
     <row r="48">
@@ -6109,10 +6109,10 @@
         <v>1.4</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4309</v>
+        <v>0.4916</v>
       </c>
       <c r="J48" t="n">
-        <v>11.2034</v>
+        <v>12.7816</v>
       </c>
     </row>
     <row r="49">
@@ -6149,10 +6149,10 @@
         <v>1.29</v>
       </c>
       <c r="I49" t="n">
-        <v>0.36</v>
+        <v>0.395</v>
       </c>
       <c r="J49" t="n">
-        <v>9.359999999999999</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="50">
@@ -6189,10 +6189,10 @@
         <v>1.28</v>
       </c>
       <c r="I50" t="n">
-        <v>0.3534</v>
+        <v>0.3842</v>
       </c>
       <c r="J50" t="n">
-        <v>9.1884</v>
+        <v>9.9892</v>
       </c>
     </row>
     <row r="51">
@@ -6229,10 +6229,10 @@
         <v>0.87</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1966</v>
+        <v>-0.2035</v>
       </c>
       <c r="J51" t="n">
-        <v>-5.1116</v>
+        <v>-5.291</v>
       </c>
     </row>
     <row r="52">
@@ -6269,10 +6269,10 @@
         <v>1.31</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6424</v>
+        <v>0.7071</v>
       </c>
       <c r="J52" t="n">
-        <v>21.8416</v>
+        <v>24.0414</v>
       </c>
     </row>
     <row r="53">
@@ -6309,10 +6309,10 @@
         <v>1.25</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.6132</v>
       </c>
       <c r="J53" t="n">
-        <v>18.938</v>
+        <v>20.8488</v>
       </c>
     </row>
     <row r="54">
@@ -6349,10 +6349,10 @@
         <v>1.17</v>
       </c>
       <c r="I54" t="n">
-        <v>0.4387</v>
+        <v>0.4809</v>
       </c>
       <c r="J54" t="n">
-        <v>14.9158</v>
+        <v>16.3506</v>
       </c>
     </row>
     <row r="55">
@@ -6389,10 +6389,10 @@
         <v>0.9</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3728</v>
+        <v>-0.3586</v>
       </c>
       <c r="J55" t="n">
-        <v>-12.6752</v>
+        <v>-12.1924</v>
       </c>
     </row>
     <row r="56">
@@ -6429,10 +6429,10 @@
         <v>0.79</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.6713</v>
+        <v>-0.6274</v>
       </c>
       <c r="J56" t="n">
-        <v>-22.8242</v>
+        <v>-21.3316</v>
       </c>
     </row>
     <row r="57">
@@ -6469,10 +6469,10 @@
         <v>1.43</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6231</v>
+        <v>0.6957</v>
       </c>
       <c r="J57" t="n">
-        <v>21.1854</v>
+        <v>23.6538</v>
       </c>
     </row>
     <row r="58">
@@ -6509,10 +6509,10 @@
         <v>1.35</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5446</v>
+        <v>0.6071</v>
       </c>
       <c r="J58" t="n">
-        <v>18.5164</v>
+        <v>20.6414</v>
       </c>
     </row>
     <row r="59">
@@ -6549,10 +6549,10 @@
         <v>0.82</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2223</v>
+        <v>-0.2351</v>
       </c>
       <c r="J59" t="n">
-        <v>-7.5582</v>
+        <v>-7.9934</v>
       </c>
     </row>
     <row r="60">
@@ -6589,10 +6589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2324</v>
+        <v>-0.2451</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.9016</v>
+        <v>-8.333399999999999</v>
       </c>
     </row>
     <row r="61">
@@ -6629,10 +6629,10 @@
         <v>0.74</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3014</v>
+        <v>-0.3131</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.2476</v>
+        <v>-10.6454</v>
       </c>
     </row>
     <row r="62">
@@ -6669,10 +6669,10 @@
         <v>1.07</v>
       </c>
       <c r="I62" t="n">
-        <v>0.185</v>
+        <v>0.1926</v>
       </c>
       <c r="J62" t="n">
-        <v>7.77</v>
+        <v>8.0892</v>
       </c>
     </row>
     <row r="63">
@@ -6709,10 +6709,10 @@
         <v>1.06</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1631</v>
+        <v>0.1711</v>
       </c>
       <c r="J63" t="n">
-        <v>6.8502</v>
+        <v>7.1862</v>
       </c>
     </row>
     <row r="64">
@@ -6749,10 +6749,10 @@
         <v>1.01</v>
       </c>
       <c r="I64" t="n">
-        <v>0.0385</v>
+        <v>0.0439</v>
       </c>
       <c r="J64" t="n">
-        <v>1.617</v>
+        <v>1.8438</v>
       </c>
     </row>
     <row r="65">
@@ -6789,10 +6789,10 @@
         <v>1</v>
       </c>
       <c r="I65" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0004</v>
       </c>
       <c r="J65" t="n">
-        <v>0.0252</v>
+        <v>0.0168</v>
       </c>
     </row>
     <row r="66">
@@ -6829,10 +6829,10 @@
         <v>0.83</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2079</v>
+        <v>-0.2217</v>
       </c>
       <c r="J66" t="n">
-        <v>-8.7318</v>
+        <v>-9.311400000000001</v>
       </c>
     </row>
     <row r="67">
@@ -6869,10 +6869,10 @@
         <v>1.25</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5655</v>
+        <v>0.6206</v>
       </c>
       <c r="J67" t="n">
-        <v>23.751</v>
+        <v>26.0652</v>
       </c>
     </row>
     <row r="68">
@@ -6909,10 +6909,10 @@
         <v>1.11</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3503</v>
+        <v>0.3574</v>
       </c>
       <c r="J68" t="n">
-        <v>14.7126</v>
+        <v>15.0108</v>
       </c>
     </row>
     <row r="69">
@@ -6949,10 +6949,10 @@
         <v>1.05</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1865</v>
+        <v>0.193</v>
       </c>
       <c r="J69" t="n">
-        <v>7.833</v>
+        <v>8.106</v>
       </c>
     </row>
     <row r="70">
@@ -6989,10 +6989,10 @@
         <v>0.99</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.0643</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="J70" t="n">
-        <v>-2.7006</v>
+        <v>-2.7762</v>
       </c>
     </row>
     <row r="71">
@@ -7029,10 +7029,10 @@
         <v>0.84</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5296</v>
+        <v>-0.503</v>
       </c>
       <c r="J71" t="n">
-        <v>-22.2432</v>
+        <v>-21.126</v>
       </c>
     </row>
     <row r="72">
@@ -7069,10 +7069,10 @@
         <v>1.14</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3644</v>
+        <v>0.3719</v>
       </c>
       <c r="J72" t="n">
-        <v>7.6524</v>
+        <v>7.8099</v>
       </c>
     </row>
     <row r="73">
@@ -7109,10 +7109,10 @@
         <v>0.84</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.1807</v>
+        <v>-0.1983</v>
       </c>
       <c r="J73" t="n">
-        <v>-3.7947</v>
+        <v>-4.1643</v>
       </c>
     </row>
     <row r="74">
@@ -7149,10 +7149,10 @@
         <v>0.83</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.1903</v>
+        <v>-0.2081</v>
       </c>
       <c r="J74" t="n">
-        <v>-3.9963</v>
+        <v>-4.3701</v>
       </c>
     </row>
     <row r="75">
@@ -7189,10 +7189,10 @@
         <v>0.79</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2295</v>
+        <v>-0.2472</v>
       </c>
       <c r="J75" t="n">
-        <v>-4.8195</v>
+        <v>-5.1912</v>
       </c>
     </row>
     <row r="76">
@@ -7229,10 +7229,10 @@
         <v>0.61</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4012</v>
+        <v>-0.4136</v>
       </c>
       <c r="J76" t="n">
-        <v>-8.4252</v>
+        <v>-8.685600000000001</v>
       </c>
     </row>
     <row r="77">
@@ -7269,10 +7269,10 @@
         <v>1.83</v>
       </c>
       <c r="I77" t="n">
-        <v>1.2384</v>
+        <v>1.3559</v>
       </c>
       <c r="J77" t="n">
-        <v>26.0064</v>
+        <v>28.4739</v>
       </c>
     </row>
     <row r="78">
@@ -7309,10 +7309,10 @@
         <v>1.59</v>
       </c>
       <c r="I78" t="n">
-        <v>0.952</v>
+        <v>1.0525</v>
       </c>
       <c r="J78" t="n">
-        <v>19.992</v>
+        <v>22.1025</v>
       </c>
     </row>
     <row r="79">
@@ -7349,10 +7349,10 @@
         <v>1.16</v>
       </c>
       <c r="I79" t="n">
-        <v>0.3936</v>
+        <v>0.4351</v>
       </c>
       <c r="J79" t="n">
-        <v>8.265599999999999</v>
+        <v>9.1371</v>
       </c>
     </row>
     <row r="80">
@@ -7389,10 +7389,10 @@
         <v>1.05</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1223</v>
+        <v>0.1485</v>
       </c>
       <c r="J80" t="n">
-        <v>2.5683</v>
+        <v>3.1185</v>
       </c>
     </row>
     <row r="81">
@@ -7429,10 +7429,10 @@
         <v>1</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.0788</v>
+        <v>-0.0547</v>
       </c>
       <c r="J81" t="n">
-        <v>-1.6548</v>
+        <v>-1.1487</v>
       </c>
     </row>
     <row r="82">
@@ -7469,10 +7469,10 @@
         <v>1.09</v>
       </c>
       <c r="I82" t="n">
-        <v>0.2085</v>
+        <v>0.2089</v>
       </c>
       <c r="J82" t="n">
-        <v>5.6295</v>
+        <v>5.6403</v>
       </c>
     </row>
     <row r="83">
@@ -7509,10 +7509,10 @@
         <v>0.83</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.1919</v>
+        <v>-0.2093</v>
       </c>
       <c r="J83" t="n">
-        <v>-5.1813</v>
+        <v>-5.6511</v>
       </c>
     </row>
     <row r="84">
@@ -7549,10 +7549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2118</v>
+        <v>-0.2291</v>
       </c>
       <c r="J84" t="n">
-        <v>-5.7186</v>
+        <v>-6.1857</v>
       </c>
     </row>
     <row r="85">
@@ -7589,10 +7589,10 @@
         <v>0.79</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2315</v>
+        <v>-0.2487</v>
       </c>
       <c r="J85" t="n">
-        <v>-6.2505</v>
+        <v>-6.7149</v>
       </c>
     </row>
     <row r="86">
@@ -7629,10 +7629,10 @@
         <v>0.77</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2511</v>
+        <v>-0.268</v>
       </c>
       <c r="J86" t="n">
-        <v>-6.7797</v>
+        <v>-7.236</v>
       </c>
     </row>
     <row r="87">
@@ -7669,10 +7669,10 @@
         <v>1.46</v>
       </c>
       <c r="I87" t="n">
-        <v>0.4795</v>
+        <v>0.5468</v>
       </c>
       <c r="J87" t="n">
-        <v>12.9465</v>
+        <v>14.7636</v>
       </c>
     </row>
     <row r="88">
@@ -7709,10 +7709,10 @@
         <v>1.44</v>
       </c>
       <c r="I88" t="n">
-        <v>0.4664</v>
+        <v>0.5315</v>
       </c>
       <c r="J88" t="n">
-        <v>12.5928</v>
+        <v>14.3505</v>
       </c>
     </row>
     <row r="89">
@@ -7749,10 +7749,10 @@
         <v>1.27</v>
       </c>
       <c r="I89" t="n">
-        <v>0.3522</v>
+        <v>0.3801</v>
       </c>
       <c r="J89" t="n">
-        <v>9.509399999999999</v>
+        <v>10.2627</v>
       </c>
     </row>
     <row r="90">
@@ -7789,10 +7789,10 @@
         <v>1.03</v>
       </c>
       <c r="I90" t="n">
-        <v>0.0432</v>
+        <v>0.0577</v>
       </c>
       <c r="J90" t="n">
-        <v>1.1664</v>
+        <v>1.5579</v>
       </c>
     </row>
     <row r="91">
@@ -7829,10 +7829,10 @@
         <v>0.77</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2887</v>
+        <v>-0.2974</v>
       </c>
       <c r="J91" t="n">
-        <v>-7.7949</v>
+        <v>-8.0298</v>
       </c>
     </row>
     <row r="92">
@@ -7869,10 +7869,10 @@
         <v>1.41</v>
       </c>
       <c r="I92" t="n">
-        <v>0.7546</v>
+        <v>0.8343</v>
       </c>
       <c r="J92" t="n">
-        <v>18.865</v>
+        <v>20.8575</v>
       </c>
     </row>
     <row r="93">
@@ -7909,10 +7909,10 @@
         <v>1.4</v>
       </c>
       <c r="I93" t="n">
-        <v>0.7415</v>
+        <v>0.82</v>
       </c>
       <c r="J93" t="n">
-        <v>18.5375</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="94">
@@ -7949,10 +7949,10 @@
         <v>1.3</v>
       </c>
       <c r="I94" t="n">
-        <v>0.6074000000000001</v>
+        <v>0.6734</v>
       </c>
       <c r="J94" t="n">
-        <v>15.185</v>
+        <v>16.835</v>
       </c>
     </row>
     <row r="95">
@@ -7989,10 +7989,10 @@
         <v>0.95</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2464</v>
+        <v>-0.2344</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.16</v>
+        <v>-5.86</v>
       </c>
     </row>
     <row r="96">
@@ -8029,10 +8029,10 @@
         <v>0.86</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.512</v>
+        <v>-0.4799</v>
       </c>
       <c r="J96" t="n">
-        <v>-12.8</v>
+        <v>-11.9975</v>
       </c>
     </row>
     <row r="97">
@@ -8069,10 +8069,10 @@
         <v>1.12</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3263</v>
+        <v>0.3217</v>
       </c>
       <c r="J97" t="n">
-        <v>8.157500000000001</v>
+        <v>8.0425</v>
       </c>
     </row>
     <row r="98">
@@ -8109,10 +8109,10 @@
         <v>0.95</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.06370000000000001</v>
+        <v>-0.0767</v>
       </c>
       <c r="J98" t="n">
-        <v>-1.5925</v>
+        <v>-1.9175</v>
       </c>
     </row>
     <row r="99">
@@ -8149,10 +8149,10 @@
         <v>0.91</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1113</v>
+        <v>-0.1265</v>
       </c>
       <c r="J99" t="n">
-        <v>-2.7825</v>
+        <v>-3.1625</v>
       </c>
     </row>
     <row r="100">
@@ -8189,10 +8189,10 @@
         <v>0.84</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1839</v>
+        <v>-0.2007</v>
       </c>
       <c r="J100" t="n">
-        <v>-4.5975</v>
+        <v>-5.0175</v>
       </c>
     </row>
     <row r="101">
@@ -8229,10 +8229,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4519</v>
+        <v>-0.4611</v>
       </c>
       <c r="J101" t="n">
-        <v>-11.2975</v>
+        <v>-11.5275</v>
       </c>
     </row>
     <row r="102">
@@ -8269,10 +8269,10 @@
         <v>1.45</v>
       </c>
       <c r="I102" t="n">
-        <v>0.8318</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="J102" t="n">
-        <v>23.2904</v>
+        <v>25.5584</v>
       </c>
     </row>
     <row r="103">
@@ -8309,10 +8309,10 @@
         <v>1.1</v>
       </c>
       <c r="I103" t="n">
-        <v>0.3224</v>
+        <v>0.325</v>
       </c>
       <c r="J103" t="n">
-        <v>9.027200000000001</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="104">
@@ -8349,10 +8349,10 @@
         <v>1.05</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1784</v>
+        <v>0.1875</v>
       </c>
       <c r="J104" t="n">
-        <v>4.9952</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="105">
@@ -8389,10 +8389,10 @@
         <v>1.01</v>
       </c>
       <c r="I105" t="n">
-        <v>0.0338</v>
+        <v>0.0454</v>
       </c>
       <c r="J105" t="n">
-        <v>0.9464</v>
+        <v>1.2712</v>
       </c>
     </row>
     <row r="106">
@@ -8429,10 +8429,10 @@
         <v>0.85</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.515</v>
+        <v>-0.4875</v>
       </c>
       <c r="J106" t="n">
-        <v>-14.42</v>
+        <v>-13.65</v>
       </c>
     </row>
     <row r="107">
@@ -8469,10 +8469,10 @@
         <v>1.16</v>
       </c>
       <c r="I107" t="n">
-        <v>0.3549</v>
+        <v>0.3681</v>
       </c>
       <c r="J107" t="n">
-        <v>9.937200000000001</v>
+        <v>10.3068</v>
       </c>
     </row>
     <row r="108">
@@ -8509,10 +8509,10 @@
         <v>1.04</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1197</v>
+        <v>0.1272</v>
       </c>
       <c r="J108" t="n">
-        <v>3.3516</v>
+        <v>3.5616</v>
       </c>
     </row>
     <row r="109">
@@ -8549,10 +8549,10 @@
         <v>1.02</v>
       </c>
       <c r="I109" t="n">
-        <v>0.0692</v>
+        <v>0.0756</v>
       </c>
       <c r="J109" t="n">
-        <v>1.9376</v>
+        <v>2.1168</v>
       </c>
     </row>
     <row r="110">
@@ -8589,10 +8589,10 @@
         <v>0.98</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.0347</v>
+        <v>-0.0418</v>
       </c>
       <c r="J110" t="n">
-        <v>-0.9716</v>
+        <v>-1.1704</v>
       </c>
     </row>
     <row r="111">
@@ -8629,10 +8629,10 @@
         <v>0.71</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3247</v>
+        <v>-0.3368</v>
       </c>
       <c r="J111" t="n">
-        <v>-9.0916</v>
+        <v>-9.430400000000001</v>
       </c>
     </row>
     <row r="112">
@@ -8669,10 +8669,10 @@
         <v>0.84</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.1717</v>
+        <v>-0.1915</v>
       </c>
       <c r="J112" t="n">
-        <v>-3.9491</v>
+        <v>-4.4045</v>
       </c>
     </row>
     <row r="113">
@@ -8709,10 +8709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.2026</v>
+        <v>-0.2221</v>
       </c>
       <c r="J113" t="n">
-        <v>-4.6598</v>
+        <v>-5.1083</v>
       </c>
     </row>
     <row r="114">
@@ -8749,10 +8749,10 @@
         <v>0.74</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2686</v>
+        <v>-0.2875</v>
       </c>
       <c r="J114" t="n">
-        <v>-6.1778</v>
+        <v>-6.6125</v>
       </c>
     </row>
     <row r="115">
@@ -8789,10 +8789,10 @@
         <v>0.74</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2686</v>
+        <v>-0.2875</v>
       </c>
       <c r="J115" t="n">
-        <v>-6.1778</v>
+        <v>-6.6125</v>
       </c>
     </row>
     <row r="116">
@@ -8829,10 +8829,10 @@
         <v>0.72</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.2874</v>
+        <v>-0.3059</v>
       </c>
       <c r="J116" t="n">
-        <v>-6.6102</v>
+        <v>-7.0357</v>
       </c>
     </row>
     <row r="117">
@@ -8869,10 +8869,10 @@
         <v>1.65</v>
       </c>
       <c r="I117" t="n">
-        <v>1.0255</v>
+        <v>1.1307</v>
       </c>
       <c r="J117" t="n">
-        <v>23.5865</v>
+        <v>26.0061</v>
       </c>
     </row>
     <row r="118">
@@ -8909,10 +8909,10 @@
         <v>1.49</v>
       </c>
       <c r="I118" t="n">
-        <v>0.8299</v>
+        <v>0.9212</v>
       </c>
       <c r="J118" t="n">
-        <v>19.0877</v>
+        <v>21.1876</v>
       </c>
     </row>
     <row r="119">
@@ -8949,10 +8949,10 @@
         <v>1.33</v>
       </c>
       <c r="I119" t="n">
-        <v>0.6289</v>
+        <v>0.7015</v>
       </c>
       <c r="J119" t="n">
-        <v>14.4647</v>
+        <v>16.1345</v>
       </c>
     </row>
     <row r="120">
@@ -8989,10 +8989,10 @@
         <v>1.14</v>
       </c>
       <c r="I120" t="n">
-        <v>0.3633</v>
+        <v>0.3909</v>
       </c>
       <c r="J120" t="n">
-        <v>8.3559</v>
+        <v>8.9907</v>
       </c>
     </row>
     <row r="121">
@@ -9029,10 +9029,10 @@
         <v>1</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.0779</v>
+        <v>-0.054</v>
       </c>
       <c r="J121" t="n">
-        <v>-1.7917</v>
+        <v>-1.242</v>
       </c>
     </row>
     <row r="122">
@@ -9069,10 +9069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.065</v>
+        <v>-0.0813</v>
       </c>
       <c r="J122" t="n">
-        <v>-1.43</v>
+        <v>-1.7886</v>
       </c>
     </row>
     <row r="123">
@@ -9109,10 +9109,10 @@
         <v>0.93</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.0775</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="J123" t="n">
-        <v>-1.705</v>
+        <v>-2.0724</v>
       </c>
     </row>
     <row r="124">
@@ -9149,10 +9149,10 @@
         <v>0.83</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.1877</v>
+        <v>-0.2061</v>
       </c>
       <c r="J124" t="n">
-        <v>-4.1294</v>
+        <v>-4.5342</v>
       </c>
     </row>
     <row r="125">
@@ -9189,10 +9189,10 @@
         <v>0.78</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2354</v>
+        <v>-0.2538</v>
       </c>
       <c r="J125" t="n">
-        <v>-5.1788</v>
+        <v>-5.5836</v>
       </c>
     </row>
     <row r="126">
@@ -9229,10 +9229,10 @@
         <v>0.57</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4341</v>
+        <v>-0.4456</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.5502</v>
+        <v>-9.8032</v>
       </c>
     </row>
     <row r="127">
@@ -9269,10 +9269,10 @@
         <v>1.57</v>
       </c>
       <c r="I127" t="n">
-        <v>0.9358</v>
+        <v>1.0337</v>
       </c>
       <c r="J127" t="n">
-        <v>20.5876</v>
+        <v>22.7414</v>
       </c>
     </row>
     <row r="128">
@@ -9309,10 +9309,10 @@
         <v>1.36</v>
       </c>
       <c r="I128" t="n">
-        <v>0.6712</v>
+        <v>0.7472</v>
       </c>
       <c r="J128" t="n">
-        <v>14.7664</v>
+        <v>16.4384</v>
       </c>
     </row>
     <row r="129">
@@ -9349,10 +9349,10 @@
         <v>1.31</v>
       </c>
       <c r="I129" t="n">
-        <v>0.6065</v>
+        <v>0.6758</v>
       </c>
       <c r="J129" t="n">
-        <v>13.343</v>
+        <v>14.8676</v>
       </c>
     </row>
     <row r="130">
@@ -9389,10 +9389,10 @@
         <v>1.25</v>
       </c>
       <c r="I130" t="n">
-        <v>0.5281</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="J130" t="n">
-        <v>11.6182</v>
+        <v>12.9404</v>
       </c>
     </row>
     <row r="131">
@@ -9429,10 +9429,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3034</v>
+        <v>-0.2823</v>
       </c>
       <c r="J131" t="n">
-        <v>-6.6748</v>
+        <v>-6.2106</v>
       </c>
     </row>
     <row r="132">
@@ -9469,10 +9469,10 @@
         <v>0.63</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.3069</v>
+        <v>-0.337</v>
       </c>
       <c r="J132" t="n">
-        <v>-5.8311</v>
+        <v>-6.403</v>
       </c>
     </row>
     <row r="133">
@@ -9509,10 +9509,10 @@
         <v>0.59</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.3502</v>
+        <v>-0.3773</v>
       </c>
       <c r="J133" t="n">
-        <v>-6.6538</v>
+        <v>-7.1687</v>
       </c>
     </row>
     <row r="134">
@@ -9549,10 +9549,10 @@
         <v>0.55</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.3919</v>
+        <v>-0.416</v>
       </c>
       <c r="J134" t="n">
-        <v>-7.4461</v>
+        <v>-7.904</v>
       </c>
     </row>
     <row r="135">
@@ -9589,10 +9589,10 @@
         <v>0.43</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.5037</v>
+        <v>-0.5203</v>
       </c>
       <c r="J135" t="n">
-        <v>-9.5703</v>
+        <v>-9.8857</v>
       </c>
     </row>
     <row r="136">
@@ -9629,10 +9629,10 @@
         <v>0.16</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.7771</v>
+        <v>-0.7683</v>
       </c>
       <c r="J136" t="n">
-        <v>-14.7649</v>
+        <v>-14.5977</v>
       </c>
     </row>
     <row r="137">
@@ -9669,10 +9669,10 @@
         <v>1.93</v>
       </c>
       <c r="I137" t="n">
-        <v>1.3015</v>
+        <v>1.4307</v>
       </c>
       <c r="J137" t="n">
-        <v>24.7285</v>
+        <v>27.1833</v>
       </c>
     </row>
     <row r="138">
@@ -9709,10 +9709,10 @@
         <v>1.56</v>
       </c>
       <c r="I138" t="n">
-        <v>0.8852</v>
+        <v>0.9871</v>
       </c>
       <c r="J138" t="n">
-        <v>16.8188</v>
+        <v>18.7549</v>
       </c>
     </row>
     <row r="139">
@@ -9749,10 +9749,10 @@
         <v>1.52</v>
       </c>
       <c r="I139" t="n">
-        <v>0.84</v>
+        <v>0.9379</v>
       </c>
       <c r="J139" t="n">
-        <v>15.96</v>
+        <v>17.8201</v>
       </c>
     </row>
     <row r="140">
@@ -9789,10 +9789,10 @@
         <v>1.46</v>
       </c>
       <c r="I140" t="n">
-        <v>0.7689</v>
+        <v>0.8605</v>
       </c>
       <c r="J140" t="n">
-        <v>14.6091</v>
+        <v>16.3495</v>
       </c>
     </row>
     <row r="141">
@@ -9829,10 +9829,10 @@
         <v>1.28</v>
       </c>
       <c r="I141" t="n">
-        <v>0.5381</v>
+        <v>0.6069</v>
       </c>
       <c r="J141" t="n">
-        <v>10.2239</v>
+        <v>11.5311</v>
       </c>
     </row>
     <row r="142">
@@ -9869,10 +9869,10 @@
         <v>1.57</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5594</v>
+        <v>0.6384</v>
       </c>
       <c r="J142" t="n">
-        <v>13.985</v>
+        <v>15.96</v>
       </c>
     </row>
     <row r="143">
@@ -9909,10 +9909,10 @@
         <v>1.24</v>
       </c>
       <c r="I143" t="n">
-        <v>0.3336</v>
+        <v>0.3521</v>
       </c>
       <c r="J143" t="n">
-        <v>8.34</v>
+        <v>8.8025</v>
       </c>
     </row>
     <row r="144">
@@ -9949,10 +9949,10 @@
         <v>1.16</v>
       </c>
       <c r="I144" t="n">
-        <v>0.2383</v>
+        <v>0.2547</v>
       </c>
       <c r="J144" t="n">
-        <v>5.9575</v>
+        <v>6.3675</v>
       </c>
     </row>
     <row r="145">
@@ -9989,10 +9989,10 @@
         <v>1.11</v>
       </c>
       <c r="I145" t="n">
-        <v>0.1735</v>
+        <v>0.1898</v>
       </c>
       <c r="J145" t="n">
-        <v>4.3375</v>
+        <v>4.745</v>
       </c>
     </row>
     <row r="146">
@@ -10029,10 +10029,10 @@
         <v>0.58</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4595</v>
+        <v>-0.4641</v>
       </c>
       <c r="J146" t="n">
-        <v>-11.4875</v>
+        <v>-11.6025</v>
       </c>
     </row>
     <row r="147">
@@ -10069,10 +10069,10 @@
         <v>1.56</v>
       </c>
       <c r="I147" t="n">
-        <v>0.6158</v>
+        <v>0.6892</v>
       </c>
       <c r="J147" t="n">
-        <v>15.395</v>
+        <v>17.23</v>
       </c>
     </row>
     <row r="148">
@@ -10109,10 +10109,10 @@
         <v>1</v>
       </c>
       <c r="I148" t="n">
-        <v>0.0019</v>
+        <v>0.0014</v>
       </c>
       <c r="J148" t="n">
-        <v>0.0475</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="149">
@@ -10149,10 +10149,10 @@
         <v>0.91</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1209</v>
+        <v>-0.1337</v>
       </c>
       <c r="J149" t="n">
-        <v>-3.0225</v>
+        <v>-3.3425</v>
       </c>
     </row>
     <row r="150">
@@ -10189,10 +10189,10 @@
         <v>0.83</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2063</v>
+        <v>-0.2204</v>
       </c>
       <c r="J150" t="n">
-        <v>-5.1575</v>
+        <v>-5.51</v>
       </c>
     </row>
     <row r="151">
@@ -10229,10 +10229,10 @@
         <v>0.6</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4271</v>
+        <v>-0.4356</v>
       </c>
       <c r="J151" t="n">
-        <v>-10.6775</v>
+        <v>-10.89</v>
       </c>
     </row>
     <row r="152">
@@ -10269,10 +10269,10 @@
         <v>1.01</v>
       </c>
       <c r="I152" t="n">
-        <v>0.1093</v>
+        <v>0.0955</v>
       </c>
       <c r="J152" t="n">
-        <v>2.5139</v>
+        <v>2.1965</v>
       </c>
     </row>
     <row r="153">
@@ -10309,10 +10309,10 @@
         <v>0.76</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.2503</v>
+        <v>-0.2695</v>
       </c>
       <c r="J153" t="n">
-        <v>-5.7569</v>
+        <v>-6.1985</v>
       </c>
     </row>
     <row r="154">
@@ -10349,10 +10349,10 @@
         <v>0.72</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2879</v>
+        <v>-0.3063</v>
       </c>
       <c r="J154" t="n">
-        <v>-6.6217</v>
+        <v>-7.0449</v>
       </c>
     </row>
     <row r="155">
@@ -10389,10 +10389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3163</v>
+        <v>-0.3338</v>
       </c>
       <c r="J155" t="n">
-        <v>-7.2749</v>
+        <v>-7.6774</v>
       </c>
     </row>
     <row r="156">
@@ -10429,10 +10429,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3163</v>
+        <v>-0.3338</v>
       </c>
       <c r="J156" t="n">
-        <v>-7.2749</v>
+        <v>-7.6774</v>
       </c>
     </row>
     <row r="157">
@@ -10469,10 +10469,10 @@
         <v>1.66</v>
       </c>
       <c r="I157" t="n">
-        <v>1.0402</v>
+        <v>1.1459</v>
       </c>
       <c r="J157" t="n">
-        <v>23.9246</v>
+        <v>26.3557</v>
       </c>
     </row>
     <row r="158">
@@ -10509,10 +10509,10 @@
         <v>1.36</v>
       </c>
       <c r="I158" t="n">
-        <v>0.6681</v>
+        <v>0.7446</v>
       </c>
       <c r="J158" t="n">
-        <v>15.3663</v>
+        <v>17.1258</v>
       </c>
     </row>
     <row r="159">
@@ -10549,10 +10549,10 @@
         <v>1.34</v>
       </c>
       <c r="I159" t="n">
-        <v>0.6425999999999999</v>
+        <v>0.7165</v>
       </c>
       <c r="J159" t="n">
-        <v>14.7798</v>
+        <v>16.4795</v>
       </c>
     </row>
     <row r="160">
@@ -10589,10 +10589,10 @@
         <v>1.12</v>
       </c>
       <c r="I160" t="n">
-        <v>0.3294</v>
+        <v>0.3436</v>
       </c>
       <c r="J160" t="n">
-        <v>7.5762</v>
+        <v>7.9028</v>
       </c>
     </row>
     <row r="161">
@@ -10629,10 +10629,10 @@
         <v>1.07</v>
       </c>
       <c r="I161" t="n">
-        <v>0.1887</v>
+        <v>0.2104</v>
       </c>
       <c r="J161" t="n">
-        <v>4.3401</v>
+        <v>4.8392</v>
       </c>
     </row>
     <row r="162">
@@ -10669,10 +10669,10 @@
         <v>1.9</v>
       </c>
       <c r="I162" t="n">
-        <v>1.2779</v>
+        <v>1.4042</v>
       </c>
       <c r="J162" t="n">
-        <v>23.0022</v>
+        <v>25.2756</v>
       </c>
     </row>
     <row r="163">
@@ -10709,10 +10709,10 @@
         <v>1.61</v>
       </c>
       <c r="I163" t="n">
-        <v>0.9475</v>
+        <v>1.0533</v>
       </c>
       <c r="J163" t="n">
-        <v>17.055</v>
+        <v>18.9594</v>
       </c>
     </row>
     <row r="164">
@@ -10749,10 +10749,10 @@
         <v>1.52</v>
       </c>
       <c r="I164" t="n">
-        <v>0.8431999999999999</v>
+        <v>0.9406</v>
       </c>
       <c r="J164" t="n">
-        <v>15.1776</v>
+        <v>16.9308</v>
       </c>
     </row>
     <row r="165">
@@ -10789,10 +10789,10 @@
         <v>1.49</v>
       </c>
       <c r="I165" t="n">
-        <v>0.8089</v>
+        <v>0.9032</v>
       </c>
       <c r="J165" t="n">
-        <v>14.5602</v>
+        <v>16.2576</v>
       </c>
     </row>
     <row r="166">
@@ -10829,10 +10829,10 @@
         <v>0.98</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2107</v>
+        <v>-0.1812</v>
       </c>
       <c r="J166" t="n">
-        <v>-3.7926</v>
+        <v>-3.2616</v>
       </c>
     </row>
     <row r="167">
@@ -10869,10 +10869,10 @@
         <v>0.65</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.3074</v>
+        <v>-0.3341</v>
       </c>
       <c r="J167" t="n">
-        <v>-5.5332</v>
+        <v>-6.0138</v>
       </c>
     </row>
     <row r="168">
@@ -10909,10 +10909,10 @@
         <v>0.59</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.3685</v>
+        <v>-0.3916</v>
       </c>
       <c r="J168" t="n">
-        <v>-6.633</v>
+        <v>-7.0488</v>
       </c>
     </row>
     <row r="169">
@@ -10949,10 +10949,10 @@
         <v>0.59</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.3685</v>
+        <v>-0.3916</v>
       </c>
       <c r="J169" t="n">
-        <v>-6.633</v>
+        <v>-7.0488</v>
       </c>
     </row>
     <row r="170">
@@ -10989,10 +10989,10 @@
         <v>0.41</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.5354</v>
+        <v>-0.5477</v>
       </c>
       <c r="J170" t="n">
-        <v>-9.6372</v>
+        <v>-9.858599999999999</v>
       </c>
     </row>
     <row r="171">
@@ -11029,10 +11029,10 @@
         <v>0.39</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5548</v>
+        <v>-0.5655</v>
       </c>
       <c r="J171" t="n">
-        <v>-9.9864</v>
+        <v>-10.179</v>
       </c>
     </row>
     <row r="172">
@@ -11069,10 +11069,10 @@
         <v>1.44</v>
       </c>
       <c r="I172" t="n">
-        <v>0.8196</v>
+        <v>0.8995</v>
       </c>
       <c r="J172" t="n">
-        <v>22.1292</v>
+        <v>24.2865</v>
       </c>
     </row>
     <row r="173">
@@ -11109,10 +11109,10 @@
         <v>1.21</v>
       </c>
       <c r="I173" t="n">
-        <v>0.4978</v>
+        <v>0.5475</v>
       </c>
       <c r="J173" t="n">
-        <v>13.4406</v>
+        <v>14.7825</v>
       </c>
     </row>
     <row r="174">
@@ -11149,10 +11149,10 @@
         <v>1.2</v>
       </c>
       <c r="I174" t="n">
-        <v>0.483</v>
+        <v>0.531</v>
       </c>
       <c r="J174" t="n">
-        <v>13.041</v>
+        <v>14.337</v>
       </c>
     </row>
     <row r="175">
@@ -11189,10 +11189,10 @@
         <v>1.06</v>
       </c>
       <c r="I175" t="n">
-        <v>0.2106</v>
+        <v>0.2179</v>
       </c>
       <c r="J175" t="n">
-        <v>5.6862</v>
+        <v>5.8833</v>
       </c>
     </row>
     <row r="176">
@@ -11229,10 +11229,10 @@
         <v>0.53</v>
       </c>
       <c r="I176" t="n">
-        <v>-1.3002</v>
+        <v>-1.1722</v>
       </c>
       <c r="J176" t="n">
-        <v>-35.1054</v>
+        <v>-31.6494</v>
       </c>
     </row>
     <row r="177">
@@ -11269,10 +11269,10 @@
         <v>1.29</v>
       </c>
       <c r="I177" t="n">
-        <v>0.4947</v>
+        <v>0.5481</v>
       </c>
       <c r="J177" t="n">
-        <v>13.3569</v>
+        <v>14.7987</v>
       </c>
     </row>
     <row r="178">
@@ -11309,10 +11309,10 @@
         <v>1.12</v>
       </c>
       <c r="I178" t="n">
-        <v>0.2915</v>
+        <v>0.2945</v>
       </c>
       <c r="J178" t="n">
-        <v>7.8705</v>
+        <v>7.9515</v>
       </c>
     </row>
     <row r="179">
@@ -11349,10 +11349,10 @@
         <v>1.04</v>
       </c>
       <c r="I179" t="n">
-        <v>0.1197</v>
+        <v>0.1272</v>
       </c>
       <c r="J179" t="n">
-        <v>3.2319</v>
+        <v>3.4344</v>
       </c>
     </row>
     <row r="180">
@@ -11389,10 +11389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.0863</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="J180" t="n">
-        <v>-2.3301</v>
+        <v>-2.6352</v>
       </c>
     </row>
     <row r="181">
@@ -11429,10 +11429,10 @@
         <v>0.52</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4998</v>
+        <v>-0.5047</v>
       </c>
       <c r="J181" t="n">
-        <v>-13.4946</v>
+        <v>-13.6269</v>
       </c>
     </row>
     <row r="182">
@@ -11469,10 +11469,10 @@
         <v>1.39</v>
       </c>
       <c r="I182" t="n">
-        <v>0.5127</v>
+        <v>0.5191</v>
       </c>
       <c r="J182" t="n">
-        <v>13.8429</v>
+        <v>14.0157</v>
       </c>
     </row>
     <row r="183">
@@ -11509,10 +11509,10 @@
         <v>1.23</v>
       </c>
       <c r="I183" t="n">
-        <v>0.3242</v>
+        <v>0.3392</v>
       </c>
       <c r="J183" t="n">
-        <v>8.753399999999999</v>
+        <v>9.1584</v>
       </c>
     </row>
     <row r="184">
@@ -11549,10 +11549,10 @@
         <v>1.16</v>
       </c>
       <c r="I184" t="n">
-        <v>0.2373</v>
+        <v>0.254</v>
       </c>
       <c r="J184" t="n">
-        <v>6.4071</v>
+        <v>6.858</v>
       </c>
     </row>
     <row r="185">
@@ -11589,10 +11589,10 @@
         <v>1.08</v>
       </c>
       <c r="I185" t="n">
-        <v>0.13</v>
+        <v>0.146</v>
       </c>
       <c r="J185" t="n">
-        <v>3.51</v>
+        <v>3.942</v>
       </c>
     </row>
     <row r="186">
@@ -11629,10 +11629,10 @@
         <v>0.85</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2034</v>
+        <v>-0.2135</v>
       </c>
       <c r="J186" t="n">
-        <v>-5.4918</v>
+        <v>-5.7645</v>
       </c>
     </row>
     <row r="187">
@@ -11669,10 +11669,10 @@
         <v>1.16</v>
       </c>
       <c r="I187" t="n">
-        <v>0.2965</v>
+        <v>0.2986</v>
       </c>
       <c r="J187" t="n">
-        <v>8.0055</v>
+        <v>8.062200000000001</v>
       </c>
     </row>
     <row r="188">
@@ -11709,10 +11709,10 @@
         <v>1.08</v>
       </c>
       <c r="I188" t="n">
-        <v>0.1715</v>
+        <v>0.1773</v>
       </c>
       <c r="J188" t="n">
-        <v>4.6305</v>
+        <v>4.7871</v>
       </c>
     </row>
     <row r="189">
@@ -11749,10 +11749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.0822</v>
+        <v>-0.0946</v>
       </c>
       <c r="J189" t="n">
-        <v>-2.2194</v>
+        <v>-2.5542</v>
       </c>
     </row>
     <row r="190">
@@ -11789,10 +11789,10 @@
         <v>0.79</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2406</v>
+        <v>-0.2557</v>
       </c>
       <c r="J190" t="n">
-        <v>-6.4962</v>
+        <v>-6.9039</v>
       </c>
     </row>
     <row r="191">
@@ -11829,10 +11829,10 @@
         <v>0.68</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3469</v>
+        <v>-0.3595</v>
       </c>
       <c r="J191" t="n">
-        <v>-9.366300000000001</v>
+        <v>-9.7065</v>
       </c>
     </row>
     <row r="192">
@@ -11869,10 +11869,10 @@
         <v>1.25</v>
       </c>
       <c r="I192" t="n">
-        <v>0.5172</v>
+        <v>0.5083</v>
       </c>
       <c r="J192" t="n">
-        <v>15.516</v>
+        <v>15.249</v>
       </c>
     </row>
     <row r="193">
@@ -11909,10 +11909,10 @@
         <v>1.07</v>
       </c>
       <c r="I193" t="n">
-        <v>0.1765</v>
+        <v>0.1865</v>
       </c>
       <c r="J193" t="n">
-        <v>5.295</v>
+        <v>5.595</v>
       </c>
     </row>
     <row r="194">
@@ -11949,10 +11949,10 @@
         <v>0.98</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.0393</v>
+        <v>-0.0452</v>
       </c>
       <c r="J194" t="n">
-        <v>-1.179</v>
+        <v>-1.356</v>
       </c>
     </row>
     <row r="195">
@@ -11989,10 +11989,10 @@
         <v>0.95</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.0796</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="J195" t="n">
-        <v>-2.388</v>
+        <v>-2.667</v>
       </c>
     </row>
     <row r="196">
@@ -12029,10 +12029,10 @@
         <v>0.93</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.1039</v>
+        <v>-0.1145</v>
       </c>
       <c r="J196" t="n">
-        <v>-3.117</v>
+        <v>-3.435</v>
       </c>
     </row>
     <row r="197">
@@ -12069,10 +12069,10 @@
         <v>1.16</v>
       </c>
       <c r="I197" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.4926</v>
       </c>
       <c r="J197" t="n">
-        <v>15.438</v>
+        <v>14.778</v>
       </c>
     </row>
     <row r="198">
@@ -12109,10 +12109,10 @@
         <v>1.04</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1638</v>
+        <v>0.1684</v>
       </c>
       <c r="J198" t="n">
-        <v>4.914</v>
+        <v>5.052</v>
       </c>
     </row>
     <row r="199">
@@ -12149,10 +12149,10 @@
         <v>0.97</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1304</v>
+        <v>-0.1357</v>
       </c>
       <c r="J199" t="n">
-        <v>-3.912</v>
+        <v>-4.071</v>
       </c>
     </row>
     <row r="200">
@@ -12189,10 +12189,10 @@
         <v>0.93</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2605</v>
+        <v>-0.2599</v>
       </c>
       <c r="J200" t="n">
-        <v>-7.815</v>
+        <v>-7.797</v>
       </c>
     </row>
     <row r="201">
@@ -12229,10 +12229,10 @@
         <v>0.91</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3203</v>
+        <v>-0.3155</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.609</v>
+        <v>-9.465</v>
       </c>
     </row>
     <row r="202">
@@ -12269,10 +12269,10 @@
         <v>1.15</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3796</v>
+        <v>0.3715</v>
       </c>
       <c r="J202" t="n">
-        <v>11.388</v>
+        <v>11.145</v>
       </c>
     </row>
     <row r="203">
@@ -12309,10 +12309,10 @@
         <v>0.89</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.1347</v>
+        <v>-0.1501</v>
       </c>
       <c r="J203" t="n">
-        <v>-4.041</v>
+        <v>-4.503</v>
       </c>
     </row>
     <row r="204">
@@ -12349,10 +12349,10 @@
         <v>0.85</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1763</v>
+        <v>-0.1925</v>
       </c>
       <c r="J204" t="n">
-        <v>-5.289</v>
+        <v>-5.775</v>
       </c>
     </row>
     <row r="205">
@@ -12389,10 +12389,10 @@
         <v>0.82</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2068</v>
+        <v>-0.2231</v>
       </c>
       <c r="J205" t="n">
-        <v>-6.204</v>
+        <v>-6.693</v>
       </c>
     </row>
     <row r="206">
@@ -12429,10 +12429,10 @@
         <v>0.79</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.2368</v>
+        <v>-0.2528</v>
       </c>
       <c r="J206" t="n">
-        <v>-7.104</v>
+        <v>-7.584</v>
       </c>
     </row>
     <row r="207">
@@ -12469,10 +12469,10 @@
         <v>1.55</v>
       </c>
       <c r="I207" t="n">
-        <v>1.2036</v>
+        <v>1.171</v>
       </c>
       <c r="J207" t="n">
-        <v>36.108</v>
+        <v>35.13</v>
       </c>
     </row>
     <row r="208">
@@ -12509,10 +12509,10 @@
         <v>1.19</v>
       </c>
       <c r="I208" t="n">
-        <v>0.5357</v>
+        <v>0.5233</v>
       </c>
       <c r="J208" t="n">
-        <v>16.071</v>
+        <v>15.699</v>
       </c>
     </row>
     <row r="209">
@@ -12549,10 +12549,10 @@
         <v>1.18</v>
       </c>
       <c r="I209" t="n">
-        <v>0.5114</v>
+        <v>0.5013</v>
       </c>
       <c r="J209" t="n">
-        <v>15.342</v>
+        <v>15.039</v>
       </c>
     </row>
     <row r="210">
@@ -12589,10 +12589,10 @@
         <v>1.06</v>
       </c>
       <c r="I210" t="n">
-        <v>0.1827</v>
+        <v>0.1987</v>
       </c>
       <c r="J210" t="n">
-        <v>5.481</v>
+        <v>5.961</v>
       </c>
     </row>
     <row r="211">
@@ -12629,10 +12629,10 @@
         <v>1.05</v>
       </c>
       <c r="I211" t="n">
-        <v>0.1508</v>
+        <v>0.1685</v>
       </c>
       <c r="J211" t="n">
-        <v>4.524</v>
+        <v>5.055</v>
       </c>
     </row>
     <row r="212">
@@ -12669,10 +12669,10 @@
         <v>1.29</v>
       </c>
       <c r="I212" t="n">
-        <v>0.4043</v>
+        <v>0.4148</v>
       </c>
       <c r="J212" t="n">
-        <v>14.5548</v>
+        <v>14.9328</v>
       </c>
     </row>
     <row r="213">
@@ -12709,10 +12709,10 @@
         <v>1.19</v>
       </c>
       <c r="I213" t="n">
-        <v>0.2809</v>
+        <v>0.2956</v>
       </c>
       <c r="J213" t="n">
-        <v>10.1124</v>
+        <v>10.6416</v>
       </c>
     </row>
     <row r="214">
@@ -12749,10 +12749,10 @@
         <v>1.16</v>
       </c>
       <c r="I214" t="n">
-        <v>0.2424</v>
+        <v>0.2578</v>
       </c>
       <c r="J214" t="n">
-        <v>8.7264</v>
+        <v>9.280799999999999</v>
       </c>
     </row>
     <row r="215">
@@ -12789,10 +12789,10 @@
         <v>0.98</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.0455</v>
+        <v>-0.05</v>
       </c>
       <c r="J215" t="n">
-        <v>-1.638</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="216">
@@ -12829,10 +12829,10 @@
         <v>0.87</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.1777</v>
+        <v>-0.1886</v>
       </c>
       <c r="J216" t="n">
-        <v>-6.3972</v>
+        <v>-6.7896</v>
       </c>
     </row>
     <row r="217">
@@ -12869,10 +12869,10 @@
         <v>1.2</v>
       </c>
       <c r="I217" t="n">
-        <v>0.3377</v>
+        <v>0.3412</v>
       </c>
       <c r="J217" t="n">
-        <v>12.1572</v>
+        <v>12.2832</v>
       </c>
     </row>
     <row r="218">
@@ -12909,10 +12909,10 @@
         <v>1.07</v>
       </c>
       <c r="I218" t="n">
-        <v>0.1419</v>
+        <v>0.1511</v>
       </c>
       <c r="J218" t="n">
-        <v>5.1084</v>
+        <v>5.4396</v>
       </c>
     </row>
     <row r="219">
@@ -12949,10 +12949,10 @@
         <v>0.97</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.0493</v>
+        <v>-0.0577</v>
       </c>
       <c r="J219" t="n">
-        <v>-1.7748</v>
+        <v>-2.0772</v>
       </c>
     </row>
     <row r="220">
@@ -12989,10 +12989,10 @@
         <v>0.86</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1765</v>
+        <v>-0.1902</v>
       </c>
       <c r="J220" t="n">
-        <v>-6.354</v>
+        <v>-6.8472</v>
       </c>
     </row>
     <row r="221">
@@ -13029,10 +13029,10 @@
         <v>0.86</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.1765</v>
+        <v>-0.1902</v>
       </c>
       <c r="J221" t="n">
-        <v>-6.354</v>
+        <v>-6.8472</v>
       </c>
     </row>
     <row r="222">
@@ -13069,10 +13069,10 @@
         <v>1.28</v>
       </c>
       <c r="I222" t="n">
-        <v>0.598</v>
+        <v>0.5772</v>
       </c>
       <c r="J222" t="n">
-        <v>16.744</v>
+        <v>16.1616</v>
       </c>
     </row>
     <row r="223">
@@ -13109,10 +13109,10 @@
         <v>1.06</v>
       </c>
       <c r="I223" t="n">
-        <v>0.1713</v>
+        <v>0.177</v>
       </c>
       <c r="J223" t="n">
-        <v>4.7964</v>
+        <v>4.956</v>
       </c>
     </row>
     <row r="224">
@@ -13149,10 +13149,10 @@
         <v>0.93</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.096</v>
+        <v>-0.1084</v>
       </c>
       <c r="J224" t="n">
-        <v>-2.688</v>
+        <v>-3.0352</v>
       </c>
     </row>
     <row r="225">
@@ -13189,10 +13189,10 @@
         <v>0.86</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1728</v>
+        <v>-0.1873</v>
       </c>
       <c r="J225" t="n">
-        <v>-4.8384</v>
+        <v>-5.2444</v>
       </c>
     </row>
     <row r="226">
@@ -13229,10 +13229,10 @@
         <v>0.67</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.36</v>
+        <v>-0.3715</v>
       </c>
       <c r="J226" t="n">
-        <v>-10.08</v>
+        <v>-10.402</v>
       </c>
     </row>
     <row r="227">
@@ -13269,10 +13269,10 @@
         <v>1.6</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2896</v>
+        <v>1.2586</v>
       </c>
       <c r="J227" t="n">
-        <v>36.1088</v>
+        <v>35.2408</v>
       </c>
     </row>
     <row r="228">
@@ -13309,10 +13309,10 @@
         <v>1.36</v>
       </c>
       <c r="I228" t="n">
-        <v>0.9524</v>
+        <v>0.8902</v>
       </c>
       <c r="J228" t="n">
-        <v>26.6672</v>
+        <v>24.9256</v>
       </c>
     </row>
     <row r="229">
@@ -13349,10 +13349,10 @@
         <v>1.07</v>
       </c>
       <c r="I229" t="n">
-        <v>0.2316</v>
+        <v>0.2402</v>
       </c>
       <c r="J229" t="n">
-        <v>6.4848</v>
+        <v>6.7256</v>
       </c>
     </row>
     <row r="230">
@@ -13389,10 +13389,10 @@
         <v>1.03</v>
       </c>
       <c r="I230" t="n">
-        <v>0.102</v>
+        <v>0.1164</v>
       </c>
       <c r="J230" t="n">
-        <v>2.856</v>
+        <v>3.2592</v>
       </c>
     </row>
     <row r="231">
@@ -13429,10 +13429,10 @@
         <v>0.59</v>
       </c>
       <c r="I231" t="n">
-        <v>-1.1703</v>
+        <v>-1.0598</v>
       </c>
       <c r="J231" t="n">
-        <v>-32.7684</v>
+        <v>-29.6744</v>
       </c>
     </row>
     <row r="232">
@@ -13469,10 +13469,10 @@
         <v>1.33</v>
       </c>
       <c r="I232" t="n">
-        <v>0.6807</v>
+        <v>0.653</v>
       </c>
       <c r="J232" t="n">
-        <v>19.0596</v>
+        <v>18.284</v>
       </c>
     </row>
     <row r="233">
@@ -13509,10 +13509,10 @@
         <v>0.97</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.0479</v>
+        <v>-0.0566</v>
       </c>
       <c r="J233" t="n">
-        <v>-1.3412</v>
+        <v>-1.5848</v>
       </c>
     </row>
     <row r="234">
@@ -13549,10 +13549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.0854</v>
+        <v>-0.0969</v>
       </c>
       <c r="J234" t="n">
-        <v>-2.3912</v>
+        <v>-2.7132</v>
       </c>
     </row>
     <row r="235">
@@ -13589,10 +13589,10 @@
         <v>0.86</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1742</v>
+        <v>-0.1884</v>
       </c>
       <c r="J235" t="n">
-        <v>-4.8776</v>
+        <v>-5.2752</v>
       </c>
     </row>
     <row r="236">
@@ -13629,10 +13629,10 @@
         <v>0.76</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.2753</v>
+        <v>-0.2888</v>
       </c>
       <c r="J236" t="n">
-        <v>-7.7084</v>
+        <v>-8.086399999999999</v>
       </c>
     </row>
     <row r="237">
@@ -13669,10 +13669,10 @@
         <v>1.47</v>
       </c>
       <c r="I237" t="n">
-        <v>1.1238</v>
+        <v>1.0812</v>
       </c>
       <c r="J237" t="n">
-        <v>31.4664</v>
+        <v>30.2736</v>
       </c>
     </row>
     <row r="238">
@@ -13709,10 +13709,10 @@
         <v>1.23</v>
       </c>
       <c r="I238" t="n">
-        <v>0.6511</v>
+        <v>0.6227</v>
       </c>
       <c r="J238" t="n">
-        <v>18.2308</v>
+        <v>17.4356</v>
       </c>
     </row>
     <row r="239">
@@ -13749,10 +13749,10 @@
         <v>1.21</v>
       </c>
       <c r="I239" t="n">
-        <v>0.602</v>
+        <v>0.579</v>
       </c>
       <c r="J239" t="n">
-        <v>16.856</v>
+        <v>16.212</v>
       </c>
     </row>
     <row r="240">
@@ -13789,10 +13789,10 @@
         <v>0.85</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.5226</v>
+        <v>-0.4928</v>
       </c>
       <c r="J240" t="n">
-        <v>-14.6328</v>
+        <v>-13.7984</v>
       </c>
     </row>
     <row r="241">
@@ -13829,10 +13829,10 @@
         <v>0.84</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5496</v>
+        <v>-0.5171</v>
       </c>
       <c r="J241" t="n">
-        <v>-15.3888</v>
+        <v>-14.4788</v>
       </c>
     </row>
     <row r="242">
@@ -13869,10 +13869,10 @@
         <v>1.17</v>
       </c>
       <c r="I242" t="n">
-        <v>0.3368</v>
+        <v>0.332</v>
       </c>
       <c r="J242" t="n">
-        <v>9.0936</v>
+        <v>8.964</v>
       </c>
     </row>
     <row r="243">
@@ -13909,10 +13909,10 @@
         <v>1.01</v>
       </c>
       <c r="I243" t="n">
-        <v>0.0575</v>
+        <v>0.0552</v>
       </c>
       <c r="J243" t="n">
-        <v>1.5525</v>
+        <v>1.4904</v>
       </c>
     </row>
     <row r="244">
@@ -13949,10 +13949,10 @@
         <v>0.93</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.0851</v>
+        <v>-0.1001</v>
       </c>
       <c r="J244" t="n">
-        <v>-2.2977</v>
+        <v>-2.7027</v>
       </c>
     </row>
     <row r="245">
@@ -13989,10 +13989,10 @@
         <v>0.63</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.3842</v>
+        <v>-0.397</v>
       </c>
       <c r="J245" t="n">
-        <v>-10.3734</v>
+        <v>-10.719</v>
       </c>
     </row>
     <row r="246">
@@ -14029,10 +14029,10 @@
         <v>0.53</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4768</v>
+        <v>-0.4851</v>
       </c>
       <c r="J246" t="n">
-        <v>-12.8736</v>
+        <v>-13.0977</v>
       </c>
     </row>
     <row r="247">
@@ -14069,10 +14069,10 @@
         <v>1.45</v>
       </c>
       <c r="I247" t="n">
-        <v>0.5743</v>
+        <v>0.578</v>
       </c>
       <c r="J247" t="n">
-        <v>15.5061</v>
+        <v>15.606</v>
       </c>
     </row>
     <row r="248">
@@ -14109,10 +14109,10 @@
         <v>1.13</v>
       </c>
       <c r="I248" t="n">
-        <v>0.1965</v>
+        <v>0.2139</v>
       </c>
       <c r="J248" t="n">
-        <v>5.3055</v>
+        <v>5.7753</v>
       </c>
     </row>
     <row r="249">
@@ -14149,10 +14149,10 @@
         <v>1.12</v>
       </c>
       <c r="I249" t="n">
-        <v>0.1831</v>
+        <v>0.2005</v>
       </c>
       <c r="J249" t="n">
-        <v>4.9437</v>
+        <v>5.4135</v>
       </c>
     </row>
     <row r="250">
@@ -14189,10 +14189,10 @@
         <v>1.1</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1554</v>
+        <v>0.1726</v>
       </c>
       <c r="J250" t="n">
-        <v>4.1958</v>
+        <v>4.6602</v>
       </c>
     </row>
     <row r="251">
@@ -14229,10 +14229,10 @@
         <v>1.06</v>
       </c>
       <c r="I251" t="n">
-        <v>0.096</v>
+        <v>0.1122</v>
       </c>
       <c r="J251" t="n">
-        <v>2.592</v>
+        <v>3.0294</v>
       </c>
     </row>
     <row r="252">
@@ -14269,10 +14269,10 @@
         <v>1.42</v>
       </c>
       <c r="I252" t="n">
-        <v>1.0694</v>
+        <v>1.0166</v>
       </c>
       <c r="J252" t="n">
-        <v>31.0126</v>
+        <v>29.4814</v>
       </c>
     </row>
     <row r="253">
@@ -14309,10 +14309,10 @@
         <v>1.25</v>
       </c>
       <c r="I253" t="n">
-        <v>0.7148</v>
+        <v>0.6763</v>
       </c>
       <c r="J253" t="n">
-        <v>20.7292</v>
+        <v>19.6127</v>
       </c>
     </row>
     <row r="254">
@@ -14349,10 +14349,10 @@
         <v>1.01</v>
       </c>
       <c r="I254" t="n">
-        <v>0.0374</v>
+        <v>0.0478</v>
       </c>
       <c r="J254" t="n">
-        <v>1.0846</v>
+        <v>1.3862</v>
       </c>
     </row>
     <row r="255">
@@ -14389,10 +14389,10 @@
         <v>0.93</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.2816</v>
+        <v>-0.2745</v>
       </c>
       <c r="J255" t="n">
-        <v>-8.166399999999999</v>
+        <v>-7.9605</v>
       </c>
     </row>
     <row r="256">
@@ -14429,10 +14429,10 @@
         <v>0.78</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.6953</v>
+        <v>-0.649</v>
       </c>
       <c r="J256" t="n">
-        <v>-20.1637</v>
+        <v>-18.821</v>
       </c>
     </row>
     <row r="257">
@@ -14469,10 +14469,10 @@
         <v>1.58</v>
       </c>
       <c r="I257" t="n">
-        <v>1.0389</v>
+        <v>0.9958</v>
       </c>
       <c r="J257" t="n">
-        <v>30.1281</v>
+        <v>28.8782</v>
       </c>
     </row>
     <row r="258">
@@ -14509,10 +14509,10 @@
         <v>1.18</v>
       </c>
       <c r="I258" t="n">
-        <v>0.3935</v>
+        <v>0.3933</v>
       </c>
       <c r="J258" t="n">
-        <v>11.4115</v>
+        <v>11.4057</v>
       </c>
     </row>
     <row r="259">
@@ -14549,10 +14549,10 @@
         <v>0.86</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1807</v>
+        <v>-0.1934</v>
       </c>
       <c r="J259" t="n">
-        <v>-5.2403</v>
+        <v>-5.6086</v>
       </c>
     </row>
     <row r="260">
@@ -14589,10 +14589,10 @@
         <v>0.83</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2119</v>
+        <v>-0.2247</v>
       </c>
       <c r="J260" t="n">
-        <v>-6.1451</v>
+        <v>-6.5163</v>
       </c>
     </row>
     <row r="261">
@@ -14629,10 +14629,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3488</v>
+        <v>-0.3593</v>
       </c>
       <c r="J261" t="n">
-        <v>-10.1152</v>
+        <v>-10.4197</v>
       </c>
     </row>
     <row r="262">
@@ -14669,10 +14669,10 @@
         <v>2.04</v>
       </c>
       <c r="I262" t="n">
-        <v>1.7221</v>
+        <v>1.7276</v>
       </c>
       <c r="J262" t="n">
-        <v>34.442</v>
+        <v>34.552</v>
       </c>
     </row>
     <row r="263">
@@ -14709,10 +14709,10 @@
         <v>1.72</v>
       </c>
       <c r="I263" t="n">
-        <v>1.3581</v>
+        <v>1.345</v>
       </c>
       <c r="J263" t="n">
-        <v>27.162</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="264">
@@ -14749,10 +14749,10 @@
         <v>1.31</v>
       </c>
       <c r="I264" t="n">
-        <v>0.7706</v>
+        <v>0.7417</v>
       </c>
       <c r="J264" t="n">
-        <v>15.412</v>
+        <v>14.834</v>
       </c>
     </row>
     <row r="265">
@@ -14789,10 +14789,10 @@
         <v>1.09</v>
       </c>
       <c r="I265" t="n">
-        <v>0.2195</v>
+        <v>0.2458</v>
       </c>
       <c r="J265" t="n">
-        <v>4.39</v>
+        <v>4.916</v>
       </c>
     </row>
     <row r="266">
@@ -14829,10 +14829,10 @@
         <v>1.04</v>
       </c>
       <c r="I266" t="n">
-        <v>0.0644</v>
+        <v>0.0994</v>
       </c>
       <c r="J266" t="n">
-        <v>1.288</v>
+        <v>1.988</v>
       </c>
     </row>
     <row r="267">
@@ -14869,10 +14869,10 @@
         <v>0.87</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.1087</v>
+        <v>-0.1351</v>
       </c>
       <c r="J267" t="n">
-        <v>-2.174</v>
+        <v>-2.702</v>
       </c>
     </row>
     <row r="268">
@@ -14909,10 +14909,10 @@
         <v>0.72</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.2711</v>
+        <v>-0.2935</v>
       </c>
       <c r="J268" t="n">
-        <v>-5.422</v>
+        <v>-5.87</v>
       </c>
     </row>
     <row r="269">
@@ -14949,10 +14949,10 @@
         <v>0.63</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.3539</v>
+        <v>-0.3735</v>
       </c>
       <c r="J269" t="n">
-        <v>-7.078</v>
+        <v>-7.47</v>
       </c>
     </row>
     <row r="270">
@@ -14989,10 +14989,10 @@
         <v>0.6</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3813</v>
+        <v>-0.3996</v>
       </c>
       <c r="J270" t="n">
-        <v>-7.626</v>
+        <v>-7.992</v>
       </c>
     </row>
     <row r="271">
@@ -15029,10 +15029,10 @@
         <v>0.44</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5311</v>
+        <v>-0.5403</v>
       </c>
       <c r="J271" t="n">
-        <v>-10.622</v>
+        <v>-10.806</v>
       </c>
     </row>
     <row r="272">
@@ -15069,10 +15069,10 @@
         <v>1.3</v>
       </c>
       <c r="I272" t="n">
-        <v>0.59</v>
+        <v>0.5774</v>
       </c>
       <c r="J272" t="n">
-        <v>21.24</v>
+        <v>20.7864</v>
       </c>
     </row>
     <row r="273">
@@ -15109,10 +15109,10 @@
         <v>1.23</v>
       </c>
       <c r="I273" t="n">
-        <v>0.4695</v>
+        <v>0.4667</v>
       </c>
       <c r="J273" t="n">
-        <v>16.902</v>
+        <v>16.8012</v>
       </c>
     </row>
     <row r="274">
@@ -15149,10 +15149,10 @@
         <v>1.18</v>
       </c>
       <c r="I274" t="n">
-        <v>0.3804</v>
+        <v>0.3838</v>
       </c>
       <c r="J274" t="n">
-        <v>13.6944</v>
+        <v>13.8168</v>
       </c>
     </row>
     <row r="275">
@@ -15189,10 +15189,10 @@
         <v>0.91</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.1318</v>
+        <v>-0.1422</v>
       </c>
       <c r="J275" t="n">
-        <v>-4.7448</v>
+        <v>-5.1192</v>
       </c>
     </row>
     <row r="276">
@@ -15229,10 +15229,10 @@
         <v>0.78</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.2678</v>
+        <v>-0.279</v>
       </c>
       <c r="J276" t="n">
-        <v>-9.6408</v>
+        <v>-10.044</v>
       </c>
     </row>
     <row r="277">
@@ -15269,10 +15269,10 @@
         <v>1.1</v>
       </c>
       <c r="I277" t="n">
-        <v>0.3539</v>
+        <v>0.3455</v>
       </c>
       <c r="J277" t="n">
-        <v>12.7404</v>
+        <v>12.438</v>
       </c>
     </row>
     <row r="278">
@@ -15309,10 +15309,10 @@
         <v>1.01</v>
       </c>
       <c r="I278" t="n">
-        <v>0.0564</v>
+        <v>0.0607</v>
       </c>
       <c r="J278" t="n">
-        <v>2.0304</v>
+        <v>2.1852</v>
       </c>
     </row>
     <row r="279">
@@ -15349,10 +15349,10 @@
         <v>0.99</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.0514</v>
+        <v>-0.0574</v>
       </c>
       <c r="J279" t="n">
-        <v>-1.8504</v>
+        <v>-2.0664</v>
       </c>
     </row>
     <row r="280">
@@ -15389,10 +15389,10 @@
         <v>0.97</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.1269</v>
+        <v>-0.1333</v>
       </c>
       <c r="J280" t="n">
-        <v>-4.5684</v>
+        <v>-4.7988</v>
       </c>
     </row>
     <row r="281">
@@ -15429,10 +15429,10 @@
         <v>0.86</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.457</v>
+        <v>-0.4414</v>
       </c>
       <c r="J281" t="n">
-        <v>-16.452</v>
+        <v>-15.8904</v>
       </c>
     </row>
     <row r="282">
@@ -15469,10 +15469,10 @@
         <v>1.25</v>
       </c>
       <c r="I282" t="n">
-        <v>0.658</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="J282" t="n">
-        <v>13.818</v>
+        <v>12.8604</v>
       </c>
     </row>
     <row r="283">
@@ -15509,10 +15509,10 @@
         <v>1.05</v>
       </c>
       <c r="I283" t="n">
-        <v>0.2287</v>
+        <v>0.2133</v>
       </c>
       <c r="J283" t="n">
-        <v>4.8027</v>
+        <v>4.4793</v>
       </c>
     </row>
     <row r="284">
@@ -15549,10 +15549,10 @@
         <v>0.59</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.4078</v>
+        <v>-0.4219</v>
       </c>
       <c r="J284" t="n">
-        <v>-8.563800000000001</v>
+        <v>-8.8599</v>
       </c>
     </row>
     <row r="285">
@@ -15589,10 +15589,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.4358</v>
+        <v>-0.4485</v>
       </c>
       <c r="J285" t="n">
-        <v>-9.1518</v>
+        <v>-9.4185</v>
       </c>
     </row>
     <row r="286">
@@ -15629,10 +15629,10 @@
         <v>0.34</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.6389</v>
+        <v>-0.6382</v>
       </c>
       <c r="J286" t="n">
-        <v>-13.4169</v>
+        <v>-13.4022</v>
       </c>
     </row>
     <row r="287">
@@ -15669,10 +15669,10 @@
         <v>1.85</v>
       </c>
       <c r="I287" t="n">
-        <v>1.525</v>
+        <v>1.5184</v>
       </c>
       <c r="J287" t="n">
-        <v>32.025</v>
+        <v>31.8864</v>
       </c>
     </row>
     <row r="288">
@@ -15709,10 +15709,10 @@
         <v>1.66</v>
       </c>
       <c r="I288" t="n">
-        <v>1.3019</v>
+        <v>1.2826</v>
       </c>
       <c r="J288" t="n">
-        <v>27.3399</v>
+        <v>26.9346</v>
       </c>
     </row>
     <row r="289">
@@ -15749,10 +15749,10 @@
         <v>1.4</v>
       </c>
       <c r="I289" t="n">
-        <v>0.97</v>
+        <v>0.9195</v>
       </c>
       <c r="J289" t="n">
-        <v>20.37</v>
+        <v>19.3095</v>
       </c>
     </row>
     <row r="290">
@@ -15789,10 +15789,10 @@
         <v>1.07</v>
       </c>
       <c r="I290" t="n">
-        <v>0.1761</v>
+        <v>0.2015</v>
       </c>
       <c r="J290" t="n">
-        <v>3.6981</v>
+        <v>4.2315</v>
       </c>
     </row>
     <row r="291">
@@ -15829,10 +15829,10 @@
         <v>0.85</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.58</v>
+        <v>-0.5332</v>
       </c>
       <c r="J291" t="n">
-        <v>-12.18</v>
+        <v>-11.1972</v>
       </c>
     </row>
     <row r="292">
@@ -15869,10 +15869,10 @@
         <v>1.04</v>
       </c>
       <c r="I292" t="n">
-        <v>0.1956</v>
+        <v>0.1827</v>
       </c>
       <c r="J292" t="n">
-        <v>4.4988</v>
+        <v>4.2021</v>
       </c>
     </row>
     <row r="293">
@@ -15909,10 +15909,10 @@
         <v>0.86</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.1507</v>
+        <v>-0.1704</v>
       </c>
       <c r="J293" t="n">
-        <v>-3.4661</v>
+        <v>-3.9192</v>
       </c>
     </row>
     <row r="294">
@@ -15949,10 +15949,10 @@
         <v>0.74</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.2688</v>
+        <v>-0.2877</v>
       </c>
       <c r="J294" t="n">
-        <v>-6.1824</v>
+        <v>-6.6171</v>
       </c>
     </row>
     <row r="295">
@@ -15989,10 +15989,10 @@
         <v>0.73</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.2782</v>
+        <v>-0.2969</v>
       </c>
       <c r="J295" t="n">
-        <v>-6.3986</v>
+        <v>-6.8287</v>
       </c>
     </row>
     <row r="296">
@@ -16029,10 +16029,10 @@
         <v>0.49</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.5028</v>
+        <v>-0.5112</v>
       </c>
       <c r="J296" t="n">
-        <v>-11.5644</v>
+        <v>-11.7576</v>
       </c>
     </row>
     <row r="297">
@@ -16069,10 +16069,10 @@
         <v>1.58</v>
       </c>
       <c r="I297" t="n">
-        <v>1.2152</v>
+        <v>1.1882</v>
       </c>
       <c r="J297" t="n">
-        <v>27.9496</v>
+        <v>27.3286</v>
       </c>
     </row>
     <row r="298">
@@ -16109,10 +16109,10 @@
         <v>1.43</v>
       </c>
       <c r="I298" t="n">
-        <v>1.0266</v>
+        <v>0.9784</v>
       </c>
       <c r="J298" t="n">
-        <v>23.6118</v>
+        <v>22.5032</v>
       </c>
     </row>
     <row r="299">
@@ -16149,10 +16149,10 @@
         <v>1.28</v>
       </c>
       <c r="I299" t="n">
-        <v>0.7262</v>
+        <v>0.6979</v>
       </c>
       <c r="J299" t="n">
-        <v>16.7026</v>
+        <v>16.0517</v>
       </c>
     </row>
     <row r="300">
@@ -16189,10 +16189,10 @@
         <v>1.2</v>
       </c>
       <c r="I300" t="n">
-        <v>0.5377</v>
+        <v>0.5299</v>
       </c>
       <c r="J300" t="n">
-        <v>12.3671</v>
+        <v>12.1877</v>
       </c>
     </row>
     <row r="301">
@@ -16229,10 +16229,10 @@
         <v>1.1</v>
       </c>
       <c r="I301" t="n">
-        <v>0.2749</v>
+        <v>0.291</v>
       </c>
       <c r="J301" t="n">
-        <v>6.3227</v>
+        <v>6.693</v>
       </c>
     </row>
     <row r="302">
@@ -16269,10 +16269,10 @@
         <v>1.06</v>
       </c>
       <c r="I302" t="n">
-        <v>0.2081</v>
+        <v>0.2039</v>
       </c>
       <c r="J302" t="n">
-        <v>4.9944</v>
+        <v>4.8936</v>
       </c>
     </row>
     <row r="303">
@@ -16309,10 +16309,10 @@
         <v>0.99</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.0015</v>
+        <v>-0.0106</v>
       </c>
       <c r="J303" t="n">
-        <v>-0.036</v>
+        <v>-0.2544</v>
       </c>
     </row>
     <row r="304">
@@ -16349,10 +16349,10 @@
         <v>0.78</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.2403</v>
+        <v>-0.2576</v>
       </c>
       <c r="J304" t="n">
-        <v>-5.7672</v>
+        <v>-6.1824</v>
       </c>
     </row>
     <row r="305">
@@ -16389,10 +16389,10 @@
         <v>0.72</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.2984</v>
+        <v>-0.3145</v>
       </c>
       <c r="J305" t="n">
-        <v>-7.1616</v>
+        <v>-7.548</v>
       </c>
     </row>
     <row r="306">
@@ -16429,10 +16429,10 @@
         <v>0.7</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.3175</v>
+        <v>-0.333</v>
       </c>
       <c r="J306" t="n">
-        <v>-7.62</v>
+        <v>-7.992</v>
       </c>
     </row>
     <row r="307">
@@ -16469,10 +16469,10 @@
         <v>1.5</v>
       </c>
       <c r="I307" t="n">
-        <v>1.1292</v>
+        <v>1.0934</v>
       </c>
       <c r="J307" t="n">
-        <v>27.1008</v>
+        <v>26.2416</v>
       </c>
     </row>
     <row r="308">
@@ -16509,10 +16509,10 @@
         <v>1.31</v>
       </c>
       <c r="I308" t="n">
-        <v>0.8028</v>
+        <v>0.7637</v>
       </c>
       <c r="J308" t="n">
-        <v>19.2672</v>
+        <v>18.3288</v>
       </c>
     </row>
     <row r="309">
@@ -16549,10 +16549,10 @@
         <v>1.29</v>
       </c>
       <c r="I309" t="n">
-        <v>0.7579</v>
+        <v>0.724</v>
       </c>
       <c r="J309" t="n">
-        <v>18.1896</v>
+        <v>17.376</v>
       </c>
     </row>
     <row r="310">
@@ -16589,10 +16589,10 @@
         <v>1.12</v>
       </c>
       <c r="I310" t="n">
-        <v>0.3454</v>
+        <v>0.3526</v>
       </c>
       <c r="J310" t="n">
-        <v>8.2896</v>
+        <v>8.462400000000001</v>
       </c>
     </row>
     <row r="311">
@@ -16629,10 +16629,10 @@
         <v>1.05</v>
       </c>
       <c r="I311" t="n">
-        <v>0.1391</v>
+        <v>0.1603</v>
       </c>
       <c r="J311" t="n">
-        <v>3.3384</v>
+        <v>3.8472</v>
       </c>
     </row>
     <row r="312">
@@ -16669,10 +16669,10 @@
         <v>1.2</v>
       </c>
       <c r="I312" t="n">
-        <v>0.5952</v>
+        <v>0.5693</v>
       </c>
       <c r="J312" t="n">
-        <v>23.808</v>
+        <v>22.772</v>
       </c>
     </row>
     <row r="313">
@@ -16709,10 +16709,10 @@
         <v>1.18</v>
       </c>
       <c r="I313" t="n">
-        <v>0.5439000000000001</v>
+        <v>0.5235</v>
       </c>
       <c r="J313" t="n">
-        <v>21.756</v>
+        <v>20.94</v>
       </c>
     </row>
     <row r="314">
@@ -16749,10 +16749,10 @@
         <v>1.1</v>
       </c>
       <c r="I314" t="n">
-        <v>0.3298</v>
+        <v>0.3288</v>
       </c>
       <c r="J314" t="n">
-        <v>13.192</v>
+        <v>13.152</v>
       </c>
     </row>
     <row r="315">
@@ -16789,10 +16789,10 @@
         <v>1.04</v>
       </c>
       <c r="I315" t="n">
-        <v>0.152</v>
+        <v>0.1604</v>
       </c>
       <c r="J315" t="n">
-        <v>6.08</v>
+        <v>6.416</v>
       </c>
     </row>
     <row r="316">
@@ -16829,10 +16829,10 @@
         <v>0.8</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.6398</v>
+        <v>-0.6005</v>
       </c>
       <c r="J316" t="n">
-        <v>-25.592</v>
+        <v>-24.02</v>
       </c>
     </row>
     <row r="317">
@@ -16869,10 +16869,10 @@
         <v>1.2</v>
       </c>
       <c r="I317" t="n">
-        <v>0.4284</v>
+        <v>0.4262</v>
       </c>
       <c r="J317" t="n">
-        <v>17.136</v>
+        <v>17.048</v>
       </c>
     </row>
     <row r="318">
@@ -16909,10 +16909,10 @@
         <v>1.17</v>
       </c>
       <c r="I318" t="n">
-        <v>0.3733</v>
+        <v>0.3748</v>
       </c>
       <c r="J318" t="n">
-        <v>14.932</v>
+        <v>14.992</v>
       </c>
     </row>
     <row r="319">
@@ -16949,10 +16949,10 @@
         <v>1.04</v>
       </c>
       <c r="I319" t="n">
-        <v>0.1108</v>
+        <v>0.1208</v>
       </c>
       <c r="J319" t="n">
-        <v>4.432</v>
+        <v>4.832</v>
       </c>
     </row>
     <row r="320">
@@ -16989,10 +16989,10 @@
         <v>0.96</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.06660000000000001</v>
+        <v>-0.0751</v>
       </c>
       <c r="J320" t="n">
-        <v>-2.664</v>
+        <v>-3.004</v>
       </c>
     </row>
     <row r="321">
@@ -17029,10 +17029,10 @@
         <v>0.8</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.2429</v>
+        <v>-0.2555</v>
       </c>
       <c r="J321" t="n">
-        <v>-9.715999999999999</v>
+        <v>-10.22</v>
       </c>
     </row>
     <row r="322">
@@ -17069,10 +17069,10 @@
         <v>1.57</v>
       </c>
       <c r="I322" t="n">
-        <v>1.2221</v>
+        <v>1.1921</v>
       </c>
       <c r="J322" t="n">
-        <v>31.7746</v>
+        <v>30.9946</v>
       </c>
     </row>
     <row r="323">
@@ -17109,10 +17109,10 @@
         <v>1.27</v>
       </c>
       <c r="I323" t="n">
-        <v>0.7169</v>
+        <v>0.6868</v>
       </c>
       <c r="J323" t="n">
-        <v>18.6394</v>
+        <v>17.8568</v>
       </c>
     </row>
     <row r="324">
@@ -17149,10 +17149,10 @@
         <v>1.22</v>
       </c>
       <c r="I324" t="n">
-        <v>0.6028</v>
+        <v>0.5847</v>
       </c>
       <c r="J324" t="n">
-        <v>15.6728</v>
+        <v>15.2022</v>
       </c>
     </row>
     <row r="325">
@@ -17189,10 +17189,10 @@
         <v>1.15</v>
       </c>
       <c r="I325" t="n">
-        <v>0.4302</v>
+        <v>0.4289</v>
       </c>
       <c r="J325" t="n">
-        <v>11.1852</v>
+        <v>11.1514</v>
       </c>
     </row>
     <row r="326">
@@ -17229,10 +17229,10 @@
         <v>0.95</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.2584</v>
+        <v>-0.2429</v>
       </c>
       <c r="J326" t="n">
-        <v>-6.7184</v>
+        <v>-6.3154</v>
       </c>
     </row>
     <row r="327">
@@ -17269,10 +17269,10 @@
         <v>1</v>
       </c>
       <c r="I327" t="n">
-        <v>0.0274</v>
+        <v>0.0197</v>
       </c>
       <c r="J327" t="n">
-        <v>0.7124</v>
+        <v>0.5122</v>
       </c>
     </row>
     <row r="328">
@@ -17309,10 +17309,10 @@
         <v>0.92</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.1002</v>
+        <v>-0.1149</v>
       </c>
       <c r="J328" t="n">
-        <v>-2.6052</v>
+        <v>-2.9874</v>
       </c>
     </row>
     <row r="329">
@@ -17349,10 +17349,10 @@
         <v>0.89</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.1333</v>
+        <v>-0.149</v>
       </c>
       <c r="J329" t="n">
-        <v>-3.4658</v>
+        <v>-3.874</v>
       </c>
     </row>
     <row r="330">
@@ -17389,10 +17389,10 @@
         <v>0.88</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.1436</v>
+        <v>-0.1597</v>
       </c>
       <c r="J330" t="n">
-        <v>-3.7336</v>
+        <v>-4.1522</v>
       </c>
     </row>
     <row r="331">
@@ -17429,10 +17429,10 @@
         <v>0.7</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.3213</v>
+        <v>-0.336</v>
       </c>
       <c r="J331" t="n">
-        <v>-8.3538</v>
+        <v>-8.736000000000001</v>
       </c>
     </row>
     <row r="332">
@@ -17469,10 +17469,10 @@
         <v>1.46</v>
       </c>
       <c r="I332" t="n">
-        <v>0.8993</v>
+        <v>0.849</v>
       </c>
       <c r="J332" t="n">
-        <v>37.7706</v>
+        <v>35.658</v>
       </c>
     </row>
     <row r="333">
@@ -17509,10 +17509,10 @@
         <v>1.03</v>
       </c>
       <c r="I333" t="n">
-        <v>0.0965</v>
+        <v>0.1033</v>
       </c>
       <c r="J333" t="n">
-        <v>4.053</v>
+        <v>4.3386</v>
       </c>
     </row>
     <row r="334">
@@ -17549,10 +17549,10 @@
         <v>1</v>
       </c>
       <c r="I334" t="n">
-        <v>0.0032</v>
+        <v>0.0022</v>
       </c>
       <c r="J334" t="n">
-        <v>0.1344</v>
+        <v>0.0924</v>
       </c>
     </row>
     <row r="335">
@@ -17589,10 +17589,10 @@
         <v>0.7</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.3335</v>
+        <v>-0.3455</v>
       </c>
       <c r="J335" t="n">
-        <v>-14.007</v>
+        <v>-14.511</v>
       </c>
     </row>
     <row r="336">
@@ -17629,10 +17629,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.343</v>
+        <v>-0.3547</v>
       </c>
       <c r="J336" t="n">
-        <v>-14.406</v>
+        <v>-14.8974</v>
       </c>
     </row>
     <row r="337">
@@ -17669,10 +17669,10 @@
         <v>1.34</v>
       </c>
       <c r="I337" t="n">
-        <v>0.9318</v>
+        <v>0.8668</v>
       </c>
       <c r="J337" t="n">
-        <v>39.1356</v>
+        <v>36.4056</v>
       </c>
     </row>
     <row r="338">
@@ -17709,10 +17709,10 @@
         <v>1.26</v>
       </c>
       <c r="I338" t="n">
-        <v>0.7409</v>
+        <v>0.699</v>
       </c>
       <c r="J338" t="n">
-        <v>31.1178</v>
+        <v>29.358</v>
       </c>
     </row>
     <row r="339">
@@ -17749,10 +17749,10 @@
         <v>1.15</v>
       </c>
       <c r="I339" t="n">
-        <v>0.4626</v>
+        <v>0.4509</v>
       </c>
       <c r="J339" t="n">
-        <v>19.4292</v>
+        <v>18.9378</v>
       </c>
     </row>
     <row r="340">
@@ -17789,10 +17789,10 @@
         <v>0.91</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.3407</v>
+        <v>-0.3297</v>
       </c>
       <c r="J340" t="n">
-        <v>-14.3094</v>
+        <v>-13.8474</v>
       </c>
     </row>
     <row r="341">
@@ -17829,10 +17829,10 @@
         <v>0.71</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.8697</v>
+        <v>-0.8022</v>
       </c>
       <c r="J341" t="n">
-        <v>-36.5274</v>
+        <v>-33.6924</v>
       </c>
     </row>
     <row r="342">
@@ -17869,10 +17869,10 @@
         <v>1.65</v>
       </c>
       <c r="I342" t="n">
-        <v>1.1041</v>
+        <v>1.073</v>
       </c>
       <c r="J342" t="n">
-        <v>32.0189</v>
+        <v>31.117</v>
       </c>
     </row>
     <row r="343">
@@ -17909,10 +17909,10 @@
         <v>1.18</v>
       </c>
       <c r="I343" t="n">
-        <v>0.3924</v>
+        <v>0.3925</v>
       </c>
       <c r="J343" t="n">
-        <v>11.3796</v>
+        <v>11.3825</v>
       </c>
     </row>
     <row r="344">
@@ -17949,10 +17949,10 @@
         <v>0.87</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.1705</v>
+        <v>-0.183</v>
       </c>
       <c r="J344" t="n">
-        <v>-4.9445</v>
+        <v>-5.307</v>
       </c>
     </row>
     <row r="345">
@@ -17989,10 +17989,10 @@
         <v>0.84</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.202</v>
+        <v>-0.2148</v>
       </c>
       <c r="J345" t="n">
-        <v>-5.858</v>
+        <v>-6.2292</v>
       </c>
     </row>
     <row r="346">
@@ -18029,10 +18029,10 @@
         <v>0.62</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.4142</v>
+        <v>-0.4222</v>
       </c>
       <c r="J346" t="n">
-        <v>-12.0118</v>
+        <v>-12.2438</v>
       </c>
     </row>
     <row r="347">
@@ -18069,10 +18069,10 @@
         <v>1.39</v>
       </c>
       <c r="I347" t="n">
-        <v>1.027</v>
+        <v>0.9654</v>
       </c>
       <c r="J347" t="n">
-        <v>29.783</v>
+        <v>27.9966</v>
       </c>
     </row>
     <row r="348">
@@ -18109,10 +18109,10 @@
         <v>1.23</v>
       </c>
       <c r="I348" t="n">
-        <v>0.6669</v>
+        <v>0.6337</v>
       </c>
       <c r="J348" t="n">
-        <v>19.3401</v>
+        <v>18.3773</v>
       </c>
     </row>
     <row r="349">
@@ -18149,10 +18149,10 @@
         <v>1.14</v>
       </c>
       <c r="I349" t="n">
-        <v>0.4361</v>
+        <v>0.4269</v>
       </c>
       <c r="J349" t="n">
-        <v>12.6469</v>
+        <v>12.3801</v>
       </c>
     </row>
     <row r="350">
@@ -18189,10 +18189,10 @@
         <v>0.88</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.4271</v>
+        <v>-0.4089</v>
       </c>
       <c r="J350" t="n">
-        <v>-12.3859</v>
+        <v>-11.8581</v>
       </c>
     </row>
     <row r="351">
@@ -18229,10 +18229,10 @@
         <v>0.73</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.8203</v>
+        <v>-0.759</v>
       </c>
       <c r="J351" t="n">
-        <v>-23.7887</v>
+        <v>-22.011</v>
       </c>
     </row>
     <row r="352">
@@ -18269,10 +18269,10 @@
         <v>1.26</v>
       </c>
       <c r="I352" t="n">
-        <v>0.731</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="J352" t="n">
-        <v>21.93</v>
+        <v>20.76</v>
       </c>
     </row>
     <row r="353">
@@ -18309,10 +18309,10 @@
         <v>1.19</v>
       </c>
       <c r="I353" t="n">
-        <v>0.5579</v>
+        <v>0.5384</v>
       </c>
       <c r="J353" t="n">
-        <v>16.737</v>
+        <v>16.152</v>
       </c>
     </row>
     <row r="354">
@@ -18349,10 +18349,10 @@
         <v>1.08</v>
       </c>
       <c r="I354" t="n">
-        <v>0.2675</v>
+        <v>0.2723</v>
       </c>
       <c r="J354" t="n">
-        <v>8.025</v>
+        <v>8.169</v>
       </c>
     </row>
     <row r="355">
@@ -18389,10 +18389,10 @@
         <v>1.05</v>
       </c>
       <c r="I355" t="n">
-        <v>0.1766</v>
+        <v>0.1863</v>
       </c>
       <c r="J355" t="n">
-        <v>5.298</v>
+        <v>5.589</v>
       </c>
     </row>
     <row r="356">
@@ -18429,10 +18429,10 @@
         <v>0.92</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.3181</v>
+        <v>-0.3071</v>
       </c>
       <c r="J356" t="n">
-        <v>-9.542999999999999</v>
+        <v>-9.212999999999999</v>
       </c>
     </row>
     <row r="357">
@@ -18469,10 +18469,10 @@
         <v>1.38</v>
       </c>
       <c r="I357" t="n">
-        <v>0.7648</v>
+        <v>0.729</v>
       </c>
       <c r="J357" t="n">
-        <v>22.944</v>
+        <v>21.87</v>
       </c>
     </row>
     <row r="358">
@@ -18509,10 +18509,10 @@
         <v>1.21</v>
       </c>
       <c r="I358" t="n">
-        <v>0.4652</v>
+        <v>0.4567</v>
       </c>
       <c r="J358" t="n">
-        <v>13.956</v>
+        <v>13.701</v>
       </c>
     </row>
     <row r="359">
@@ -18549,10 +18549,10 @@
         <v>0.83</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.2058</v>
+        <v>-0.22</v>
       </c>
       <c r="J359" t="n">
-        <v>-6.174</v>
+        <v>-6.6</v>
       </c>
     </row>
     <row r="360">
@@ -18589,10 +18589,10 @@
         <v>0.77</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.2659</v>
+        <v>-0.2796</v>
       </c>
       <c r="J360" t="n">
-        <v>-7.977</v>
+        <v>-8.388</v>
       </c>
     </row>
     <row r="361">
@@ -18629,10 +18629,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.343</v>
+        <v>-0.3547</v>
       </c>
       <c r="J361" t="n">
-        <v>-10.29</v>
+        <v>-10.641</v>
       </c>
     </row>
     <row r="362">
@@ -18669,10 +18669,10 @@
         <v>1.63</v>
       </c>
       <c r="I362" t="n">
-        <v>1.2921</v>
+        <v>1.2673</v>
       </c>
       <c r="J362" t="n">
-        <v>29.7183</v>
+        <v>29.1479</v>
       </c>
     </row>
     <row r="363">
@@ -18709,10 +18709,10 @@
         <v>1.5</v>
       </c>
       <c r="I363" t="n">
-        <v>1.13</v>
+        <v>1.0941</v>
       </c>
       <c r="J363" t="n">
-        <v>25.99</v>
+        <v>25.1643</v>
       </c>
     </row>
     <row r="364">
@@ -18749,10 +18749,10 @@
         <v>1.31</v>
       </c>
       <c r="I364" t="n">
-        <v>0.8037</v>
+        <v>0.7643</v>
       </c>
       <c r="J364" t="n">
-        <v>18.4851</v>
+        <v>17.5789</v>
       </c>
     </row>
     <row r="365">
@@ -18789,10 +18789,10 @@
         <v>1.22</v>
       </c>
       <c r="I365" t="n">
-        <v>0.5998</v>
+        <v>0.5827</v>
       </c>
       <c r="J365" t="n">
-        <v>13.7954</v>
+        <v>13.4021</v>
       </c>
     </row>
     <row r="366">
@@ -18829,10 +18829,10 @@
         <v>0.59</v>
       </c>
       <c r="I366" t="n">
-        <v>-1.194</v>
+        <v>-1.0766</v>
       </c>
       <c r="J366" t="n">
-        <v>-27.462</v>
+        <v>-24.7618</v>
       </c>
     </row>
     <row r="367">
@@ -18869,10 +18869,10 @@
         <v>1.4</v>
       </c>
       <c r="I367" t="n">
-        <v>0.8007</v>
+        <v>0.7608</v>
       </c>
       <c r="J367" t="n">
-        <v>18.4161</v>
+        <v>17.4984</v>
       </c>
     </row>
     <row r="368">
@@ -18909,10 +18909,10 @@
         <v>1.29</v>
       </c>
       <c r="I368" t="n">
-        <v>0.6107</v>
+        <v>0.5897</v>
       </c>
       <c r="J368" t="n">
-        <v>14.0461</v>
+        <v>13.5631</v>
       </c>
     </row>
     <row r="369">
@@ -18949,10 +18949,10 @@
         <v>0.97</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.0479</v>
+        <v>-0.0566</v>
       </c>
       <c r="J369" t="n">
-        <v>-1.1017</v>
+        <v>-1.3018</v>
       </c>
     </row>
     <row r="370">
@@ -18989,10 +18989,10 @@
         <v>0.66</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.3707</v>
+        <v>-0.3816</v>
       </c>
       <c r="J370" t="n">
-        <v>-8.5261</v>
+        <v>-8.7768</v>
       </c>
     </row>
     <row r="371">
@@ -19029,10 +19029,10 @@
         <v>0.54</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.4808</v>
+        <v>-0.4868</v>
       </c>
       <c r="J371" t="n">
-        <v>-11.0584</v>
+        <v>-11.1964</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7128/event_7128_evp_summary.xlsx
+++ b/database/event/7128/event_7128_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.9454</v>
+        <v>5.9531</v>
       </c>
       <c r="C2" t="n">
-        <v>3.5485</v>
+        <v>3.5531</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0823</v>
+        <v>2.1061</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9454</v>
+        <v>5.9531</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2816</v>
+        <v>2.2941</v>
       </c>
       <c r="G2" t="n">
-        <v>3.6638</v>
+        <v>3.659</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2816</v>
+        <v>2.3073</v>
       </c>
       <c r="I2" t="n">
-        <v>2.2816</v>
+        <v>2.3073</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6638</v>
+        <v>3.659</v>
       </c>
       <c r="K2" t="n">
         <v>47</v>
@@ -529,7 +529,7 @@
         <v>209</v>
       </c>
       <c r="M2" t="n">
-        <v>5.9454</v>
+        <v>5.9663</v>
       </c>
       <c r="N2" t="n">
         <v>256</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.9969</v>
+        <v>4.956</v>
       </c>
       <c r="C3" t="n">
-        <v>2.9824</v>
+        <v>2.958</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6505</v>
+        <v>1.6519</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9969</v>
+        <v>4.956</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8639</v>
+        <v>1.8548</v>
       </c>
       <c r="G3" t="n">
-        <v>3.133</v>
+        <v>3.1012</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8639</v>
+        <v>1.8548</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8639</v>
+        <v>1.8548</v>
       </c>
       <c r="J3" t="n">
-        <v>3.133</v>
+        <v>3.1012</v>
       </c>
       <c r="K3" t="n">
         <v>57</v>
@@ -575,7 +575,7 @@
         <v>184</v>
       </c>
       <c r="M3" t="n">
-        <v>4.9969</v>
+        <v>4.956</v>
       </c>
       <c r="N3" t="n">
         <v>241</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.7571</v>
+        <v>4.5698</v>
       </c>
       <c r="C4" t="n">
-        <v>2.8393</v>
+        <v>2.7275</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5413</v>
+        <v>1.476</v>
       </c>
       <c r="E4" t="n">
-        <v>4.7571</v>
+        <v>4.5698</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8104</v>
+        <v>1.7451</v>
       </c>
       <c r="G4" t="n">
-        <v>2.9467</v>
+        <v>2.8247</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8104</v>
+        <v>1.7451</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8104</v>
+        <v>1.7451</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9467</v>
+        <v>2.8247</v>
       </c>
       <c r="K4" t="n">
         <v>92</v>
@@ -621,7 +621,7 @@
         <v>168</v>
       </c>
       <c r="M4" t="n">
-        <v>4.757099999999999</v>
+        <v>4.5698</v>
       </c>
       <c r="N4" t="n">
         <v>260</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.7052</v>
+        <v>4.4847</v>
       </c>
       <c r="C5" t="n">
-        <v>2.8083</v>
+        <v>2.6767</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5177</v>
+        <v>1.4372</v>
       </c>
       <c r="E5" t="n">
-        <v>4.7052</v>
+        <v>4.4847</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7862</v>
+        <v>0.8048</v>
       </c>
       <c r="G5" t="n">
-        <v>3.919</v>
+        <v>3.6799</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7862</v>
+        <v>0.8048</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7862</v>
+        <v>0.8048</v>
       </c>
       <c r="J5" t="n">
-        <v>3.919</v>
+        <v>3.6799</v>
       </c>
       <c r="K5" t="n">
         <v>57</v>
@@ -667,7 +667,7 @@
         <v>184</v>
       </c>
       <c r="M5" t="n">
-        <v>4.7052</v>
+        <v>4.4847</v>
       </c>
       <c r="N5" t="n">
         <v>241</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1952</v>
+        <v>4.1019</v>
       </c>
       <c r="C6" t="n">
-        <v>2.5039</v>
+        <v>2.4482</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2855</v>
+        <v>1.2628</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1952</v>
+        <v>4.1019</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4219</v>
+        <v>1.3723</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7733</v>
+        <v>2.7296</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4219</v>
+        <v>1.3723</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4219</v>
+        <v>1.3723</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7733</v>
+        <v>2.7296</v>
       </c>
       <c r="K6" t="n">
         <v>47</v>
@@ -713,7 +713,7 @@
         <v>209</v>
       </c>
       <c r="M6" t="n">
-        <v>4.1952</v>
+        <v>4.101900000000001</v>
       </c>
       <c r="N6" t="n">
         <v>256</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.8586</v>
+        <v>3.7447</v>
       </c>
       <c r="C7" t="n">
-        <v>2.303</v>
+        <v>2.235</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1323</v>
+        <v>1.1001</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8586</v>
+        <v>3.7447</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3433</v>
+        <v>1.3451</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5153</v>
+        <v>2.3996</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3433</v>
+        <v>1.3451</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3433</v>
+        <v>1.3451</v>
       </c>
       <c r="J7" t="n">
-        <v>2.5153</v>
+        <v>2.3996</v>
       </c>
       <c r="K7" t="n">
         <v>57</v>
@@ -759,7 +759,7 @@
         <v>184</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8586</v>
+        <v>3.7447</v>
       </c>
       <c r="N7" t="n">
         <v>241</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7979</v>
+        <v>3.7334</v>
       </c>
       <c r="C8" t="n">
-        <v>2.2668</v>
+        <v>2.2283</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1047</v>
+        <v>1.095</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7979</v>
+        <v>3.7334</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2936</v>
+        <v>1.2398</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5043</v>
+        <v>2.4936</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2936</v>
+        <v>1.2398</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2936</v>
+        <v>1.2398</v>
       </c>
       <c r="J8" t="n">
-        <v>2.5043</v>
+        <v>2.4936</v>
       </c>
       <c r="K8" t="n">
         <v>47</v>
@@ -805,7 +805,7 @@
         <v>209</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7979</v>
+        <v>3.7334</v>
       </c>
       <c r="N8" t="n">
         <v>256</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.6852</v>
+        <v>3.5926</v>
       </c>
       <c r="C9" t="n">
-        <v>2.1995</v>
+        <v>2.1442</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0534</v>
+        <v>1.0308</v>
       </c>
       <c r="E9" t="n">
-        <v>3.6852</v>
+        <v>3.5926</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9982</v>
+        <v>0.9252</v>
       </c>
       <c r="G9" t="n">
-        <v>2.687</v>
+        <v>2.6674</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9982</v>
+        <v>0.9252</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9982</v>
+        <v>0.9252</v>
       </c>
       <c r="J9" t="n">
-        <v>2.687</v>
+        <v>2.6674</v>
       </c>
       <c r="K9" t="n">
         <v>66</v>
@@ -851,7 +851,7 @@
         <v>130</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6852</v>
+        <v>3.5926</v>
       </c>
       <c r="N9" t="n">
         <v>196</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.5869</v>
+        <v>3.4427</v>
       </c>
       <c r="C10" t="n">
-        <v>2.1408</v>
+        <v>2.0548</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0086</v>
+        <v>0.9625</v>
       </c>
       <c r="E10" t="n">
-        <v>3.5869</v>
+        <v>3.4427</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8236</v>
+        <v>1.8197</v>
       </c>
       <c r="G10" t="n">
-        <v>1.7633</v>
+        <v>1.623</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8236</v>
+        <v>1.8197</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8236</v>
+        <v>1.8197</v>
       </c>
       <c r="J10" t="n">
-        <v>1.7633</v>
+        <v>1.623</v>
       </c>
       <c r="K10" t="n">
         <v>92</v>
@@ -897,7 +897,7 @@
         <v>168</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5869</v>
+        <v>3.4427</v>
       </c>
       <c r="N10" t="n">
         <v>260</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.0171</v>
+        <v>2.9466</v>
       </c>
       <c r="C11" t="n">
-        <v>1.8008</v>
+        <v>1.7587</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7492</v>
+        <v>0.7365</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0171</v>
+        <v>2.9466</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1387</v>
+        <v>1.1094</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8784</v>
+        <v>1.8372</v>
       </c>
       <c r="H11" t="n">
-        <v>1.1387</v>
+        <v>1.1094</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1387</v>
+        <v>1.1094</v>
       </c>
       <c r="J11" t="n">
-        <v>1.8784</v>
+        <v>1.8372</v>
       </c>
       <c r="K11" t="n">
         <v>47</v>
@@ -943,7 +943,7 @@
         <v>209</v>
       </c>
       <c r="M11" t="n">
-        <v>3.0171</v>
+        <v>2.9466</v>
       </c>
       <c r="N11" t="n">
         <v>256</v>
@@ -952,93 +952,93 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Maden</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.9761</v>
+        <v>2.8225</v>
       </c>
       <c r="C12" t="n">
-        <v>1.7763</v>
+        <v>1.6846</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7306</v>
+        <v>0.68</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9761</v>
+        <v>2.8225</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1441</v>
+        <v>0.9478</v>
       </c>
       <c r="G12" t="n">
-        <v>2.832</v>
+        <v>1.8747</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1441</v>
+        <v>0.9478</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1441</v>
+        <v>0.9478</v>
       </c>
       <c r="J12" t="n">
-        <v>2.832</v>
+        <v>1.8747</v>
       </c>
       <c r="K12" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="L12" t="n">
-        <v>184</v>
+        <v>130</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9761</v>
+        <v>2.8225</v>
       </c>
       <c r="N12" t="n">
-        <v>241</v>
+        <v>196</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>Maden</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.8517</v>
+        <v>2.7601</v>
       </c>
       <c r="C13" t="n">
-        <v>1.702</v>
+        <v>1.6474</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.6516</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8517</v>
+        <v>2.7601</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0156</v>
+        <v>0.1296</v>
       </c>
       <c r="G13" t="n">
-        <v>1.8361</v>
+        <v>2.6305</v>
       </c>
       <c r="H13" t="n">
-        <v>1.0156</v>
+        <v>0.1296</v>
       </c>
       <c r="I13" t="n">
-        <v>1.0156</v>
+        <v>0.1296</v>
       </c>
       <c r="J13" t="n">
-        <v>1.8361</v>
+        <v>2.6305</v>
       </c>
       <c r="K13" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="L13" t="n">
-        <v>130</v>
+        <v>184</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8517</v>
+        <v>2.7601</v>
       </c>
       <c r="N13" t="n">
-        <v>196</v>
+        <v>241</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.2459</v>
+        <v>2.1849</v>
       </c>
       <c r="C14" t="n">
-        <v>1.3405</v>
+        <v>1.3041</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3982</v>
+        <v>0.3895</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2459</v>
+        <v>2.1849</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1312</v>
+        <v>1.1303</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1147</v>
+        <v>1.0546</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1312</v>
+        <v>1.1303</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1312</v>
+        <v>1.1303</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1147</v>
+        <v>1.0546</v>
       </c>
       <c r="K14" t="n">
         <v>92</v>
@@ -1081,7 +1081,7 @@
         <v>168</v>
       </c>
       <c r="M14" t="n">
-        <v>2.2459</v>
+        <v>2.1849</v>
       </c>
       <c r="N14" t="n">
         <v>260</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.781</v>
+        <v>1.7824</v>
       </c>
       <c r="C15" t="n">
-        <v>1.063</v>
+        <v>1.0638</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1865</v>
+        <v>0.2062</v>
       </c>
       <c r="E15" t="n">
-        <v>1.781</v>
+        <v>1.7824</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3525</v>
+        <v>1.3393</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4285</v>
+        <v>0.4431</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3525</v>
+        <v>1.3393</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3525</v>
+        <v>1.3393</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4285</v>
+        <v>0.4431</v>
       </c>
       <c r="K15" t="n">
         <v>66</v>
@@ -1127,7 +1127,7 @@
         <v>130</v>
       </c>
       <c r="M15" t="n">
-        <v>1.781</v>
+        <v>1.7824</v>
       </c>
       <c r="N15" t="n">
         <v>196</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.7341</v>
+        <v>1.5442</v>
       </c>
       <c r="C16" t="n">
-        <v>1.035</v>
+        <v>0.9217</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1652</v>
+        <v>0.0977</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7341</v>
+        <v>1.5442</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6642</v>
+        <v>0.6462</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0699</v>
+        <v>0.898</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6642</v>
+        <v>0.6462</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6642</v>
+        <v>0.6462</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0699</v>
+        <v>0.898</v>
       </c>
       <c r="K16" t="n">
         <v>87</v>
@@ -1173,7 +1173,7 @@
         <v>80</v>
       </c>
       <c r="M16" t="n">
-        <v>1.7341</v>
+        <v>1.5442</v>
       </c>
       <c r="N16" t="n">
         <v>167</v>
@@ -1182,369 +1182,369 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.5256</v>
+        <v>1.5324</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9106</v>
+        <v>0.9146</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0703</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5256</v>
+        <v>1.5324</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0158</v>
+        <v>1.9437</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5414</v>
+        <v>-0.4113</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0158</v>
+        <v>1.9437</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0158</v>
+        <v>1.9437</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5414</v>
+        <v>-0.4113</v>
       </c>
       <c r="K17" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="L17" t="n">
-        <v>130</v>
+        <v>45</v>
       </c>
       <c r="M17" t="n">
-        <v>1.5256</v>
+        <v>1.5324</v>
       </c>
       <c r="N17" t="n">
-        <v>196</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.514</v>
+        <v>1.4952</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9036</v>
+        <v>0.8924</v>
       </c>
       <c r="D18" t="n">
-        <v>0.065</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>1.514</v>
+        <v>1.4952</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9593</v>
+        <v>-0.0095</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4453</v>
+        <v>1.5047</v>
       </c>
       <c r="H18" t="n">
-        <v>1.9593</v>
+        <v>-0.0095</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9593</v>
+        <v>-0.0095</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4453</v>
+        <v>1.5047</v>
       </c>
       <c r="K18" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="L18" t="n">
-        <v>45</v>
+        <v>130</v>
       </c>
       <c r="M18" t="n">
-        <v>1.514</v>
+        <v>1.4952</v>
       </c>
       <c r="N18" t="n">
-        <v>98</v>
+        <v>196</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.3496</v>
+        <v>1.33</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8055</v>
+        <v>0.7938</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0098</v>
+        <v>0.0001</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3496</v>
+        <v>1.33</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9213</v>
+        <v>1.6043</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4283</v>
+        <v>-0.2743</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9213</v>
+        <v>1.6043</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9213</v>
+        <v>1.6043</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4283</v>
+        <v>-0.2743</v>
       </c>
       <c r="K19" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="L19" t="n">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="M19" t="n">
-        <v>1.3496</v>
+        <v>1.33</v>
       </c>
       <c r="N19" t="n">
-        <v>167</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.3291</v>
+        <v>1.3169</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7933</v>
+        <v>0.786</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0192</v>
+        <v>-0.0059</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3291</v>
+        <v>1.3169</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6325</v>
+        <v>1.4593</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3034</v>
+        <v>-0.1424</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6325</v>
+        <v>1.4593</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6325</v>
+        <v>1.4593</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3034</v>
+        <v>-0.1424</v>
       </c>
       <c r="K20" t="n">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="L20" t="n">
         <v>45</v>
       </c>
       <c r="M20" t="n">
-        <v>1.3291</v>
+        <v>1.3169</v>
       </c>
       <c r="N20" t="n">
-        <v>98</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.3054</v>
+        <v>1.2711</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7791</v>
+        <v>0.7587</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.03</v>
+        <v>-0.0267</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3054</v>
+        <v>1.2711</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4025</v>
+        <v>0.86</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.09710000000000001</v>
+        <v>0.4111</v>
       </c>
       <c r="H21" t="n">
-        <v>1.4025</v>
+        <v>0.86</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4025</v>
+        <v>0.86</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.09710000000000001</v>
+        <v>0.4111</v>
       </c>
       <c r="K21" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="L21" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="M21" t="n">
-        <v>1.3054</v>
+        <v>1.2711</v>
       </c>
       <c r="N21" t="n">
-        <v>121</v>
+        <v>167</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>oSee</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.1898</v>
+        <v>1.0963</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7101</v>
+        <v>0.6543</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.08260000000000001</v>
+        <v>-0.1064</v>
       </c>
       <c r="E22" t="n">
-        <v>1.1898</v>
+        <v>1.0963</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1898</v>
+        <v>1.7288</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.6325</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1898</v>
+        <v>1.7288</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1898</v>
+        <v>1.7288</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.6325</v>
       </c>
       <c r="K22" t="n">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1898</v>
+        <v>1.0963</v>
       </c>
       <c r="N22" t="n">
-        <v>57</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>oSee</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.1208</v>
+        <v>1.0847</v>
       </c>
       <c r="C23" t="n">
-        <v>0.669</v>
+        <v>0.6474</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.114</v>
+        <v>-0.1117</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1208</v>
+        <v>1.0847</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2806</v>
+        <v>1.0847</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8401999999999999</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2806</v>
+        <v>1.0847</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2806</v>
+        <v>1.0847</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8401999999999999</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="L23" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1208</v>
+        <v>1.0847</v>
       </c>
       <c r="N23" t="n">
-        <v>196</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.03</v>
+        <v>1.0628</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6148</v>
+        <v>0.6343</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1553</v>
+        <v>-0.1216</v>
       </c>
       <c r="E24" t="n">
-        <v>1.03</v>
+        <v>1.0628</v>
       </c>
       <c r="F24" t="n">
-        <v>1.6753</v>
+        <v>0.2761</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.6453</v>
+        <v>0.7867</v>
       </c>
       <c r="H24" t="n">
-        <v>1.6753</v>
+        <v>0.2761</v>
       </c>
       <c r="I24" t="n">
-        <v>1.6753</v>
+        <v>0.2761</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6453</v>
+        <v>0.7867</v>
       </c>
       <c r="K24" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="L24" t="n">
-        <v>45</v>
+        <v>130</v>
       </c>
       <c r="M24" t="n">
-        <v>1.03</v>
+        <v>1.0628</v>
       </c>
       <c r="N24" t="n">
-        <v>121</v>
+        <v>196</v>
       </c>
     </row>
     <row r="25">
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.026</v>
+        <v>0.9227</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.5507</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1571</v>
+        <v>-0.1855</v>
       </c>
       <c r="E25" t="n">
-        <v>1.026</v>
+        <v>0.9227</v>
       </c>
       <c r="F25" t="n">
-        <v>1.5005</v>
+        <v>1.4426</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.4745</v>
+        <v>-0.5199</v>
       </c>
       <c r="H25" t="n">
-        <v>1.5005</v>
+        <v>1.4426</v>
       </c>
       <c r="I25" t="n">
-        <v>1.5005</v>
+        <v>1.4426</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.4745</v>
+        <v>-0.5199</v>
       </c>
       <c r="K25" t="n">
         <v>71</v>
@@ -1587,7 +1587,7 @@
         <v>67</v>
       </c>
       <c r="M25" t="n">
-        <v>1.026</v>
+        <v>0.9227000000000001</v>
       </c>
       <c r="N25" t="n">
         <v>138</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8362000000000001</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4991</v>
+        <v>0.4311</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2435</v>
+        <v>-0.2767</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8362000000000001</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8362000000000001</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8362000000000001</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8362000000000001</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.8362000000000001</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="N26" t="n">
         <v>76</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8349</v>
+        <v>0.7211</v>
       </c>
       <c r="C27" t="n">
-        <v>0.4983</v>
+        <v>0.4304</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2441</v>
+        <v>-0.2773</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8349</v>
+        <v>0.7211</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8349</v>
+        <v>0.7211</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8349</v>
+        <v>0.7211</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8349</v>
+        <v>0.7211</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.8349</v>
+        <v>0.7211</v>
       </c>
       <c r="N27" t="n">
         <v>87</v>
@@ -1688,47 +1688,47 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>nawwk</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.7125</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4846</v>
+        <v>0.4253</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.2546</v>
+        <v>-0.2812</v>
       </c>
       <c r="E28" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.7125</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.7125</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.7125</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.7125</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.7125</v>
       </c>
       <c r="N28" t="n">
-        <v>87</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8036</v>
+        <v>0.6969</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4796</v>
+        <v>0.4159</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.2584</v>
+        <v>-0.2883</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8036</v>
+        <v>0.6969</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8036</v>
+        <v>0.6969</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8036</v>
+        <v>0.6969</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8036</v>
+        <v>0.6969</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.8036</v>
+        <v>0.6969</v>
       </c>
       <c r="N29" t="n">
         <v>92</v>
@@ -1780,139 +1780,139 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>neaLaN</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7521</v>
+        <v>0.679</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4489</v>
+        <v>0.4053</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.2818</v>
+        <v>-0.2965</v>
       </c>
       <c r="E30" t="n">
-        <v>0.7521</v>
+        <v>0.679</v>
       </c>
       <c r="F30" t="n">
-        <v>1.6644</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.9123</v>
+        <v>0.0606</v>
       </c>
       <c r="H30" t="n">
-        <v>1.6644</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>1.6644</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.9123</v>
+        <v>0.0606</v>
       </c>
       <c r="K30" t="n">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="L30" t="n">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="M30" t="n">
-        <v>0.7521000000000001</v>
+        <v>0.6789999999999999</v>
       </c>
       <c r="N30" t="n">
-        <v>138</v>
+        <v>167</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>nawwk</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7183</v>
+        <v>0.6669</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4287</v>
+        <v>0.398</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.2972</v>
+        <v>-0.302</v>
       </c>
       <c r="E31" t="n">
-        <v>0.7183</v>
+        <v>0.6669</v>
       </c>
       <c r="F31" t="n">
-        <v>0.7183</v>
+        <v>0.6669</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.7183</v>
+        <v>0.6669</v>
       </c>
       <c r="I31" t="n">
-        <v>0.7183</v>
+        <v>0.6669</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.7183</v>
+        <v>0.6669</v>
       </c>
       <c r="N31" t="n">
-        <v>71</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>neaLaN</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.68</v>
+        <v>0.6413</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4059</v>
+        <v>0.3828</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.3147</v>
+        <v>-0.3136</v>
       </c>
       <c r="E32" t="n">
-        <v>0.68</v>
+        <v>0.6413</v>
       </c>
       <c r="F32" t="n">
-        <v>0.68</v>
+        <v>1.6222</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.9809</v>
       </c>
       <c r="H32" t="n">
-        <v>0.68</v>
+        <v>1.6222</v>
       </c>
       <c r="I32" t="n">
-        <v>0.68</v>
+        <v>1.6222</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.9809</v>
       </c>
       <c r="K32" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="M32" t="n">
-        <v>0.68</v>
+        <v>0.6413000000000001</v>
       </c>
       <c r="N32" t="n">
-        <v>57</v>
+        <v>138</v>
       </c>
     </row>
     <row r="33">
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6342</v>
+        <v>0.6039</v>
       </c>
       <c r="C33" t="n">
-        <v>0.3785</v>
+        <v>0.3604</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.3355</v>
+        <v>-0.3307</v>
       </c>
       <c r="E33" t="n">
-        <v>0.6342</v>
+        <v>0.6039</v>
       </c>
       <c r="F33" t="n">
-        <v>0.6342</v>
+        <v>0.6039</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.6342</v>
+        <v>0.6039</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6342</v>
+        <v>0.6039</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.6342</v>
+        <v>0.6039</v>
       </c>
       <c r="N33" t="n">
         <v>71</v>
@@ -1964,139 +1964,139 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6198</v>
+        <v>0.5841</v>
       </c>
       <c r="C34" t="n">
-        <v>0.3699</v>
+        <v>0.3486</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.3421</v>
+        <v>-0.3397</v>
       </c>
       <c r="E34" t="n">
-        <v>0.6198</v>
+        <v>0.5841</v>
       </c>
       <c r="F34" t="n">
-        <v>0.5516</v>
+        <v>0.5841</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0682</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5516</v>
+        <v>0.5841</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5516</v>
+        <v>0.5841</v>
       </c>
       <c r="J34" t="n">
-        <v>0.0682</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="L34" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.6198</v>
+        <v>0.5841</v>
       </c>
       <c r="N34" t="n">
-        <v>167</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5704</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3404</v>
+        <v>0.3258</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.3645</v>
+        <v>-0.3571</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5704</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7773</v>
+        <v>0.8976</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.2069</v>
+        <v>-0.3517</v>
       </c>
       <c r="H35" t="n">
-        <v>0.7773</v>
+        <v>0.8976</v>
       </c>
       <c r="I35" t="n">
-        <v>0.7773</v>
+        <v>0.8976</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.2069</v>
+        <v>-0.3517</v>
       </c>
       <c r="K35" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="L35" t="n">
         <v>45</v>
       </c>
       <c r="M35" t="n">
-        <v>0.5704</v>
+        <v>0.5458999999999999</v>
       </c>
       <c r="N35" t="n">
-        <v>121</v>
+        <v>98</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5689</v>
+        <v>0.5187</v>
       </c>
       <c r="C36" t="n">
-        <v>0.3395</v>
+        <v>0.3096</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.3652</v>
+        <v>-0.3695</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5689</v>
+        <v>0.5187</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9506</v>
+        <v>0.7479</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.3817</v>
+        <v>-0.2292</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9506</v>
+        <v>0.7479</v>
       </c>
       <c r="I36" t="n">
-        <v>0.9506</v>
+        <v>0.7479</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.3817</v>
+        <v>-0.2292</v>
       </c>
       <c r="K36" t="n">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="L36" t="n">
         <v>45</v>
       </c>
       <c r="M36" t="n">
-        <v>0.5689</v>
+        <v>0.5187</v>
       </c>
       <c r="N36" t="n">
-        <v>98</v>
+        <v>121</v>
       </c>
     </row>
     <row r="37">
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5677</v>
+        <v>0.5017</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3388</v>
+        <v>0.2994</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.3658</v>
+        <v>-0.3772</v>
       </c>
       <c r="E37" t="n">
-        <v>0.5677</v>
+        <v>0.5017</v>
       </c>
       <c r="F37" t="n">
-        <v>0.5677</v>
+        <v>0.5017</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.5677</v>
+        <v>0.5017</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5677</v>
+        <v>0.5017</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.5677</v>
+        <v>0.5017</v>
       </c>
       <c r="N37" t="n">
         <v>76</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4958</v>
+        <v>0.4098</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2959</v>
+        <v>0.2446</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.3985</v>
+        <v>-0.4191</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4958</v>
+        <v>0.4098</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4958</v>
+        <v>0.4098</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.4958</v>
+        <v>0.4098</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4958</v>
+        <v>0.4098</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.4958</v>
+        <v>0.4098</v>
       </c>
       <c r="N38" t="n">
         <v>71</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.4061</v>
+        <v>0.3658</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2424</v>
+        <v>0.2183</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.4393</v>
+        <v>-0.4391</v>
       </c>
       <c r="E39" t="n">
-        <v>0.4061</v>
+        <v>0.3658</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4061</v>
+        <v>0.3658</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.4061</v>
+        <v>0.3658</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4061</v>
+        <v>0.3658</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.4061</v>
+        <v>0.3658</v>
       </c>
       <c r="N39" t="n">
         <v>53</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.3757</v>
+        <v>0.2966</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2242</v>
+        <v>0.177</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.4532</v>
+        <v>-0.4707</v>
       </c>
       <c r="E40" t="n">
-        <v>0.3757</v>
+        <v>0.2966</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3757</v>
+        <v>0.2966</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.3757</v>
+        <v>0.2966</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3757</v>
+        <v>0.2966</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.3757</v>
+        <v>0.2966</v>
       </c>
       <c r="N40" t="n">
         <v>92</v>
@@ -2286,185 +2286,185 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BOROS</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.3113</v>
+        <v>0.269</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1858</v>
+        <v>0.1606</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.4825</v>
+        <v>-0.4832</v>
       </c>
       <c r="E41" t="n">
-        <v>0.3113</v>
+        <v>0.269</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3113</v>
+        <v>0.269</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.3113</v>
+        <v>0.269</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3113</v>
+        <v>0.269</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.3113</v>
+        <v>0.269</v>
       </c>
       <c r="N41" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>BOROS</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.3101</v>
+        <v>0.2677</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1851</v>
+        <v>0.1598</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.483</v>
+        <v>-0.4838</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3101</v>
+        <v>0.2677</v>
       </c>
       <c r="F42" t="n">
-        <v>0.3101</v>
+        <v>0.2677</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.3101</v>
+        <v>0.2677</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3101</v>
+        <v>0.2677</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.3101</v>
+        <v>0.2677</v>
       </c>
       <c r="N42" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>roeJ</t>
+          <t>KEi</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.2422</v>
+        <v>0.1986</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1446</v>
+        <v>0.1185</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.5139</v>
+        <v>-0.5153</v>
       </c>
       <c r="E43" t="n">
-        <v>0.2422</v>
+        <v>0.1986</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2422</v>
+        <v>0.1986</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2422</v>
+        <v>0.1986</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2422</v>
+        <v>0.1986</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.2422</v>
+        <v>0.1986</v>
       </c>
       <c r="N43" t="n">
-        <v>53</v>
+        <v>92</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>KEi</t>
+          <t>roeJ</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2315</v>
+        <v>0.1873</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1382</v>
+        <v>0.1118</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.5188</v>
+        <v>-0.5205</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2315</v>
+        <v>0.1873</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2315</v>
+        <v>0.1873</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2315</v>
+        <v>0.1873</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2315</v>
+        <v>0.1873</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>92</v>
+        <v>53</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.2315</v>
+        <v>0.1873</v>
       </c>
       <c r="N44" t="n">
-        <v>92</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45">
@@ -2474,28 +2474,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.2258</v>
+        <v>0.187</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1348</v>
+        <v>0.1116</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.5214</v>
+        <v>-0.5206</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2258</v>
+        <v>0.187</v>
       </c>
       <c r="F45" t="n">
-        <v>0.2258</v>
+        <v>0.187</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2258</v>
+        <v>0.187</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2258</v>
+        <v>0.187</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.2258</v>
+        <v>0.187</v>
       </c>
       <c r="N45" t="n">
         <v>66</v>
@@ -2520,31 +2520,31 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.1305</v>
+        <v>0.1066</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0779</v>
+        <v>0.0636</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.5648</v>
+        <v>-0.5572</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1305</v>
+        <v>0.1066</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1479</v>
+        <v>0.1561</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.0174</v>
+        <v>-0.0495</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1479</v>
+        <v>0.1561</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1479</v>
+        <v>0.1561</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.0174</v>
+        <v>-0.0495</v>
       </c>
       <c r="K46" t="n">
         <v>76</v>
@@ -2553,7 +2553,7 @@
         <v>45</v>
       </c>
       <c r="M46" t="n">
-        <v>0.1305</v>
+        <v>0.1066</v>
       </c>
       <c r="N46" t="n">
         <v>121</v>
@@ -2566,28 +2566,28 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.0707</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0554</v>
+        <v>0.0422</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.582</v>
+        <v>-0.5736</v>
       </c>
       <c r="E47" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.0707</v>
       </c>
       <c r="F47" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.0707</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.0707</v>
       </c>
       <c r="I47" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.0707</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.0707</v>
       </c>
       <c r="N47" t="n">
         <v>92</v>
@@ -2612,28 +2612,28 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.0751</v>
+        <v>0.0292</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0448</v>
+        <v>0.0174</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.59</v>
+        <v>-0.5925</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0751</v>
+        <v>0.0292</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0751</v>
+        <v>0.0292</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0751</v>
+        <v>0.0292</v>
       </c>
       <c r="I48" t="n">
-        <v>0.0751</v>
+        <v>0.0292</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.0751</v>
+        <v>0.0292</v>
       </c>
       <c r="N48" t="n">
         <v>53</v>
@@ -2658,28 +2658,28 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.0272</v>
+        <v>0.0054</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0162</v>
+        <v>0.0032</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.6118</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0272</v>
+        <v>0.0054</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0272</v>
+        <v>0.0054</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0272</v>
+        <v>0.0054</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0272</v>
+        <v>0.0054</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2691,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.0272</v>
+        <v>0.0054</v>
       </c>
       <c r="N49" t="n">
         <v>87</v>
@@ -2700,93 +2700,93 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.1073</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.0386</v>
+        <v>-0.064</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.6536999999999999</v>
+        <v>-0.6546999999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.1073</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.1073</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.1073</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.1073</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.1073</v>
       </c>
       <c r="N50" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.0838</v>
+        <v>-0.1121</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.05</v>
+        <v>-0.0669</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.6624</v>
+        <v>-0.6569</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.0838</v>
+        <v>-0.1121</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.0838</v>
+        <v>-0.1121</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.0838</v>
+        <v>-0.1121</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.0838</v>
+        <v>-0.1121</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.0838</v>
+        <v>-0.1121</v>
       </c>
       <c r="N51" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="52">
@@ -2796,28 +2796,28 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.1318</v>
+        <v>-0.1466</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.6842</v>
+        <v>-0.6726</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.1318</v>
+        <v>-0.1466</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.1318</v>
+        <v>-0.1466</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.1318</v>
+        <v>-0.1466</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.1318</v>
+        <v>-0.1466</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.1318</v>
+        <v>-0.1466</v>
       </c>
       <c r="N52" t="n">
         <v>47</v>
@@ -2842,28 +2842,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.181</v>
+        <v>-0.1608</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.108</v>
+        <v>-0.096</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.7066</v>
+        <v>-0.679</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.181</v>
+        <v>-0.1608</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.181</v>
+        <v>-0.1608</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.181</v>
+        <v>-0.1608</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.181</v>
+        <v>-0.1608</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.181</v>
+        <v>-0.1608</v>
       </c>
       <c r="N53" t="n">
         <v>47</v>
@@ -2884,32 +2884,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.2152</v>
+        <v>-0.202</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.1284</v>
+        <v>-0.1206</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.7222</v>
+        <v>-0.6978</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.2152</v>
+        <v>-0.202</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.2152</v>
+        <v>-0.202</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.2152</v>
+        <v>-0.202</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2152</v>
+        <v>-0.202</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.2152</v>
+        <v>-0.202</v>
       </c>
       <c r="N54" t="n">
         <v>66</v>
@@ -2930,124 +2930,124 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.2157</v>
+        <v>-0.2167</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.1287</v>
+        <v>-0.1293</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.7224</v>
+        <v>-0.7045</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.2157</v>
+        <v>-0.2167</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0605</v>
+        <v>-0.2167</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.2762</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.0605</v>
+        <v>-0.2167</v>
       </c>
       <c r="I55" t="n">
-        <v>0.0605</v>
+        <v>-0.2167</v>
       </c>
       <c r="J55" t="n">
-        <v>-0.2762</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
         <v>87</v>
       </c>
       <c r="L55" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.2157</v>
+        <v>-0.2167</v>
       </c>
       <c r="N55" t="n">
-        <v>167</v>
+        <v>87</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>lauNX</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.2213</v>
+        <v>-0.2212</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.1321</v>
+        <v>-0.132</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.7249</v>
+        <v>-0.7066</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.2213</v>
+        <v>-0.2212</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.2213</v>
+        <v>-0.2212</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.2213</v>
+        <v>-0.2212</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2213</v>
+        <v>-0.2212</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.2213</v>
+        <v>-0.2212</v>
       </c>
       <c r="N56" t="n">
-        <v>87</v>
+        <v>66</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.2348</v>
+        <v>-0.2277</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.1401</v>
+        <v>-0.1359</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.7311</v>
+        <v>-0.7095</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.2348</v>
+        <v>-0.2277</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.2348</v>
+        <v>-0.2277</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.2348</v>
+        <v>-0.2277</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.2348</v>
+        <v>-0.2277</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -3059,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.2348</v>
+        <v>-0.2277</v>
       </c>
       <c r="N57" t="n">
         <v>66</v>
@@ -3068,139 +3068,139 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>lauNX</t>
+          <t>dexter</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.2358</v>
+        <v>-0.2443</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.1407</v>
+        <v>-0.1458</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.7315</v>
+        <v>-0.7171</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.2358</v>
+        <v>-0.2443</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.2358</v>
+        <v>-0.2443</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.2358</v>
+        <v>-0.2443</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.2358</v>
+        <v>-0.2443</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.2358</v>
+        <v>-0.2443</v>
       </c>
       <c r="N58" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>dexter</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.2766</v>
+        <v>-0.2631</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.1651</v>
+        <v>-0.157</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.7501</v>
+        <v>-0.7256</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.2766</v>
+        <v>-0.2631</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.2766</v>
+        <v>0.0562</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>-0.3193</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.2766</v>
+        <v>0.0562</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2766</v>
+        <v>0.0562</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>-0.3193</v>
       </c>
       <c r="K59" t="n">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.2766</v>
+        <v>-0.2631</v>
       </c>
       <c r="N59" t="n">
-        <v>53</v>
+        <v>167</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>acoR</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.2949</v>
+        <v>-0.3597</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.176</v>
+        <v>-0.2147</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.7584</v>
+        <v>-0.7696</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.2949</v>
+        <v>-0.3597</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.3081</v>
+        <v>-0.3597</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0132</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.3081</v>
+        <v>-0.3597</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3081</v>
+        <v>-0.3597</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0132</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="L60" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.2949</v>
+        <v>-0.3597</v>
       </c>
       <c r="N60" t="n">
-        <v>138</v>
+        <v>87</v>
       </c>
     </row>
     <row r="61">
@@ -3210,31 +3210,31 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.3413</v>
+        <v>-0.3655</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.2037</v>
+        <v>-0.2181</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7796</v>
+        <v>-0.7723</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.3413</v>
+        <v>-0.3655</v>
       </c>
       <c r="F61" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.0434</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.4225</v>
+        <v>-0.4089</v>
       </c>
       <c r="H61" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.0434</v>
       </c>
       <c r="I61" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.0434</v>
       </c>
       <c r="J61" t="n">
-        <v>-0.4225</v>
+        <v>-0.4089</v>
       </c>
       <c r="K61" t="n">
         <v>87</v>
@@ -3243,7 +3243,7 @@
         <v>80</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.3413</v>
+        <v>-0.3655</v>
       </c>
       <c r="N61" t="n">
         <v>167</v>
@@ -3252,35 +3252,35 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>volt</t>
+          <t>acoR</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.3837</v>
+        <v>-0.3663</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.229</v>
+        <v>-0.2186</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7989000000000001</v>
+        <v>-0.7727000000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.3837</v>
+        <v>-0.3663</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.3753</v>
+        <v>-0.3217</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0446</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.3753</v>
+        <v>-0.3217</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.3753</v>
+        <v>-0.3217</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0446</v>
       </c>
       <c r="K62" t="n">
         <v>71</v>
@@ -3289,7 +3289,7 @@
         <v>67</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.3837</v>
+        <v>-0.3663</v>
       </c>
       <c r="N62" t="n">
         <v>138</v>
@@ -3302,28 +3302,28 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.3843</v>
+        <v>-0.3958</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.2294</v>
+        <v>-0.2362</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7991</v>
+        <v>-0.7861</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.3843</v>
+        <v>-0.3958</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.3843</v>
+        <v>-0.3958</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.3843</v>
+        <v>-0.3958</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.3843</v>
+        <v>-0.3958</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -3335,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.3843</v>
+        <v>-0.3958</v>
       </c>
       <c r="N63" t="n">
         <v>76</v>
@@ -3344,170 +3344,170 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.4088</v>
+        <v>-0.4137</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.244</v>
+        <v>-0.2469</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.8103</v>
+        <v>-0.7942</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.4088</v>
+        <v>-0.4137</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.4088</v>
+        <v>-0.4137</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.4088</v>
+        <v>-0.4137</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.4088</v>
+        <v>-0.4137</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.4088</v>
+        <v>-0.4137</v>
       </c>
       <c r="N64" t="n">
-        <v>87</v>
+        <v>71</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>volt</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.42</v>
+        <v>-0.4186</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.2507</v>
+        <v>-0.2498</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8154</v>
+        <v>-0.7965</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.42</v>
+        <v>-0.4186</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.42</v>
+        <v>-0.3925</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>-0.0261</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.42</v>
+        <v>-0.3925</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.42</v>
+        <v>-0.3925</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>-0.0261</v>
       </c>
       <c r="K65" t="n">
         <v>71</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.42</v>
+        <v>-0.4186</v>
       </c>
       <c r="N65" t="n">
-        <v>71</v>
+        <v>138</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.4204</v>
+        <v>-0.4234</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.2509</v>
+        <v>-0.2527</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8156</v>
+        <v>-0.7987</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.4204</v>
+        <v>-0.4234</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.4204</v>
+        <v>0.286</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>-0.7094</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.4204</v>
+        <v>0.286</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4204</v>
+        <v>0.286</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>-0.7094</v>
       </c>
       <c r="K66" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.4204</v>
+        <v>-0.4234000000000001</v>
       </c>
       <c r="N66" t="n">
-        <v>76</v>
+        <v>98</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.4523</v>
+        <v>-0.4268</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.27</v>
+        <v>-0.2547</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8300999999999999</v>
+        <v>-0.8002</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.4523</v>
+        <v>-0.4268</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.4523</v>
+        <v>-0.4268</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.4523</v>
+        <v>-0.4268</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.4523</v>
+        <v>-0.4268</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -3519,7 +3519,7 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.4523</v>
+        <v>-0.4268</v>
       </c>
       <c r="N67" t="n">
         <v>76</v>
@@ -3528,185 +3528,185 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.4575</v>
+        <v>-0.4672</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.2731</v>
+        <v>-0.2788</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8325</v>
+        <v>-0.8186</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.4575</v>
+        <v>-0.4672</v>
       </c>
       <c r="F68" t="n">
-        <v>0.2756</v>
+        <v>-0.4672</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.7331</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>0.2756</v>
+        <v>-0.4672</v>
       </c>
       <c r="I68" t="n">
-        <v>0.2756</v>
+        <v>-0.4672</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.7331</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="L68" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.4575</v>
+        <v>-0.4672</v>
       </c>
       <c r="N68" t="n">
-        <v>98</v>
+        <v>76</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>jL</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.5175999999999999</v>
+        <v>-0.4928</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.3089</v>
+        <v>-0.2941</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8598</v>
+        <v>-0.8303</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.5175999999999999</v>
+        <v>-0.4928</v>
       </c>
       <c r="F69" t="n">
-        <v>0.3787</v>
+        <v>-0.4928</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.8963</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>0.3787</v>
+        <v>-0.4928</v>
       </c>
       <c r="I69" t="n">
-        <v>0.3787</v>
+        <v>-0.4928</v>
       </c>
       <c r="J69" t="n">
-        <v>-0.8963</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="L69" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.5176000000000001</v>
+        <v>-0.4928</v>
       </c>
       <c r="N69" t="n">
-        <v>121</v>
+        <v>71</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>Patsi</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.5285</v>
+        <v>-0.5348000000000001</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.3154</v>
+        <v>-0.3192</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8648</v>
+        <v>-0.8494</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.5285</v>
+        <v>-0.5348000000000001</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.5285</v>
+        <v>-0.5348000000000001</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.5285</v>
+        <v>-0.5348000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.5285</v>
+        <v>-0.5348000000000001</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.5285</v>
+        <v>-0.5348000000000001</v>
       </c>
       <c r="N70" t="n">
-        <v>71</v>
+        <v>57</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Patsi</t>
+          <t>jL</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.5641</v>
+        <v>-0.5642</v>
       </c>
       <c r="C71" t="n">
         <v>-0.3367</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.881</v>
+        <v>-0.8628</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.5641</v>
+        <v>-0.5642</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.5641</v>
+        <v>0.3292</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>-0.8934</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.5641</v>
+        <v>0.3292</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5641</v>
+        <v>0.3292</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>-0.8934</v>
       </c>
       <c r="K71" t="n">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.5641</v>
+        <v>-0.5642</v>
       </c>
       <c r="N71" t="n">
-        <v>57</v>
+        <v>121</v>
       </c>
     </row>
     <row r="72">
@@ -3716,28 +3716,28 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.6299</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.376</v>
+        <v>-0.3565</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9109</v>
+        <v>-0.8779</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.6299</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.6299</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.6299</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.6299</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.6299</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="N72" t="n">
         <v>47</v>
@@ -3762,28 +3762,28 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.6647</v>
+        <v>-0.6054</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.3967</v>
+        <v>-0.3613</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9268</v>
+        <v>-0.8816000000000001</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.6647</v>
+        <v>-0.6054</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.6647</v>
+        <v>-0.6054</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.6647</v>
+        <v>-0.6054</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.6647</v>
+        <v>-0.6054</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -3795,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.6647</v>
+        <v>-0.6054</v>
       </c>
       <c r="N73" t="n">
         <v>92</v>
@@ -3808,28 +3808,28 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.7688</v>
+        <v>-0.7503</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.4589</v>
+        <v>-0.4478</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9742</v>
+        <v>-0.9476</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.7688</v>
+        <v>-0.7503</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.7688</v>
+        <v>-0.7503</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.7688</v>
+        <v>-0.7503</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.7688</v>
+        <v>-0.7503</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -3841,7 +3841,7 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-0.7688</v>
+        <v>-0.7503</v>
       </c>
       <c r="N74" t="n">
         <v>47</v>
@@ -3854,28 +3854,28 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.9172</v>
+        <v>-0.9193</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.5474</v>
+        <v>-0.5487</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0417</v>
+        <v>-1.0246</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.9172</v>
+        <v>-0.9193</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.9172</v>
+        <v>-0.9193</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.9172</v>
+        <v>-0.9193</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.9172</v>
+        <v>-0.9193</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-0.9172</v>
+        <v>-0.9193</v>
       </c>
       <c r="N75" t="n">
         <v>57</v>
@@ -3900,31 +3900,31 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.3163</v>
+        <v>-1.3313</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.7856</v>
+        <v>-0.7946</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.2234</v>
+        <v>-1.2123</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.3163</v>
+        <v>-1.3313</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.8043</v>
+        <v>-0.8528</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.512</v>
+        <v>-0.4785</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.8043</v>
+        <v>-0.8528</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.8043</v>
+        <v>-0.8528</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.512</v>
+        <v>-0.4785</v>
       </c>
       <c r="K76" t="n">
         <v>53</v>
@@ -3933,7 +3933,7 @@
         <v>45</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.3163</v>
+        <v>-1.3313</v>
       </c>
       <c r="N76" t="n">
         <v>98</v>
@@ -3942,93 +3942,93 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>Keoz</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.5998</v>
+        <v>-1.6535</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.9548</v>
+        <v>-0.9869</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.3525</v>
+        <v>-1.359</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.5998</v>
+        <v>-1.6535</v>
       </c>
       <c r="F77" t="n">
-        <v>0.6435999999999999</v>
+        <v>-0.6535</v>
       </c>
       <c r="G77" t="n">
-        <v>-2.2434</v>
+        <v>-1</v>
       </c>
       <c r="H77" t="n">
-        <v>0.6435999999999999</v>
+        <v>-0.6535</v>
       </c>
       <c r="I77" t="n">
-        <v>0.6435999999999999</v>
+        <v>-0.6535</v>
       </c>
       <c r="J77" t="n">
-        <v>-2.2434</v>
+        <v>-1</v>
       </c>
       <c r="K77" t="n">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="L77" t="n">
-        <v>209</v>
+        <v>67</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.5998</v>
+        <v>-1.6535</v>
       </c>
       <c r="N77" t="n">
-        <v>256</v>
+        <v>138</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Keoz</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.7386</v>
+        <v>-1.6556</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.0377</v>
+        <v>-0.9881</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.4156</v>
+        <v>-1.36</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.7386</v>
+        <v>-1.6556</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.7386</v>
+        <v>0.5795</v>
       </c>
       <c r="G78" t="n">
-        <v>-1</v>
+        <v>-2.2351</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.7386</v>
+        <v>0.5795</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.7386</v>
+        <v>0.5795</v>
       </c>
       <c r="J78" t="n">
-        <v>-1</v>
+        <v>-2.2351</v>
       </c>
       <c r="K78" t="n">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="L78" t="n">
-        <v>67</v>
+        <v>209</v>
       </c>
       <c r="M78" t="n">
-        <v>-1.7386</v>
+        <v>-1.6556</v>
       </c>
       <c r="N78" t="n">
-        <v>138</v>
+        <v>256</v>
       </c>
     </row>
     <row r="79">
@@ -4038,31 +4038,31 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.1056</v>
+        <v>-2.0699</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.2567</v>
+        <v>-1.2354</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.5827</v>
+        <v>-1.5487</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.1056</v>
+        <v>-2.0699</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.4258</v>
+        <v>-1.4098</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.6798</v>
+        <v>-0.6601</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.4258</v>
+        <v>-1.4098</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.4258</v>
+        <v>-1.4098</v>
       </c>
       <c r="J79" t="n">
-        <v>-0.6798</v>
+        <v>-0.6601</v>
       </c>
       <c r="K79" t="n">
         <v>92</v>
@@ -4071,7 +4071,7 @@
         <v>168</v>
       </c>
       <c r="M79" t="n">
-        <v>-2.1056</v>
+        <v>-2.0699</v>
       </c>
       <c r="N79" t="n">
         <v>260</v>
@@ -4084,31 +4084,31 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.3979</v>
+        <v>-2.2117</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.4312</v>
+        <v>-1.3201</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.7158</v>
+        <v>-1.6133</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.3979</v>
+        <v>-2.2117</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.5666</v>
+        <v>-0.5262</v>
       </c>
       <c r="G80" t="n">
-        <v>-1.8313</v>
+        <v>-1.6855</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.5666</v>
+        <v>-0.5262</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.5666</v>
+        <v>-0.5262</v>
       </c>
       <c r="J80" t="n">
-        <v>-1.8313</v>
+        <v>-1.6855</v>
       </c>
       <c r="K80" t="n">
         <v>92</v>
@@ -4117,7 +4117,7 @@
         <v>168</v>
       </c>
       <c r="M80" t="n">
-        <v>-2.3979</v>
+        <v>-2.2117</v>
       </c>
       <c r="N80" t="n">
         <v>260</v>
@@ -4130,31 +4130,31 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.5099</v>
+        <v>-2.3032</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.498</v>
+        <v>-1.3747</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.7668</v>
+        <v>-1.655</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.5099</v>
+        <v>-2.3032</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.9746</v>
+        <v>-0.8983</v>
       </c>
       <c r="G81" t="n">
-        <v>-1.5353</v>
+        <v>-1.4049</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.9746</v>
+        <v>-0.8983</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.9746</v>
+        <v>-0.8983</v>
       </c>
       <c r="J81" t="n">
-        <v>-1.5353</v>
+        <v>-1.4049</v>
       </c>
       <c r="K81" t="n">
         <v>57</v>
@@ -4163,7 +4163,7 @@
         <v>184</v>
       </c>
       <c r="M81" t="n">
-        <v>-2.5099</v>
+        <v>-2.3032</v>
       </c>
       <c r="N81" t="n">
         <v>241</v>
@@ -4269,10 +4269,10 @@
         <v>1.62</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7286</v>
+        <v>0.6564</v>
       </c>
       <c r="J2" t="n">
-        <v>16.7578</v>
+        <v>15.0972</v>
       </c>
     </row>
     <row r="3">
@@ -4309,10 +4309,10 @@
         <v>1.43</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5406</v>
+        <v>0.4724</v>
       </c>
       <c r="J3" t="n">
-        <v>12.4338</v>
+        <v>10.8652</v>
       </c>
     </row>
     <row r="4">
@@ -4349,10 +4349,10 @@
         <v>1.34</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4475</v>
+        <v>0.3845</v>
       </c>
       <c r="J4" t="n">
-        <v>10.2925</v>
+        <v>8.843500000000001</v>
       </c>
     </row>
     <row r="5">
@@ -4389,10 +4389,10 @@
         <v>1.14</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2164</v>
+        <v>0.1748</v>
       </c>
       <c r="J5" t="n">
-        <v>4.9772</v>
+        <v>4.0204</v>
       </c>
     </row>
     <row r="6">
@@ -4429,10 +4429,10 @@
         <v>0.97</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.081</v>
+        <v>-0.0673</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.863</v>
+        <v>-1.5479</v>
       </c>
     </row>
     <row r="7">
@@ -4469,10 +4469,10 @@
         <v>1.12</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2885</v>
+        <v>0.2866</v>
       </c>
       <c r="J7" t="n">
-        <v>6.6355</v>
+        <v>6.5918</v>
       </c>
     </row>
     <row r="8">
@@ -4509,10 +4509,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2205</v>
+        <v>-0.2045</v>
       </c>
       <c r="J8" t="n">
-        <v>-5.0715</v>
+        <v>-4.7035</v>
       </c>
     </row>
     <row r="9">
@@ -4549,10 +4549,10 @@
         <v>0.67</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.35</v>
+        <v>-0.3355</v>
       </c>
       <c r="J9" t="n">
-        <v>-8.050000000000001</v>
+        <v>-7.7165</v>
       </c>
     </row>
     <row r="10">
@@ -4589,10 +4589,10 @@
         <v>0.63</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.386</v>
+        <v>-0.3736</v>
       </c>
       <c r="J10" t="n">
-        <v>-8.878</v>
+        <v>-8.5928</v>
       </c>
     </row>
     <row r="11">
@@ -4629,10 +4629,10 @@
         <v>0.55</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.457</v>
+        <v>-0.4507</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.511</v>
+        <v>-10.3661</v>
       </c>
     </row>
     <row r="12">
@@ -4669,10 +4669,10 @@
         <v>1.17</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3792</v>
+        <v>0.3239</v>
       </c>
       <c r="J12" t="n">
-        <v>10.6176</v>
+        <v>9.0692</v>
       </c>
     </row>
     <row r="13">
@@ -4709,10 +4709,10 @@
         <v>1.13</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3073</v>
+        <v>0.2563</v>
       </c>
       <c r="J13" t="n">
-        <v>8.6044</v>
+        <v>7.1764</v>
       </c>
     </row>
     <row r="14">
@@ -4749,10 +4749,10 @@
         <v>1.01</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0425</v>
+        <v>0.029</v>
       </c>
       <c r="J14" t="n">
-        <v>1.19</v>
+        <v>0.8120000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -4789,10 +4789,10 @@
         <v>0.9</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.148</v>
+        <v>-0.1282</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.144</v>
+        <v>-3.5896</v>
       </c>
     </row>
     <row r="16">
@@ -4829,10 +4829,10 @@
         <v>0.85</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2026</v>
+        <v>-0.1819</v>
       </c>
       <c r="J16" t="n">
-        <v>-5.6728</v>
+        <v>-5.0932</v>
       </c>
     </row>
     <row r="17">
@@ -4869,10 +4869,10 @@
         <v>1.35</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8983</v>
+        <v>0.881</v>
       </c>
       <c r="J17" t="n">
-        <v>25.1524</v>
+        <v>24.668</v>
       </c>
     </row>
     <row r="18">
@@ -4909,10 +4909,10 @@
         <v>1.24</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6647</v>
+        <v>0.629</v>
       </c>
       <c r="J18" t="n">
-        <v>18.6116</v>
+        <v>17.612</v>
       </c>
     </row>
     <row r="19">
@@ -4949,10 +4949,10 @@
         <v>1.05</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1936</v>
+        <v>0.1616</v>
       </c>
       <c r="J19" t="n">
-        <v>5.4208</v>
+        <v>4.5248</v>
       </c>
     </row>
     <row r="20">
@@ -4989,10 +4989,10 @@
         <v>0.85</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4775</v>
+        <v>-0.435</v>
       </c>
       <c r="J20" t="n">
-        <v>-13.37</v>
+        <v>-12.18</v>
       </c>
     </row>
     <row r="21">
@@ -5029,10 +5029,10 @@
         <v>0.72</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7745</v>
+        <v>-0.7478</v>
       </c>
       <c r="J21" t="n">
-        <v>-21.686</v>
+        <v>-20.9384</v>
       </c>
     </row>
     <row r="22">
@@ -5069,10 +5069,10 @@
         <v>1.09</v>
       </c>
       <c r="I22" t="n">
-        <v>0.276</v>
+        <v>0.2308</v>
       </c>
       <c r="J22" t="n">
-        <v>6.9</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="23">
@@ -5109,10 +5109,10 @@
         <v>0.98</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0257</v>
+        <v>-0.0185</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6425</v>
+        <v>-0.4625</v>
       </c>
     </row>
     <row r="24">
@@ -5149,10 +5149,10 @@
         <v>0.74</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2936</v>
+        <v>-0.2759</v>
       </c>
       <c r="J24" t="n">
-        <v>-7.34</v>
+        <v>-6.8975</v>
       </c>
     </row>
     <row r="25">
@@ -5189,10 +5189,10 @@
         <v>0.73</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.303</v>
+        <v>-0.2856</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.575</v>
+        <v>-7.14</v>
       </c>
     </row>
     <row r="26">
@@ -5229,10 +5229,10 @@
         <v>0.61</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4123</v>
+        <v>-0.402</v>
       </c>
       <c r="J26" t="n">
-        <v>-10.3075</v>
+        <v>-10.05</v>
       </c>
     </row>
     <row r="27">
@@ -5269,10 +5269,10 @@
         <v>1.56</v>
       </c>
       <c r="I27" t="n">
-        <v>1.2532</v>
+        <v>1.2756</v>
       </c>
       <c r="J27" t="n">
-        <v>31.33</v>
+        <v>31.89</v>
       </c>
     </row>
     <row r="28">
@@ -5309,10 +5309,10 @@
         <v>1.3</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7549</v>
+        <v>0.7275</v>
       </c>
       <c r="J28" t="n">
-        <v>18.8725</v>
+        <v>18.1875</v>
       </c>
     </row>
     <row r="29">
@@ -5349,10 +5349,10 @@
         <v>1.21</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5674</v>
+        <v>0.5331</v>
       </c>
       <c r="J29" t="n">
-        <v>14.185</v>
+        <v>13.3275</v>
       </c>
     </row>
     <row r="30">
@@ -5389,10 +5389,10 @@
         <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0318</v>
+        <v>-0.0262</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.795</v>
+        <v>-0.655</v>
       </c>
     </row>
     <row r="31">
@@ -5429,10 +5429,10 @@
         <v>0.88</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4306</v>
+        <v>-0.3895</v>
       </c>
       <c r="J31" t="n">
-        <v>-10.765</v>
+        <v>-9.737500000000001</v>
       </c>
     </row>
     <row r="32">
@@ -5469,10 +5469,10 @@
         <v>1.38</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8007</v>
+        <v>0.7846</v>
       </c>
       <c r="J32" t="n">
-        <v>22.4196</v>
+        <v>21.9688</v>
       </c>
     </row>
     <row r="33">
@@ -5509,10 +5509,10 @@
         <v>1.25</v>
       </c>
       <c r="I33" t="n">
-        <v>0.604</v>
+        <v>0.592</v>
       </c>
       <c r="J33" t="n">
-        <v>16.912</v>
+        <v>16.576</v>
       </c>
     </row>
     <row r="34">
@@ -5549,10 +5549,10 @@
         <v>1.04</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1489</v>
+        <v>0.1241</v>
       </c>
       <c r="J34" t="n">
-        <v>4.1692</v>
+        <v>3.4748</v>
       </c>
     </row>
     <row r="35">
@@ -5589,10 +5589,10 @@
         <v>1.01</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0376</v>
+        <v>0.0273</v>
       </c>
       <c r="J35" t="n">
-        <v>1.0528</v>
+        <v>0.7644</v>
       </c>
     </row>
     <row r="36">
@@ -5629,10 +5629,10 @@
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.0222</v>
+        <v>-0.0169</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.6216</v>
+        <v>-0.4732</v>
       </c>
     </row>
     <row r="37">
@@ -5669,10 +5669,10 @@
         <v>1.03</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1341</v>
+        <v>0.1036</v>
       </c>
       <c r="J37" t="n">
-        <v>3.7548</v>
+        <v>2.9008</v>
       </c>
     </row>
     <row r="38">
@@ -5709,10 +5709,10 @@
         <v>0.99</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0045</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.2464</v>
+        <v>-0.126</v>
       </c>
     </row>
     <row r="39">
@@ -5749,10 +5749,10 @@
         <v>0.93</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.09810000000000001</v>
+        <v>-0.0843</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.7468</v>
+        <v>-2.3604</v>
       </c>
     </row>
     <row r="40">
@@ -5789,10 +5789,10 @@
         <v>0.64</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3864</v>
+        <v>-0.3738</v>
       </c>
       <c r="J40" t="n">
-        <v>-10.8192</v>
+        <v>-10.4664</v>
       </c>
     </row>
     <row r="41">
@@ -5829,10 +5829,10 @@
         <v>0.6</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4221</v>
+        <v>-0.4127</v>
       </c>
       <c r="J41" t="n">
-        <v>-11.8188</v>
+        <v>-11.5556</v>
       </c>
     </row>
     <row r="42">
@@ -5869,10 +5869,10 @@
         <v>1.12</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2665</v>
+        <v>0.2568</v>
       </c>
       <c r="J42" t="n">
-        <v>6.929</v>
+        <v>6.6768</v>
       </c>
     </row>
     <row r="43">
@@ -5909,10 +5909,10 @@
         <v>1.1</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2347</v>
+        <v>0.2229</v>
       </c>
       <c r="J43" t="n">
-        <v>6.1022</v>
+        <v>5.7954</v>
       </c>
     </row>
     <row r="44">
@@ -5949,10 +5949,10 @@
         <v>0.71</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.3207</v>
+        <v>-0.3041</v>
       </c>
       <c r="J44" t="n">
-        <v>-8.338200000000001</v>
+        <v>-7.9066</v>
       </c>
     </row>
     <row r="45">
@@ -5989,10 +5989,10 @@
         <v>0.64</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3846</v>
+        <v>-0.3718</v>
       </c>
       <c r="J45" t="n">
-        <v>-9.999599999999999</v>
+        <v>-9.6668</v>
       </c>
     </row>
     <row r="46">
@@ -6029,10 +6029,10 @@
         <v>0.54</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4731</v>
+        <v>-0.4691</v>
       </c>
       <c r="J46" t="n">
-        <v>-12.3006</v>
+        <v>-12.1966</v>
       </c>
     </row>
     <row r="47">
@@ -6069,10 +6069,10 @@
         <v>1.64</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6677</v>
+        <v>0.6246</v>
       </c>
       <c r="J47" t="n">
-        <v>17.3602</v>
+        <v>16.2396</v>
       </c>
     </row>
     <row r="48">
@@ -6109,10 +6109,10 @@
         <v>1.4</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4916</v>
+        <v>0.4434</v>
       </c>
       <c r="J48" t="n">
-        <v>12.7816</v>
+        <v>11.5284</v>
       </c>
     </row>
     <row r="49">
@@ -6149,10 +6149,10 @@
         <v>1.29</v>
       </c>
       <c r="I49" t="n">
-        <v>0.395</v>
+        <v>0.3359</v>
       </c>
       <c r="J49" t="n">
-        <v>10.27</v>
+        <v>8.7334</v>
       </c>
     </row>
     <row r="50">
@@ -6189,10 +6189,10 @@
         <v>1.28</v>
       </c>
       <c r="I50" t="n">
-        <v>0.3842</v>
+        <v>0.326</v>
       </c>
       <c r="J50" t="n">
-        <v>9.9892</v>
+        <v>8.476000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -6229,10 +6229,10 @@
         <v>0.87</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2035</v>
+        <v>-0.185</v>
       </c>
       <c r="J51" t="n">
-        <v>-5.291</v>
+        <v>-4.81</v>
       </c>
     </row>
     <row r="52">
@@ -6269,10 +6269,10 @@
         <v>1.31</v>
       </c>
       <c r="I52" t="n">
-        <v>0.7071</v>
+        <v>0.6915</v>
       </c>
       <c r="J52" t="n">
-        <v>24.0414</v>
+        <v>23.511</v>
       </c>
     </row>
     <row r="53">
@@ -6309,10 +6309,10 @@
         <v>1.25</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6132</v>
+        <v>0.5999</v>
       </c>
       <c r="J53" t="n">
-        <v>20.8488</v>
+        <v>20.3966</v>
       </c>
     </row>
     <row r="54">
@@ -6349,10 +6349,10 @@
         <v>1.17</v>
       </c>
       <c r="I54" t="n">
-        <v>0.4809</v>
+        <v>0.4555</v>
       </c>
       <c r="J54" t="n">
-        <v>16.3506</v>
+        <v>15.487</v>
       </c>
     </row>
     <row r="55">
@@ -6389,10 +6389,10 @@
         <v>0.9</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3586</v>
+        <v>-0.316</v>
       </c>
       <c r="J55" t="n">
-        <v>-12.1924</v>
+        <v>-10.744</v>
       </c>
     </row>
     <row r="56">
@@ -6429,10 +6429,10 @@
         <v>0.79</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.6274</v>
+        <v>-0.591</v>
       </c>
       <c r="J56" t="n">
-        <v>-21.3316</v>
+        <v>-20.094</v>
       </c>
     </row>
     <row r="57">
@@ -6469,10 +6469,10 @@
         <v>1.43</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6957</v>
+        <v>0.6627</v>
       </c>
       <c r="J57" t="n">
-        <v>23.6538</v>
+        <v>22.5318</v>
       </c>
     </row>
     <row r="58">
@@ -6509,10 +6509,10 @@
         <v>1.35</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6071</v>
+        <v>0.5785</v>
       </c>
       <c r="J58" t="n">
-        <v>20.6414</v>
+        <v>19.669</v>
       </c>
     </row>
     <row r="59">
@@ -6549,10 +6549,10 @@
         <v>0.82</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2351</v>
+        <v>-0.2148</v>
       </c>
       <c r="J59" t="n">
-        <v>-7.9934</v>
+        <v>-7.3032</v>
       </c>
     </row>
     <row r="60">
@@ -6589,10 +6589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2451</v>
+        <v>-0.2251</v>
       </c>
       <c r="J60" t="n">
-        <v>-8.333399999999999</v>
+        <v>-7.6534</v>
       </c>
     </row>
     <row r="61">
@@ -6629,10 +6629,10 @@
         <v>0.74</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3131</v>
+        <v>-0.2961</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.6454</v>
+        <v>-10.0674</v>
       </c>
     </row>
     <row r="62">
@@ -6669,10 +6669,10 @@
         <v>1.07</v>
       </c>
       <c r="I62" t="n">
-        <v>0.1926</v>
+        <v>0.1524</v>
       </c>
       <c r="J62" t="n">
-        <v>8.0892</v>
+        <v>6.4008</v>
       </c>
     </row>
     <row r="63">
@@ -6709,10 +6709,10 @@
         <v>1.06</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1711</v>
+        <v>0.1336</v>
       </c>
       <c r="J63" t="n">
-        <v>7.1862</v>
+        <v>5.6112</v>
       </c>
     </row>
     <row r="64">
@@ -6749,10 +6749,10 @@
         <v>1.01</v>
       </c>
       <c r="I64" t="n">
-        <v>0.0439</v>
+        <v>0.0296</v>
       </c>
       <c r="J64" t="n">
-        <v>1.8438</v>
+        <v>1.2432</v>
       </c>
     </row>
     <row r="65">
@@ -6789,10 +6789,10 @@
         <v>1</v>
       </c>
       <c r="I65" t="n">
-        <v>0.0004</v>
+        <v>0.0001</v>
       </c>
       <c r="J65" t="n">
-        <v>0.0168</v>
+        <v>0.0042</v>
       </c>
     </row>
     <row r="66">
@@ -6829,10 +6829,10 @@
         <v>0.83</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2217</v>
+        <v>-0.2011</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.311400000000001</v>
+        <v>-8.446199999999999</v>
       </c>
     </row>
     <row r="67">
@@ -6869,10 +6869,10 @@
         <v>1.25</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6206</v>
+        <v>0.6069</v>
       </c>
       <c r="J67" t="n">
-        <v>26.0652</v>
+        <v>25.4898</v>
       </c>
     </row>
     <row r="68">
@@ -6909,10 +6909,10 @@
         <v>1.11</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3574</v>
+        <v>0.3167</v>
       </c>
       <c r="J68" t="n">
-        <v>15.0108</v>
+        <v>13.3014</v>
       </c>
     </row>
     <row r="69">
@@ -6949,10 +6949,10 @@
         <v>1.05</v>
       </c>
       <c r="I69" t="n">
-        <v>0.193</v>
+        <v>0.1614</v>
       </c>
       <c r="J69" t="n">
-        <v>8.106</v>
+        <v>6.7788</v>
       </c>
     </row>
     <row r="70">
@@ -6989,10 +6989,10 @@
         <v>0.99</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.06610000000000001</v>
+        <v>-0.0476</v>
       </c>
       <c r="J70" t="n">
-        <v>-2.7762</v>
+        <v>-1.9992</v>
       </c>
     </row>
     <row r="71">
@@ -7029,10 +7029,10 @@
         <v>0.84</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.503</v>
+        <v>-0.4611</v>
       </c>
       <c r="J71" t="n">
-        <v>-21.126</v>
+        <v>-19.3662</v>
       </c>
     </row>
     <row r="72">
@@ -7069,10 +7069,10 @@
         <v>1.14</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3719</v>
+        <v>0.3212</v>
       </c>
       <c r="J72" t="n">
-        <v>7.8099</v>
+        <v>6.7452</v>
       </c>
     </row>
     <row r="73">
@@ -7109,10 +7109,10 @@
         <v>0.84</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.1983</v>
+        <v>-0.1802</v>
       </c>
       <c r="J73" t="n">
-        <v>-4.1643</v>
+        <v>-3.7842</v>
       </c>
     </row>
     <row r="74">
@@ -7149,10 +7149,10 @@
         <v>0.83</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.2081</v>
+        <v>-0.1897</v>
       </c>
       <c r="J74" t="n">
-        <v>-4.3701</v>
+        <v>-3.9837</v>
       </c>
     </row>
     <row r="75">
@@ -7189,10 +7189,10 @@
         <v>0.79</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2472</v>
+        <v>-0.2285</v>
       </c>
       <c r="J75" t="n">
-        <v>-5.1912</v>
+        <v>-4.7985</v>
       </c>
     </row>
     <row r="76">
@@ -7229,10 +7229,10 @@
         <v>0.61</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4136</v>
+        <v>-0.4034</v>
       </c>
       <c r="J76" t="n">
-        <v>-8.685600000000001</v>
+        <v>-8.471399999999999</v>
       </c>
     </row>
     <row r="77">
@@ -7269,10 +7269,10 @@
         <v>1.83</v>
       </c>
       <c r="I77" t="n">
-        <v>1.3559</v>
+        <v>1.3629</v>
       </c>
       <c r="J77" t="n">
-        <v>28.4739</v>
+        <v>28.6209</v>
       </c>
     </row>
     <row r="78">
@@ -7309,10 +7309,10 @@
         <v>1.59</v>
       </c>
       <c r="I78" t="n">
-        <v>1.0525</v>
+        <v>1.0422</v>
       </c>
       <c r="J78" t="n">
-        <v>22.1025</v>
+        <v>21.8862</v>
       </c>
     </row>
     <row r="79">
@@ -7349,10 +7349,10 @@
         <v>1.16</v>
       </c>
       <c r="I79" t="n">
-        <v>0.4351</v>
+        <v>0.4064</v>
       </c>
       <c r="J79" t="n">
-        <v>9.1371</v>
+        <v>8.5344</v>
       </c>
     </row>
     <row r="80">
@@ -7389,10 +7389,10 @@
         <v>1.05</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1485</v>
+        <v>0.1221</v>
       </c>
       <c r="J80" t="n">
-        <v>3.1185</v>
+        <v>2.5641</v>
       </c>
     </row>
     <row r="81">
@@ -7429,10 +7429,10 @@
         <v>1</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.0547</v>
+        <v>-0.0506</v>
       </c>
       <c r="J81" t="n">
-        <v>-1.1487</v>
+        <v>-1.0626</v>
       </c>
     </row>
     <row r="82">
@@ -7469,10 +7469,10 @@
         <v>1.09</v>
       </c>
       <c r="I82" t="n">
-        <v>0.2089</v>
+        <v>0.1941</v>
       </c>
       <c r="J82" t="n">
-        <v>5.6403</v>
+        <v>5.2407</v>
       </c>
     </row>
     <row r="83">
@@ -7509,10 +7509,10 @@
         <v>0.83</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.2093</v>
+        <v>-0.1904</v>
       </c>
       <c r="J83" t="n">
-        <v>-5.6511</v>
+        <v>-5.1408</v>
       </c>
     </row>
     <row r="84">
@@ -7549,10 +7549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2291</v>
+        <v>-0.2101</v>
       </c>
       <c r="J84" t="n">
-        <v>-6.1857</v>
+        <v>-5.6727</v>
       </c>
     </row>
     <row r="85">
@@ -7589,10 +7589,10 @@
         <v>0.79</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2487</v>
+        <v>-0.2297</v>
       </c>
       <c r="J85" t="n">
-        <v>-6.7149</v>
+        <v>-6.2019</v>
       </c>
     </row>
     <row r="86">
@@ -7629,10 +7629,10 @@
         <v>0.77</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.268</v>
+        <v>-0.2493</v>
       </c>
       <c r="J86" t="n">
-        <v>-7.236</v>
+        <v>-6.7311</v>
       </c>
     </row>
     <row r="87">
@@ -7669,10 +7669,10 @@
         <v>1.46</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5468</v>
+        <v>0.5103</v>
       </c>
       <c r="J87" t="n">
-        <v>14.7636</v>
+        <v>13.7781</v>
       </c>
     </row>
     <row r="88">
@@ -7709,10 +7709,10 @@
         <v>1.44</v>
       </c>
       <c r="I88" t="n">
-        <v>0.5315</v>
+        <v>0.4924</v>
       </c>
       <c r="J88" t="n">
-        <v>14.3505</v>
+        <v>13.2948</v>
       </c>
     </row>
     <row r="89">
@@ -7749,10 +7749,10 @@
         <v>1.27</v>
       </c>
       <c r="I89" t="n">
-        <v>0.3801</v>
+        <v>0.3197</v>
       </c>
       <c r="J89" t="n">
-        <v>10.2627</v>
+        <v>8.6319</v>
       </c>
     </row>
     <row r="90">
@@ -7789,10 +7789,10 @@
         <v>1.03</v>
       </c>
       <c r="I90" t="n">
-        <v>0.0577</v>
+        <v>0.0409</v>
       </c>
       <c r="J90" t="n">
-        <v>1.5579</v>
+        <v>1.1043</v>
       </c>
     </row>
     <row r="91">
@@ -7829,10 +7829,10 @@
         <v>0.77</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2974</v>
+        <v>-0.2812</v>
       </c>
       <c r="J91" t="n">
-        <v>-8.0298</v>
+        <v>-7.5924</v>
       </c>
     </row>
     <row r="92">
@@ -7869,10 +7869,10 @@
         <v>1.41</v>
       </c>
       <c r="I92" t="n">
-        <v>0.8343</v>
+        <v>0.8185</v>
       </c>
       <c r="J92" t="n">
-        <v>20.8575</v>
+        <v>20.4625</v>
       </c>
     </row>
     <row r="93">
@@ -7909,10 +7909,10 @@
         <v>1.4</v>
       </c>
       <c r="I93" t="n">
-        <v>0.82</v>
+        <v>0.8042</v>
       </c>
       <c r="J93" t="n">
-        <v>20.5</v>
+        <v>20.105</v>
       </c>
     </row>
     <row r="94">
@@ -7949,10 +7949,10 @@
         <v>1.3</v>
       </c>
       <c r="I94" t="n">
-        <v>0.6734</v>
+        <v>0.6599</v>
       </c>
       <c r="J94" t="n">
-        <v>16.835</v>
+        <v>16.4975</v>
       </c>
     </row>
     <row r="95">
@@ -7989,10 +7989,10 @@
         <v>0.95</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2344</v>
+        <v>-0.1977</v>
       </c>
       <c r="J95" t="n">
-        <v>-5.86</v>
+        <v>-4.9425</v>
       </c>
     </row>
     <row r="96">
@@ -8029,10 +8029,10 @@
         <v>0.86</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4799</v>
+        <v>-0.4395</v>
       </c>
       <c r="J96" t="n">
-        <v>-11.9975</v>
+        <v>-10.9875</v>
       </c>
     </row>
     <row r="97">
@@ -8069,10 +8069,10 @@
         <v>1.12</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3217</v>
+        <v>0.2714</v>
       </c>
       <c r="J97" t="n">
-        <v>8.0425</v>
+        <v>6.785</v>
       </c>
     </row>
     <row r="98">
@@ -8109,10 +8109,10 @@
         <v>0.95</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.0767</v>
+        <v>-0.0643</v>
       </c>
       <c r="J98" t="n">
-        <v>-1.9175</v>
+        <v>-1.6075</v>
       </c>
     </row>
     <row r="99">
@@ -8149,10 +8149,10 @@
         <v>0.91</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1265</v>
+        <v>-0.1103</v>
       </c>
       <c r="J99" t="n">
-        <v>-3.1625</v>
+        <v>-2.7575</v>
       </c>
     </row>
     <row r="100">
@@ -8189,10 +8189,10 @@
         <v>0.84</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2007</v>
+        <v>-0.1815</v>
       </c>
       <c r="J100" t="n">
-        <v>-5.0175</v>
+        <v>-4.5375</v>
       </c>
     </row>
     <row r="101">
@@ -8229,10 +8229,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4611</v>
+        <v>-0.4562</v>
       </c>
       <c r="J101" t="n">
-        <v>-11.5275</v>
+        <v>-11.405</v>
       </c>
     </row>
     <row r="102">
@@ -8269,10 +8269,10 @@
         <v>1.45</v>
       </c>
       <c r="I102" t="n">
-        <v>0.9127999999999999</v>
+        <v>0.8989</v>
       </c>
       <c r="J102" t="n">
-        <v>25.5584</v>
+        <v>25.1692</v>
       </c>
     </row>
     <row r="103">
@@ -8309,10 +8309,10 @@
         <v>1.1</v>
       </c>
       <c r="I103" t="n">
-        <v>0.325</v>
+        <v>0.2874</v>
       </c>
       <c r="J103" t="n">
-        <v>9.1</v>
+        <v>8.0472</v>
       </c>
     </row>
     <row r="104">
@@ -8349,10 +8349,10 @@
         <v>1.05</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1875</v>
+        <v>0.1584</v>
       </c>
       <c r="J104" t="n">
-        <v>5.25</v>
+        <v>4.4352</v>
       </c>
     </row>
     <row r="105">
@@ -8389,10 +8389,10 @@
         <v>1.01</v>
       </c>
       <c r="I105" t="n">
-        <v>0.0454</v>
+        <v>0.034</v>
       </c>
       <c r="J105" t="n">
-        <v>1.2712</v>
+        <v>0.952</v>
       </c>
     </row>
     <row r="106">
@@ -8429,10 +8429,10 @@
         <v>0.85</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4875</v>
+        <v>-0.4456</v>
       </c>
       <c r="J106" t="n">
-        <v>-13.65</v>
+        <v>-12.4768</v>
       </c>
     </row>
     <row r="107">
@@ -8469,10 +8469,10 @@
         <v>1.16</v>
       </c>
       <c r="I107" t="n">
-        <v>0.3681</v>
+        <v>0.3132</v>
       </c>
       <c r="J107" t="n">
-        <v>10.3068</v>
+        <v>8.769600000000001</v>
       </c>
     </row>
     <row r="108">
@@ -8509,10 +8509,10 @@
         <v>1.04</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1272</v>
+        <v>0.096</v>
       </c>
       <c r="J108" t="n">
-        <v>3.5616</v>
+        <v>2.688</v>
       </c>
     </row>
     <row r="109">
@@ -8549,10 +8549,10 @@
         <v>1.02</v>
       </c>
       <c r="I109" t="n">
-        <v>0.0756</v>
+        <v>0.0538</v>
       </c>
       <c r="J109" t="n">
-        <v>2.1168</v>
+        <v>1.5064</v>
       </c>
     </row>
     <row r="110">
@@ -8589,10 +8589,10 @@
         <v>0.98</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.0418</v>
+        <v>-0.032</v>
       </c>
       <c r="J110" t="n">
-        <v>-1.1704</v>
+        <v>-0.896</v>
       </c>
     </row>
     <row r="111">
@@ -8629,10 +8629,10 @@
         <v>0.71</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3368</v>
+        <v>-0.3211</v>
       </c>
       <c r="J111" t="n">
-        <v>-9.430400000000001</v>
+        <v>-8.9908</v>
       </c>
     </row>
     <row r="112">
@@ -8669,10 +8669,10 @@
         <v>0.84</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.1915</v>
+        <v>-0.1754</v>
       </c>
       <c r="J112" t="n">
-        <v>-4.4045</v>
+        <v>-4.0342</v>
       </c>
     </row>
     <row r="113">
@@ -8709,10 +8709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.2221</v>
+        <v>-0.2058</v>
       </c>
       <c r="J113" t="n">
-        <v>-5.1083</v>
+        <v>-4.7334</v>
       </c>
     </row>
     <row r="114">
@@ -8749,10 +8749,10 @@
         <v>0.74</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2875</v>
+        <v>-0.271</v>
       </c>
       <c r="J114" t="n">
-        <v>-6.6125</v>
+        <v>-6.233</v>
       </c>
     </row>
     <row r="115">
@@ -8789,10 +8789,10 @@
         <v>0.74</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2875</v>
+        <v>-0.271</v>
       </c>
       <c r="J115" t="n">
-        <v>-6.6125</v>
+        <v>-6.233</v>
       </c>
     </row>
     <row r="116">
@@ -8829,10 +8829,10 @@
         <v>0.72</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3059</v>
+        <v>-0.2897</v>
       </c>
       <c r="J116" t="n">
-        <v>-7.0357</v>
+        <v>-6.6631</v>
       </c>
     </row>
     <row r="117">
@@ -8869,10 +8869,10 @@
         <v>1.65</v>
       </c>
       <c r="I117" t="n">
-        <v>1.1307</v>
+        <v>1.1234</v>
       </c>
       <c r="J117" t="n">
-        <v>26.0061</v>
+        <v>25.8382</v>
       </c>
     </row>
     <row r="118">
@@ -8909,10 +8909,10 @@
         <v>1.49</v>
       </c>
       <c r="I118" t="n">
-        <v>0.9212</v>
+        <v>0.9082</v>
       </c>
       <c r="J118" t="n">
-        <v>21.1876</v>
+        <v>20.8886</v>
       </c>
     </row>
     <row r="119">
@@ -8949,10 +8949,10 @@
         <v>1.33</v>
       </c>
       <c r="I119" t="n">
-        <v>0.7015</v>
+        <v>0.6916</v>
       </c>
       <c r="J119" t="n">
-        <v>16.1345</v>
+        <v>15.9068</v>
       </c>
     </row>
     <row r="120">
@@ -8989,10 +8989,10 @@
         <v>1.14</v>
       </c>
       <c r="I120" t="n">
-        <v>0.3909</v>
+        <v>0.359</v>
       </c>
       <c r="J120" t="n">
-        <v>8.9907</v>
+        <v>8.257</v>
       </c>
     </row>
     <row r="121">
@@ -9029,10 +9029,10 @@
         <v>1</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.054</v>
+        <v>-0.0499</v>
       </c>
       <c r="J121" t="n">
-        <v>-1.242</v>
+        <v>-1.1477</v>
       </c>
     </row>
     <row r="122">
@@ -9069,10 +9069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.0813</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="J122" t="n">
-        <v>-1.7886</v>
+        <v>-1.507</v>
       </c>
     </row>
     <row r="123">
@@ -9109,10 +9109,10 @@
         <v>0.93</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.09420000000000001</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="J123" t="n">
-        <v>-2.0724</v>
+        <v>-1.7754</v>
       </c>
     </row>
     <row r="124">
@@ -9149,10 +9149,10 @@
         <v>0.83</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2061</v>
+        <v>-0.1888</v>
       </c>
       <c r="J124" t="n">
-        <v>-4.5342</v>
+        <v>-4.1536</v>
       </c>
     </row>
     <row r="125">
@@ -9189,10 +9189,10 @@
         <v>0.78</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2538</v>
+        <v>-0.2359</v>
       </c>
       <c r="J125" t="n">
-        <v>-5.5836</v>
+        <v>-5.1898</v>
       </c>
     </row>
     <row r="126">
@@ -9229,10 +9229,10 @@
         <v>0.57</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4456</v>
+        <v>-0.4384</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.8032</v>
+        <v>-9.6448</v>
       </c>
     </row>
     <row r="127">
@@ -9269,10 +9269,10 @@
         <v>1.57</v>
       </c>
       <c r="I127" t="n">
-        <v>1.0337</v>
+        <v>1.0224</v>
       </c>
       <c r="J127" t="n">
-        <v>22.7414</v>
+        <v>22.4928</v>
       </c>
     </row>
     <row r="128">
@@ -9309,10 +9309,10 @@
         <v>1.36</v>
       </c>
       <c r="I128" t="n">
-        <v>0.7472</v>
+        <v>0.7346</v>
       </c>
       <c r="J128" t="n">
-        <v>16.4384</v>
+        <v>16.1612</v>
       </c>
     </row>
     <row r="129">
@@ -9349,10 +9349,10 @@
         <v>1.31</v>
       </c>
       <c r="I129" t="n">
-        <v>0.6758</v>
+        <v>0.6655</v>
       </c>
       <c r="J129" t="n">
-        <v>14.8676</v>
+        <v>14.641</v>
       </c>
     </row>
     <row r="130">
@@ -9389,10 +9389,10 @@
         <v>1.25</v>
       </c>
       <c r="I130" t="n">
-        <v>0.5881999999999999</v>
+        <v>0.582</v>
       </c>
       <c r="J130" t="n">
-        <v>12.9404</v>
+        <v>12.804</v>
       </c>
     </row>
     <row r="131">
@@ -9429,10 +9429,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2823</v>
+        <v>-0.2458</v>
       </c>
       <c r="J131" t="n">
-        <v>-6.2106</v>
+        <v>-5.4076</v>
       </c>
     </row>
     <row r="132">
@@ -9469,10 +9469,10 @@
         <v>0.63</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.337</v>
+        <v>-0.3274</v>
       </c>
       <c r="J132" t="n">
-        <v>-6.403</v>
+        <v>-6.2206</v>
       </c>
     </row>
     <row r="133">
@@ -9509,10 +9509,10 @@
         <v>0.59</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.3773</v>
+        <v>-0.3719</v>
       </c>
       <c r="J133" t="n">
-        <v>-7.1687</v>
+        <v>-7.0661</v>
       </c>
     </row>
     <row r="134">
@@ -9549,10 +9549,10 @@
         <v>0.55</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.416</v>
+        <v>-0.4139</v>
       </c>
       <c r="J134" t="n">
-        <v>-7.904</v>
+        <v>-7.8641</v>
       </c>
     </row>
     <row r="135">
@@ -9589,10 +9589,10 @@
         <v>0.43</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.5203</v>
+        <v>-0.5227000000000001</v>
       </c>
       <c r="J135" t="n">
-        <v>-9.8857</v>
+        <v>-9.9313</v>
       </c>
     </row>
     <row r="136">
@@ -9629,10 +9629,10 @@
         <v>0.16</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.7683</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="J136" t="n">
-        <v>-14.5977</v>
+        <v>-15.428</v>
       </c>
     </row>
     <row r="137">
@@ -9669,10 +9669,10 @@
         <v>1.93</v>
       </c>
       <c r="I137" t="n">
-        <v>1.4307</v>
+        <v>1.4426</v>
       </c>
       <c r="J137" t="n">
-        <v>27.1833</v>
+        <v>27.4094</v>
       </c>
     </row>
     <row r="138">
@@ -9709,10 +9709,10 @@
         <v>1.56</v>
       </c>
       <c r="I138" t="n">
-        <v>0.9871</v>
+        <v>0.9813</v>
       </c>
       <c r="J138" t="n">
-        <v>18.7549</v>
+        <v>18.6447</v>
       </c>
     </row>
     <row r="139">
@@ -9749,10 +9749,10 @@
         <v>1.52</v>
       </c>
       <c r="I139" t="n">
-        <v>0.9379</v>
+        <v>0.9318</v>
       </c>
       <c r="J139" t="n">
-        <v>17.8201</v>
+        <v>17.7042</v>
       </c>
     </row>
     <row r="140">
@@ -9789,10 +9789,10 @@
         <v>1.46</v>
       </c>
       <c r="I140" t="n">
-        <v>0.8605</v>
+        <v>0.8545</v>
       </c>
       <c r="J140" t="n">
-        <v>16.3495</v>
+        <v>16.2355</v>
       </c>
     </row>
     <row r="141">
@@ -9829,10 +9829,10 @@
         <v>1.28</v>
       </c>
       <c r="I141" t="n">
-        <v>0.6069</v>
+        <v>0.6042</v>
       </c>
       <c r="J141" t="n">
-        <v>11.5311</v>
+        <v>11.4798</v>
       </c>
     </row>
     <row r="142">
@@ -9869,10 +9869,10 @@
         <v>1.57</v>
       </c>
       <c r="I142" t="n">
-        <v>0.6384</v>
+        <v>0.5986</v>
       </c>
       <c r="J142" t="n">
-        <v>15.96</v>
+        <v>14.965</v>
       </c>
     </row>
     <row r="143">
@@ -9909,10 +9909,10 @@
         <v>1.24</v>
       </c>
       <c r="I143" t="n">
-        <v>0.3521</v>
+        <v>0.2928</v>
       </c>
       <c r="J143" t="n">
-        <v>8.8025</v>
+        <v>7.32</v>
       </c>
     </row>
     <row r="144">
@@ -9949,10 +9949,10 @@
         <v>1.16</v>
       </c>
       <c r="I144" t="n">
-        <v>0.2547</v>
+        <v>0.2056</v>
       </c>
       <c r="J144" t="n">
-        <v>6.3675</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="145">
@@ -9989,10 +9989,10 @@
         <v>1.11</v>
       </c>
       <c r="I145" t="n">
-        <v>0.1898</v>
+        <v>0.1495</v>
       </c>
       <c r="J145" t="n">
-        <v>4.745</v>
+        <v>3.7375</v>
       </c>
     </row>
     <row r="146">
@@ -10029,10 +10029,10 @@
         <v>0.58</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4641</v>
+        <v>-0.4628</v>
       </c>
       <c r="J146" t="n">
-        <v>-11.6025</v>
+        <v>-11.57</v>
       </c>
     </row>
     <row r="147">
@@ -10069,10 +10069,10 @@
         <v>1.56</v>
       </c>
       <c r="I147" t="n">
-        <v>0.6892</v>
+        <v>0.737</v>
       </c>
       <c r="J147" t="n">
-        <v>17.23</v>
+        <v>18.425</v>
       </c>
     </row>
     <row r="148">
@@ -10109,10 +10109,10 @@
         <v>1</v>
       </c>
       <c r="I148" t="n">
-        <v>0.0014</v>
+        <v>0.0007</v>
       </c>
       <c r="J148" t="n">
-        <v>0.035</v>
+        <v>0.0175</v>
       </c>
     </row>
     <row r="149">
@@ -10149,10 +10149,10 @@
         <v>0.91</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1337</v>
+        <v>-0.1149</v>
       </c>
       <c r="J149" t="n">
-        <v>-3.3425</v>
+        <v>-2.8725</v>
       </c>
     </row>
     <row r="150">
@@ -10189,10 +10189,10 @@
         <v>0.83</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2204</v>
+        <v>-0.1999</v>
       </c>
       <c r="J150" t="n">
-        <v>-5.51</v>
+        <v>-4.9975</v>
       </c>
     </row>
     <row r="151">
@@ -10229,10 +10229,10 @@
         <v>0.6</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4356</v>
+        <v>-0.4289</v>
       </c>
       <c r="J151" t="n">
-        <v>-10.89</v>
+        <v>-10.7225</v>
       </c>
     </row>
     <row r="152">
@@ -10269,10 +10269,10 @@
         <v>1.01</v>
       </c>
       <c r="I152" t="n">
-        <v>0.0955</v>
+        <v>0.0772</v>
       </c>
       <c r="J152" t="n">
-        <v>2.1965</v>
+        <v>1.7756</v>
       </c>
     </row>
     <row r="153">
@@ -10309,10 +10309,10 @@
         <v>0.76</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.2695</v>
+        <v>-0.2528</v>
       </c>
       <c r="J153" t="n">
-        <v>-6.1985</v>
+        <v>-5.8144</v>
       </c>
     </row>
     <row r="154">
@@ -10349,10 +10349,10 @@
         <v>0.72</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.3063</v>
+        <v>-0.29</v>
       </c>
       <c r="J154" t="n">
-        <v>-7.0449</v>
+        <v>-6.67</v>
       </c>
     </row>
     <row r="155">
@@ -10389,10 +10389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3338</v>
+        <v>-0.3184</v>
       </c>
       <c r="J155" t="n">
-        <v>-7.6774</v>
+        <v>-7.3232</v>
       </c>
     </row>
     <row r="156">
@@ -10429,10 +10429,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3338</v>
+        <v>-0.3184</v>
       </c>
       <c r="J156" t="n">
-        <v>-7.6774</v>
+        <v>-7.3232</v>
       </c>
     </row>
     <row r="157">
@@ -10469,10 +10469,10 @@
         <v>1.66</v>
       </c>
       <c r="I157" t="n">
-        <v>1.1459</v>
+        <v>1.1393</v>
       </c>
       <c r="J157" t="n">
-        <v>26.3557</v>
+        <v>26.2039</v>
       </c>
     </row>
     <row r="158">
@@ -10509,10 +10509,10 @@
         <v>1.36</v>
       </c>
       <c r="I158" t="n">
-        <v>0.7446</v>
+        <v>0.7328</v>
       </c>
       <c r="J158" t="n">
-        <v>17.1258</v>
+        <v>16.8544</v>
       </c>
     </row>
     <row r="159">
@@ -10549,10 +10549,10 @@
         <v>1.34</v>
       </c>
       <c r="I159" t="n">
-        <v>0.7165</v>
+        <v>0.7056</v>
       </c>
       <c r="J159" t="n">
-        <v>16.4795</v>
+        <v>16.2288</v>
       </c>
     </row>
     <row r="160">
@@ -10589,10 +10589,10 @@
         <v>1.12</v>
       </c>
       <c r="I160" t="n">
-        <v>0.3436</v>
+        <v>0.3116</v>
       </c>
       <c r="J160" t="n">
-        <v>7.9028</v>
+        <v>7.1668</v>
       </c>
     </row>
     <row r="161">
@@ -10629,10 +10629,10 @@
         <v>1.07</v>
       </c>
       <c r="I161" t="n">
-        <v>0.2104</v>
+        <v>0.1812</v>
       </c>
       <c r="J161" t="n">
-        <v>4.8392</v>
+        <v>4.1676</v>
       </c>
     </row>
     <row r="162">
@@ -10669,10 +10669,10 @@
         <v>1.9</v>
       </c>
       <c r="I162" t="n">
-        <v>1.4042</v>
+        <v>1.4139</v>
       </c>
       <c r="J162" t="n">
-        <v>25.2756</v>
+        <v>25.4502</v>
       </c>
     </row>
     <row r="163">
@@ -10709,10 +10709,10 @@
         <v>1.61</v>
       </c>
       <c r="I163" t="n">
-        <v>1.0533</v>
+        <v>1.0467</v>
       </c>
       <c r="J163" t="n">
-        <v>18.9594</v>
+        <v>18.8406</v>
       </c>
     </row>
     <row r="164">
@@ -10749,10 +10749,10 @@
         <v>1.52</v>
       </c>
       <c r="I164" t="n">
-        <v>0.9406</v>
+        <v>0.9329</v>
       </c>
       <c r="J164" t="n">
-        <v>16.9308</v>
+        <v>16.7922</v>
       </c>
     </row>
     <row r="165">
@@ -10789,10 +10789,10 @@
         <v>1.49</v>
       </c>
       <c r="I165" t="n">
-        <v>0.9032</v>
+        <v>0.8955</v>
       </c>
       <c r="J165" t="n">
-        <v>16.2576</v>
+        <v>16.119</v>
       </c>
     </row>
     <row r="166">
@@ -10829,10 +10829,10 @@
         <v>0.98</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.1812</v>
+        <v>-0.1607</v>
       </c>
       <c r="J166" t="n">
-        <v>-3.2616</v>
+        <v>-2.8926</v>
       </c>
     </row>
     <row r="167">
@@ -10869,10 +10869,10 @@
         <v>0.65</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.3341</v>
+        <v>-0.3252</v>
       </c>
       <c r="J167" t="n">
-        <v>-6.0138</v>
+        <v>-5.8536</v>
       </c>
     </row>
     <row r="168">
@@ -10909,10 +10909,10 @@
         <v>0.59</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.3916</v>
+        <v>-0.3866</v>
       </c>
       <c r="J168" t="n">
-        <v>-7.0488</v>
+        <v>-6.9588</v>
       </c>
     </row>
     <row r="169">
@@ -10949,10 +10949,10 @@
         <v>0.59</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.3916</v>
+        <v>-0.3866</v>
       </c>
       <c r="J169" t="n">
-        <v>-7.0488</v>
+        <v>-6.9588</v>
       </c>
     </row>
     <row r="170">
@@ -10989,10 +10989,10 @@
         <v>0.41</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.5477</v>
+        <v>-0.5513</v>
       </c>
       <c r="J170" t="n">
-        <v>-9.858599999999999</v>
+        <v>-9.923400000000001</v>
       </c>
     </row>
     <row r="171">
@@ -11029,10 +11029,10 @@
         <v>0.39</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5655</v>
+        <v>-0.5713</v>
       </c>
       <c r="J171" t="n">
-        <v>-10.179</v>
+        <v>-10.2834</v>
       </c>
     </row>
     <row r="172">
@@ -11069,10 +11069,10 @@
         <v>1.44</v>
       </c>
       <c r="I172" t="n">
-        <v>0.8995</v>
+        <v>0.8852</v>
       </c>
       <c r="J172" t="n">
-        <v>24.2865</v>
+        <v>23.9004</v>
       </c>
     </row>
     <row r="173">
@@ -11109,10 +11109,10 @@
         <v>1.21</v>
       </c>
       <c r="I173" t="n">
-        <v>0.5475</v>
+        <v>0.5367</v>
       </c>
       <c r="J173" t="n">
-        <v>14.7825</v>
+        <v>14.4909</v>
       </c>
     </row>
     <row r="174">
@@ -11149,10 +11149,10 @@
         <v>1.2</v>
       </c>
       <c r="I174" t="n">
-        <v>0.531</v>
+        <v>0.5189</v>
       </c>
       <c r="J174" t="n">
-        <v>14.337</v>
+        <v>14.0103</v>
       </c>
     </row>
     <row r="175">
@@ -11189,10 +11189,10 @@
         <v>1.06</v>
       </c>
       <c r="I175" t="n">
-        <v>0.2179</v>
+        <v>0.1862</v>
       </c>
       <c r="J175" t="n">
-        <v>5.8833</v>
+        <v>5.0274</v>
       </c>
     </row>
     <row r="176">
@@ -11229,10 +11229,10 @@
         <v>0.53</v>
       </c>
       <c r="I176" t="n">
-        <v>-1.1722</v>
+        <v>-1.1951</v>
       </c>
       <c r="J176" t="n">
-        <v>-31.6494</v>
+        <v>-32.2677</v>
       </c>
     </row>
     <row r="177">
@@ -11269,10 +11269,10 @@
         <v>1.29</v>
       </c>
       <c r="I177" t="n">
-        <v>0.5481</v>
+        <v>0.5218</v>
       </c>
       <c r="J177" t="n">
-        <v>14.7987</v>
+        <v>14.0886</v>
       </c>
     </row>
     <row r="178">
@@ -11309,10 +11309,10 @@
         <v>1.12</v>
       </c>
       <c r="I178" t="n">
-        <v>0.2945</v>
+        <v>0.2442</v>
       </c>
       <c r="J178" t="n">
-        <v>7.9515</v>
+        <v>6.5934</v>
       </c>
     </row>
     <row r="179">
@@ -11349,10 +11349,10 @@
         <v>1.04</v>
       </c>
       <c r="I179" t="n">
-        <v>0.1272</v>
+        <v>0.096</v>
       </c>
       <c r="J179" t="n">
-        <v>3.4344</v>
+        <v>2.592</v>
       </c>
     </row>
     <row r="180">
@@ -11389,10 +11389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.09760000000000001</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="J180" t="n">
-        <v>-2.6352</v>
+        <v>-2.1924</v>
       </c>
     </row>
     <row r="181">
@@ -11429,10 +11429,10 @@
         <v>0.52</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.5047</v>
+        <v>-0.5068</v>
       </c>
       <c r="J181" t="n">
-        <v>-13.6269</v>
+        <v>-13.6836</v>
       </c>
     </row>
     <row r="182">
@@ -11469,10 +11469,10 @@
         <v>1.39</v>
       </c>
       <c r="I182" t="n">
-        <v>0.5191</v>
+        <v>0.45</v>
       </c>
       <c r="J182" t="n">
-        <v>14.0157</v>
+        <v>12.15</v>
       </c>
     </row>
     <row r="183">
@@ -11509,10 +11509,10 @@
         <v>1.23</v>
       </c>
       <c r="I183" t="n">
-        <v>0.3392</v>
+        <v>0.2812</v>
       </c>
       <c r="J183" t="n">
-        <v>9.1584</v>
+        <v>7.5924</v>
       </c>
     </row>
     <row r="184">
@@ -11549,10 +11549,10 @@
         <v>1.16</v>
       </c>
       <c r="I184" t="n">
-        <v>0.254</v>
+        <v>0.2053</v>
       </c>
       <c r="J184" t="n">
-        <v>6.858</v>
+        <v>5.5431</v>
       </c>
     </row>
     <row r="185">
@@ -11589,10 +11589,10 @@
         <v>1.08</v>
       </c>
       <c r="I185" t="n">
-        <v>0.146</v>
+        <v>0.1127</v>
       </c>
       <c r="J185" t="n">
-        <v>3.942</v>
+        <v>3.0429</v>
       </c>
     </row>
     <row r="186">
@@ -11629,10 +11629,10 @@
         <v>0.85</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2135</v>
+        <v>-0.1935</v>
       </c>
       <c r="J186" t="n">
-        <v>-5.7645</v>
+        <v>-5.2245</v>
       </c>
     </row>
     <row r="187">
@@ -11669,10 +11669,10 @@
         <v>1.16</v>
       </c>
       <c r="I187" t="n">
-        <v>0.2986</v>
+        <v>0.287</v>
       </c>
       <c r="J187" t="n">
-        <v>8.062200000000001</v>
+        <v>7.749</v>
       </c>
     </row>
     <row r="188">
@@ -11709,10 +11709,10 @@
         <v>1.08</v>
       </c>
       <c r="I188" t="n">
-        <v>0.1773</v>
+        <v>0.16</v>
       </c>
       <c r="J188" t="n">
-        <v>4.7871</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="189">
@@ -11749,10 +11749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.0946</v>
+        <v>-0.0795</v>
       </c>
       <c r="J189" t="n">
-        <v>-2.5542</v>
+        <v>-2.1465</v>
       </c>
     </row>
     <row r="190">
@@ -11789,10 +11789,10 @@
         <v>0.79</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2557</v>
+        <v>-0.236</v>
       </c>
       <c r="J190" t="n">
-        <v>-6.9039</v>
+        <v>-6.372</v>
       </c>
     </row>
     <row r="191">
@@ -11829,10 +11829,10 @@
         <v>0.68</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3595</v>
+        <v>-0.3452</v>
       </c>
       <c r="J191" t="n">
-        <v>-9.7065</v>
+        <v>-9.320399999999999</v>
       </c>
     </row>
     <row r="192">
@@ -11869,10 +11869,10 @@
         <v>1.25</v>
       </c>
       <c r="I192" t="n">
-        <v>0.5083</v>
+        <v>0.449</v>
       </c>
       <c r="J192" t="n">
-        <v>15.249</v>
+        <v>13.47</v>
       </c>
     </row>
     <row r="193">
@@ -11909,10 +11909,10 @@
         <v>1.07</v>
       </c>
       <c r="I193" t="n">
-        <v>0.1865</v>
+        <v>0.1482</v>
       </c>
       <c r="J193" t="n">
-        <v>5.595</v>
+        <v>4.446</v>
       </c>
     </row>
     <row r="194">
@@ -11949,10 +11949,10 @@
         <v>0.98</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.0452</v>
+        <v>-0.0341</v>
       </c>
       <c r="J194" t="n">
-        <v>-1.356</v>
+        <v>-1.023</v>
       </c>
     </row>
     <row r="195">
@@ -11989,10 +11989,10 @@
         <v>0.95</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.08890000000000001</v>
+        <v>-0.0726</v>
       </c>
       <c r="J195" t="n">
-        <v>-2.667</v>
+        <v>-2.178</v>
       </c>
     </row>
     <row r="196">
@@ -12029,10 +12029,10 @@
         <v>0.93</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.1145</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="J196" t="n">
-        <v>-3.435</v>
+        <v>-2.886</v>
       </c>
     </row>
     <row r="197">
@@ -12069,10 +12069,10 @@
         <v>1.16</v>
       </c>
       <c r="I197" t="n">
-        <v>0.4926</v>
+        <v>0.4503</v>
       </c>
       <c r="J197" t="n">
-        <v>14.778</v>
+        <v>13.509</v>
       </c>
     </row>
     <row r="198">
@@ -12109,10 +12109,10 @@
         <v>1.04</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1684</v>
+        <v>0.137</v>
       </c>
       <c r="J198" t="n">
-        <v>5.052</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="199">
@@ -12149,10 +12149,10 @@
         <v>0.97</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1357</v>
+        <v>-0.1078</v>
       </c>
       <c r="J199" t="n">
-        <v>-4.071</v>
+        <v>-3.234</v>
       </c>
     </row>
     <row r="200">
@@ -12189,10 +12189,10 @@
         <v>0.93</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2599</v>
+        <v>-0.2213</v>
       </c>
       <c r="J200" t="n">
-        <v>-7.797</v>
+        <v>-6.639</v>
       </c>
     </row>
     <row r="201">
@@ -12229,10 +12229,10 @@
         <v>0.91</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3155</v>
+        <v>-0.2744</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.465</v>
+        <v>-8.231999999999999</v>
       </c>
     </row>
     <row r="202">
@@ -12269,10 +12269,10 @@
         <v>1.15</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3715</v>
+        <v>0.318</v>
       </c>
       <c r="J202" t="n">
-        <v>11.145</v>
+        <v>9.539999999999999</v>
       </c>
     </row>
     <row r="203">
@@ -12309,10 +12309,10 @@
         <v>0.89</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.1501</v>
+        <v>-0.1321</v>
       </c>
       <c r="J203" t="n">
-        <v>-4.503</v>
+        <v>-3.963</v>
       </c>
     </row>
     <row r="204">
@@ -12349,10 +12349,10 @@
         <v>0.85</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1925</v>
+        <v>-0.1729</v>
       </c>
       <c r="J204" t="n">
-        <v>-5.775</v>
+        <v>-5.187</v>
       </c>
     </row>
     <row r="205">
@@ -12389,10 +12389,10 @@
         <v>0.82</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2231</v>
+        <v>-0.2032</v>
       </c>
       <c r="J205" t="n">
-        <v>-6.693</v>
+        <v>-6.096</v>
       </c>
     </row>
     <row r="206">
@@ -12429,10 +12429,10 @@
         <v>0.79</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.2528</v>
+        <v>-0.2332</v>
       </c>
       <c r="J206" t="n">
-        <v>-7.584</v>
+        <v>-6.996</v>
       </c>
     </row>
     <row r="207">
@@ -12469,10 +12469,10 @@
         <v>1.55</v>
       </c>
       <c r="I207" t="n">
-        <v>1.171</v>
+        <v>1.1849</v>
       </c>
       <c r="J207" t="n">
-        <v>35.13</v>
+        <v>35.547</v>
       </c>
     </row>
     <row r="208">
@@ -12509,10 +12509,10 @@
         <v>1.19</v>
       </c>
       <c r="I208" t="n">
-        <v>0.5233</v>
+        <v>0.4892</v>
       </c>
       <c r="J208" t="n">
-        <v>15.699</v>
+        <v>14.676</v>
       </c>
     </row>
     <row r="209">
@@ -12549,10 +12549,10 @@
         <v>1.18</v>
       </c>
       <c r="I209" t="n">
-        <v>0.5013</v>
+        <v>0.467</v>
       </c>
       <c r="J209" t="n">
-        <v>15.039</v>
+        <v>14.01</v>
       </c>
     </row>
     <row r="210">
@@ -12589,10 +12589,10 @@
         <v>1.06</v>
       </c>
       <c r="I210" t="n">
-        <v>0.1987</v>
+        <v>0.1706</v>
       </c>
       <c r="J210" t="n">
-        <v>5.961</v>
+        <v>5.118</v>
       </c>
     </row>
     <row r="211">
@@ -12629,10 +12629,10 @@
         <v>1.05</v>
       </c>
       <c r="I211" t="n">
-        <v>0.1685</v>
+        <v>0.1424</v>
       </c>
       <c r="J211" t="n">
-        <v>5.055</v>
+        <v>4.272</v>
       </c>
     </row>
     <row r="212">
@@ -12669,10 +12669,10 @@
         <v>1.29</v>
       </c>
       <c r="I212" t="n">
-        <v>0.4148</v>
+        <v>0.3505</v>
       </c>
       <c r="J212" t="n">
-        <v>14.9328</v>
+        <v>12.618</v>
       </c>
     </row>
     <row r="213">
@@ -12709,10 +12709,10 @@
         <v>1.19</v>
       </c>
       <c r="I213" t="n">
-        <v>0.2956</v>
+        <v>0.2411</v>
       </c>
       <c r="J213" t="n">
-        <v>10.6416</v>
+        <v>8.679600000000001</v>
       </c>
     </row>
     <row r="214">
@@ -12749,10 +12749,10 @@
         <v>1.16</v>
       </c>
       <c r="I214" t="n">
-        <v>0.2578</v>
+        <v>0.2075</v>
       </c>
       <c r="J214" t="n">
-        <v>9.280799999999999</v>
+        <v>7.47</v>
       </c>
     </row>
     <row r="215">
@@ -12789,10 +12789,10 @@
         <v>0.98</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.05</v>
+        <v>-0.0381</v>
       </c>
       <c r="J215" t="n">
-        <v>-1.8</v>
+        <v>-1.3716</v>
       </c>
     </row>
     <row r="216">
@@ -12829,10 +12829,10 @@
         <v>0.87</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.1886</v>
+        <v>-0.1682</v>
       </c>
       <c r="J216" t="n">
-        <v>-6.7896</v>
+        <v>-6.0552</v>
       </c>
     </row>
     <row r="217">
@@ -12869,10 +12869,10 @@
         <v>1.2</v>
       </c>
       <c r="I217" t="n">
-        <v>0.3412</v>
+        <v>0.3324</v>
       </c>
       <c r="J217" t="n">
-        <v>12.2832</v>
+        <v>11.9664</v>
       </c>
     </row>
     <row r="218">
@@ -12909,10 +12909,10 @@
         <v>1.07</v>
       </c>
       <c r="I218" t="n">
-        <v>0.1511</v>
+        <v>0.1342</v>
       </c>
       <c r="J218" t="n">
-        <v>5.4396</v>
+        <v>4.8312</v>
       </c>
     </row>
     <row r="219">
@@ -12949,10 +12949,10 @@
         <v>0.97</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.0577</v>
+        <v>-0.0453</v>
       </c>
       <c r="J219" t="n">
-        <v>-2.0772</v>
+        <v>-1.6308</v>
       </c>
     </row>
     <row r="220">
@@ -12989,10 +12989,10 @@
         <v>0.86</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1902</v>
+        <v>-0.1696</v>
       </c>
       <c r="J220" t="n">
-        <v>-6.8472</v>
+        <v>-6.1056</v>
       </c>
     </row>
     <row r="221">
@@ -13029,10 +13029,10 @@
         <v>0.86</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.1902</v>
+        <v>-0.1696</v>
       </c>
       <c r="J221" t="n">
-        <v>-6.8472</v>
+        <v>-6.1056</v>
       </c>
     </row>
     <row r="222">
@@ -13069,10 +13069,10 @@
         <v>1.28</v>
       </c>
       <c r="I222" t="n">
-        <v>0.5772</v>
+        <v>0.5193</v>
       </c>
       <c r="J222" t="n">
-        <v>16.1616</v>
+        <v>14.5404</v>
       </c>
     </row>
     <row r="223">
@@ -13109,10 +13109,10 @@
         <v>1.06</v>
       </c>
       <c r="I223" t="n">
-        <v>0.177</v>
+        <v>0.1383</v>
       </c>
       <c r="J223" t="n">
-        <v>4.956</v>
+        <v>3.8724</v>
       </c>
     </row>
     <row r="224">
@@ -13149,10 +13149,10 @@
         <v>0.93</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1084</v>
+        <v>-0.0915</v>
       </c>
       <c r="J224" t="n">
-        <v>-3.0352</v>
+        <v>-2.562</v>
       </c>
     </row>
     <row r="225">
@@ -13189,10 +13189,10 @@
         <v>0.86</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1873</v>
+        <v>-0.167</v>
       </c>
       <c r="J225" t="n">
-        <v>-5.2444</v>
+        <v>-4.676</v>
       </c>
     </row>
     <row r="226">
@@ -13229,10 +13229,10 @@
         <v>0.67</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3715</v>
+        <v>-0.3582</v>
       </c>
       <c r="J226" t="n">
-        <v>-10.402</v>
+        <v>-10.0296</v>
       </c>
     </row>
     <row r="227">
@@ -13269,10 +13269,10 @@
         <v>1.6</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2586</v>
+        <v>1.2784</v>
       </c>
       <c r="J227" t="n">
-        <v>35.2408</v>
+        <v>35.7952</v>
       </c>
     </row>
     <row r="228">
@@ -13309,10 +13309,10 @@
         <v>1.36</v>
       </c>
       <c r="I228" t="n">
-        <v>0.8902</v>
+        <v>0.8712</v>
       </c>
       <c r="J228" t="n">
-        <v>24.9256</v>
+        <v>24.3936</v>
       </c>
     </row>
     <row r="229">
@@ -13349,10 +13349,10 @@
         <v>1.07</v>
       </c>
       <c r="I229" t="n">
-        <v>0.2402</v>
+        <v>0.2086</v>
       </c>
       <c r="J229" t="n">
-        <v>6.7256</v>
+        <v>5.8408</v>
       </c>
     </row>
     <row r="230">
@@ -13389,10 +13389,10 @@
         <v>1.03</v>
       </c>
       <c r="I230" t="n">
-        <v>0.1164</v>
+        <v>0.0949</v>
       </c>
       <c r="J230" t="n">
-        <v>3.2592</v>
+        <v>2.6572</v>
       </c>
     </row>
     <row r="231">
@@ -13429,10 +13429,10 @@
         <v>0.59</v>
       </c>
       <c r="I231" t="n">
-        <v>-1.0598</v>
+        <v>-1.0676</v>
       </c>
       <c r="J231" t="n">
-        <v>-29.6744</v>
+        <v>-29.8928</v>
       </c>
     </row>
     <row r="232">
@@ -13469,10 +13469,10 @@
         <v>1.33</v>
       </c>
       <c r="I232" t="n">
-        <v>0.653</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="J232" t="n">
-        <v>18.284</v>
+        <v>16.6964</v>
       </c>
     </row>
     <row r="233">
@@ -13509,10 +13509,10 @@
         <v>0.97</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.0566</v>
+        <v>-0.0448</v>
       </c>
       <c r="J233" t="n">
-        <v>-1.5848</v>
+        <v>-1.2544</v>
       </c>
     </row>
     <row r="234">
@@ -13549,10 +13549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.0969</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="J234" t="n">
-        <v>-2.7132</v>
+        <v>-2.2596</v>
       </c>
     </row>
     <row r="235">
@@ -13589,10 +13589,10 @@
         <v>0.86</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1884</v>
+        <v>-0.168</v>
       </c>
       <c r="J235" t="n">
-        <v>-5.2752</v>
+        <v>-4.704</v>
       </c>
     </row>
     <row r="236">
@@ -13629,10 +13629,10 @@
         <v>0.76</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.2888</v>
+        <v>-0.2702</v>
       </c>
       <c r="J236" t="n">
-        <v>-8.086399999999999</v>
+        <v>-7.5656</v>
       </c>
     </row>
     <row r="237">
@@ -13669,10 +13669,10 @@
         <v>1.47</v>
       </c>
       <c r="I237" t="n">
-        <v>1.0812</v>
+        <v>1.0913</v>
       </c>
       <c r="J237" t="n">
-        <v>30.2736</v>
+        <v>30.5564</v>
       </c>
     </row>
     <row r="238">
@@ -13709,10 +13709,10 @@
         <v>1.23</v>
       </c>
       <c r="I238" t="n">
-        <v>0.6227</v>
+        <v>0.5866</v>
       </c>
       <c r="J238" t="n">
-        <v>17.4356</v>
+        <v>16.4248</v>
       </c>
     </row>
     <row r="239">
@@ -13749,10 +13749,10 @@
         <v>1.21</v>
       </c>
       <c r="I239" t="n">
-        <v>0.579</v>
+        <v>0.5415</v>
       </c>
       <c r="J239" t="n">
-        <v>16.212</v>
+        <v>15.162</v>
       </c>
     </row>
     <row r="240">
@@ -13789,10 +13789,10 @@
         <v>0.85</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.4928</v>
+        <v>-0.4515</v>
       </c>
       <c r="J240" t="n">
-        <v>-13.7984</v>
+        <v>-12.642</v>
       </c>
     </row>
     <row r="241">
@@ -13829,10 +13829,10 @@
         <v>0.84</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5171</v>
+        <v>-0.4764</v>
       </c>
       <c r="J241" t="n">
-        <v>-14.4788</v>
+        <v>-13.3392</v>
       </c>
     </row>
     <row r="242">
@@ -13869,10 +13869,10 @@
         <v>1.17</v>
       </c>
       <c r="I242" t="n">
-        <v>0.332</v>
+        <v>0.3263</v>
       </c>
       <c r="J242" t="n">
-        <v>8.964</v>
+        <v>8.8101</v>
       </c>
     </row>
     <row r="243">
@@ -13909,10 +13909,10 @@
         <v>1.01</v>
       </c>
       <c r="I243" t="n">
-        <v>0.0552</v>
+        <v>0.045</v>
       </c>
       <c r="J243" t="n">
-        <v>1.4904</v>
+        <v>1.215</v>
       </c>
     </row>
     <row r="244">
@@ -13949,10 +13949,10 @@
         <v>0.93</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.1001</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="J244" t="n">
-        <v>-2.7027</v>
+        <v>-2.322</v>
       </c>
     </row>
     <row r="245">
@@ -13989,10 +13989,10 @@
         <v>0.63</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.397</v>
+        <v>-0.3854</v>
       </c>
       <c r="J245" t="n">
-        <v>-10.719</v>
+        <v>-10.4058</v>
       </c>
     </row>
     <row r="246">
@@ -14029,10 +14029,10 @@
         <v>0.53</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4851</v>
+        <v>-0.4829</v>
       </c>
       <c r="J246" t="n">
-        <v>-13.0977</v>
+        <v>-13.0383</v>
       </c>
     </row>
     <row r="247">
@@ -14069,10 +14069,10 @@
         <v>1.45</v>
       </c>
       <c r="I247" t="n">
-        <v>0.578</v>
+        <v>0.5072</v>
       </c>
       <c r="J247" t="n">
-        <v>15.606</v>
+        <v>13.6944</v>
       </c>
     </row>
     <row r="248">
@@ -14109,10 +14109,10 @@
         <v>1.13</v>
       </c>
       <c r="I248" t="n">
-        <v>0.2139</v>
+        <v>0.1711</v>
       </c>
       <c r="J248" t="n">
-        <v>5.7753</v>
+        <v>4.6197</v>
       </c>
     </row>
     <row r="249">
@@ -14149,10 +14149,10 @@
         <v>1.12</v>
       </c>
       <c r="I249" t="n">
-        <v>0.2005</v>
+        <v>0.1595</v>
       </c>
       <c r="J249" t="n">
-        <v>5.4135</v>
+        <v>4.3065</v>
       </c>
     </row>
     <row r="250">
@@ -14189,10 +14189,10 @@
         <v>1.1</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1726</v>
+        <v>0.1357</v>
       </c>
       <c r="J250" t="n">
-        <v>4.6602</v>
+        <v>3.6639</v>
       </c>
     </row>
     <row r="251">
@@ -14229,10 +14229,10 @@
         <v>1.06</v>
       </c>
       <c r="I251" t="n">
-        <v>0.1122</v>
+        <v>0.0848</v>
       </c>
       <c r="J251" t="n">
-        <v>3.0294</v>
+        <v>2.2896</v>
       </c>
     </row>
     <row r="252">
@@ -14269,10 +14269,10 @@
         <v>1.42</v>
       </c>
       <c r="I252" t="n">
-        <v>1.0166</v>
+        <v>1.0174</v>
       </c>
       <c r="J252" t="n">
-        <v>29.4814</v>
+        <v>29.5046</v>
       </c>
     </row>
     <row r="253">
@@ -14309,10 +14309,10 @@
         <v>1.25</v>
       </c>
       <c r="I253" t="n">
-        <v>0.6763</v>
+        <v>0.6415</v>
       </c>
       <c r="J253" t="n">
-        <v>19.6127</v>
+        <v>18.6035</v>
       </c>
     </row>
     <row r="254">
@@ -14349,10 +14349,10 @@
         <v>1.01</v>
       </c>
       <c r="I254" t="n">
-        <v>0.0478</v>
+        <v>0.036</v>
       </c>
       <c r="J254" t="n">
-        <v>1.3862</v>
+        <v>1.044</v>
       </c>
     </row>
     <row r="255">
@@ -14389,10 +14389,10 @@
         <v>0.93</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.2745</v>
+        <v>-0.2343</v>
       </c>
       <c r="J255" t="n">
-        <v>-7.9605</v>
+        <v>-6.7947</v>
       </c>
     </row>
     <row r="256">
@@ -14429,10 +14429,10 @@
         <v>0.78</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.649</v>
+        <v>-0.6137</v>
       </c>
       <c r="J256" t="n">
-        <v>-18.821</v>
+        <v>-17.7973</v>
       </c>
     </row>
     <row r="257">
@@ -14469,10 +14469,10 @@
         <v>1.58</v>
       </c>
       <c r="I257" t="n">
-        <v>0.9958</v>
+        <v>0.9638</v>
       </c>
       <c r="J257" t="n">
-        <v>28.8782</v>
+        <v>27.9502</v>
       </c>
     </row>
     <row r="258">
@@ -14509,10 +14509,10 @@
         <v>1.18</v>
       </c>
       <c r="I258" t="n">
-        <v>0.3933</v>
+        <v>0.3374</v>
       </c>
       <c r="J258" t="n">
-        <v>11.4057</v>
+        <v>9.784599999999999</v>
       </c>
     </row>
     <row r="259">
@@ -14549,10 +14549,10 @@
         <v>0.86</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1934</v>
+        <v>-0.1727</v>
       </c>
       <c r="J259" t="n">
-        <v>-5.6086</v>
+        <v>-5.0083</v>
       </c>
     </row>
     <row r="260">
@@ -14589,10 +14589,10 @@
         <v>0.83</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2247</v>
+        <v>-0.2042</v>
       </c>
       <c r="J260" t="n">
-        <v>-6.5163</v>
+        <v>-5.9218</v>
       </c>
     </row>
     <row r="261">
@@ -14629,10 +14629,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3593</v>
+        <v>-0.3456</v>
       </c>
       <c r="J261" t="n">
-        <v>-10.4197</v>
+        <v>-10.0224</v>
       </c>
     </row>
     <row r="262">
@@ -14669,10 +14669,10 @@
         <v>2.04</v>
       </c>
       <c r="I262" t="n">
-        <v>1.7276</v>
+        <v>1.7788</v>
       </c>
       <c r="J262" t="n">
-        <v>34.552</v>
+        <v>35.576</v>
       </c>
     </row>
     <row r="263">
@@ -14709,10 +14709,10 @@
         <v>1.72</v>
       </c>
       <c r="I263" t="n">
-        <v>1.345</v>
+        <v>1.3673</v>
       </c>
       <c r="J263" t="n">
-        <v>26.9</v>
+        <v>27.346</v>
       </c>
     </row>
     <row r="264">
@@ -14749,10 +14749,10 @@
         <v>1.31</v>
       </c>
       <c r="I264" t="n">
-        <v>0.7417</v>
+        <v>0.7248</v>
       </c>
       <c r="J264" t="n">
-        <v>14.834</v>
+        <v>14.496</v>
       </c>
     </row>
     <row r="265">
@@ -14789,10 +14789,10 @@
         <v>1.09</v>
       </c>
       <c r="I265" t="n">
-        <v>0.2458</v>
+        <v>0.2134</v>
       </c>
       <c r="J265" t="n">
-        <v>4.916</v>
+        <v>4.268</v>
       </c>
     </row>
     <row r="266">
@@ -14829,10 +14829,10 @@
         <v>1.04</v>
       </c>
       <c r="I266" t="n">
-        <v>0.0994</v>
+        <v>0.0731</v>
       </c>
       <c r="J266" t="n">
-        <v>1.988</v>
+        <v>1.462</v>
       </c>
     </row>
     <row r="267">
@@ -14869,10 +14869,10 @@
         <v>0.87</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.1351</v>
+        <v>-0.1173</v>
       </c>
       <c r="J267" t="n">
-        <v>-2.702</v>
+        <v>-2.346</v>
       </c>
     </row>
     <row r="268">
@@ -14909,10 +14909,10 @@
         <v>0.72</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.2935</v>
+        <v>-0.2811</v>
       </c>
       <c r="J268" t="n">
-        <v>-5.87</v>
+        <v>-5.622</v>
       </c>
     </row>
     <row r="269">
@@ -14949,10 +14949,10 @@
         <v>0.63</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.3735</v>
+        <v>-0.3627</v>
       </c>
       <c r="J269" t="n">
-        <v>-7.47</v>
+        <v>-7.254</v>
       </c>
     </row>
     <row r="270">
@@ -14989,10 +14989,10 @@
         <v>0.6</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3996</v>
+        <v>-0.3898</v>
       </c>
       <c r="J270" t="n">
-        <v>-7.992</v>
+        <v>-7.796</v>
       </c>
     </row>
     <row r="271">
@@ -15029,10 +15029,10 @@
         <v>0.44</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5403</v>
+        <v>-0.5434</v>
       </c>
       <c r="J271" t="n">
-        <v>-10.806</v>
+        <v>-10.868</v>
       </c>
     </row>
     <row r="272">
@@ -15069,10 +15069,10 @@
         <v>1.3</v>
       </c>
       <c r="I272" t="n">
-        <v>0.5774</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="J272" t="n">
-        <v>20.7864</v>
+        <v>18.6336</v>
       </c>
     </row>
     <row r="273">
@@ -15109,10 +15109,10 @@
         <v>1.23</v>
       </c>
       <c r="I273" t="n">
-        <v>0.4667</v>
+        <v>0.4086</v>
       </c>
       <c r="J273" t="n">
-        <v>16.8012</v>
+        <v>14.7096</v>
       </c>
     </row>
     <row r="274">
@@ -15149,10 +15149,10 @@
         <v>1.18</v>
       </c>
       <c r="I274" t="n">
-        <v>0.3838</v>
+        <v>0.3292</v>
       </c>
       <c r="J274" t="n">
-        <v>13.8168</v>
+        <v>11.8512</v>
       </c>
     </row>
     <row r="275">
@@ -15189,10 +15189,10 @@
         <v>0.91</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.1422</v>
+        <v>-0.1225</v>
       </c>
       <c r="J275" t="n">
-        <v>-5.1192</v>
+        <v>-4.41</v>
       </c>
     </row>
     <row r="276">
@@ -15229,10 +15229,10 @@
         <v>0.78</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.279</v>
+        <v>-0.2606</v>
       </c>
       <c r="J276" t="n">
-        <v>-10.044</v>
+        <v>-9.381600000000001</v>
       </c>
     </row>
     <row r="277">
@@ -15269,10 +15269,10 @@
         <v>1.1</v>
       </c>
       <c r="I277" t="n">
-        <v>0.3455</v>
+        <v>0.3032</v>
       </c>
       <c r="J277" t="n">
-        <v>12.438</v>
+        <v>10.9152</v>
       </c>
     </row>
     <row r="278">
@@ -15309,10 +15309,10 @@
         <v>1.01</v>
       </c>
       <c r="I278" t="n">
-        <v>0.0607</v>
+        <v>0.0438</v>
       </c>
       <c r="J278" t="n">
-        <v>2.1852</v>
+        <v>1.5768</v>
       </c>
     </row>
     <row r="279">
@@ -15349,10 +15349,10 @@
         <v>0.99</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.0574</v>
+        <v>-0.0422</v>
       </c>
       <c r="J279" t="n">
-        <v>-2.0664</v>
+        <v>-1.5192</v>
       </c>
     </row>
     <row r="280">
@@ -15389,10 +15389,10 @@
         <v>0.97</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.1333</v>
+        <v>-0.1063</v>
       </c>
       <c r="J280" t="n">
-        <v>-4.7988</v>
+        <v>-3.8268</v>
       </c>
     </row>
     <row r="281">
@@ -15429,10 +15429,10 @@
         <v>0.86</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4414</v>
+        <v>-0.3986</v>
       </c>
       <c r="J281" t="n">
-        <v>-15.8904</v>
+        <v>-14.3496</v>
       </c>
     </row>
     <row r="282">
@@ -15469,10 +15469,10 @@
         <v>1.25</v>
       </c>
       <c r="I282" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.5746</v>
       </c>
       <c r="J282" t="n">
-        <v>12.8604</v>
+        <v>12.0666</v>
       </c>
     </row>
     <row r="283">
@@ -15509,10 +15509,10 @@
         <v>1.05</v>
       </c>
       <c r="I283" t="n">
-        <v>0.2133</v>
+        <v>0.1796</v>
       </c>
       <c r="J283" t="n">
-        <v>4.4793</v>
+        <v>3.7716</v>
       </c>
     </row>
     <row r="284">
@@ -15549,10 +15549,10 @@
         <v>0.59</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.4219</v>
+        <v>-0.4123</v>
       </c>
       <c r="J284" t="n">
-        <v>-8.8599</v>
+        <v>-8.658300000000001</v>
       </c>
     </row>
     <row r="285">
@@ -15589,10 +15589,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.4485</v>
+        <v>-0.4413</v>
       </c>
       <c r="J285" t="n">
-        <v>-9.4185</v>
+        <v>-9.267300000000001</v>
       </c>
     </row>
     <row r="286">
@@ -15629,10 +15629,10 @@
         <v>0.34</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.6382</v>
+        <v>-0.6587</v>
       </c>
       <c r="J286" t="n">
-        <v>-13.4022</v>
+        <v>-13.8327</v>
       </c>
     </row>
     <row r="287">
@@ -15669,10 +15669,10 @@
         <v>1.85</v>
       </c>
       <c r="I287" t="n">
-        <v>1.5184</v>
+        <v>1.5516</v>
       </c>
       <c r="J287" t="n">
-        <v>31.8864</v>
+        <v>32.5836</v>
       </c>
     </row>
     <row r="288">
@@ -15709,10 +15709,10 @@
         <v>1.66</v>
       </c>
       <c r="I288" t="n">
-        <v>1.2826</v>
+        <v>1.3013</v>
       </c>
       <c r="J288" t="n">
-        <v>26.9346</v>
+        <v>27.3273</v>
       </c>
     </row>
     <row r="289">
@@ -15749,10 +15749,10 @@
         <v>1.4</v>
       </c>
       <c r="I289" t="n">
-        <v>0.9195</v>
+        <v>0.9111</v>
       </c>
       <c r="J289" t="n">
-        <v>19.3095</v>
+        <v>19.1331</v>
       </c>
     </row>
     <row r="290">
@@ -15789,10 +15789,10 @@
         <v>1.07</v>
       </c>
       <c r="I290" t="n">
-        <v>0.2015</v>
+        <v>0.1718</v>
       </c>
       <c r="J290" t="n">
-        <v>4.2315</v>
+        <v>3.6078</v>
       </c>
     </row>
     <row r="291">
@@ -15829,10 +15829,10 @@
         <v>0.85</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.5332</v>
+        <v>-0.4997</v>
       </c>
       <c r="J291" t="n">
-        <v>-11.1972</v>
+        <v>-10.4937</v>
       </c>
     </row>
     <row r="292">
@@ -15869,10 +15869,10 @@
         <v>1.04</v>
       </c>
       <c r="I292" t="n">
-        <v>0.1827</v>
+        <v>0.1507</v>
       </c>
       <c r="J292" t="n">
-        <v>4.2021</v>
+        <v>3.4661</v>
       </c>
     </row>
     <row r="293">
@@ -15909,10 +15909,10 @@
         <v>0.86</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.1704</v>
+        <v>-0.1545</v>
       </c>
       <c r="J293" t="n">
-        <v>-3.9192</v>
+        <v>-3.5535</v>
       </c>
     </row>
     <row r="294">
@@ -15949,10 +15949,10 @@
         <v>0.74</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.2877</v>
+        <v>-0.2712</v>
       </c>
       <c r="J294" t="n">
-        <v>-6.6171</v>
+        <v>-6.2376</v>
       </c>
     </row>
     <row r="295">
@@ -15989,10 +15989,10 @@
         <v>0.73</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.2969</v>
+        <v>-0.2805</v>
       </c>
       <c r="J295" t="n">
-        <v>-6.8287</v>
+        <v>-6.4515</v>
       </c>
     </row>
     <row r="296">
@@ -16029,10 +16029,10 @@
         <v>0.49</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.5112</v>
+        <v>-0.5115</v>
       </c>
       <c r="J296" t="n">
-        <v>-11.7576</v>
+        <v>-11.7645</v>
       </c>
     </row>
     <row r="297">
@@ -16069,10 +16069,10 @@
         <v>1.58</v>
       </c>
       <c r="I297" t="n">
-        <v>1.1882</v>
+        <v>1.203</v>
       </c>
       <c r="J297" t="n">
-        <v>27.3286</v>
+        <v>27.669</v>
       </c>
     </row>
     <row r="298">
@@ -16109,10 +16109,10 @@
         <v>1.43</v>
       </c>
       <c r="I298" t="n">
-        <v>0.9784</v>
+        <v>0.975</v>
       </c>
       <c r="J298" t="n">
-        <v>22.5032</v>
+        <v>22.425</v>
       </c>
     </row>
     <row r="299">
@@ -16149,10 +16149,10 @@
         <v>1.28</v>
       </c>
       <c r="I299" t="n">
-        <v>0.6979</v>
+        <v>0.6742</v>
       </c>
       <c r="J299" t="n">
-        <v>16.0517</v>
+        <v>15.5066</v>
       </c>
     </row>
     <row r="300">
@@ -16189,10 +16189,10 @@
         <v>1.2</v>
       </c>
       <c r="I300" t="n">
-        <v>0.5299</v>
+        <v>0.5002</v>
       </c>
       <c r="J300" t="n">
-        <v>12.1877</v>
+        <v>11.5046</v>
       </c>
     </row>
     <row r="301">
@@ -16229,10 +16229,10 @@
         <v>1.1</v>
       </c>
       <c r="I301" t="n">
-        <v>0.291</v>
+        <v>0.2595</v>
       </c>
       <c r="J301" t="n">
-        <v>6.693</v>
+        <v>5.9685</v>
       </c>
     </row>
     <row r="302">
@@ -16269,10 +16269,10 @@
         <v>1.06</v>
       </c>
       <c r="I302" t="n">
-        <v>0.2039</v>
+        <v>0.1639</v>
       </c>
       <c r="J302" t="n">
-        <v>4.8936</v>
+        <v>3.9336</v>
       </c>
     </row>
     <row r="303">
@@ -16309,10 +16309,10 @@
         <v>0.99</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.0106</v>
+        <v>-0.0063</v>
       </c>
       <c r="J303" t="n">
-        <v>-0.2544</v>
+        <v>-0.1512</v>
       </c>
     </row>
     <row r="304">
@@ -16349,10 +16349,10 @@
         <v>0.78</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.2576</v>
+        <v>-0.2388</v>
       </c>
       <c r="J304" t="n">
-        <v>-6.1824</v>
+        <v>-5.7312</v>
       </c>
     </row>
     <row r="305">
@@ -16389,10 +16389,10 @@
         <v>0.72</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.3145</v>
+        <v>-0.2973</v>
       </c>
       <c r="J305" t="n">
-        <v>-7.548</v>
+        <v>-7.1352</v>
       </c>
     </row>
     <row r="306">
@@ -16429,10 +16429,10 @@
         <v>0.7</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.333</v>
+        <v>-0.3168</v>
       </c>
       <c r="J306" t="n">
-        <v>-7.992</v>
+        <v>-7.6032</v>
       </c>
     </row>
     <row r="307">
@@ -16469,10 +16469,10 @@
         <v>1.5</v>
       </c>
       <c r="I307" t="n">
-        <v>1.0934</v>
+        <v>1.1043</v>
       </c>
       <c r="J307" t="n">
-        <v>26.2416</v>
+        <v>26.5032</v>
       </c>
     </row>
     <row r="308">
@@ -16509,10 +16509,10 @@
         <v>1.31</v>
       </c>
       <c r="I308" t="n">
-        <v>0.7637</v>
+        <v>0.7396</v>
       </c>
       <c r="J308" t="n">
-        <v>18.3288</v>
+        <v>17.7504</v>
       </c>
     </row>
     <row r="309">
@@ -16549,10 +16549,10 @@
         <v>1.29</v>
       </c>
       <c r="I309" t="n">
-        <v>0.724</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="J309" t="n">
-        <v>17.376</v>
+        <v>16.7544</v>
       </c>
     </row>
     <row r="310">
@@ -16589,10 +16589,10 @@
         <v>1.12</v>
       </c>
       <c r="I310" t="n">
-        <v>0.3526</v>
+        <v>0.32</v>
       </c>
       <c r="J310" t="n">
-        <v>8.462400000000001</v>
+        <v>7.68</v>
       </c>
     </row>
     <row r="311">
@@ -16629,10 +16629,10 @@
         <v>1.05</v>
       </c>
       <c r="I311" t="n">
-        <v>0.1603</v>
+        <v>0.1344</v>
       </c>
       <c r="J311" t="n">
-        <v>3.8472</v>
+        <v>3.2256</v>
       </c>
     </row>
     <row r="312">
@@ -16669,10 +16669,10 @@
         <v>1.2</v>
       </c>
       <c r="I312" t="n">
-        <v>0.5693</v>
+        <v>0.5298</v>
       </c>
       <c r="J312" t="n">
-        <v>22.772</v>
+        <v>21.192</v>
       </c>
     </row>
     <row r="313">
@@ -16709,10 +16709,10 @@
         <v>1.18</v>
       </c>
       <c r="I313" t="n">
-        <v>0.5235</v>
+        <v>0.4829</v>
       </c>
       <c r="J313" t="n">
-        <v>20.94</v>
+        <v>19.316</v>
       </c>
     </row>
     <row r="314">
@@ -16749,10 +16749,10 @@
         <v>1.1</v>
       </c>
       <c r="I314" t="n">
-        <v>0.3288</v>
+        <v>0.2897</v>
       </c>
       <c r="J314" t="n">
-        <v>13.152</v>
+        <v>11.588</v>
       </c>
     </row>
     <row r="315">
@@ -16789,10 +16789,10 @@
         <v>1.04</v>
       </c>
       <c r="I315" t="n">
-        <v>0.1604</v>
+        <v>0.1327</v>
       </c>
       <c r="J315" t="n">
-        <v>6.416</v>
+        <v>5.308</v>
       </c>
     </row>
     <row r="316">
@@ -16829,10 +16829,10 @@
         <v>0.8</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.6005</v>
+        <v>-0.5624</v>
       </c>
       <c r="J316" t="n">
-        <v>-24.02</v>
+        <v>-22.496</v>
       </c>
     </row>
     <row r="317">
@@ -16869,10 +16869,10 @@
         <v>1.2</v>
       </c>
       <c r="I317" t="n">
-        <v>0.4262</v>
+        <v>0.369</v>
       </c>
       <c r="J317" t="n">
-        <v>17.048</v>
+        <v>14.76</v>
       </c>
     </row>
     <row r="318">
@@ -16909,10 +16909,10 @@
         <v>1.17</v>
       </c>
       <c r="I318" t="n">
-        <v>0.3748</v>
+        <v>0.3199</v>
       </c>
       <c r="J318" t="n">
-        <v>14.992</v>
+        <v>12.796</v>
       </c>
     </row>
     <row r="319">
@@ -16949,10 +16949,10 @@
         <v>1.04</v>
       </c>
       <c r="I319" t="n">
-        <v>0.1208</v>
+        <v>0.0921</v>
       </c>
       <c r="J319" t="n">
-        <v>4.832</v>
+        <v>3.684</v>
       </c>
     </row>
     <row r="320">
@@ -16989,10 +16989,10 @@
         <v>0.96</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.0751</v>
+        <v>-0.0602</v>
       </c>
       <c r="J320" t="n">
-        <v>-3.004</v>
+        <v>-2.408</v>
       </c>
     </row>
     <row r="321">
@@ -17029,10 +17029,10 @@
         <v>0.8</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.2555</v>
+        <v>-0.2358</v>
       </c>
       <c r="J321" t="n">
-        <v>-10.22</v>
+        <v>-9.432</v>
       </c>
     </row>
     <row r="322">
@@ -17069,10 +17069,10 @@
         <v>1.57</v>
       </c>
       <c r="I322" t="n">
-        <v>1.1921</v>
+        <v>1.2066</v>
       </c>
       <c r="J322" t="n">
-        <v>30.9946</v>
+        <v>31.3716</v>
       </c>
     </row>
     <row r="323">
@@ -17109,10 +17109,10 @@
         <v>1.27</v>
       </c>
       <c r="I323" t="n">
-        <v>0.6868</v>
+        <v>0.6581</v>
       </c>
       <c r="J323" t="n">
-        <v>17.8568</v>
+        <v>17.1106</v>
       </c>
     </row>
     <row r="324">
@@ -17149,10 +17149,10 @@
         <v>1.22</v>
       </c>
       <c r="I324" t="n">
-        <v>0.5847</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="J324" t="n">
-        <v>15.2022</v>
+        <v>14.3754</v>
       </c>
     </row>
     <row r="325">
@@ -17189,10 +17189,10 @@
         <v>1.15</v>
       </c>
       <c r="I325" t="n">
-        <v>0.4289</v>
+        <v>0.3954</v>
       </c>
       <c r="J325" t="n">
-        <v>11.1514</v>
+        <v>10.2804</v>
       </c>
     </row>
     <row r="326">
@@ -17229,10 +17229,10 @@
         <v>0.95</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.2429</v>
+        <v>-0.2068</v>
       </c>
       <c r="J326" t="n">
-        <v>-6.3154</v>
+        <v>-5.3768</v>
       </c>
     </row>
     <row r="327">
@@ -17269,10 +17269,10 @@
         <v>1</v>
       </c>
       <c r="I327" t="n">
-        <v>0.0197</v>
+        <v>0.0146</v>
       </c>
       <c r="J327" t="n">
-        <v>0.5122</v>
+        <v>0.3796</v>
       </c>
     </row>
     <row r="328">
@@ -17309,10 +17309,10 @@
         <v>0.92</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.1149</v>
+        <v>-0.0994</v>
       </c>
       <c r="J328" t="n">
-        <v>-2.9874</v>
+        <v>-2.5844</v>
       </c>
     </row>
     <row r="329">
@@ -17349,10 +17349,10 @@
         <v>0.89</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.149</v>
+        <v>-0.1316</v>
       </c>
       <c r="J329" t="n">
-        <v>-3.874</v>
+        <v>-3.4216</v>
       </c>
     </row>
     <row r="330">
@@ -17389,10 +17389,10 @@
         <v>0.88</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.1597</v>
+        <v>-0.1418</v>
       </c>
       <c r="J330" t="n">
-        <v>-4.1522</v>
+        <v>-3.6868</v>
       </c>
     </row>
     <row r="331">
@@ -17429,10 +17429,10 @@
         <v>0.7</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.336</v>
+        <v>-0.3198</v>
       </c>
       <c r="J331" t="n">
-        <v>-8.736000000000001</v>
+        <v>-8.3148</v>
       </c>
     </row>
     <row r="332">
@@ -17469,10 +17469,10 @@
         <v>1.46</v>
       </c>
       <c r="I332" t="n">
-        <v>0.849</v>
+        <v>0.8023</v>
       </c>
       <c r="J332" t="n">
-        <v>35.658</v>
+        <v>33.6966</v>
       </c>
     </row>
     <row r="333">
@@ -17509,10 +17509,10 @@
         <v>1.03</v>
       </c>
       <c r="I333" t="n">
-        <v>0.1033</v>
+        <v>0.076</v>
       </c>
       <c r="J333" t="n">
-        <v>4.3386</v>
+        <v>3.192</v>
       </c>
     </row>
     <row r="334">
@@ -17549,10 +17549,10 @@
         <v>1</v>
       </c>
       <c r="I334" t="n">
-        <v>0.0022</v>
+        <v>0.001</v>
       </c>
       <c r="J334" t="n">
-        <v>0.0924</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="335">
@@ -17589,10 +17589,10 @@
         <v>0.7</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.3455</v>
+        <v>-0.3304</v>
       </c>
       <c r="J335" t="n">
-        <v>-14.511</v>
+        <v>-13.8768</v>
       </c>
     </row>
     <row r="336">
@@ -17629,10 +17629,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.3547</v>
+        <v>-0.3403</v>
       </c>
       <c r="J336" t="n">
-        <v>-14.8974</v>
+        <v>-14.2926</v>
       </c>
     </row>
     <row r="337">
@@ -17669,10 +17669,10 @@
         <v>1.34</v>
       </c>
       <c r="I337" t="n">
-        <v>0.8668</v>
+        <v>0.8458</v>
       </c>
       <c r="J337" t="n">
-        <v>36.4056</v>
+        <v>35.5236</v>
       </c>
     </row>
     <row r="338">
@@ -17709,10 +17709,10 @@
         <v>1.26</v>
       </c>
       <c r="I338" t="n">
-        <v>0.699</v>
+        <v>0.6654</v>
       </c>
       <c r="J338" t="n">
-        <v>29.358</v>
+        <v>27.9468</v>
       </c>
     </row>
     <row r="339">
@@ -17749,10 +17749,10 @@
         <v>1.15</v>
       </c>
       <c r="I339" t="n">
-        <v>0.4509</v>
+        <v>0.41</v>
       </c>
       <c r="J339" t="n">
-        <v>18.9378</v>
+        <v>17.22</v>
       </c>
     </row>
     <row r="340">
@@ -17789,10 +17789,10 @@
         <v>0.91</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.3297</v>
+        <v>-0.2876</v>
       </c>
       <c r="J340" t="n">
-        <v>-13.8474</v>
+        <v>-12.0792</v>
       </c>
     </row>
     <row r="341">
@@ -17829,10 +17829,10 @@
         <v>0.71</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.8022</v>
+        <v>-0.7786</v>
       </c>
       <c r="J341" t="n">
-        <v>-33.6924</v>
+        <v>-32.7012</v>
       </c>
     </row>
     <row r="342">
@@ -17869,10 +17869,10 @@
         <v>1.65</v>
       </c>
       <c r="I342" t="n">
-        <v>1.073</v>
+        <v>1.0578</v>
       </c>
       <c r="J342" t="n">
-        <v>31.117</v>
+        <v>30.6762</v>
       </c>
     </row>
     <row r="343">
@@ -17909,10 +17909,10 @@
         <v>1.18</v>
       </c>
       <c r="I343" t="n">
-        <v>0.3925</v>
+        <v>0.3367</v>
       </c>
       <c r="J343" t="n">
-        <v>11.3825</v>
+        <v>9.7643</v>
       </c>
     </row>
     <row r="344">
@@ -17949,10 +17949,10 @@
         <v>0.87</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.183</v>
+        <v>-0.1624</v>
       </c>
       <c r="J344" t="n">
-        <v>-5.307</v>
+        <v>-4.7096</v>
       </c>
     </row>
     <row r="345">
@@ -17989,10 +17989,10 @@
         <v>0.84</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.2148</v>
+        <v>-0.1942</v>
       </c>
       <c r="J345" t="n">
-        <v>-6.2292</v>
+        <v>-5.6318</v>
       </c>
     </row>
     <row r="346">
@@ -18029,10 +18029,10 @@
         <v>0.62</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.4222</v>
+        <v>-0.4147</v>
       </c>
       <c r="J346" t="n">
-        <v>-12.2438</v>
+        <v>-12.0263</v>
       </c>
     </row>
     <row r="347">
@@ -18069,10 +18069,10 @@
         <v>1.39</v>
       </c>
       <c r="I347" t="n">
-        <v>0.9654</v>
+        <v>0.9568</v>
       </c>
       <c r="J347" t="n">
-        <v>27.9966</v>
+        <v>27.7472</v>
       </c>
     </row>
     <row r="348">
@@ -18109,10 +18109,10 @@
         <v>1.23</v>
       </c>
       <c r="I348" t="n">
-        <v>0.6337</v>
+        <v>0.5968</v>
       </c>
       <c r="J348" t="n">
-        <v>18.3773</v>
+        <v>17.3072</v>
       </c>
     </row>
     <row r="349">
@@ -18149,10 +18149,10 @@
         <v>1.14</v>
       </c>
       <c r="I349" t="n">
-        <v>0.4269</v>
+        <v>0.3861</v>
       </c>
       <c r="J349" t="n">
-        <v>12.3801</v>
+        <v>11.1969</v>
       </c>
     </row>
     <row r="350">
@@ -18189,10 +18189,10 @@
         <v>0.88</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.4089</v>
+        <v>-0.3659</v>
       </c>
       <c r="J350" t="n">
-        <v>-11.8581</v>
+        <v>-10.6111</v>
       </c>
     </row>
     <row r="351">
@@ -18229,10 +18229,10 @@
         <v>0.73</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.759</v>
+        <v>-0.7317</v>
       </c>
       <c r="J351" t="n">
-        <v>-22.011</v>
+        <v>-21.2193</v>
       </c>
     </row>
     <row r="352">
@@ -18269,10 +18269,10 @@
         <v>1.26</v>
       </c>
       <c r="I352" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.6585</v>
       </c>
       <c r="J352" t="n">
-        <v>20.76</v>
+        <v>19.755</v>
       </c>
     </row>
     <row r="353">
@@ -18309,10 +18309,10 @@
         <v>1.19</v>
       </c>
       <c r="I353" t="n">
-        <v>0.5384</v>
+        <v>0.4992</v>
       </c>
       <c r="J353" t="n">
-        <v>16.152</v>
+        <v>14.976</v>
       </c>
     </row>
     <row r="354">
@@ -18349,10 +18349,10 @@
         <v>1.08</v>
       </c>
       <c r="I354" t="n">
-        <v>0.2723</v>
+        <v>0.2376</v>
       </c>
       <c r="J354" t="n">
-        <v>8.169</v>
+        <v>7.128</v>
       </c>
     </row>
     <row r="355">
@@ -18389,10 +18389,10 @@
         <v>1.05</v>
       </c>
       <c r="I355" t="n">
-        <v>0.1863</v>
+        <v>0.1575</v>
       </c>
       <c r="J355" t="n">
-        <v>5.589</v>
+        <v>4.725</v>
       </c>
     </row>
     <row r="356">
@@ -18429,10 +18429,10 @@
         <v>0.92</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.3071</v>
+        <v>-0.2658</v>
       </c>
       <c r="J356" t="n">
-        <v>-9.212999999999999</v>
+        <v>-7.974</v>
       </c>
     </row>
     <row r="357">
@@ -18469,10 +18469,10 @@
         <v>1.38</v>
       </c>
       <c r="I357" t="n">
-        <v>0.729</v>
+        <v>0.675</v>
       </c>
       <c r="J357" t="n">
-        <v>21.87</v>
+        <v>20.25</v>
       </c>
     </row>
     <row r="358">
@@ -18509,10 +18509,10 @@
         <v>1.21</v>
       </c>
       <c r="I358" t="n">
-        <v>0.4567</v>
+        <v>0.3988</v>
       </c>
       <c r="J358" t="n">
-        <v>13.701</v>
+        <v>11.964</v>
       </c>
     </row>
     <row r="359">
@@ -18549,10 +18549,10 @@
         <v>0.83</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.22</v>
+        <v>-0.1995</v>
       </c>
       <c r="J359" t="n">
-        <v>-6.6</v>
+        <v>-5.985</v>
       </c>
     </row>
     <row r="360">
@@ -18589,10 +18589,10 @@
         <v>0.77</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.2796</v>
+        <v>-0.2606</v>
       </c>
       <c r="J360" t="n">
-        <v>-8.388</v>
+        <v>-7.818</v>
       </c>
     </row>
     <row r="361">
@@ -18629,10 +18629,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.3547</v>
+        <v>-0.3403</v>
       </c>
       <c r="J361" t="n">
-        <v>-10.641</v>
+        <v>-10.209</v>
       </c>
     </row>
     <row r="362">
@@ -18669,10 +18669,10 @@
         <v>1.63</v>
       </c>
       <c r="I362" t="n">
-        <v>1.2673</v>
+        <v>1.2852</v>
       </c>
       <c r="J362" t="n">
-        <v>29.1479</v>
+        <v>29.5596</v>
       </c>
     </row>
     <row r="363">
@@ -18709,10 +18709,10 @@
         <v>1.5</v>
       </c>
       <c r="I363" t="n">
-        <v>1.0941</v>
+        <v>1.1051</v>
       </c>
       <c r="J363" t="n">
-        <v>25.1643</v>
+        <v>25.4173</v>
       </c>
     </row>
     <row r="364">
@@ -18749,10 +18749,10 @@
         <v>1.31</v>
       </c>
       <c r="I364" t="n">
-        <v>0.7643</v>
+        <v>0.7401</v>
       </c>
       <c r="J364" t="n">
-        <v>17.5789</v>
+        <v>17.0223</v>
       </c>
     </row>
     <row r="365">
@@ -18789,10 +18789,10 @@
         <v>1.22</v>
       </c>
       <c r="I365" t="n">
-        <v>0.5827</v>
+        <v>0.5518</v>
       </c>
       <c r="J365" t="n">
-        <v>13.4021</v>
+        <v>12.6914</v>
       </c>
     </row>
     <row r="366">
@@ -18829,10 +18829,10 @@
         <v>0.59</v>
       </c>
       <c r="I366" t="n">
-        <v>-1.0766</v>
+        <v>-1.0904</v>
       </c>
       <c r="J366" t="n">
-        <v>-24.7618</v>
+        <v>-25.0792</v>
       </c>
     </row>
     <row r="367">
@@ -18869,10 +18869,10 @@
         <v>1.4</v>
       </c>
       <c r="I367" t="n">
-        <v>0.7608</v>
+        <v>0.7086</v>
       </c>
       <c r="J367" t="n">
-        <v>17.4984</v>
+        <v>16.2978</v>
       </c>
     </row>
     <row r="368">
@@ -18909,10 +18909,10 @@
         <v>1.29</v>
       </c>
       <c r="I368" t="n">
-        <v>0.5897</v>
+        <v>0.5315</v>
       </c>
       <c r="J368" t="n">
-        <v>13.5631</v>
+        <v>12.2245</v>
       </c>
     </row>
     <row r="369">
@@ -18949,10 +18949,10 @@
         <v>0.97</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.0566</v>
+        <v>-0.0448</v>
       </c>
       <c r="J369" t="n">
-        <v>-1.3018</v>
+        <v>-1.0304</v>
       </c>
     </row>
     <row r="370">
@@ -18989,10 +18989,10 @@
         <v>0.66</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.3816</v>
+        <v>-0.3694</v>
       </c>
       <c r="J370" t="n">
-        <v>-8.7768</v>
+        <v>-8.4962</v>
       </c>
     </row>
     <row r="371">
@@ -19029,10 +19029,10 @@
         <v>0.54</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.4868</v>
+        <v>-0.4864</v>
       </c>
       <c r="J371" t="n">
-        <v>-11.1964</v>
+        <v>-11.1872</v>
       </c>
     </row>
   </sheetData>
